--- a/rawdata/Bulanan/10. Okt-LD.xlsx
+++ b/rawdata/Bulanan/10. Okt-LD.xlsx
@@ -457,34 +457,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>7,562</v>
+        <v>7,946</v>
       </c>
       <c r="F2" t="str">
-        <v>3,642</v>
+        <v>3,864</v>
       </c>
       <c r="G2" t="str">
-        <v>991</v>
+        <v>1,052</v>
       </c>
       <c r="H2" t="str">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="I2" t="str">
-        <v>2,032,241,955</v>
+        <v>2,169,465,883</v>
       </c>
       <c r="J2" t="str">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="K2" t="str">
-        <v>7,733,399,042</v>
+        <v>8,230,005,830</v>
       </c>
       <c r="L2" t="str">
-        <v>27,461,036,131</v>
+        <v>29,002,619,350</v>
       </c>
       <c r="M2" t="str">
-        <v>15,026,955,255</v>
+        <v>15,948,367,784</v>
       </c>
       <c r="N2" t="str">
-        <v>54.72%</v>
+        <v>54.99%</v>
       </c>
     </row>
     <row r="3">
@@ -501,34 +501,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>11,357</v>
+        <v>11,924</v>
       </c>
       <c r="F3" t="str">
-        <v>1,590</v>
+        <v>1,684</v>
       </c>
       <c r="G3" t="str">
-        <v>1,750</v>
+        <v>1,855</v>
       </c>
       <c r="H3" t="str">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I3" t="str">
-        <v>1,263,373,376</v>
+        <v>1,326,391,069</v>
       </c>
       <c r="J3" t="str">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="K3" t="str">
-        <v>4,082,880,325</v>
+        <v>4,331,910,322</v>
       </c>
       <c r="L3" t="str">
-        <v>45,661,473,258</v>
+        <v>48,330,580,645</v>
       </c>
       <c r="M3" t="str">
-        <v>7,671,991,860</v>
+        <v>8,136,543,822</v>
       </c>
       <c r="N3" t="str">
-        <v>16.80%</v>
+        <v>16.84%</v>
       </c>
     </row>
     <row r="4">
@@ -545,34 +545,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>2,212</v>
+        <v>2,310</v>
       </c>
       <c r="F4" t="str">
-        <v>989</v>
+        <v>1,032</v>
       </c>
       <c r="G4" t="str">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="H4" t="str">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I4" t="str">
-        <v>608,998,524</v>
+        <v>671,642,495</v>
       </c>
       <c r="J4" t="str">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K4" t="str">
-        <v>2,452,602,989</v>
+        <v>2,508,446,502</v>
       </c>
       <c r="L4" t="str">
-        <v>8,173,834,716</v>
+        <v>8,525,196,607</v>
       </c>
       <c r="M4" t="str">
-        <v>4,607,293,197</v>
+        <v>4,804,772,883</v>
       </c>
       <c r="N4" t="str">
-        <v>56.37%</v>
+        <v>56.36%</v>
       </c>
     </row>
     <row r="5">
@@ -589,19 +589,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>4,142</v>
+        <v>4,322</v>
       </c>
       <c r="F5" t="str">
-        <v>966</v>
+        <v>1,019</v>
       </c>
       <c r="G5" t="str">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H5" t="str">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I5" t="str">
-        <v>113,127,370</v>
+        <v>135,018,834</v>
       </c>
       <c r="J5" t="str">
         <v>2</v>
@@ -610,13 +610,13 @@
         <v>38,695,454</v>
       </c>
       <c r="L5" t="str">
-        <v>5,122,249,474</v>
+        <v>5,319,960,793</v>
       </c>
       <c r="M5" t="str">
-        <v>1,826,366,187</v>
+        <v>1,928,051,393</v>
       </c>
       <c r="N5" t="str">
-        <v>35.66%</v>
+        <v>36.24%</v>
       </c>
     </row>
     <row r="6">
@@ -633,10 +633,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>17,278</v>
+        <v>18,315</v>
       </c>
       <c r="F6" t="str">
-        <v>3,958</v>
+        <v>4,218</v>
       </c>
       <c r="G6" t="str">
         <v>86</v>
@@ -654,13 +654,13 @@
         <v>101,641,843</v>
       </c>
       <c r="L6" t="str">
-        <v>21,656,581,333</v>
+        <v>22,673,840,027</v>
       </c>
       <c r="M6" t="str">
-        <v>6,484,758,107</v>
+        <v>6,804,217,690</v>
       </c>
       <c r="N6" t="str">
-        <v>29.94%</v>
+        <v>30.01%</v>
       </c>
     </row>
     <row r="7">
@@ -677,34 +677,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>5,452</v>
+        <v>5,734</v>
       </c>
       <c r="F7" t="str">
-        <v>2,538</v>
+        <v>2,696</v>
       </c>
       <c r="G7" t="str">
-        <v>3,662</v>
+        <v>3,869</v>
       </c>
       <c r="H7" t="str">
-        <v>754</v>
+        <v>805</v>
       </c>
       <c r="I7" t="str">
-        <v>9,141,737,906</v>
+        <v>9,744,031,111</v>
       </c>
       <c r="J7" t="str">
-        <v>519</v>
+        <v>555</v>
       </c>
       <c r="K7" t="str">
-        <v>10,723,874,457</v>
+        <v>11,494,429,271</v>
       </c>
       <c r="L7" t="str">
-        <v>61,551,840,742</v>
+        <v>64,899,087,526</v>
       </c>
       <c r="M7" t="str">
-        <v>26,715,411,082</v>
+        <v>28,470,100,222</v>
       </c>
       <c r="N7" t="str">
-        <v>43.40%</v>
+        <v>43.87%</v>
       </c>
     </row>
     <row r="8">
@@ -721,10 +721,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>1,629</v>
+        <v>1,734</v>
       </c>
       <c r="F8" t="str">
-        <v>323</v>
+        <v>365</v>
       </c>
       <c r="G8" t="str">
         <v>0</v>
@@ -742,13 +742,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="str">
-        <v>2,170,765,560</v>
+        <v>2,273,710,735</v>
       </c>
       <c r="M8" t="str">
-        <v>577,635,880</v>
+        <v>643,666,258</v>
       </c>
       <c r="N8" t="str">
-        <v>26.61%</v>
+        <v>28.31%</v>
       </c>
     </row>
     <row r="9">
@@ -765,13 +765,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>2,625</v>
+        <v>2,732</v>
       </c>
       <c r="F9" t="str">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G9" t="str">
-        <v>6,019</v>
+        <v>6,331</v>
       </c>
       <c r="H9" t="str">
         <v>0</v>
@@ -786,13 +786,13 @@
         <v>100,379,570</v>
       </c>
       <c r="L9" t="str">
-        <v>7,388,028,565</v>
+        <v>7,708,622,014</v>
       </c>
       <c r="M9" t="str">
-        <v>105,424,507</v>
+        <v>105,724,507</v>
       </c>
       <c r="N9" t="str">
-        <v>1.43%</v>
+        <v>1.37%</v>
       </c>
     </row>
     <row r="10">
@@ -809,13 +809,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>2,190</v>
+        <v>2,277</v>
       </c>
       <c r="F10" t="str">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G10" t="str">
-        <v>4,153</v>
+        <v>4,381</v>
       </c>
       <c r="H10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="str">
-        <v>6,020,840,665</v>
+        <v>6,272,003,903</v>
       </c>
       <c r="M10" t="str">
-        <v>58,483,739</v>
+        <v>70,667,632</v>
       </c>
       <c r="N10" t="str">
-        <v>0.97%</v>
+        <v>1.13%</v>
       </c>
     </row>
     <row r="11">
@@ -853,13 +853,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>2,682</v>
+        <v>2,803</v>
       </c>
       <c r="F11" t="str">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G11" t="str">
-        <v>7,342</v>
+        <v>7,769</v>
       </c>
       <c r="H11" t="str">
         <v>0</v>
@@ -874,10 +874,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>10,108,699,675</v>
+        <v>10,561,565,378</v>
       </c>
       <c r="M11" t="str">
-        <v>98,616,312</v>
+        <v>104,015,453</v>
       </c>
       <c r="N11" t="str">
         <v>0.98%</v>
@@ -897,13 +897,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>1,669</v>
+        <v>1,745</v>
       </c>
       <c r="F12" t="str">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G12" t="str">
-        <v>5,084</v>
+        <v>5,370</v>
       </c>
       <c r="H12" t="str">
         <v>2</v>
@@ -918,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>6,225,396,446</v>
+        <v>6,467,842,623</v>
       </c>
       <c r="M12" t="str">
-        <v>149,387,695</v>
+        <v>174,281,255</v>
       </c>
       <c r="N12" t="str">
-        <v>2.40%</v>
+        <v>2.69%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>924</v>
+        <v>954</v>
       </c>
       <c r="F13" t="str">
         <v>23</v>
       </c>
       <c r="G13" t="str">
-        <v>2,923</v>
+        <v>3,046</v>
       </c>
       <c r="H13" t="str">
         <v>1</v>
@@ -962,13 +962,13 @@
         <v>20,084,148</v>
       </c>
       <c r="L13" t="str">
-        <v>3,450,545,357</v>
+        <v>3,586,195,403</v>
       </c>
       <c r="M13" t="str">
         <v>66,541,558</v>
       </c>
       <c r="N13" t="str">
-        <v>1.93%</v>
+        <v>1.86%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>2,359</v>
+        <v>2,467</v>
       </c>
       <c r="F14" t="str">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G14" t="str">
-        <v>6,938</v>
+        <v>7,321</v>
       </c>
       <c r="H14" t="str">
         <v>0</v>
@@ -1006,13 +1006,13 @@
         <v>0</v>
       </c>
       <c r="L14" t="str">
-        <v>8,797,300,369</v>
+        <v>9,123,893,499</v>
       </c>
       <c r="M14" t="str">
-        <v>121,903,885</v>
+        <v>129,867,127</v>
       </c>
       <c r="N14" t="str">
-        <v>1.39%</v>
+        <v>1.42%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>3,321</v>
+        <v>3,496</v>
       </c>
       <c r="F15" t="str">
         <v>23</v>
       </c>
       <c r="G15" t="str">
-        <v>9,971</v>
+        <v>10,464</v>
       </c>
       <c r="H15" t="str">
         <v>0</v>
@@ -1050,13 +1050,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="str">
-        <v>12,830,514,870</v>
+        <v>13,388,867,791</v>
       </c>
       <c r="M15" t="str">
         <v>72,170,546</v>
       </c>
       <c r="N15" t="str">
-        <v>0.56%</v>
+        <v>0.54%</v>
       </c>
     </row>
     <row r="16">
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>1,474</v>
+        <v>1,564</v>
       </c>
       <c r="F16" t="str">
         <v>24</v>
       </c>
       <c r="G16" t="str">
-        <v>3,630</v>
+        <v>3,839</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>233,859,144</v>
       </c>
       <c r="L16" t="str">
-        <v>5,180,841,360</v>
+        <v>5,586,104,377</v>
       </c>
       <c r="M16" t="str">
         <v>152,455,057</v>
       </c>
       <c r="N16" t="str">
-        <v>2.94%</v>
+        <v>2.73%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>1,844</v>
+        <v>1,957</v>
       </c>
       <c r="F17" t="str">
         <v>27</v>
       </c>
       <c r="G17" t="str">
-        <v>4,293</v>
+        <v>4,519</v>
       </c>
       <c r="H17" t="str">
         <v>0</v>
@@ -1138,13 +1138,13 @@
         <v>100,898,460</v>
       </c>
       <c r="L17" t="str">
-        <v>6,044,121,037</v>
+        <v>6,472,980,934</v>
       </c>
       <c r="M17" t="str">
         <v>98,456,810</v>
       </c>
       <c r="N17" t="str">
-        <v>1.63%</v>
+        <v>1.52%</v>
       </c>
     </row>
     <row r="18">
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>2,769</v>
+        <v>2,894</v>
       </c>
       <c r="F18" t="str">
         <v>46</v>
       </c>
       <c r="G18" t="str">
-        <v>9,888</v>
+        <v>10,403</v>
       </c>
       <c r="H18" t="str">
         <v>1</v>
@@ -1182,13 +1182,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="str">
-        <v>12,236,010,903</v>
+        <v>12,788,861,696</v>
       </c>
       <c r="M18" t="str">
         <v>69,810,881</v>
       </c>
       <c r="N18" t="str">
-        <v>0.57%</v>
+        <v>0.55%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="F19" t="str">
         <v>1</v>
       </c>
       <c r="G19" t="str">
-        <v>1,678</v>
+        <v>1,753</v>
       </c>
       <c r="H19" t="str">
         <v>0</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>1,962,451,067</v>
+        <v>2,032,543,072</v>
       </c>
       <c r="M19" t="str">
         <v>8,938,285</v>
       </c>
       <c r="N19" t="str">
-        <v>0.46%</v>
+        <v>0.44%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>3,233</v>
+        <v>3,380</v>
       </c>
       <c r="F20" t="str">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G20" t="str">
-        <v>11,269</v>
+        <v>11,832</v>
       </c>
       <c r="H20" t="str">
         <v>1</v>
@@ -1270,13 +1270,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="str">
-        <v>13,842,763,894</v>
+        <v>14,479,511,724</v>
       </c>
       <c r="M20" t="str">
-        <v>92,634,320</v>
+        <v>92,734,320</v>
       </c>
       <c r="N20" t="str">
-        <v>0.67%</v>
+        <v>0.64%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>21,827</v>
+        <v>22,080</v>
       </c>
       <c r="F21" t="str">
-        <v>658</v>
+        <v>701</v>
       </c>
       <c r="G21" t="str">
-        <v>431,389</v>
+        <v>455,633</v>
       </c>
       <c r="H21" t="str">
         <v>3</v>
@@ -1308,19 +1308,19 @@
         <v>37,959,330</v>
       </c>
       <c r="J21" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K21" t="str">
-        <v>119,912,728</v>
+        <v>167,912,728</v>
       </c>
       <c r="L21" t="str">
-        <v>96,929,819,317</v>
+        <v>97,858,941,979</v>
       </c>
       <c r="M21" t="str">
-        <v>1,679,880,781</v>
+        <v>1,825,090,211</v>
       </c>
       <c r="N21" t="str">
-        <v>1.73%</v>
+        <v>1.87%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,13 +1337,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>1,198</v>
+        <v>1,199</v>
       </c>
       <c r="F22" t="str">
         <v>3</v>
       </c>
       <c r="G22" t="str">
-        <v>9,625</v>
+        <v>10,160</v>
       </c>
       <c r="H22" t="str">
         <v>0</v>
@@ -1358,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="str">
-        <v>13,262,190,810</v>
+        <v>13,262,750,896</v>
       </c>
       <c r="M22" t="str">
         <v>12,940,251</v>
@@ -1381,34 +1381,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E23" t="str">
-        <v>30,696</v>
+        <v>32,655</v>
       </c>
       <c r="F23" t="str">
-        <v>1,385</v>
+        <v>1,484</v>
       </c>
       <c r="G23" t="str">
-        <v>2,774</v>
+        <v>2,922</v>
       </c>
       <c r="H23" t="str">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="I23" t="str">
-        <v>2,482,419,975</v>
+        <v>2,629,200,130</v>
       </c>
       <c r="J23" t="str">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="K23" t="str">
-        <v>2,734,514,346</v>
+        <v>3,113,672,466</v>
       </c>
       <c r="L23" t="str">
-        <v>101,176,767,450</v>
+        <v>106,991,449,119</v>
       </c>
       <c r="M23" t="str">
-        <v>7,801,286,650</v>
+        <v>8,463,700,391</v>
       </c>
       <c r="N23" t="str">
-        <v>7.71%</v>
+        <v>7.91%</v>
       </c>
     </row>
     <row r="24">
@@ -1425,13 +1425,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>1,477</v>
+        <v>1,550</v>
       </c>
       <c r="F24" t="str">
-        <v>486</v>
+        <v>508</v>
       </c>
       <c r="G24" t="str">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H24" t="str">
         <v>5</v>
@@ -1440,19 +1440,19 @@
         <v>61,623,069</v>
       </c>
       <c r="J24" t="str">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K24" t="str">
-        <v>360,298,759</v>
+        <v>378,003,597</v>
       </c>
       <c r="L24" t="str">
-        <v>3,751,130,150</v>
+        <v>3,909,944,853</v>
       </c>
       <c r="M24" t="str">
-        <v>1,038,698,771</v>
+        <v>1,092,479,240</v>
       </c>
       <c r="N24" t="str">
-        <v>27.69%</v>
+        <v>27.94%</v>
       </c>
     </row>
     <row r="25">
@@ -1469,13 +1469,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E25" t="str">
-        <v>3,716</v>
+        <v>3,860</v>
       </c>
       <c r="F25" t="str">
-        <v>1,123</v>
+        <v>1,169</v>
       </c>
       <c r="G25" t="str">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="H25" t="str">
         <v>27</v>
@@ -1484,19 +1484,19 @@
         <v>344,401,228</v>
       </c>
       <c r="J25" t="str">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K25" t="str">
-        <v>489,207,022</v>
+        <v>530,333,830</v>
       </c>
       <c r="L25" t="str">
-        <v>9,459,026,260</v>
+        <v>9,880,369,175</v>
       </c>
       <c r="M25" t="str">
-        <v>2,329,080,156</v>
+        <v>2,406,586,064</v>
       </c>
       <c r="N25" t="str">
-        <v>24.62%</v>
+        <v>24.36%</v>
       </c>
     </row>
     <row r="26">
@@ -1513,10 +1513,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>1,540</v>
+        <v>1,620</v>
       </c>
       <c r="F26" t="str">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="G26" t="str">
         <v>0</v>
@@ -1534,13 +1534,13 @@
         <v>0</v>
       </c>
       <c r="L26" t="str">
-        <v>1,712,488,630</v>
+        <v>1,792,642,986</v>
       </c>
       <c r="M26" t="str">
-        <v>407,343,695</v>
+        <v>423,436,630</v>
       </c>
       <c r="N26" t="str">
-        <v>23.79%</v>
+        <v>23.62%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,10 +1557,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>12,175</v>
+        <v>13,075</v>
       </c>
       <c r="F27" t="str">
-        <v>2,121</v>
+        <v>2,279</v>
       </c>
       <c r="G27" t="str">
         <v>1</v>
@@ -1578,13 +1578,13 @@
         <v>0</v>
       </c>
       <c r="L27" t="str">
-        <v>13,702,551,184</v>
+        <v>14,610,417,659</v>
       </c>
       <c r="M27" t="str">
-        <v>2,651,481,291</v>
+        <v>2,834,814,154</v>
       </c>
       <c r="N27" t="str">
-        <v>19.35%</v>
+        <v>19.40%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,34 +1601,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>2,776</v>
+        <v>2,917</v>
       </c>
       <c r="F28" t="str">
-        <v>916</v>
+        <v>967</v>
       </c>
       <c r="G28" t="str">
-        <v>1,048</v>
+        <v>1,093</v>
       </c>
       <c r="H28" t="str">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="I28" t="str">
-        <v>2,261,653,003</v>
+        <v>2,421,463,452</v>
       </c>
       <c r="J28" t="str">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="K28" t="str">
-        <v>2,448,049,016</v>
+        <v>2,565,373,484</v>
       </c>
       <c r="L28" t="str">
-        <v>29,409,499,095</v>
+        <v>30,801,950,178</v>
       </c>
       <c r="M28" t="str">
-        <v>8,113,890,836</v>
+        <v>8,550,242,846</v>
       </c>
       <c r="N28" t="str">
-        <v>27.59%</v>
+        <v>27.76%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,10 +1645,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>2,672</v>
+        <v>2,791</v>
       </c>
       <c r="F29" t="str">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="G29" t="str">
         <v>0</v>
@@ -1666,13 +1666,13 @@
         <v>0</v>
       </c>
       <c r="L29" t="str">
-        <v>3,037,469,330</v>
+        <v>3,158,143,248</v>
       </c>
       <c r="M29" t="str">
-        <v>606,648,838</v>
+        <v>622,809,119</v>
       </c>
       <c r="N29" t="str">
-        <v>19.97%</v>
+        <v>19.72%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,19 +1689,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>3,125</v>
+        <v>3,241</v>
       </c>
       <c r="F30" t="str">
-        <v>514</v>
+        <v>533</v>
       </c>
       <c r="G30" t="str">
-        <v>1,387</v>
+        <v>1,468</v>
       </c>
       <c r="H30" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I30" t="str">
-        <v>52,160,152</v>
+        <v>65,830,949</v>
       </c>
       <c r="J30" t="str">
         <v>5</v>
@@ -1710,13 +1710,13 @@
         <v>84,536,012</v>
       </c>
       <c r="L30" t="str">
-        <v>8,313,424,630</v>
+        <v>8,580,000,954</v>
       </c>
       <c r="M30" t="str">
-        <v>789,737,560</v>
+        <v>830,538,892</v>
       </c>
       <c r="N30" t="str">
-        <v>9.50%</v>
+        <v>9.68%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,13 +1733,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>859</v>
+        <v>898</v>
       </c>
       <c r="F31" t="str">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="G31" t="str">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="H31" t="str">
         <v>5</v>
@@ -1754,13 +1754,13 @@
         <v>15,120,660</v>
       </c>
       <c r="L31" t="str">
-        <v>2,150,935,065</v>
+        <v>2,223,708,422</v>
       </c>
       <c r="M31" t="str">
-        <v>357,680,298</v>
+        <v>372,091,408</v>
       </c>
       <c r="N31" t="str">
-        <v>16.63%</v>
+        <v>16.73%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,10 +1777,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>2,161</v>
+        <v>2,260</v>
       </c>
       <c r="F32" t="str">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="G32" t="str">
         <v>96</v>
@@ -1798,13 +1798,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="str">
-        <v>2,449,963,960</v>
+        <v>2,558,183,990</v>
       </c>
       <c r="M32" t="str">
-        <v>416,510,380</v>
+        <v>426,858,394</v>
       </c>
       <c r="N32" t="str">
-        <v>17.00%</v>
+        <v>16.69%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,13 +1821,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>5,757</v>
+        <v>6,259</v>
       </c>
       <c r="F33" t="str">
-        <v>613</v>
+        <v>658</v>
       </c>
       <c r="G33" t="str">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="H33" t="str">
         <v>4</v>
@@ -1842,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="str">
-        <v>6,684,717,305</v>
+        <v>7,228,776,029</v>
       </c>
       <c r="M33" t="str">
-        <v>804,034,431</v>
+        <v>847,580,482</v>
       </c>
       <c r="N33" t="str">
-        <v>12.03%</v>
+        <v>11.73%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,34 +1865,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>997</v>
+        <v>1,072</v>
       </c>
       <c r="F34" t="str">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="G34" t="str">
-        <v>1,506</v>
+        <v>1,652</v>
       </c>
       <c r="H34" t="str">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I34" t="str">
-        <v>426,632,711</v>
+        <v>514,537,816</v>
       </c>
       <c r="J34" t="str">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="K34" t="str">
-        <v>651,406,642</v>
+        <v>793,460,058</v>
       </c>
       <c r="L34" t="str">
-        <v>10,168,304,224</v>
+        <v>10,900,665,531</v>
       </c>
       <c r="M34" t="str">
-        <v>1,674,477,700</v>
+        <v>1,965,919,421</v>
       </c>
       <c r="N34" t="str">
-        <v>16.47%</v>
+        <v>18.03%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,10 +1909,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>3,345</v>
+        <v>3,525</v>
       </c>
       <c r="F35" t="str">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="G35" t="str">
         <v>231</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="L35" t="str">
-        <v>3,815,969,795</v>
+        <v>3,977,161,524</v>
       </c>
       <c r="M35" t="str">
-        <v>393,716,918</v>
+        <v>423,899,866</v>
       </c>
       <c r="N35" t="str">
-        <v>10.32%</v>
+        <v>10.66%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,13 +1953,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>2,064</v>
+        <v>2,214</v>
       </c>
       <c r="F36" t="str">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="G36" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H36" t="str">
         <v>0</v>
@@ -1974,13 +1974,13 @@
         <v>0</v>
       </c>
       <c r="L36" t="str">
-        <v>2,282,865,241</v>
+        <v>2,442,857,539</v>
       </c>
       <c r="M36" t="str">
-        <v>231,775,276</v>
+        <v>252,387,235</v>
       </c>
       <c r="N36" t="str">
-        <v>10.15%</v>
+        <v>10.33%</v>
       </c>
     </row>
     <row r="37">
@@ -2041,34 +2041,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>842</v>
+        <v>879</v>
       </c>
       <c r="F38" t="str">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="G38" t="str">
-        <v>1,545</v>
+        <v>1,641</v>
       </c>
       <c r="H38" t="str">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I38" t="str">
-        <v>348,769,369</v>
+        <v>383,834,630</v>
       </c>
       <c r="J38" t="str">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K38" t="str">
-        <v>308,230,585</v>
+        <v>327,611,272</v>
       </c>
       <c r="L38" t="str">
-        <v>8,499,415,419</v>
+        <v>8,866,732,954</v>
       </c>
       <c r="M38" t="str">
-        <v>1,069,338,160</v>
+        <v>1,195,654,944</v>
       </c>
       <c r="N38" t="str">
-        <v>12.58%</v>
+        <v>13.48%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,13 +2085,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>4,912</v>
+        <v>5,077</v>
       </c>
       <c r="F39" t="str">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="G39" t="str">
-        <v>5,581</v>
+        <v>5,877</v>
       </c>
       <c r="H39" t="str">
         <v>2</v>
@@ -2106,10 +2106,10 @@
         <v>84,725,256</v>
       </c>
       <c r="L39" t="str">
-        <v>11,830,482,338</v>
+        <v>12,245,012,399</v>
       </c>
       <c r="M39" t="str">
-        <v>354,211,803</v>
+        <v>365,985,764</v>
       </c>
       <c r="N39" t="str">
         <v>2.99%</v>
@@ -2173,13 +2173,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>888</v>
+        <v>1,025</v>
       </c>
       <c r="F41" t="str">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G41" t="str">
-        <v>1,155</v>
+        <v>1,218</v>
       </c>
       <c r="H41" t="str">
         <v>2</v>
@@ -2194,13 +2194,13 @@
         <v>50,770,592</v>
       </c>
       <c r="L41" t="str">
-        <v>2,155,719,616</v>
+        <v>2,376,605,228</v>
       </c>
       <c r="M41" t="str">
-        <v>134,764,999</v>
+        <v>136,758,629</v>
       </c>
       <c r="N41" t="str">
-        <v>6.25%</v>
+        <v>5.75%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>697</v>
+        <v>764</v>
       </c>
       <c r="F42" t="str">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G42" t="str">
-        <v>1,162</v>
+        <v>1,231</v>
       </c>
       <c r="H42" t="str">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>66,445,865</v>
       </c>
       <c r="L42" t="str">
-        <v>1,894,401,958</v>
+        <v>2,003,475,858</v>
       </c>
       <c r="M42" t="str">
-        <v>92,076,996</v>
+        <v>92,376,996</v>
       </c>
       <c r="N42" t="str">
-        <v>4.86%</v>
+        <v>4.61%</v>
       </c>
     </row>
     <row r="43">
@@ -2261,13 +2261,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E43" t="str">
-        <v>2,787</v>
+        <v>3,057</v>
       </c>
       <c r="F43" t="str">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G43" t="str">
-        <v>4,964</v>
+        <v>5,229</v>
       </c>
       <c r="H43" t="str">
         <v>6</v>
@@ -2282,13 +2282,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="str">
-        <v>7,626,267,918</v>
+        <v>8,079,425,517</v>
       </c>
       <c r="M43" t="str">
-        <v>310,898,406</v>
+        <v>342,535,988</v>
       </c>
       <c r="N43" t="str">
-        <v>4.08%</v>
+        <v>4.24%</v>
       </c>
     </row>
     <row r="44">
@@ -2305,13 +2305,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>2,143</v>
+        <v>2,431</v>
       </c>
       <c r="F44" t="str">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="G44" t="str">
-        <v>2,795</v>
+        <v>2,965</v>
       </c>
       <c r="H44" t="str">
         <v>3</v>
@@ -2326,13 +2326,13 @@
         <v>54,162,704</v>
       </c>
       <c r="L44" t="str">
-        <v>5,563,499,379</v>
+        <v>6,182,403,241</v>
       </c>
       <c r="M44" t="str">
-        <v>215,715,097</v>
+        <v>240,379,742</v>
       </c>
       <c r="N44" t="str">
-        <v>3.88%</v>
+        <v>3.89%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,13 +2349,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>2,443</v>
+        <v>2,676</v>
       </c>
       <c r="F45" t="str">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G45" t="str">
-        <v>4,142</v>
+        <v>4,346</v>
       </c>
       <c r="H45" t="str">
         <v>3</v>
@@ -2364,19 +2364,19 @@
         <v>36,961,262</v>
       </c>
       <c r="J45" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K45" t="str">
-        <v>99,036,954</v>
+        <v>118,755,538</v>
       </c>
       <c r="L45" t="str">
-        <v>6,243,515,427</v>
+        <v>6,638,639,248</v>
       </c>
       <c r="M45" t="str">
-        <v>391,759,194</v>
+        <v>418,836,813</v>
       </c>
       <c r="N45" t="str">
-        <v>6.27%</v>
+        <v>6.31%</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata/Bulanan/10. Okt-LD.xlsx
+++ b/rawdata/Bulanan/10. Okt-LD.xlsx
@@ -457,34 +457,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>7,946</v>
+        <v>8,295</v>
       </c>
       <c r="F2" t="str">
-        <v>3,864</v>
+        <v>4,057</v>
       </c>
       <c r="G2" t="str">
-        <v>1,052</v>
+        <v>1,106</v>
       </c>
       <c r="H2" t="str">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="I2" t="str">
-        <v>2,169,465,883</v>
+        <v>2,300,387,904</v>
       </c>
       <c r="J2" t="str">
-        <v>416</v>
+        <v>439</v>
       </c>
       <c r="K2" t="str">
-        <v>8,230,005,830</v>
+        <v>8,656,581,683</v>
       </c>
       <c r="L2" t="str">
-        <v>29,002,619,350</v>
+        <v>30,513,516,022</v>
       </c>
       <c r="M2" t="str">
-        <v>15,948,367,784</v>
+        <v>16,895,531,025</v>
       </c>
       <c r="N2" t="str">
-        <v>54.99%</v>
+        <v>55.37%</v>
       </c>
     </row>
     <row r="3">
@@ -501,34 +501,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>11,924</v>
+        <v>12,507</v>
       </c>
       <c r="F3" t="str">
-        <v>1,684</v>
+        <v>1,777</v>
       </c>
       <c r="G3" t="str">
-        <v>1,855</v>
+        <v>1,954</v>
       </c>
       <c r="H3" t="str">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="I3" t="str">
-        <v>1,326,391,069</v>
+        <v>1,433,086,696</v>
       </c>
       <c r="J3" t="str">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="K3" t="str">
-        <v>4,331,910,322</v>
+        <v>4,619,570,854</v>
       </c>
       <c r="L3" t="str">
-        <v>48,330,580,645</v>
+        <v>50,796,238,154</v>
       </c>
       <c r="M3" t="str">
-        <v>8,136,543,822</v>
+        <v>8,657,247,019</v>
       </c>
       <c r="N3" t="str">
-        <v>16.84%</v>
+        <v>17.04%</v>
       </c>
     </row>
     <row r="4">
@@ -545,34 +545,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>2,310</v>
+        <v>2,426</v>
       </c>
       <c r="F4" t="str">
-        <v>1,032</v>
+        <v>1,091</v>
       </c>
       <c r="G4" t="str">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="H4" t="str">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I4" t="str">
-        <v>671,642,495</v>
+        <v>762,469,082</v>
       </c>
       <c r="J4" t="str">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K4" t="str">
-        <v>2,508,446,502</v>
+        <v>2,690,415,857</v>
       </c>
       <c r="L4" t="str">
-        <v>8,525,196,607</v>
+        <v>9,080,170,407</v>
       </c>
       <c r="M4" t="str">
-        <v>4,804,772,883</v>
+        <v>5,137,957,280</v>
       </c>
       <c r="N4" t="str">
-        <v>56.36%</v>
+        <v>56.58%</v>
       </c>
     </row>
     <row r="5">
@@ -589,13 +589,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>4,322</v>
+        <v>4,523</v>
       </c>
       <c r="F5" t="str">
-        <v>1,019</v>
+        <v>1,071</v>
       </c>
       <c r="G5" t="str">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H5" t="str">
         <v>11</v>
@@ -610,13 +610,13 @@
         <v>38,695,454</v>
       </c>
       <c r="L5" t="str">
-        <v>5,319,960,793</v>
+        <v>5,539,558,843</v>
       </c>
       <c r="M5" t="str">
-        <v>1,928,051,393</v>
+        <v>2,020,836,392</v>
       </c>
       <c r="N5" t="str">
-        <v>36.24%</v>
+        <v>36.48%</v>
       </c>
     </row>
     <row r="6">
@@ -633,10 +633,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>18,315</v>
+        <v>19,516</v>
       </c>
       <c r="F6" t="str">
-        <v>4,218</v>
+        <v>4,551</v>
       </c>
       <c r="G6" t="str">
         <v>86</v>
@@ -654,13 +654,13 @@
         <v>101,641,843</v>
       </c>
       <c r="L6" t="str">
-        <v>22,673,840,027</v>
+        <v>23,977,704,160</v>
       </c>
       <c r="M6" t="str">
-        <v>6,804,217,690</v>
+        <v>7,280,561,260</v>
       </c>
       <c r="N6" t="str">
-        <v>30.01%</v>
+        <v>30.36%</v>
       </c>
     </row>
     <row r="7">
@@ -677,34 +677,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>5,734</v>
+        <v>6,034</v>
       </c>
       <c r="F7" t="str">
-        <v>2,696</v>
+        <v>2,837</v>
       </c>
       <c r="G7" t="str">
-        <v>3,869</v>
+        <v>4,062</v>
       </c>
       <c r="H7" t="str">
-        <v>805</v>
+        <v>844</v>
       </c>
       <c r="I7" t="str">
-        <v>9,744,031,111</v>
+        <v>10,221,392,747</v>
       </c>
       <c r="J7" t="str">
-        <v>555</v>
+        <v>576</v>
       </c>
       <c r="K7" t="str">
-        <v>11,494,429,271</v>
+        <v>11,944,457,911</v>
       </c>
       <c r="L7" t="str">
-        <v>64,899,087,526</v>
+        <v>68,281,537,859</v>
       </c>
       <c r="M7" t="str">
-        <v>28,470,100,222</v>
+        <v>29,877,494,195</v>
       </c>
       <c r="N7" t="str">
-        <v>43.87%</v>
+        <v>43.76%</v>
       </c>
     </row>
     <row r="8">
@@ -721,10 +721,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>1,734</v>
+        <v>1,883</v>
       </c>
       <c r="F8" t="str">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="G8" t="str">
         <v>0</v>
@@ -742,13 +742,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="str">
-        <v>2,273,710,735</v>
+        <v>2,431,855,674</v>
       </c>
       <c r="M8" t="str">
-        <v>643,666,258</v>
+        <v>693,926,189</v>
       </c>
       <c r="N8" t="str">
-        <v>28.31%</v>
+        <v>28.53%</v>
       </c>
     </row>
     <row r="9">
@@ -765,13 +765,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>2,732</v>
+        <v>2,840</v>
       </c>
       <c r="F9" t="str">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G9" t="str">
-        <v>6,331</v>
+        <v>6,636</v>
       </c>
       <c r="H9" t="str">
         <v>0</v>
@@ -786,13 +786,13 @@
         <v>100,379,570</v>
       </c>
       <c r="L9" t="str">
-        <v>7,708,622,014</v>
+        <v>7,949,775,615</v>
       </c>
       <c r="M9" t="str">
-        <v>105,724,507</v>
+        <v>113,552,439</v>
       </c>
       <c r="N9" t="str">
-        <v>1.37%</v>
+        <v>1.43%</v>
       </c>
     </row>
     <row r="10">
@@ -809,13 +809,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>2,277</v>
+        <v>2,367</v>
       </c>
       <c r="F10" t="str">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G10" t="str">
-        <v>4,381</v>
+        <v>4,612</v>
       </c>
       <c r="H10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="str">
-        <v>6,272,003,903</v>
+        <v>6,532,250,680</v>
       </c>
       <c r="M10" t="str">
-        <v>70,667,632</v>
+        <v>87,599,666</v>
       </c>
       <c r="N10" t="str">
-        <v>1.13%</v>
+        <v>1.34%</v>
       </c>
     </row>
     <row r="11">
@@ -853,13 +853,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>2,803</v>
+        <v>2,929</v>
       </c>
       <c r="F11" t="str">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G11" t="str">
-        <v>7,769</v>
+        <v>8,197</v>
       </c>
       <c r="H11" t="str">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>10,561,565,378</v>
+        <v>11,002,210,914</v>
       </c>
       <c r="M11" t="str">
-        <v>104,015,453</v>
+        <v>106,070,487</v>
       </c>
       <c r="N11" t="str">
-        <v>0.98%</v>
+        <v>0.96%</v>
       </c>
     </row>
     <row r="12">
@@ -897,13 +897,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>1,745</v>
+        <v>1,822</v>
       </c>
       <c r="F12" t="str">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G12" t="str">
-        <v>5,370</v>
+        <v>5,658</v>
       </c>
       <c r="H12" t="str">
         <v>2</v>
@@ -918,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>6,467,842,623</v>
+        <v>6,813,257,320</v>
       </c>
       <c r="M12" t="str">
-        <v>174,281,255</v>
+        <v>178,880,796</v>
       </c>
       <c r="N12" t="str">
-        <v>2.69%</v>
+        <v>2.63%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>954</v>
+        <v>986</v>
       </c>
       <c r="F13" t="str">
         <v>23</v>
       </c>
       <c r="G13" t="str">
-        <v>3,046</v>
+        <v>3,165</v>
       </c>
       <c r="H13" t="str">
         <v>1</v>
@@ -962,13 +962,13 @@
         <v>20,084,148</v>
       </c>
       <c r="L13" t="str">
-        <v>3,586,195,403</v>
+        <v>3,708,664,421</v>
       </c>
       <c r="M13" t="str">
         <v>66,541,558</v>
       </c>
       <c r="N13" t="str">
-        <v>1.86%</v>
+        <v>1.79%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>2,467</v>
+        <v>2,579</v>
       </c>
       <c r="F14" t="str">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G14" t="str">
-        <v>7,321</v>
+        <v>7,704</v>
       </c>
       <c r="H14" t="str">
         <v>0</v>
@@ -1006,13 +1006,13 @@
         <v>0</v>
       </c>
       <c r="L14" t="str">
-        <v>9,123,893,499</v>
+        <v>9,514,985,560</v>
       </c>
       <c r="M14" t="str">
-        <v>129,867,127</v>
+        <v>138,213,917</v>
       </c>
       <c r="N14" t="str">
-        <v>1.42%</v>
+        <v>1.45%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>3,496</v>
+        <v>3,684</v>
       </c>
       <c r="F15" t="str">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G15" t="str">
-        <v>10,464</v>
+        <v>10,942</v>
       </c>
       <c r="H15" t="str">
         <v>0</v>
@@ -1050,13 +1050,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="str">
-        <v>13,388,867,791</v>
+        <v>14,066,665,663</v>
       </c>
       <c r="M15" t="str">
-        <v>72,170,546</v>
+        <v>73,392,657</v>
       </c>
       <c r="N15" t="str">
-        <v>0.54%</v>
+        <v>0.52%</v>
       </c>
     </row>
     <row r="16">
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>1,564</v>
+        <v>1,651</v>
       </c>
       <c r="F16" t="str">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G16" t="str">
-        <v>3,839</v>
+        <v>4,046</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>233,859,144</v>
       </c>
       <c r="L16" t="str">
-        <v>5,586,104,377</v>
+        <v>5,860,786,852</v>
       </c>
       <c r="M16" t="str">
-        <v>152,455,057</v>
+        <v>152,993,257</v>
       </c>
       <c r="N16" t="str">
-        <v>2.73%</v>
+        <v>2.61%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>1,957</v>
+        <v>2,067</v>
       </c>
       <c r="F17" t="str">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G17" t="str">
-        <v>4,519</v>
+        <v>4,738</v>
       </c>
       <c r="H17" t="str">
         <v>0</v>
@@ -1138,13 +1138,13 @@
         <v>100,898,460</v>
       </c>
       <c r="L17" t="str">
-        <v>6,472,980,934</v>
+        <v>6,793,108,493</v>
       </c>
       <c r="M17" t="str">
-        <v>98,456,810</v>
+        <v>98,756,810</v>
       </c>
       <c r="N17" t="str">
-        <v>1.52%</v>
+        <v>1.45%</v>
       </c>
     </row>
     <row r="18">
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>2,894</v>
+        <v>3,041</v>
       </c>
       <c r="F18" t="str">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G18" t="str">
-        <v>10,403</v>
+        <v>10,925</v>
       </c>
       <c r="H18" t="str">
         <v>1</v>
@@ -1182,13 +1182,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="str">
-        <v>12,788,861,696</v>
+        <v>13,459,608,131</v>
       </c>
       <c r="M18" t="str">
-        <v>69,810,881</v>
+        <v>105,969,609</v>
       </c>
       <c r="N18" t="str">
-        <v>0.55%</v>
+        <v>0.79%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>483</v>
+        <v>508</v>
       </c>
       <c r="F19" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" t="str">
-        <v>1,753</v>
+        <v>1,829</v>
       </c>
       <c r="H19" t="str">
         <v>0</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>2,032,543,072</v>
+        <v>2,153,162,993</v>
       </c>
       <c r="M19" t="str">
-        <v>8,938,285</v>
+        <v>9,767,651</v>
       </c>
       <c r="N19" t="str">
-        <v>0.44%</v>
+        <v>0.45%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>3,380</v>
+        <v>3,551</v>
       </c>
       <c r="F20" t="str">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G20" t="str">
-        <v>11,832</v>
+        <v>12,394</v>
       </c>
       <c r="H20" t="str">
         <v>1</v>
@@ -1270,13 +1270,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="str">
-        <v>14,479,511,724</v>
+        <v>15,245,411,333</v>
       </c>
       <c r="M20" t="str">
-        <v>92,734,320</v>
+        <v>105,992,692</v>
       </c>
       <c r="N20" t="str">
-        <v>0.64%</v>
+        <v>0.70%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,34 +1293,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>22,080</v>
+        <v>22,320</v>
       </c>
       <c r="F21" t="str">
-        <v>701</v>
+        <v>758</v>
       </c>
       <c r="G21" t="str">
-        <v>455,633</v>
+        <v>479,904</v>
       </c>
       <c r="H21" t="str">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I21" t="str">
-        <v>37,959,330</v>
+        <v>70,959,330</v>
       </c>
       <c r="J21" t="str">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K21" t="str">
-        <v>167,912,728</v>
+        <v>215,912,728</v>
       </c>
       <c r="L21" t="str">
-        <v>97,858,941,979</v>
+        <v>98,840,448,503</v>
       </c>
       <c r="M21" t="str">
-        <v>1,825,090,211</v>
+        <v>1,976,073,179</v>
       </c>
       <c r="N21" t="str">
-        <v>1.87%</v>
+        <v>2.00%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,13 +1337,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>1,199</v>
+        <v>1,201</v>
       </c>
       <c r="F22" t="str">
         <v>3</v>
       </c>
       <c r="G22" t="str">
-        <v>10,160</v>
+        <v>10,695</v>
       </c>
       <c r="H22" t="str">
         <v>0</v>
@@ -1358,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="str">
-        <v>13,262,750,896</v>
+        <v>13,263,855,868</v>
       </c>
       <c r="M22" t="str">
         <v>12,940,251</v>
@@ -1381,34 +1381,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E23" t="str">
-        <v>32,655</v>
+        <v>34,615</v>
       </c>
       <c r="F23" t="str">
-        <v>1,484</v>
+        <v>1,562</v>
       </c>
       <c r="G23" t="str">
-        <v>2,922</v>
+        <v>3,082</v>
       </c>
       <c r="H23" t="str">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="I23" t="str">
-        <v>2,629,200,130</v>
+        <v>2,720,340,141</v>
       </c>
       <c r="J23" t="str">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="K23" t="str">
-        <v>3,113,672,466</v>
+        <v>3,225,180,976</v>
       </c>
       <c r="L23" t="str">
-        <v>106,991,449,119</v>
+        <v>112,918,266,342</v>
       </c>
       <c r="M23" t="str">
-        <v>8,463,700,391</v>
+        <v>8,824,602,768</v>
       </c>
       <c r="N23" t="str">
-        <v>7.91%</v>
+        <v>7.82%</v>
       </c>
     </row>
     <row r="24">
@@ -1425,34 +1425,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>1,550</v>
+        <v>1,642</v>
       </c>
       <c r="F24" t="str">
-        <v>508</v>
+        <v>532</v>
       </c>
       <c r="G24" t="str">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="H24" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I24" t="str">
-        <v>61,623,069</v>
+        <v>75,928,581</v>
       </c>
       <c r="J24" t="str">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K24" t="str">
-        <v>378,003,597</v>
+        <v>393,085,127</v>
       </c>
       <c r="L24" t="str">
-        <v>3,909,944,853</v>
+        <v>4,168,014,273</v>
       </c>
       <c r="M24" t="str">
-        <v>1,092,479,240</v>
+        <v>1,148,581,223</v>
       </c>
       <c r="N24" t="str">
-        <v>27.94%</v>
+        <v>27.56%</v>
       </c>
     </row>
     <row r="25">
@@ -1469,19 +1469,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E25" t="str">
-        <v>3,860</v>
+        <v>3,981</v>
       </c>
       <c r="F25" t="str">
-        <v>1,169</v>
+        <v>1,206</v>
       </c>
       <c r="G25" t="str">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="H25" t="str">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I25" t="str">
-        <v>344,401,228</v>
+        <v>354,458,541</v>
       </c>
       <c r="J25" t="str">
         <v>28</v>
@@ -1490,13 +1490,13 @@
         <v>530,333,830</v>
       </c>
       <c r="L25" t="str">
-        <v>9,880,369,175</v>
+        <v>10,226,011,515</v>
       </c>
       <c r="M25" t="str">
-        <v>2,406,586,064</v>
+        <v>2,504,912,718</v>
       </c>
       <c r="N25" t="str">
-        <v>24.36%</v>
+        <v>24.50%</v>
       </c>
     </row>
     <row r="26">
@@ -1513,10 +1513,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>1,620</v>
+        <v>1,716</v>
       </c>
       <c r="F26" t="str">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="G26" t="str">
         <v>0</v>
@@ -1534,13 +1534,13 @@
         <v>0</v>
       </c>
       <c r="L26" t="str">
-        <v>1,792,642,986</v>
+        <v>1,886,212,743</v>
       </c>
       <c r="M26" t="str">
-        <v>423,436,630</v>
+        <v>439,984,287</v>
       </c>
       <c r="N26" t="str">
-        <v>23.62%</v>
+        <v>23.33%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,10 +1557,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>13,075</v>
+        <v>14,068</v>
       </c>
       <c r="F27" t="str">
-        <v>2,279</v>
+        <v>2,430</v>
       </c>
       <c r="G27" t="str">
         <v>1</v>
@@ -1578,13 +1578,13 @@
         <v>0</v>
       </c>
       <c r="L27" t="str">
-        <v>14,610,417,659</v>
+        <v>15,567,324,294</v>
       </c>
       <c r="M27" t="str">
-        <v>2,834,814,154</v>
+        <v>3,009,480,701</v>
       </c>
       <c r="N27" t="str">
-        <v>19.40%</v>
+        <v>19.33%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,34 +1601,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>2,917</v>
+        <v>3,077</v>
       </c>
       <c r="F28" t="str">
-        <v>967</v>
+        <v>1,020</v>
       </c>
       <c r="G28" t="str">
-        <v>1,093</v>
+        <v>1,147</v>
       </c>
       <c r="H28" t="str">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="I28" t="str">
-        <v>2,421,463,452</v>
+        <v>2,567,450,643</v>
       </c>
       <c r="J28" t="str">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K28" t="str">
-        <v>2,565,373,484</v>
+        <v>2,653,253,720</v>
       </c>
       <c r="L28" t="str">
-        <v>30,801,950,178</v>
+        <v>32,462,649,571</v>
       </c>
       <c r="M28" t="str">
-        <v>8,550,242,846</v>
+        <v>8,985,186,608</v>
       </c>
       <c r="N28" t="str">
-        <v>27.76%</v>
+        <v>27.68%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,10 +1645,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>2,791</v>
+        <v>2,872</v>
       </c>
       <c r="F29" t="str">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="G29" t="str">
         <v>0</v>
@@ -1666,13 +1666,13 @@
         <v>0</v>
       </c>
       <c r="L29" t="str">
-        <v>3,158,143,248</v>
+        <v>3,230,904,984</v>
       </c>
       <c r="M29" t="str">
-        <v>622,809,119</v>
+        <v>635,949,244</v>
       </c>
       <c r="N29" t="str">
-        <v>19.72%</v>
+        <v>19.68%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,13 +1689,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>3,241</v>
+        <v>3,352</v>
       </c>
       <c r="F30" t="str">
-        <v>533</v>
+        <v>554</v>
       </c>
       <c r="G30" t="str">
-        <v>1,468</v>
+        <v>1,546</v>
       </c>
       <c r="H30" t="str">
         <v>6</v>
@@ -1710,13 +1710,13 @@
         <v>84,536,012</v>
       </c>
       <c r="L30" t="str">
-        <v>8,580,000,954</v>
+        <v>8,911,755,693</v>
       </c>
       <c r="M30" t="str">
-        <v>830,538,892</v>
+        <v>857,525,206</v>
       </c>
       <c r="N30" t="str">
-        <v>9.68%</v>
+        <v>9.62%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,13 +1733,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>898</v>
+        <v>936</v>
       </c>
       <c r="F31" t="str">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="G31" t="str">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="H31" t="str">
         <v>5</v>
@@ -1748,19 +1748,19 @@
         <v>57,255,540</v>
       </c>
       <c r="J31" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" t="str">
-        <v>15,120,660</v>
+        <v>30,342,050</v>
       </c>
       <c r="L31" t="str">
-        <v>2,223,708,422</v>
+        <v>2,325,563,558</v>
       </c>
       <c r="M31" t="str">
-        <v>372,091,408</v>
+        <v>407,605,255</v>
       </c>
       <c r="N31" t="str">
-        <v>16.73%</v>
+        <v>17.53%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,10 +1777,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>2,260</v>
+        <v>2,363</v>
       </c>
       <c r="F32" t="str">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="G32" t="str">
         <v>96</v>
@@ -1798,13 +1798,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="str">
-        <v>2,558,183,990</v>
+        <v>2,647,967,365</v>
       </c>
       <c r="M32" t="str">
-        <v>426,858,394</v>
+        <v>437,343,365</v>
       </c>
       <c r="N32" t="str">
-        <v>16.69%</v>
+        <v>16.52%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,13 +1821,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>6,259</v>
+        <v>6,718</v>
       </c>
       <c r="F33" t="str">
-        <v>658</v>
+        <v>720</v>
       </c>
       <c r="G33" t="str">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H33" t="str">
         <v>4</v>
@@ -1842,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="str">
-        <v>7,228,776,029</v>
+        <v>7,683,554,034</v>
       </c>
       <c r="M33" t="str">
-        <v>847,580,482</v>
+        <v>932,671,084</v>
       </c>
       <c r="N33" t="str">
-        <v>11.73%</v>
+        <v>12.14%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,19 +1865,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>1,072</v>
+        <v>1,133</v>
       </c>
       <c r="F34" t="str">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="G34" t="str">
-        <v>1,652</v>
+        <v>1,782</v>
       </c>
       <c r="H34" t="str">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I34" t="str">
-        <v>514,537,816</v>
+        <v>555,158,291</v>
       </c>
       <c r="J34" t="str">
         <v>41</v>
@@ -1886,13 +1886,13 @@
         <v>793,460,058</v>
       </c>
       <c r="L34" t="str">
-        <v>10,900,665,531</v>
+        <v>11,476,375,199</v>
       </c>
       <c r="M34" t="str">
-        <v>1,965,919,421</v>
+        <v>2,051,435,925</v>
       </c>
       <c r="N34" t="str">
-        <v>18.03%</v>
+        <v>17.88%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,10 +1909,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>3,525</v>
+        <v>3,715</v>
       </c>
       <c r="F35" t="str">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="G35" t="str">
         <v>231</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="L35" t="str">
-        <v>3,977,161,524</v>
+        <v>4,148,491,610</v>
       </c>
       <c r="M35" t="str">
-        <v>423,899,866</v>
+        <v>444,275,176</v>
       </c>
       <c r="N35" t="str">
-        <v>10.66%</v>
+        <v>10.71%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,13 +1953,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>2,214</v>
+        <v>2,350</v>
       </c>
       <c r="F36" t="str">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="G36" t="str">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H36" t="str">
         <v>0</v>
@@ -1974,13 +1974,13 @@
         <v>0</v>
       </c>
       <c r="L36" t="str">
-        <v>2,442,857,539</v>
+        <v>2,560,737,277</v>
       </c>
       <c r="M36" t="str">
-        <v>252,387,235</v>
+        <v>267,458,163</v>
       </c>
       <c r="N36" t="str">
-        <v>10.33%</v>
+        <v>10.44%</v>
       </c>
     </row>
     <row r="37">
@@ -2041,13 +2041,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>879</v>
+        <v>920</v>
       </c>
       <c r="F38" t="str">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="G38" t="str">
-        <v>1,641</v>
+        <v>1,732</v>
       </c>
       <c r="H38" t="str">
         <v>32</v>
@@ -2056,19 +2056,19 @@
         <v>383,834,630</v>
       </c>
       <c r="J38" t="str">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K38" t="str">
-        <v>327,611,272</v>
+        <v>346,410,700</v>
       </c>
       <c r="L38" t="str">
-        <v>8,866,732,954</v>
+        <v>9,179,372,527</v>
       </c>
       <c r="M38" t="str">
-        <v>1,195,654,944</v>
+        <v>1,229,232,561</v>
       </c>
       <c r="N38" t="str">
-        <v>13.48%</v>
+        <v>13.39%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,19 +2085,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>5,077</v>
+        <v>5,218</v>
       </c>
       <c r="F39" t="str">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="G39" t="str">
-        <v>5,877</v>
+        <v>6,179</v>
       </c>
       <c r="H39" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I39" t="str">
-        <v>27,082,510</v>
+        <v>37,100,895</v>
       </c>
       <c r="J39" t="str">
         <v>4</v>
@@ -2106,13 +2106,13 @@
         <v>84,725,256</v>
       </c>
       <c r="L39" t="str">
-        <v>12,245,012,399</v>
+        <v>12,728,750,525</v>
       </c>
       <c r="M39" t="str">
-        <v>365,985,764</v>
+        <v>398,682,138</v>
       </c>
       <c r="N39" t="str">
-        <v>2.99%</v>
+        <v>3.13%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,13 +2173,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>1,025</v>
+        <v>1,148</v>
       </c>
       <c r="F41" t="str">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G41" t="str">
-        <v>1,218</v>
+        <v>1,276</v>
       </c>
       <c r="H41" t="str">
         <v>2</v>
@@ -2194,13 +2194,13 @@
         <v>50,770,592</v>
       </c>
       <c r="L41" t="str">
-        <v>2,376,605,228</v>
+        <v>2,580,086,497</v>
       </c>
       <c r="M41" t="str">
-        <v>136,758,629</v>
+        <v>140,444,687</v>
       </c>
       <c r="N41" t="str">
-        <v>5.75%</v>
+        <v>5.44%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>764</v>
+        <v>825</v>
       </c>
       <c r="F42" t="str">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G42" t="str">
-        <v>1,231</v>
+        <v>1,297</v>
       </c>
       <c r="H42" t="str">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>66,445,865</v>
       </c>
       <c r="L42" t="str">
-        <v>2,003,475,858</v>
+        <v>2,140,196,613</v>
       </c>
       <c r="M42" t="str">
-        <v>92,376,996</v>
+        <v>93,098,705</v>
       </c>
       <c r="N42" t="str">
-        <v>4.61%</v>
+        <v>4.35%</v>
       </c>
     </row>
     <row r="43">
@@ -2261,19 +2261,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E43" t="str">
-        <v>3,057</v>
+        <v>3,302</v>
       </c>
       <c r="F43" t="str">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="G43" t="str">
-        <v>5,229</v>
+        <v>5,493</v>
       </c>
       <c r="H43" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I43" t="str">
-        <v>76,692,069</v>
+        <v>112,506,786</v>
       </c>
       <c r="J43" t="str">
         <v>0</v>
@@ -2282,13 +2282,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="str">
-        <v>8,079,425,517</v>
+        <v>8,539,760,329</v>
       </c>
       <c r="M43" t="str">
-        <v>342,535,988</v>
+        <v>386,278,655</v>
       </c>
       <c r="N43" t="str">
-        <v>4.24%</v>
+        <v>4.52%</v>
       </c>
     </row>
     <row r="44">
@@ -2305,19 +2305,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>2,431</v>
+        <v>2,697</v>
       </c>
       <c r="F44" t="str">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="G44" t="str">
-        <v>2,965</v>
+        <v>3,133</v>
       </c>
       <c r="H44" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I44" t="str">
-        <v>39,722,057</v>
+        <v>49,794,252</v>
       </c>
       <c r="J44" t="str">
         <v>3</v>
@@ -2326,13 +2326,13 @@
         <v>54,162,704</v>
       </c>
       <c r="L44" t="str">
-        <v>6,182,403,241</v>
+        <v>6,780,384,213</v>
       </c>
       <c r="M44" t="str">
-        <v>240,379,742</v>
+        <v>273,539,193</v>
       </c>
       <c r="N44" t="str">
-        <v>3.89%</v>
+        <v>4.03%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,13 +2349,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>2,676</v>
+        <v>2,892</v>
       </c>
       <c r="F45" t="str">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="G45" t="str">
-        <v>4,346</v>
+        <v>4,559</v>
       </c>
       <c r="H45" t="str">
         <v>3</v>
@@ -2370,13 +2370,13 @@
         <v>118,755,538</v>
       </c>
       <c r="L45" t="str">
-        <v>6,638,639,248</v>
+        <v>7,047,353,536</v>
       </c>
       <c r="M45" t="str">
-        <v>418,836,813</v>
+        <v>422,681,870</v>
       </c>
       <c r="N45" t="str">
-        <v>6.31%</v>
+        <v>6.00%</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata/Bulanan/10. Okt-LD.xlsx
+++ b/rawdata/Bulanan/10. Okt-LD.xlsx
@@ -457,34 +457,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>8,295</v>
+        <v>8,654</v>
       </c>
       <c r="F2" t="str">
-        <v>4,057</v>
+        <v>4,225</v>
       </c>
       <c r="G2" t="str">
-        <v>1,106</v>
+        <v>1,164</v>
       </c>
       <c r="H2" t="str">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="I2" t="str">
-        <v>2,300,387,904</v>
+        <v>2,400,615,471</v>
       </c>
       <c r="J2" t="str">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="K2" t="str">
-        <v>8,656,581,683</v>
+        <v>9,033,934,134</v>
       </c>
       <c r="L2" t="str">
-        <v>30,513,516,022</v>
+        <v>31,936,791,934</v>
       </c>
       <c r="M2" t="str">
-        <v>16,895,531,025</v>
+        <v>17,587,816,969</v>
       </c>
       <c r="N2" t="str">
-        <v>55.37%</v>
+        <v>55.07%</v>
       </c>
     </row>
     <row r="3">
@@ -501,34 +501,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>12,507</v>
+        <v>13,017</v>
       </c>
       <c r="F3" t="str">
-        <v>1,777</v>
+        <v>1,849</v>
       </c>
       <c r="G3" t="str">
-        <v>1,954</v>
+        <v>2,029</v>
       </c>
       <c r="H3" t="str">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I3" t="str">
-        <v>1,433,086,696</v>
+        <v>1,480,876,811</v>
       </c>
       <c r="J3" t="str">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="K3" t="str">
-        <v>4,619,570,854</v>
+        <v>4,956,852,281</v>
       </c>
       <c r="L3" t="str">
-        <v>50,796,238,154</v>
+        <v>52,832,483,571</v>
       </c>
       <c r="M3" t="str">
-        <v>8,657,247,019</v>
+        <v>9,080,394,846</v>
       </c>
       <c r="N3" t="str">
-        <v>17.04%</v>
+        <v>17.19%</v>
       </c>
     </row>
     <row r="4">
@@ -545,34 +545,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>2,426</v>
+        <v>2,546</v>
       </c>
       <c r="F4" t="str">
-        <v>1,091</v>
+        <v>1,149</v>
       </c>
       <c r="G4" t="str">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="H4" t="str">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I4" t="str">
-        <v>762,469,082</v>
+        <v>782,583,708</v>
       </c>
       <c r="J4" t="str">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="K4" t="str">
-        <v>2,690,415,857</v>
+        <v>2,817,253,580</v>
       </c>
       <c r="L4" t="str">
-        <v>9,080,170,407</v>
+        <v>9,523,187,931</v>
       </c>
       <c r="M4" t="str">
-        <v>5,137,957,280</v>
+        <v>5,389,354,024</v>
       </c>
       <c r="N4" t="str">
-        <v>56.58%</v>
+        <v>56.59%</v>
       </c>
     </row>
     <row r="5">
@@ -589,10 +589,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>4,523</v>
+        <v>4,740</v>
       </c>
       <c r="F5" t="str">
-        <v>1,071</v>
+        <v>1,116</v>
       </c>
       <c r="G5" t="str">
         <v>25</v>
@@ -610,13 +610,13 @@
         <v>38,695,454</v>
       </c>
       <c r="L5" t="str">
-        <v>5,539,558,843</v>
+        <v>5,748,223,327</v>
       </c>
       <c r="M5" t="str">
-        <v>2,020,836,392</v>
+        <v>2,064,057,797</v>
       </c>
       <c r="N5" t="str">
-        <v>36.48%</v>
+        <v>35.91%</v>
       </c>
     </row>
     <row r="6">
@@ -633,10 +633,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>19,516</v>
+        <v>20,774</v>
       </c>
       <c r="F6" t="str">
-        <v>4,551</v>
+        <v>4,857</v>
       </c>
       <c r="G6" t="str">
         <v>86</v>
@@ -654,13 +654,13 @@
         <v>101,641,843</v>
       </c>
       <c r="L6" t="str">
-        <v>23,977,704,160</v>
+        <v>25,311,875,843</v>
       </c>
       <c r="M6" t="str">
-        <v>7,280,561,260</v>
+        <v>7,709,505,086</v>
       </c>
       <c r="N6" t="str">
-        <v>30.36%</v>
+        <v>30.46%</v>
       </c>
     </row>
     <row r="7">
@@ -677,34 +677,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>6,034</v>
+        <v>6,357</v>
       </c>
       <c r="F7" t="str">
-        <v>2,837</v>
+        <v>2,985</v>
       </c>
       <c r="G7" t="str">
-        <v>4,062</v>
+        <v>4,285</v>
       </c>
       <c r="H7" t="str">
-        <v>844</v>
+        <v>897</v>
       </c>
       <c r="I7" t="str">
-        <v>10,221,392,747</v>
+        <v>10,839,519,559</v>
       </c>
       <c r="J7" t="str">
-        <v>576</v>
+        <v>602</v>
       </c>
       <c r="K7" t="str">
-        <v>11,944,457,911</v>
+        <v>12,497,510,297</v>
       </c>
       <c r="L7" t="str">
-        <v>68,281,537,859</v>
+        <v>72,128,057,848</v>
       </c>
       <c r="M7" t="str">
-        <v>29,877,494,195</v>
+        <v>31,450,986,207</v>
       </c>
       <c r="N7" t="str">
-        <v>43.76%</v>
+        <v>43.60%</v>
       </c>
     </row>
     <row r="8">
@@ -721,10 +721,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>1,883</v>
+        <v>1,954</v>
       </c>
       <c r="F8" t="str">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="G8" t="str">
         <v>0</v>
@@ -742,13 +742,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="str">
-        <v>2,431,855,674</v>
+        <v>2,499,838,442</v>
       </c>
       <c r="M8" t="str">
-        <v>693,926,189</v>
+        <v>719,929,247</v>
       </c>
       <c r="N8" t="str">
-        <v>28.53%</v>
+        <v>28.80%</v>
       </c>
     </row>
     <row r="9">
@@ -765,13 +765,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>2,840</v>
+        <v>2,954</v>
       </c>
       <c r="F9" t="str">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G9" t="str">
-        <v>6,636</v>
+        <v>6,944</v>
       </c>
       <c r="H9" t="str">
         <v>0</v>
@@ -786,10 +786,10 @@
         <v>100,379,570</v>
       </c>
       <c r="L9" t="str">
-        <v>7,949,775,615</v>
+        <v>8,397,919,854</v>
       </c>
       <c r="M9" t="str">
-        <v>113,552,439</v>
+        <v>120,007,229</v>
       </c>
       <c r="N9" t="str">
         <v>1.43%</v>
@@ -809,13 +809,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>2,367</v>
+        <v>2,463</v>
       </c>
       <c r="F10" t="str">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G10" t="str">
-        <v>4,612</v>
+        <v>4,845</v>
       </c>
       <c r="H10" t="str">
         <v>0</v>
@@ -830,10 +830,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="str">
-        <v>6,532,250,680</v>
+        <v>6,914,170,889</v>
       </c>
       <c r="M10" t="str">
-        <v>87,599,666</v>
+        <v>92,414,439</v>
       </c>
       <c r="N10" t="str">
         <v>1.34%</v>
@@ -853,13 +853,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>2,929</v>
+        <v>3,068</v>
       </c>
       <c r="F11" t="str">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G11" t="str">
-        <v>8,197</v>
+        <v>8,629</v>
       </c>
       <c r="H11" t="str">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>11,002,210,914</v>
+        <v>11,643,050,024</v>
       </c>
       <c r="M11" t="str">
-        <v>106,070,487</v>
+        <v>117,754,123</v>
       </c>
       <c r="N11" t="str">
-        <v>0.96%</v>
+        <v>1.01%</v>
       </c>
     </row>
     <row r="12">
@@ -897,19 +897,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>1,822</v>
+        <v>1,909</v>
       </c>
       <c r="F12" t="str">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G12" t="str">
-        <v>5,658</v>
+        <v>5,953</v>
       </c>
       <c r="H12" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" t="str">
-        <v>20,271,280</v>
+        <v>32,410,311</v>
       </c>
       <c r="J12" t="str">
         <v>0</v>
@@ -918,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>6,813,257,320</v>
+        <v>7,193,125,554</v>
       </c>
       <c r="M12" t="str">
-        <v>178,880,796</v>
+        <v>220,776,642</v>
       </c>
       <c r="N12" t="str">
-        <v>2.63%</v>
+        <v>3.07%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>986</v>
+        <v>1,021</v>
       </c>
       <c r="F13" t="str">
         <v>23</v>
       </c>
       <c r="G13" t="str">
-        <v>3,165</v>
+        <v>3,287</v>
       </c>
       <c r="H13" t="str">
         <v>1</v>
@@ -962,13 +962,13 @@
         <v>20,084,148</v>
       </c>
       <c r="L13" t="str">
-        <v>3,708,664,421</v>
+        <v>3,851,223,935</v>
       </c>
       <c r="M13" t="str">
         <v>66,541,558</v>
       </c>
       <c r="N13" t="str">
-        <v>1.79%</v>
+        <v>1.73%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>2,579</v>
+        <v>2,703</v>
       </c>
       <c r="F14" t="str">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G14" t="str">
-        <v>7,704</v>
+        <v>8,088</v>
       </c>
       <c r="H14" t="str">
         <v>0</v>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="str">
-        <v>9,514,985,560</v>
+        <v>9,928,685,821</v>
       </c>
       <c r="M14" t="str">
-        <v>138,213,917</v>
+        <v>143,612,048</v>
       </c>
       <c r="N14" t="str">
         <v>1.45%</v>
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>3,684</v>
+        <v>3,858</v>
       </c>
       <c r="F15" t="str">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G15" t="str">
-        <v>10,942</v>
+        <v>11,418</v>
       </c>
       <c r="H15" t="str">
         <v>0</v>
@@ -1050,13 +1050,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="str">
-        <v>14,066,665,663</v>
+        <v>14,654,446,416</v>
       </c>
       <c r="M15" t="str">
-        <v>73,392,657</v>
+        <v>82,196,516</v>
       </c>
       <c r="N15" t="str">
-        <v>0.52%</v>
+        <v>0.56%</v>
       </c>
     </row>
     <row r="16">
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>1,651</v>
+        <v>1,729</v>
       </c>
       <c r="F16" t="str">
         <v>25</v>
       </c>
       <c r="G16" t="str">
-        <v>4,046</v>
+        <v>4,256</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>233,859,144</v>
       </c>
       <c r="L16" t="str">
-        <v>5,860,786,852</v>
+        <v>6,097,620,703</v>
       </c>
       <c r="M16" t="str">
         <v>152,993,257</v>
       </c>
       <c r="N16" t="str">
-        <v>2.61%</v>
+        <v>2.51%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>2,067</v>
+        <v>2,164</v>
       </c>
       <c r="F17" t="str">
         <v>28</v>
       </c>
       <c r="G17" t="str">
-        <v>4,738</v>
+        <v>4,959</v>
       </c>
       <c r="H17" t="str">
         <v>0</v>
@@ -1138,13 +1138,13 @@
         <v>100,898,460</v>
       </c>
       <c r="L17" t="str">
-        <v>6,793,108,493</v>
+        <v>7,146,469,120</v>
       </c>
       <c r="M17" t="str">
         <v>98,756,810</v>
       </c>
       <c r="N17" t="str">
-        <v>1.45%</v>
+        <v>1.38%</v>
       </c>
     </row>
     <row r="18">
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>3,041</v>
+        <v>3,183</v>
       </c>
       <c r="F18" t="str">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G18" t="str">
-        <v>10,925</v>
+        <v>11,441</v>
       </c>
       <c r="H18" t="str">
         <v>1</v>
@@ -1182,13 +1182,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="str">
-        <v>13,459,608,131</v>
+        <v>14,020,325,672</v>
       </c>
       <c r="M18" t="str">
-        <v>105,969,609</v>
+        <v>114,838,677</v>
       </c>
       <c r="N18" t="str">
-        <v>0.79%</v>
+        <v>0.82%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>508</v>
+        <v>532</v>
       </c>
       <c r="F19" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" t="str">
-        <v>1,829</v>
+        <v>1,905</v>
       </c>
       <c r="H19" t="str">
         <v>0</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>2,153,162,993</v>
+        <v>2,250,702,075</v>
       </c>
       <c r="M19" t="str">
-        <v>9,767,651</v>
+        <v>9,860,041</v>
       </c>
       <c r="N19" t="str">
-        <v>0.45%</v>
+        <v>0.44%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>3,551</v>
+        <v>3,717</v>
       </c>
       <c r="F20" t="str">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G20" t="str">
-        <v>12,394</v>
+        <v>12,956</v>
       </c>
       <c r="H20" t="str">
         <v>1</v>
@@ -1270,13 +1270,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="str">
-        <v>15,245,411,333</v>
+        <v>15,903,423,500</v>
       </c>
       <c r="M20" t="str">
-        <v>105,992,692</v>
+        <v>106,492,692</v>
       </c>
       <c r="N20" t="str">
-        <v>0.70%</v>
+        <v>0.67%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>22,320</v>
+        <v>22,545</v>
       </c>
       <c r="F21" t="str">
-        <v>758</v>
+        <v>794</v>
       </c>
       <c r="G21" t="str">
-        <v>479,904</v>
+        <v>504,196</v>
       </c>
       <c r="H21" t="str">
         <v>6</v>
@@ -1314,13 +1314,13 @@
         <v>215,912,728</v>
       </c>
       <c r="L21" t="str">
-        <v>98,840,448,503</v>
+        <v>99,736,204,092</v>
       </c>
       <c r="M21" t="str">
-        <v>1,976,073,179</v>
+        <v>2,026,462,325</v>
       </c>
       <c r="N21" t="str">
-        <v>2.00%</v>
+        <v>2.03%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,13 +1337,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>1,201</v>
+        <v>1,203</v>
       </c>
       <c r="F22" t="str">
         <v>3</v>
       </c>
       <c r="G22" t="str">
-        <v>10,695</v>
+        <v>11,230</v>
       </c>
       <c r="H22" t="str">
         <v>0</v>
@@ -1358,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="str">
-        <v>13,263,855,868</v>
+        <v>13,265,319,030</v>
       </c>
       <c r="M22" t="str">
         <v>12,940,251</v>
@@ -1381,34 +1381,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E23" t="str">
-        <v>34,615</v>
+        <v>36,385</v>
       </c>
       <c r="F23" t="str">
-        <v>1,562</v>
+        <v>1,643</v>
       </c>
       <c r="G23" t="str">
-        <v>3,082</v>
+        <v>3,251</v>
       </c>
       <c r="H23" t="str">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="I23" t="str">
-        <v>2,720,340,141</v>
+        <v>2,895,994,773</v>
       </c>
       <c r="J23" t="str">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="K23" t="str">
-        <v>3,225,180,976</v>
+        <v>3,523,077,977</v>
       </c>
       <c r="L23" t="str">
-        <v>112,918,266,342</v>
+        <v>118,610,165,298</v>
       </c>
       <c r="M23" t="str">
-        <v>8,824,602,768</v>
+        <v>9,394,249,001</v>
       </c>
       <c r="N23" t="str">
-        <v>7.82%</v>
+        <v>7.92%</v>
       </c>
     </row>
     <row r="24">
@@ -1425,13 +1425,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>1,642</v>
+        <v>1,720</v>
       </c>
       <c r="F24" t="str">
-        <v>532</v>
+        <v>551</v>
       </c>
       <c r="G24" t="str">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="H24" t="str">
         <v>6</v>
@@ -1440,19 +1440,19 @@
         <v>75,928,581</v>
       </c>
       <c r="J24" t="str">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K24" t="str">
-        <v>393,085,127</v>
+        <v>413,967,834</v>
       </c>
       <c r="L24" t="str">
-        <v>4,168,014,273</v>
+        <v>4,402,845,322</v>
       </c>
       <c r="M24" t="str">
-        <v>1,148,581,223</v>
+        <v>1,211,782,702</v>
       </c>
       <c r="N24" t="str">
-        <v>27.56%</v>
+        <v>27.52%</v>
       </c>
     </row>
     <row r="25">
@@ -1469,34 +1469,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E25" t="str">
-        <v>3,981</v>
+        <v>4,115</v>
       </c>
       <c r="F25" t="str">
-        <v>1,206</v>
+        <v>1,252</v>
       </c>
       <c r="G25" t="str">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="H25" t="str">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I25" t="str">
-        <v>354,458,541</v>
+        <v>368,764,053</v>
       </c>
       <c r="J25" t="str">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K25" t="str">
-        <v>530,333,830</v>
+        <v>564,663,506</v>
       </c>
       <c r="L25" t="str">
-        <v>10,226,011,515</v>
+        <v>10,616,880,967</v>
       </c>
       <c r="M25" t="str">
-        <v>2,504,912,718</v>
+        <v>2,631,097,479</v>
       </c>
       <c r="N25" t="str">
-        <v>24.50%</v>
+        <v>24.78%</v>
       </c>
     </row>
     <row r="26">
@@ -1513,10 +1513,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>1,716</v>
+        <v>1,786</v>
       </c>
       <c r="F26" t="str">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="G26" t="str">
         <v>0</v>
@@ -1534,13 +1534,13 @@
         <v>0</v>
       </c>
       <c r="L26" t="str">
-        <v>1,886,212,743</v>
+        <v>1,945,486,860</v>
       </c>
       <c r="M26" t="str">
-        <v>439,984,287</v>
+        <v>462,775,073</v>
       </c>
       <c r="N26" t="str">
-        <v>23.33%</v>
+        <v>23.79%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,10 +1557,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>14,068</v>
+        <v>14,861</v>
       </c>
       <c r="F27" t="str">
-        <v>2,430</v>
+        <v>2,570</v>
       </c>
       <c r="G27" t="str">
         <v>1</v>
@@ -1578,13 +1578,13 @@
         <v>0</v>
       </c>
       <c r="L27" t="str">
-        <v>15,567,324,294</v>
+        <v>16,219,542,666</v>
       </c>
       <c r="M27" t="str">
-        <v>3,009,480,701</v>
+        <v>3,171,664,687</v>
       </c>
       <c r="N27" t="str">
-        <v>19.33%</v>
+        <v>19.55%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,34 +1601,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>3,077</v>
+        <v>3,227</v>
       </c>
       <c r="F28" t="str">
-        <v>1,020</v>
+        <v>1,066</v>
       </c>
       <c r="G28" t="str">
-        <v>1,147</v>
+        <v>1,195</v>
       </c>
       <c r="H28" t="str">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I28" t="str">
-        <v>2,567,450,643</v>
+        <v>2,611,635,871</v>
       </c>
       <c r="J28" t="str">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="K28" t="str">
-        <v>2,653,253,720</v>
+        <v>2,897,053,117</v>
       </c>
       <c r="L28" t="str">
-        <v>32,462,649,571</v>
+        <v>34,071,029,549</v>
       </c>
       <c r="M28" t="str">
-        <v>8,985,186,608</v>
+        <v>9,445,341,025</v>
       </c>
       <c r="N28" t="str">
-        <v>27.68%</v>
+        <v>27.72%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,10 +1645,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>2,872</v>
+        <v>2,979</v>
       </c>
       <c r="F29" t="str">
-        <v>488</v>
+        <v>511</v>
       </c>
       <c r="G29" t="str">
         <v>0</v>
@@ -1666,13 +1666,13 @@
         <v>0</v>
       </c>
       <c r="L29" t="str">
-        <v>3,230,904,984</v>
+        <v>3,319,615,734</v>
       </c>
       <c r="M29" t="str">
-        <v>635,949,244</v>
+        <v>654,081,046</v>
       </c>
       <c r="N29" t="str">
-        <v>19.68%</v>
+        <v>19.70%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,13 +1689,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>3,352</v>
+        <v>3,464</v>
       </c>
       <c r="F30" t="str">
-        <v>554</v>
+        <v>569</v>
       </c>
       <c r="G30" t="str">
-        <v>1,546</v>
+        <v>1,629</v>
       </c>
       <c r="H30" t="str">
         <v>6</v>
@@ -1710,13 +1710,13 @@
         <v>84,536,012</v>
       </c>
       <c r="L30" t="str">
-        <v>8,911,755,693</v>
+        <v>9,245,355,378</v>
       </c>
       <c r="M30" t="str">
-        <v>857,525,206</v>
+        <v>888,487,278</v>
       </c>
       <c r="N30" t="str">
-        <v>9.62%</v>
+        <v>9.61%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,13 +1733,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>936</v>
+        <v>974</v>
       </c>
       <c r="F31" t="str">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="G31" t="str">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="H31" t="str">
         <v>5</v>
@@ -1748,19 +1748,19 @@
         <v>57,255,540</v>
       </c>
       <c r="J31" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" t="str">
-        <v>30,342,050</v>
+        <v>47,809,288</v>
       </c>
       <c r="L31" t="str">
-        <v>2,325,563,558</v>
+        <v>2,404,991,089</v>
       </c>
       <c r="M31" t="str">
-        <v>407,605,255</v>
+        <v>446,535,601</v>
       </c>
       <c r="N31" t="str">
-        <v>17.53%</v>
+        <v>18.57%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,10 +1777,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>2,363</v>
+        <v>2,469</v>
       </c>
       <c r="F32" t="str">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G32" t="str">
         <v>96</v>
@@ -1798,13 +1798,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="str">
-        <v>2,647,967,365</v>
+        <v>2,733,801,358</v>
       </c>
       <c r="M32" t="str">
-        <v>437,343,365</v>
+        <v>454,363,870</v>
       </c>
       <c r="N32" t="str">
-        <v>16.52%</v>
+        <v>16.62%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,13 +1821,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>6,718</v>
+        <v>7,242</v>
       </c>
       <c r="F33" t="str">
-        <v>720</v>
+        <v>767</v>
       </c>
       <c r="G33" t="str">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H33" t="str">
         <v>4</v>
@@ -1842,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="str">
-        <v>7,683,554,034</v>
+        <v>8,152,143,729</v>
       </c>
       <c r="M33" t="str">
-        <v>932,671,084</v>
+        <v>969,021,331</v>
       </c>
       <c r="N33" t="str">
-        <v>12.14%</v>
+        <v>11.89%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,19 +1865,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>1,133</v>
+        <v>1,186</v>
       </c>
       <c r="F34" t="str">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="G34" t="str">
-        <v>1,782</v>
+        <v>1,901</v>
       </c>
       <c r="H34" t="str">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I34" t="str">
-        <v>555,158,291</v>
+        <v>578,248,774</v>
       </c>
       <c r="J34" t="str">
         <v>41</v>
@@ -1886,13 +1886,13 @@
         <v>793,460,058</v>
       </c>
       <c r="L34" t="str">
-        <v>11,476,375,199</v>
+        <v>11,998,114,330</v>
       </c>
       <c r="M34" t="str">
-        <v>2,051,435,925</v>
+        <v>2,163,551,846</v>
       </c>
       <c r="N34" t="str">
-        <v>17.88%</v>
+        <v>18.03%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,10 +1909,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>3,715</v>
+        <v>3,889</v>
       </c>
       <c r="F35" t="str">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="G35" t="str">
         <v>231</v>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="L35" t="str">
-        <v>4,148,491,610</v>
+        <v>4,325,820,705</v>
       </c>
       <c r="M35" t="str">
-        <v>444,275,176</v>
+        <v>463,411,349</v>
       </c>
       <c r="N35" t="str">
         <v>10.71%</v>
@@ -1953,13 +1953,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>2,350</v>
+        <v>2,521</v>
       </c>
       <c r="F36" t="str">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="G36" t="str">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H36" t="str">
         <v>0</v>
@@ -1974,13 +1974,13 @@
         <v>0</v>
       </c>
       <c r="L36" t="str">
-        <v>2,560,737,277</v>
+        <v>2,709,341,272</v>
       </c>
       <c r="M36" t="str">
-        <v>267,458,163</v>
+        <v>278,151,859</v>
       </c>
       <c r="N36" t="str">
-        <v>10.44%</v>
+        <v>10.27%</v>
       </c>
     </row>
     <row r="37">
@@ -2041,34 +2041,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>920</v>
+        <v>987</v>
       </c>
       <c r="F38" t="str">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="G38" t="str">
-        <v>1,732</v>
+        <v>1,828</v>
       </c>
       <c r="H38" t="str">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I38" t="str">
-        <v>383,834,630</v>
+        <v>418,272,300</v>
       </c>
       <c r="J38" t="str">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K38" t="str">
-        <v>346,410,700</v>
+        <v>407,358,437</v>
       </c>
       <c r="L38" t="str">
-        <v>9,179,372,527</v>
+        <v>9,760,551,749</v>
       </c>
       <c r="M38" t="str">
-        <v>1,229,232,561</v>
+        <v>1,355,575,010</v>
       </c>
       <c r="N38" t="str">
-        <v>13.39%</v>
+        <v>13.89%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,13 +2085,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>5,218</v>
+        <v>5,400</v>
       </c>
       <c r="F39" t="str">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="G39" t="str">
-        <v>6,179</v>
+        <v>6,471</v>
       </c>
       <c r="H39" t="str">
         <v>3</v>
@@ -2106,13 +2106,13 @@
         <v>84,725,256</v>
       </c>
       <c r="L39" t="str">
-        <v>12,728,750,525</v>
+        <v>13,154,453,599</v>
       </c>
       <c r="M39" t="str">
-        <v>398,682,138</v>
+        <v>421,496,379</v>
       </c>
       <c r="N39" t="str">
-        <v>3.13%</v>
+        <v>3.20%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,13 +2173,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>1,148</v>
+        <v>1,276</v>
       </c>
       <c r="F41" t="str">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G41" t="str">
-        <v>1,276</v>
+        <v>1,337</v>
       </c>
       <c r="H41" t="str">
         <v>2</v>
@@ -2194,13 +2194,13 @@
         <v>50,770,592</v>
       </c>
       <c r="L41" t="str">
-        <v>2,580,086,497</v>
+        <v>2,763,320,408</v>
       </c>
       <c r="M41" t="str">
-        <v>140,444,687</v>
+        <v>142,067,888</v>
       </c>
       <c r="N41" t="str">
-        <v>5.44%</v>
+        <v>5.14%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>825</v>
+        <v>889</v>
       </c>
       <c r="F42" t="str">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G42" t="str">
-        <v>1,297</v>
+        <v>1,366</v>
       </c>
       <c r="H42" t="str">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>66,445,865</v>
       </c>
       <c r="L42" t="str">
-        <v>2,140,196,613</v>
+        <v>2,260,442,209</v>
       </c>
       <c r="M42" t="str">
-        <v>93,098,705</v>
+        <v>93,797,576</v>
       </c>
       <c r="N42" t="str">
-        <v>4.35%</v>
+        <v>4.15%</v>
       </c>
     </row>
     <row r="43">
@@ -2261,13 +2261,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E43" t="str">
-        <v>3,302</v>
+        <v>3,558</v>
       </c>
       <c r="F43" t="str">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="G43" t="str">
-        <v>5,493</v>
+        <v>5,752</v>
       </c>
       <c r="H43" t="str">
         <v>9</v>
@@ -2276,19 +2276,19 @@
         <v>112,506,786</v>
       </c>
       <c r="J43" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="str">
-        <v>0</v>
+        <v>19,064,856</v>
       </c>
       <c r="L43" t="str">
-        <v>8,539,760,329</v>
+        <v>9,051,963,968</v>
       </c>
       <c r="M43" t="str">
-        <v>386,278,655</v>
+        <v>418,008,930</v>
       </c>
       <c r="N43" t="str">
-        <v>4.52%</v>
+        <v>4.62%</v>
       </c>
     </row>
     <row r="44">
@@ -2305,13 +2305,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>2,697</v>
+        <v>2,970</v>
       </c>
       <c r="F44" t="str">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="G44" t="str">
-        <v>3,133</v>
+        <v>3,310</v>
       </c>
       <c r="H44" t="str">
         <v>4</v>
@@ -2326,13 +2326,13 @@
         <v>54,162,704</v>
       </c>
       <c r="L44" t="str">
-        <v>6,780,384,213</v>
+        <v>7,463,115,613</v>
       </c>
       <c r="M44" t="str">
-        <v>273,539,193</v>
+        <v>281,535,618</v>
       </c>
       <c r="N44" t="str">
-        <v>4.03%</v>
+        <v>3.77%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,13 +2349,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>2,892</v>
+        <v>3,116</v>
       </c>
       <c r="F45" t="str">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G45" t="str">
-        <v>4,559</v>
+        <v>4,771</v>
       </c>
       <c r="H45" t="str">
         <v>3</v>
@@ -2370,13 +2370,13 @@
         <v>118,755,538</v>
       </c>
       <c r="L45" t="str">
-        <v>7,047,353,536</v>
+        <v>7,465,380,435</v>
       </c>
       <c r="M45" t="str">
-        <v>422,681,870</v>
+        <v>428,294,280</v>
       </c>
       <c r="N45" t="str">
-        <v>6.00%</v>
+        <v>5.74%</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata/Bulanan/10. Okt-LD.xlsx
+++ b/rawdata/Bulanan/10. Okt-LD.xlsx
@@ -457,34 +457,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>8,654</v>
+        <v>8,971</v>
       </c>
       <c r="F2" t="str">
-        <v>4,225</v>
+        <v>4,372</v>
       </c>
       <c r="G2" t="str">
-        <v>1,164</v>
+        <v>1,203</v>
       </c>
       <c r="H2" t="str">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="I2" t="str">
-        <v>2,400,615,471</v>
+        <v>2,487,955,375</v>
       </c>
       <c r="J2" t="str">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="K2" t="str">
-        <v>9,033,934,134</v>
+        <v>9,378,431,089</v>
       </c>
       <c r="L2" t="str">
-        <v>31,936,791,934</v>
+        <v>33,065,854,434</v>
       </c>
       <c r="M2" t="str">
-        <v>17,587,816,969</v>
+        <v>18,216,204,263</v>
       </c>
       <c r="N2" t="str">
-        <v>55.07%</v>
+        <v>55.09%</v>
       </c>
     </row>
     <row r="3">
@@ -501,34 +501,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>13,017</v>
+        <v>13,534</v>
       </c>
       <c r="F3" t="str">
-        <v>1,849</v>
+        <v>1,908</v>
       </c>
       <c r="G3" t="str">
-        <v>2,029</v>
+        <v>2,117</v>
       </c>
       <c r="H3" t="str">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="I3" t="str">
-        <v>1,480,876,811</v>
+        <v>1,547,013,730</v>
       </c>
       <c r="J3" t="str">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="K3" t="str">
-        <v>4,956,852,281</v>
+        <v>5,083,270,445</v>
       </c>
       <c r="L3" t="str">
-        <v>52,832,483,571</v>
+        <v>55,057,307,985</v>
       </c>
       <c r="M3" t="str">
-        <v>9,080,394,846</v>
+        <v>9,356,538,505</v>
       </c>
       <c r="N3" t="str">
-        <v>17.19%</v>
+        <v>16.99%</v>
       </c>
     </row>
     <row r="4">
@@ -545,34 +545,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>2,546</v>
+        <v>2,653</v>
       </c>
       <c r="F4" t="str">
-        <v>1,149</v>
+        <v>1,208</v>
       </c>
       <c r="G4" t="str">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="H4" t="str">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I4" t="str">
-        <v>782,583,708</v>
+        <v>831,903,962</v>
       </c>
       <c r="J4" t="str">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="K4" t="str">
-        <v>2,817,253,580</v>
+        <v>2,978,010,584</v>
       </c>
       <c r="L4" t="str">
-        <v>9,523,187,931</v>
+        <v>9,880,766,953</v>
       </c>
       <c r="M4" t="str">
-        <v>5,389,354,024</v>
+        <v>5,657,246,357</v>
       </c>
       <c r="N4" t="str">
-        <v>56.59%</v>
+        <v>57.26%</v>
       </c>
     </row>
     <row r="5">
@@ -589,10 +589,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>4,740</v>
+        <v>4,921</v>
       </c>
       <c r="F5" t="str">
-        <v>1,116</v>
+        <v>1,150</v>
       </c>
       <c r="G5" t="str">
         <v>25</v>
@@ -610,13 +610,13 @@
         <v>38,695,454</v>
       </c>
       <c r="L5" t="str">
-        <v>5,748,223,327</v>
+        <v>5,942,245,246</v>
       </c>
       <c r="M5" t="str">
-        <v>2,064,057,797</v>
+        <v>2,111,049,931</v>
       </c>
       <c r="N5" t="str">
-        <v>35.91%</v>
+        <v>35.53%</v>
       </c>
     </row>
     <row r="6">
@@ -633,13 +633,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>20,774</v>
+        <v>21,868</v>
       </c>
       <c r="F6" t="str">
-        <v>4,857</v>
+        <v>5,132</v>
       </c>
       <c r="G6" t="str">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H6" t="str">
         <v>12</v>
@@ -654,13 +654,13 @@
         <v>101,641,843</v>
       </c>
       <c r="L6" t="str">
-        <v>25,311,875,843</v>
+        <v>26,511,127,576</v>
       </c>
       <c r="M6" t="str">
-        <v>7,709,505,086</v>
+        <v>8,077,998,537</v>
       </c>
       <c r="N6" t="str">
-        <v>30.46%</v>
+        <v>30.47%</v>
       </c>
     </row>
     <row r="7">
@@ -677,34 +677,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>6,357</v>
+        <v>6,660</v>
       </c>
       <c r="F7" t="str">
-        <v>2,985</v>
+        <v>3,132</v>
       </c>
       <c r="G7" t="str">
-        <v>4,285</v>
+        <v>4,511</v>
       </c>
       <c r="H7" t="str">
-        <v>897</v>
+        <v>934</v>
       </c>
       <c r="I7" t="str">
-        <v>10,839,519,559</v>
+        <v>11,282,858,519</v>
       </c>
       <c r="J7" t="str">
-        <v>602</v>
+        <v>633</v>
       </c>
       <c r="K7" t="str">
-        <v>12,497,510,297</v>
+        <v>13,150,868,552</v>
       </c>
       <c r="L7" t="str">
-        <v>72,128,057,848</v>
+        <v>75,697,697,974</v>
       </c>
       <c r="M7" t="str">
-        <v>31,450,986,207</v>
+        <v>32,986,306,244</v>
       </c>
       <c r="N7" t="str">
-        <v>43.60%</v>
+        <v>43.58%</v>
       </c>
     </row>
     <row r="8">
@@ -721,10 +721,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>1,954</v>
+        <v>2,059</v>
       </c>
       <c r="F8" t="str">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="G8" t="str">
         <v>0</v>
@@ -742,13 +742,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="str">
-        <v>2,499,838,442</v>
+        <v>2,613,165,683</v>
       </c>
       <c r="M8" t="str">
-        <v>719,929,247</v>
+        <v>745,909,449</v>
       </c>
       <c r="N8" t="str">
-        <v>28.80%</v>
+        <v>28.54%</v>
       </c>
     </row>
     <row r="9">
@@ -765,13 +765,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>2,954</v>
+        <v>3,037</v>
       </c>
       <c r="F9" t="str">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G9" t="str">
-        <v>6,944</v>
+        <v>7,234</v>
       </c>
       <c r="H9" t="str">
         <v>0</v>
@@ -786,13 +786,13 @@
         <v>100,379,570</v>
       </c>
       <c r="L9" t="str">
-        <v>8,397,919,854</v>
+        <v>8,570,965,059</v>
       </c>
       <c r="M9" t="str">
-        <v>120,007,229</v>
+        <v>123,238,638</v>
       </c>
       <c r="N9" t="str">
-        <v>1.43%</v>
+        <v>1.44%</v>
       </c>
     </row>
     <row r="10">
@@ -809,13 +809,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>2,463</v>
+        <v>2,532</v>
       </c>
       <c r="F10" t="str">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G10" t="str">
-        <v>4,845</v>
+        <v>5,072</v>
       </c>
       <c r="H10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="str">
-        <v>6,914,170,889</v>
+        <v>7,114,017,285</v>
       </c>
       <c r="M10" t="str">
-        <v>92,414,439</v>
+        <v>92,628,067</v>
       </c>
       <c r="N10" t="str">
-        <v>1.34%</v>
+        <v>1.30%</v>
       </c>
     </row>
     <row r="11">
@@ -853,13 +853,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>3,068</v>
+        <v>3,194</v>
       </c>
       <c r="F11" t="str">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G11" t="str">
-        <v>8,629</v>
+        <v>9,068</v>
       </c>
       <c r="H11" t="str">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>11,643,050,024</v>
+        <v>12,208,505,164</v>
       </c>
       <c r="M11" t="str">
-        <v>117,754,123</v>
+        <v>118,404,123</v>
       </c>
       <c r="N11" t="str">
-        <v>1.01%</v>
+        <v>0.97%</v>
       </c>
     </row>
     <row r="12">
@@ -897,13 +897,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>1,909</v>
+        <v>1,987</v>
       </c>
       <c r="F12" t="str">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G12" t="str">
-        <v>5,953</v>
+        <v>6,240</v>
       </c>
       <c r="H12" t="str">
         <v>3</v>
@@ -918,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>7,193,125,554</v>
+        <v>7,489,212,839</v>
       </c>
       <c r="M12" t="str">
-        <v>220,776,642</v>
+        <v>221,953,022</v>
       </c>
       <c r="N12" t="str">
-        <v>3.07%</v>
+        <v>2.96%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>1,021</v>
+        <v>1,051</v>
       </c>
       <c r="F13" t="str">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G13" t="str">
-        <v>3,287</v>
+        <v>3,414</v>
       </c>
       <c r="H13" t="str">
         <v>1</v>
@@ -962,13 +962,13 @@
         <v>20,084,148</v>
       </c>
       <c r="L13" t="str">
-        <v>3,851,223,935</v>
+        <v>4,030,320,261</v>
       </c>
       <c r="M13" t="str">
-        <v>66,541,558</v>
+        <v>68,158,580</v>
       </c>
       <c r="N13" t="str">
-        <v>1.73%</v>
+        <v>1.69%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>2,703</v>
+        <v>2,812</v>
       </c>
       <c r="F14" t="str">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G14" t="str">
-        <v>8,088</v>
+        <v>8,471</v>
       </c>
       <c r="H14" t="str">
         <v>0</v>
@@ -1006,13 +1006,13 @@
         <v>0</v>
       </c>
       <c r="L14" t="str">
-        <v>9,928,685,821</v>
+        <v>10,398,529,990</v>
       </c>
       <c r="M14" t="str">
-        <v>143,612,048</v>
+        <v>147,110,471</v>
       </c>
       <c r="N14" t="str">
-        <v>1.45%</v>
+        <v>1.41%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>3,858</v>
+        <v>4,028</v>
       </c>
       <c r="F15" t="str">
         <v>26</v>
       </c>
       <c r="G15" t="str">
-        <v>11,418</v>
+        <v>11,912</v>
       </c>
       <c r="H15" t="str">
         <v>0</v>
@@ -1050,13 +1050,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="str">
-        <v>14,654,446,416</v>
+        <v>15,497,709,288</v>
       </c>
       <c r="M15" t="str">
         <v>82,196,516</v>
       </c>
       <c r="N15" t="str">
-        <v>0.56%</v>
+        <v>0.53%</v>
       </c>
     </row>
     <row r="16">
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>1,729</v>
+        <v>1,813</v>
       </c>
       <c r="F16" t="str">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G16" t="str">
-        <v>4,256</v>
+        <v>4,459</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>233,859,144</v>
       </c>
       <c r="L16" t="str">
-        <v>6,097,620,703</v>
+        <v>6,340,074,059</v>
       </c>
       <c r="M16" t="str">
-        <v>152,993,257</v>
+        <v>153,193,257</v>
       </c>
       <c r="N16" t="str">
-        <v>2.51%</v>
+        <v>2.42%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>2,164</v>
+        <v>2,269</v>
       </c>
       <c r="F17" t="str">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G17" t="str">
-        <v>4,959</v>
+        <v>5,187</v>
       </c>
       <c r="H17" t="str">
         <v>0</v>
@@ -1138,13 +1138,13 @@
         <v>100,898,460</v>
       </c>
       <c r="L17" t="str">
-        <v>7,146,469,120</v>
+        <v>7,605,560,042</v>
       </c>
       <c r="M17" t="str">
-        <v>98,756,810</v>
+        <v>106,392,638</v>
       </c>
       <c r="N17" t="str">
-        <v>1.38%</v>
+        <v>1.40%</v>
       </c>
     </row>
     <row r="18">
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>3,183</v>
+        <v>3,314</v>
       </c>
       <c r="F18" t="str">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G18" t="str">
-        <v>11,441</v>
+        <v>11,957</v>
       </c>
       <c r="H18" t="str">
         <v>1</v>
@@ -1182,13 +1182,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="str">
-        <v>14,020,325,672</v>
+        <v>14,579,924,392</v>
       </c>
       <c r="M18" t="str">
-        <v>114,838,677</v>
+        <v>115,962,099</v>
       </c>
       <c r="N18" t="str">
-        <v>0.82%</v>
+        <v>0.80%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>532</v>
+        <v>554</v>
       </c>
       <c r="F19" t="str">
         <v>3</v>
       </c>
       <c r="G19" t="str">
-        <v>1,905</v>
+        <v>1,981</v>
       </c>
       <c r="H19" t="str">
         <v>0</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>2,250,702,075</v>
+        <v>2,345,321,633</v>
       </c>
       <c r="M19" t="str">
         <v>9,860,041</v>
       </c>
       <c r="N19" t="str">
-        <v>0.44%</v>
+        <v>0.42%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>3,717</v>
+        <v>3,871</v>
       </c>
       <c r="F20" t="str">
         <v>38</v>
       </c>
       <c r="G20" t="str">
-        <v>12,956</v>
+        <v>13,528</v>
       </c>
       <c r="H20" t="str">
         <v>1</v>
@@ -1270,13 +1270,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="str">
-        <v>15,903,423,500</v>
+        <v>16,571,999,759</v>
       </c>
       <c r="M20" t="str">
         <v>106,492,692</v>
       </c>
       <c r="N20" t="str">
-        <v>0.67%</v>
+        <v>0.64%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>22,545</v>
+        <v>22,791</v>
       </c>
       <c r="F21" t="str">
-        <v>794</v>
+        <v>839</v>
       </c>
       <c r="G21" t="str">
-        <v>504,196</v>
+        <v>528,504</v>
       </c>
       <c r="H21" t="str">
         <v>6</v>
@@ -1308,19 +1308,19 @@
         <v>70,959,330</v>
       </c>
       <c r="J21" t="str">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K21" t="str">
-        <v>215,912,728</v>
+        <v>263,912,728</v>
       </c>
       <c r="L21" t="str">
-        <v>99,736,204,092</v>
+        <v>100,681,352,248</v>
       </c>
       <c r="M21" t="str">
-        <v>2,026,462,325</v>
+        <v>2,182,903,400</v>
       </c>
       <c r="N21" t="str">
-        <v>2.03%</v>
+        <v>2.17%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,13 +1337,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>1,203</v>
+        <v>1,207</v>
       </c>
       <c r="F22" t="str">
         <v>3</v>
       </c>
       <c r="G22" t="str">
-        <v>11,230</v>
+        <v>11,765</v>
       </c>
       <c r="H22" t="str">
         <v>0</v>
@@ -1358,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="str">
-        <v>13,265,319,030</v>
+        <v>13,269,089,536</v>
       </c>
       <c r="M22" t="str">
         <v>12,940,251</v>
@@ -1381,34 +1381,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E23" t="str">
-        <v>36,385</v>
+        <v>38,226</v>
       </c>
       <c r="F23" t="str">
-        <v>1,643</v>
+        <v>1,717</v>
       </c>
       <c r="G23" t="str">
-        <v>3,251</v>
+        <v>3,391</v>
       </c>
       <c r="H23" t="str">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="I23" t="str">
-        <v>2,895,994,773</v>
+        <v>3,023,044,016</v>
       </c>
       <c r="J23" t="str">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="K23" t="str">
-        <v>3,523,077,977</v>
+        <v>3,635,918,461</v>
       </c>
       <c r="L23" t="str">
-        <v>118,610,165,298</v>
+        <v>123,791,153,370</v>
       </c>
       <c r="M23" t="str">
-        <v>9,394,249,001</v>
+        <v>9,777,466,345</v>
       </c>
       <c r="N23" t="str">
-        <v>7.92%</v>
+        <v>7.90%</v>
       </c>
     </row>
     <row r="24">
@@ -1425,19 +1425,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>1,720</v>
+        <v>1,800</v>
       </c>
       <c r="F24" t="str">
-        <v>551</v>
+        <v>569</v>
       </c>
       <c r="G24" t="str">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="H24" t="str">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I24" t="str">
-        <v>75,928,581</v>
+        <v>85,985,894</v>
       </c>
       <c r="J24" t="str">
         <v>23</v>
@@ -1446,13 +1446,13 @@
         <v>413,967,834</v>
       </c>
       <c r="L24" t="str">
-        <v>4,402,845,322</v>
+        <v>4,641,615,837</v>
       </c>
       <c r="M24" t="str">
-        <v>1,211,782,702</v>
+        <v>1,247,277,922</v>
       </c>
       <c r="N24" t="str">
-        <v>27.52%</v>
+        <v>26.87%</v>
       </c>
     </row>
     <row r="25">
@@ -1469,34 +1469,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E25" t="str">
-        <v>4,115</v>
+        <v>4,276</v>
       </c>
       <c r="F25" t="str">
-        <v>1,252</v>
+        <v>1,302</v>
       </c>
       <c r="G25" t="str">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="H25" t="str">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I25" t="str">
-        <v>368,764,053</v>
+        <v>382,478,982</v>
       </c>
       <c r="J25" t="str">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K25" t="str">
-        <v>564,663,506</v>
+        <v>585,219,992</v>
       </c>
       <c r="L25" t="str">
-        <v>10,616,880,967</v>
+        <v>11,041,126,880</v>
       </c>
       <c r="M25" t="str">
-        <v>2,631,097,479</v>
+        <v>2,729,578,293</v>
       </c>
       <c r="N25" t="str">
-        <v>24.78%</v>
+        <v>24.72%</v>
       </c>
     </row>
     <row r="26">
@@ -1513,10 +1513,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>1,786</v>
+        <v>1,869</v>
       </c>
       <c r="F26" t="str">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="G26" t="str">
         <v>0</v>
@@ -1534,13 +1534,13 @@
         <v>0</v>
       </c>
       <c r="L26" t="str">
-        <v>1,945,486,860</v>
+        <v>2,014,684,788</v>
       </c>
       <c r="M26" t="str">
-        <v>462,775,073</v>
+        <v>469,990,014</v>
       </c>
       <c r="N26" t="str">
-        <v>23.79%</v>
+        <v>23.33%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,10 +1557,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>14,861</v>
+        <v>15,776</v>
       </c>
       <c r="F27" t="str">
-        <v>2,570</v>
+        <v>2,717</v>
       </c>
       <c r="G27" t="str">
         <v>1</v>
@@ -1578,13 +1578,13 @@
         <v>0</v>
       </c>
       <c r="L27" t="str">
-        <v>16,219,542,666</v>
+        <v>17,031,208,886</v>
       </c>
       <c r="M27" t="str">
-        <v>3,171,664,687</v>
+        <v>3,296,163,715</v>
       </c>
       <c r="N27" t="str">
-        <v>19.55%</v>
+        <v>19.35%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,34 +1601,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>3,227</v>
+        <v>3,384</v>
       </c>
       <c r="F28" t="str">
-        <v>1,066</v>
+        <v>1,127</v>
       </c>
       <c r="G28" t="str">
-        <v>1,195</v>
+        <v>1,259</v>
       </c>
       <c r="H28" t="str">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="I28" t="str">
-        <v>2,611,635,871</v>
+        <v>2,893,950,526</v>
       </c>
       <c r="J28" t="str">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="K28" t="str">
-        <v>2,897,053,117</v>
+        <v>3,072,898,645</v>
       </c>
       <c r="L28" t="str">
-        <v>34,071,029,549</v>
+        <v>35,824,141,318</v>
       </c>
       <c r="M28" t="str">
-        <v>9,445,341,025</v>
+        <v>10,071,956,155</v>
       </c>
       <c r="N28" t="str">
-        <v>27.72%</v>
+        <v>28.11%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,10 +1645,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>2,979</v>
+        <v>3,090</v>
       </c>
       <c r="F29" t="str">
-        <v>511</v>
+        <v>528</v>
       </c>
       <c r="G29" t="str">
         <v>0</v>
@@ -1666,13 +1666,13 @@
         <v>0</v>
       </c>
       <c r="L29" t="str">
-        <v>3,319,615,734</v>
+        <v>3,412,100,762</v>
       </c>
       <c r="M29" t="str">
-        <v>654,081,046</v>
+        <v>674,900,052</v>
       </c>
       <c r="N29" t="str">
-        <v>19.70%</v>
+        <v>19.78%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,19 +1689,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>3,464</v>
+        <v>3,756</v>
       </c>
       <c r="F30" t="str">
-        <v>569</v>
+        <v>582</v>
       </c>
       <c r="G30" t="str">
-        <v>1,629</v>
+        <v>1,692</v>
       </c>
       <c r="H30" t="str">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I30" t="str">
-        <v>65,830,949</v>
+        <v>79,992,199</v>
       </c>
       <c r="J30" t="str">
         <v>5</v>
@@ -1710,13 +1710,13 @@
         <v>84,536,012</v>
       </c>
       <c r="L30" t="str">
-        <v>9,245,355,378</v>
+        <v>10,068,215,756</v>
       </c>
       <c r="M30" t="str">
-        <v>888,487,278</v>
+        <v>931,769,502</v>
       </c>
       <c r="N30" t="str">
-        <v>9.61%</v>
+        <v>9.25%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,13 +1733,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>974</v>
+        <v>1,149</v>
       </c>
       <c r="F31" t="str">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="G31" t="str">
-        <v>328</v>
+        <v>353</v>
       </c>
       <c r="H31" t="str">
         <v>5</v>
@@ -1754,13 +1754,13 @@
         <v>47,809,288</v>
       </c>
       <c r="L31" t="str">
-        <v>2,404,991,089</v>
+        <v>2,868,849,416</v>
       </c>
       <c r="M31" t="str">
-        <v>446,535,601</v>
+        <v>454,675,517</v>
       </c>
       <c r="N31" t="str">
-        <v>18.57%</v>
+        <v>15.85%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,10 +1777,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>2,469</v>
+        <v>2,560</v>
       </c>
       <c r="F32" t="str">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="G32" t="str">
         <v>96</v>
@@ -1798,13 +1798,13 @@
         <v>0</v>
       </c>
       <c r="L32" t="str">
-        <v>2,733,801,358</v>
+        <v>2,787,992,456</v>
       </c>
       <c r="M32" t="str">
-        <v>454,363,870</v>
+        <v>464,824,689</v>
       </c>
       <c r="N32" t="str">
-        <v>16.62%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,13 +1821,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>7,242</v>
+        <v>7,663</v>
       </c>
       <c r="F33" t="str">
-        <v>767</v>
+        <v>806</v>
       </c>
       <c r="G33" t="str">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H33" t="str">
         <v>4</v>
@@ -1842,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="L33" t="str">
-        <v>8,152,143,729</v>
+        <v>8,496,154,759</v>
       </c>
       <c r="M33" t="str">
-        <v>969,021,331</v>
+        <v>1,002,727,199</v>
       </c>
       <c r="N33" t="str">
-        <v>11.89%</v>
+        <v>11.80%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,34 +1865,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>1,186</v>
+        <v>1,243</v>
       </c>
       <c r="F34" t="str">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="G34" t="str">
-        <v>1,901</v>
+        <v>2,021</v>
       </c>
       <c r="H34" t="str">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I34" t="str">
-        <v>578,248,774</v>
+        <v>589,196,901</v>
       </c>
       <c r="J34" t="str">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K34" t="str">
-        <v>793,460,058</v>
+        <v>864,595,594</v>
       </c>
       <c r="L34" t="str">
-        <v>11,998,114,330</v>
+        <v>12,550,224,537</v>
       </c>
       <c r="M34" t="str">
-        <v>2,163,551,846</v>
+        <v>2,265,073,282</v>
       </c>
       <c r="N34" t="str">
-        <v>18.03%</v>
+        <v>18.05%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,13 +1909,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>3,889</v>
+        <v>4,042</v>
       </c>
       <c r="F35" t="str">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="G35" t="str">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H35" t="str">
         <v>3</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="L35" t="str">
-        <v>4,325,820,705</v>
+        <v>4,447,050,859</v>
       </c>
       <c r="M35" t="str">
-        <v>463,411,349</v>
+        <v>472,230,634</v>
       </c>
       <c r="N35" t="str">
-        <v>10.71%</v>
+        <v>10.62%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,13 +1953,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>2,521</v>
+        <v>2,655</v>
       </c>
       <c r="F36" t="str">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="G36" t="str">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H36" t="str">
         <v>0</v>
@@ -1974,13 +1974,13 @@
         <v>0</v>
       </c>
       <c r="L36" t="str">
-        <v>2,709,341,272</v>
+        <v>2,819,984,816</v>
       </c>
       <c r="M36" t="str">
-        <v>278,151,859</v>
+        <v>294,439,857</v>
       </c>
       <c r="N36" t="str">
-        <v>10.27%</v>
+        <v>10.44%</v>
       </c>
     </row>
     <row r="37">
@@ -2041,19 +2041,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>987</v>
+        <v>1,042</v>
       </c>
       <c r="F38" t="str">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="G38" t="str">
-        <v>1,828</v>
+        <v>1,914</v>
       </c>
       <c r="H38" t="str">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I38" t="str">
-        <v>418,272,300</v>
+        <v>461,157,039</v>
       </c>
       <c r="J38" t="str">
         <v>21</v>
@@ -2062,13 +2062,13 @@
         <v>407,358,437</v>
       </c>
       <c r="L38" t="str">
-        <v>9,760,551,749</v>
+        <v>10,206,687,047</v>
       </c>
       <c r="M38" t="str">
-        <v>1,355,575,010</v>
+        <v>1,421,067,370</v>
       </c>
       <c r="N38" t="str">
-        <v>13.89%</v>
+        <v>13.92%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,13 +2085,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>5,400</v>
+        <v>5,570</v>
       </c>
       <c r="F39" t="str">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="G39" t="str">
-        <v>6,471</v>
+        <v>6,781</v>
       </c>
       <c r="H39" t="str">
         <v>3</v>
@@ -2106,13 +2106,13 @@
         <v>84,725,256</v>
       </c>
       <c r="L39" t="str">
-        <v>13,154,453,599</v>
+        <v>13,681,366,087</v>
       </c>
       <c r="M39" t="str">
-        <v>421,496,379</v>
+        <v>432,645,239</v>
       </c>
       <c r="N39" t="str">
-        <v>3.20%</v>
+        <v>3.16%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,13 +2173,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>1,276</v>
+        <v>1,369</v>
       </c>
       <c r="F41" t="str">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G41" t="str">
-        <v>1,337</v>
+        <v>1,403</v>
       </c>
       <c r="H41" t="str">
         <v>2</v>
@@ -2194,13 +2194,13 @@
         <v>50,770,592</v>
       </c>
       <c r="L41" t="str">
-        <v>2,763,320,408</v>
+        <v>2,958,982,137</v>
       </c>
       <c r="M41" t="str">
-        <v>142,067,888</v>
+        <v>143,541,465</v>
       </c>
       <c r="N41" t="str">
-        <v>5.14%</v>
+        <v>4.85%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>889</v>
+        <v>935</v>
       </c>
       <c r="F42" t="str">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G42" t="str">
-        <v>1,366</v>
+        <v>1,434</v>
       </c>
       <c r="H42" t="str">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>66,445,865</v>
       </c>
       <c r="L42" t="str">
-        <v>2,260,442,209</v>
+        <v>2,322,364,133</v>
       </c>
       <c r="M42" t="str">
-        <v>93,797,576</v>
+        <v>94,372,282</v>
       </c>
       <c r="N42" t="str">
-        <v>4.15%</v>
+        <v>4.06%</v>
       </c>
     </row>
     <row r="43">
@@ -2261,13 +2261,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E43" t="str">
-        <v>3,558</v>
+        <v>3,743</v>
       </c>
       <c r="F43" t="str">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="G43" t="str">
-        <v>5,752</v>
+        <v>6,000</v>
       </c>
       <c r="H43" t="str">
         <v>9</v>
@@ -2282,13 +2282,13 @@
         <v>19,064,856</v>
       </c>
       <c r="L43" t="str">
-        <v>9,051,963,968</v>
+        <v>9,329,816,221</v>
       </c>
       <c r="M43" t="str">
-        <v>418,008,930</v>
+        <v>434,753,150</v>
       </c>
       <c r="N43" t="str">
-        <v>4.62%</v>
+        <v>4.66%</v>
       </c>
     </row>
     <row r="44">
@@ -2305,13 +2305,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>2,970</v>
+        <v>3,344</v>
       </c>
       <c r="F44" t="str">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G44" t="str">
-        <v>3,310</v>
+        <v>3,485</v>
       </c>
       <c r="H44" t="str">
         <v>4</v>
@@ -2326,13 +2326,13 @@
         <v>54,162,704</v>
       </c>
       <c r="L44" t="str">
-        <v>7,463,115,613</v>
+        <v>8,046,067,672</v>
       </c>
       <c r="M44" t="str">
-        <v>281,535,618</v>
+        <v>286,848,533</v>
       </c>
       <c r="N44" t="str">
-        <v>3.77%</v>
+        <v>3.57%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,34 +2349,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>3,116</v>
+        <v>3,278</v>
       </c>
       <c r="F45" t="str">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="G45" t="str">
-        <v>4,771</v>
+        <v>4,972</v>
       </c>
       <c r="H45" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I45" t="str">
-        <v>36,961,262</v>
+        <v>60,689,995</v>
       </c>
       <c r="J45" t="str">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K45" t="str">
-        <v>118,755,538</v>
+        <v>134,571,733</v>
       </c>
       <c r="L45" t="str">
-        <v>7,465,380,435</v>
+        <v>7,738,536,787</v>
       </c>
       <c r="M45" t="str">
-        <v>428,294,280</v>
+        <v>496,446,330</v>
       </c>
       <c r="N45" t="str">
-        <v>5.74%</v>
+        <v>6.42%</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata/Bulanan/10. Okt-LD.xlsx
+++ b/rawdata/Bulanan/10. Okt-LD.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N48"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -457,34 +457,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>8,971</v>
+        <v>9,301</v>
       </c>
       <c r="F2" t="str">
-        <v>4,372</v>
+        <v>4,556</v>
       </c>
       <c r="G2" t="str">
-        <v>1,203</v>
+        <v>1,258</v>
       </c>
       <c r="H2" t="str">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="I2" t="str">
-        <v>2,487,955,375</v>
+        <v>2,695,641,565</v>
       </c>
       <c r="J2" t="str">
-        <v>474</v>
+        <v>497</v>
       </c>
       <c r="K2" t="str">
-        <v>9,378,431,089</v>
+        <v>9,828,345,145</v>
       </c>
       <c r="L2" t="str">
-        <v>33,065,854,434</v>
+        <v>34,444,730,377</v>
       </c>
       <c r="M2" t="str">
-        <v>18,216,204,263</v>
+        <v>19,158,293,992</v>
       </c>
       <c r="N2" t="str">
-        <v>55.09%</v>
+        <v>55.62%</v>
       </c>
     </row>
     <row r="3">
@@ -501,34 +501,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>13,534</v>
+        <v>14,074</v>
       </c>
       <c r="F3" t="str">
-        <v>1,908</v>
+        <v>2,006</v>
       </c>
       <c r="G3" t="str">
-        <v>2,117</v>
+        <v>2,212</v>
       </c>
       <c r="H3" t="str">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="I3" t="str">
-        <v>1,547,013,730</v>
+        <v>1,669,739,332</v>
       </c>
       <c r="J3" t="str">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="K3" t="str">
-        <v>5,083,270,445</v>
+        <v>5,568,131,461</v>
       </c>
       <c r="L3" t="str">
-        <v>55,057,307,985</v>
+        <v>57,461,091,910</v>
       </c>
       <c r="M3" t="str">
-        <v>9,356,538,505</v>
+        <v>10,040,064,352</v>
       </c>
       <c r="N3" t="str">
-        <v>16.99%</v>
+        <v>17.47%</v>
       </c>
     </row>
     <row r="4">
@@ -545,34 +545,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>2,653</v>
+        <v>2,764</v>
       </c>
       <c r="F4" t="str">
-        <v>1,208</v>
+        <v>1,265</v>
       </c>
       <c r="G4" t="str">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="H4" t="str">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I4" t="str">
-        <v>831,903,962</v>
+        <v>885,063,456</v>
       </c>
       <c r="J4" t="str">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="K4" t="str">
-        <v>2,978,010,584</v>
+        <v>3,137,405,783</v>
       </c>
       <c r="L4" t="str">
-        <v>9,880,766,953</v>
+        <v>10,340,982,751</v>
       </c>
       <c r="M4" t="str">
-        <v>5,657,246,357</v>
+        <v>5,939,705,352</v>
       </c>
       <c r="N4" t="str">
-        <v>57.26%</v>
+        <v>57.44%</v>
       </c>
     </row>
     <row r="5">
@@ -589,13 +589,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>4,921</v>
+        <v>5,134</v>
       </c>
       <c r="F5" t="str">
-        <v>1,150</v>
+        <v>1,210</v>
       </c>
       <c r="G5" t="str">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5" t="str">
         <v>11</v>
@@ -610,13 +610,13 @@
         <v>38,695,454</v>
       </c>
       <c r="L5" t="str">
-        <v>5,942,245,246</v>
+        <v>6,173,575,353</v>
       </c>
       <c r="M5" t="str">
-        <v>2,111,049,931</v>
+        <v>2,186,206,122</v>
       </c>
       <c r="N5" t="str">
-        <v>35.53%</v>
+        <v>35.41%</v>
       </c>
     </row>
     <row r="6">
@@ -633,13 +633,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>21,868</v>
+        <v>22,991</v>
       </c>
       <c r="F6" t="str">
-        <v>5,132</v>
+        <v>5,426</v>
       </c>
       <c r="G6" t="str">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H6" t="str">
         <v>12</v>
@@ -654,18 +654,18 @@
         <v>101,641,843</v>
       </c>
       <c r="L6" t="str">
-        <v>26,511,127,576</v>
+        <v>27,677,676,106</v>
       </c>
       <c r="M6" t="str">
-        <v>8,077,998,537</v>
+        <v>8,490,029,830</v>
       </c>
       <c r="N6" t="str">
-        <v>30.47%</v>
+        <v>30.67%</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>W-MPT02-BA</v>
+        <v>W-MPT02-AVG</v>
       </c>
       <c r="B7" t="str">
         <v>C</v>
@@ -677,39 +677,39 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>6,660</v>
+        <v>96</v>
       </c>
       <c r="F7" t="str">
-        <v>3,132</v>
+        <v>18</v>
       </c>
       <c r="G7" t="str">
-        <v>4,511</v>
+        <v>0</v>
       </c>
       <c r="H7" t="str">
-        <v>934</v>
+        <v>0</v>
       </c>
       <c r="I7" t="str">
-        <v>11,282,858,519</v>
+        <v>0</v>
       </c>
       <c r="J7" t="str">
-        <v>633</v>
+        <v>0</v>
       </c>
       <c r="K7" t="str">
-        <v>13,150,868,552</v>
+        <v>0</v>
       </c>
       <c r="L7" t="str">
-        <v>75,697,697,974</v>
+        <v>79,660,229</v>
       </c>
       <c r="M7" t="str">
-        <v>32,986,306,244</v>
+        <v>12,000,373</v>
       </c>
       <c r="N7" t="str">
-        <v>43.58%</v>
+        <v>15.06%</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>W-MPT05-C</v>
+        <v>W-MPT02-BA</v>
       </c>
       <c r="B8" t="str">
         <v>C</v>
@@ -721,42 +721,42 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>2,059</v>
+        <v>6,917</v>
       </c>
       <c r="F8" t="str">
-        <v>427</v>
+        <v>3,277</v>
       </c>
       <c r="G8" t="str">
-        <v>0</v>
+        <v>4,727</v>
       </c>
       <c r="H8" t="str">
-        <v>0</v>
+        <v>977</v>
       </c>
       <c r="I8" t="str">
-        <v>0</v>
+        <v>11,802,682,227</v>
       </c>
       <c r="J8" t="str">
-        <v>0</v>
+        <v>675</v>
       </c>
       <c r="K8" t="str">
-        <v>0</v>
+        <v>14,040,127,147</v>
       </c>
       <c r="L8" t="str">
-        <v>2,613,165,683</v>
+        <v>78,711,565,882</v>
       </c>
       <c r="M8" t="str">
-        <v>745,909,449</v>
+        <v>34,708,508,197</v>
       </c>
       <c r="N8" t="str">
-        <v>28.54%</v>
+        <v>44.10%</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>External Collection-MKM</v>
+        <v>W-MPT05-C</v>
       </c>
       <c r="B9" t="str">
-        <v>M2</v>
+        <v>C</v>
       </c>
       <c r="C9" t="str">
         <v>SEMUA</v>
@@ -765,13 +765,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>3,037</v>
+        <v>2,195</v>
       </c>
       <c r="F9" t="str">
-        <v>67</v>
+        <v>455</v>
       </c>
       <c r="G9" t="str">
-        <v>7,234</v>
+        <v>0</v>
       </c>
       <c r="H9" t="str">
         <v>0</v>
@@ -780,24 +780,24 @@
         <v>0</v>
       </c>
       <c r="J9" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" t="str">
-        <v>100,379,570</v>
+        <v>0</v>
       </c>
       <c r="L9" t="str">
-        <v>8,570,965,059</v>
+        <v>2,788,209,709</v>
       </c>
       <c r="M9" t="str">
-        <v>123,238,638</v>
+        <v>782,542,220</v>
       </c>
       <c r="N9" t="str">
-        <v>1.44%</v>
+        <v>28.07%</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>External Collection-MPT</v>
+        <v>External Collection-MKM</v>
       </c>
       <c r="B10" t="str">
         <v>M2</v>
@@ -809,13 +809,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>2,532</v>
+        <v>3,159</v>
       </c>
       <c r="F10" t="str">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G10" t="str">
-        <v>5,072</v>
+        <v>7,521</v>
       </c>
       <c r="H10" t="str">
         <v>0</v>
@@ -824,24 +824,24 @@
         <v>0</v>
       </c>
       <c r="J10" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K10" t="str">
-        <v>0</v>
+        <v>100,379,570</v>
       </c>
       <c r="L10" t="str">
-        <v>7,114,017,285</v>
+        <v>8,915,975,098</v>
       </c>
       <c r="M10" t="str">
-        <v>92,628,067</v>
+        <v>125,124,135</v>
       </c>
       <c r="N10" t="str">
-        <v>1.30%</v>
+        <v>1.40%</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>W-MKM</v>
+        <v>External Collection-MPT</v>
       </c>
       <c r="B11" t="str">
         <v>M2</v>
@@ -853,13 +853,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>3,194</v>
+        <v>2,633</v>
       </c>
       <c r="F11" t="str">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="G11" t="str">
-        <v>9,068</v>
+        <v>5,299</v>
       </c>
       <c r="H11" t="str">
         <v>0</v>
@@ -874,18 +874,18 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>12,208,505,164</v>
+        <v>7,432,463,641</v>
       </c>
       <c r="M11" t="str">
-        <v>118,404,123</v>
+        <v>98,996,301</v>
       </c>
       <c r="N11" t="str">
-        <v>0.97%</v>
+        <v>1.33%</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>W-MPT</v>
+        <v>W-MKM</v>
       </c>
       <c r="B12" t="str">
         <v>M2</v>
@@ -897,19 +897,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>1,987</v>
+        <v>3,314</v>
       </c>
       <c r="F12" t="str">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="G12" t="str">
-        <v>6,240</v>
+        <v>9,499</v>
       </c>
       <c r="H12" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I12" t="str">
-        <v>32,410,311</v>
+        <v>0</v>
       </c>
       <c r="J12" t="str">
         <v>0</v>
@@ -918,18 +918,18 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>7,489,212,839</v>
+        <v>12,564,844,748</v>
       </c>
       <c r="M12" t="str">
-        <v>221,953,022</v>
+        <v>121,067,413</v>
       </c>
       <c r="N12" t="str">
-        <v>2.96%</v>
+        <v>0.96%</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>W-MPT02</v>
+        <v>W-MPT</v>
       </c>
       <c r="B13" t="str">
         <v>M2</v>
@@ -941,39 +941,39 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>1,051</v>
+        <v>2,060</v>
       </c>
       <c r="F13" t="str">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="G13" t="str">
-        <v>3,414</v>
+        <v>6,535</v>
       </c>
       <c r="H13" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13" t="str">
-        <v>11,911,540</v>
+        <v>32,410,311</v>
       </c>
       <c r="J13" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="str">
-        <v>20,084,148</v>
+        <v>0</v>
       </c>
       <c r="L13" t="str">
-        <v>4,030,320,261</v>
+        <v>7,816,657,843</v>
       </c>
       <c r="M13" t="str">
-        <v>68,158,580</v>
+        <v>229,484,515</v>
       </c>
       <c r="N13" t="str">
-        <v>1.69%</v>
+        <v>2.94%</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>W-SO</v>
+        <v>W-MPT02</v>
       </c>
       <c r="B14" t="str">
         <v>M2</v>
@@ -985,42 +985,42 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>2,812</v>
+        <v>1,080</v>
       </c>
       <c r="F14" t="str">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="G14" t="str">
-        <v>8,471</v>
+        <v>3,541</v>
       </c>
       <c r="H14" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="str">
-        <v>0</v>
+        <v>11,911,540</v>
       </c>
       <c r="J14" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" t="str">
-        <v>0</v>
+        <v>35,694,915</v>
       </c>
       <c r="L14" t="str">
-        <v>10,398,529,990</v>
+        <v>4,130,996,484</v>
       </c>
       <c r="M14" t="str">
-        <v>147,110,471</v>
+        <v>90,046,614</v>
       </c>
       <c r="N14" t="str">
-        <v>1.41%</v>
+        <v>2.18%</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>DC09</v>
+        <v>W-SO</v>
       </c>
       <c r="B15" t="str">
-        <v>M3</v>
+        <v>M2</v>
       </c>
       <c r="C15" t="str">
         <v>SEMUA</v>
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>4,028</v>
+        <v>2,911</v>
       </c>
       <c r="F15" t="str">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="G15" t="str">
-        <v>11,912</v>
+        <v>8,860</v>
       </c>
       <c r="H15" t="str">
         <v>0</v>
@@ -1050,18 +1050,18 @@
         <v>0</v>
       </c>
       <c r="L15" t="str">
-        <v>15,497,709,288</v>
+        <v>10,888,319,801</v>
       </c>
       <c r="M15" t="str">
-        <v>82,196,516</v>
+        <v>151,425,781</v>
       </c>
       <c r="N15" t="str">
-        <v>0.53%</v>
+        <v>1.39%</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>External Collection-MKM</v>
+        <v>DC09</v>
       </c>
       <c r="B16" t="str">
         <v>M3</v>
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>1,813</v>
+        <v>4,205</v>
       </c>
       <c r="F16" t="str">
         <v>26</v>
       </c>
       <c r="G16" t="str">
-        <v>4,459</v>
+        <v>12,409</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1088,24 +1088,24 @@
         <v>0</v>
       </c>
       <c r="J16" t="str">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K16" t="str">
-        <v>233,859,144</v>
+        <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>6,340,074,059</v>
+        <v>16,240,162,759</v>
       </c>
       <c r="M16" t="str">
-        <v>153,193,257</v>
+        <v>82,196,516</v>
       </c>
       <c r="N16" t="str">
-        <v>2.42%</v>
+        <v>0.51%</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>External Collection-MPT</v>
+        <v>External Collection-MKM</v>
       </c>
       <c r="B17" t="str">
         <v>M3</v>
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>2,269</v>
+        <v>1,903</v>
       </c>
       <c r="F17" t="str">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G17" t="str">
-        <v>5,187</v>
+        <v>4,665</v>
       </c>
       <c r="H17" t="str">
         <v>0</v>
@@ -1132,24 +1132,24 @@
         <v>0</v>
       </c>
       <c r="J17" t="str">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K17" t="str">
-        <v>100,898,460</v>
+        <v>233,859,144</v>
       </c>
       <c r="L17" t="str">
-        <v>7,605,560,042</v>
+        <v>6,623,417,482</v>
       </c>
       <c r="M17" t="str">
-        <v>106,392,638</v>
+        <v>155,198,733</v>
       </c>
       <c r="N17" t="str">
-        <v>1.40%</v>
+        <v>2.34%</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>W-MKM</v>
+        <v>External Collection-MPT</v>
       </c>
       <c r="B18" t="str">
         <v>M3</v>
@@ -1161,39 +1161,39 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>3,314</v>
+        <v>2,380</v>
       </c>
       <c r="F18" t="str">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="G18" t="str">
-        <v>11,957</v>
+        <v>5,422</v>
       </c>
       <c r="H18" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="str">
-        <v>13,098,336</v>
+        <v>0</v>
       </c>
       <c r="J18" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K18" t="str">
-        <v>0</v>
+        <v>100,898,460</v>
       </c>
       <c r="L18" t="str">
-        <v>14,579,924,392</v>
+        <v>7,992,991,844</v>
       </c>
       <c r="M18" t="str">
-        <v>115,962,099</v>
+        <v>110,870,539</v>
       </c>
       <c r="N18" t="str">
-        <v>0.80%</v>
+        <v>1.39%</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>W-MPT</v>
+        <v>W-MKM</v>
       </c>
       <c r="B19" t="str">
         <v>M3</v>
@@ -1205,19 +1205,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>554</v>
+        <v>3,446</v>
       </c>
       <c r="F19" t="str">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="G19" t="str">
-        <v>1,981</v>
+        <v>12,481</v>
       </c>
       <c r="H19" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="str">
-        <v>0</v>
+        <v>13,098,336</v>
       </c>
       <c r="J19" t="str">
         <v>0</v>
@@ -1226,18 +1226,18 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>2,345,321,633</v>
+        <v>15,178,156,444</v>
       </c>
       <c r="M19" t="str">
-        <v>9,860,041</v>
+        <v>122,285,122</v>
       </c>
       <c r="N19" t="str">
-        <v>0.42%</v>
+        <v>0.81%</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>W-SO</v>
+        <v>W-MPT</v>
       </c>
       <c r="B20" t="str">
         <v>M3</v>
@@ -1249,19 +1249,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>3,871</v>
+        <v>576</v>
       </c>
       <c r="F20" t="str">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="G20" t="str">
-        <v>13,528</v>
+        <v>2,058</v>
       </c>
       <c r="H20" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="str">
-        <v>13,235,001</v>
+        <v>0</v>
       </c>
       <c r="J20" t="str">
         <v>0</v>
@@ -1270,21 +1270,21 @@
         <v>0</v>
       </c>
       <c r="L20" t="str">
-        <v>16,571,999,759</v>
+        <v>2,442,562,559</v>
       </c>
       <c r="M20" t="str">
-        <v>106,492,692</v>
+        <v>11,695,275</v>
       </c>
       <c r="N20" t="str">
-        <v>0.64%</v>
+        <v>0.48%</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>DC09</v>
+        <v>W-SO</v>
       </c>
       <c r="B21" t="str">
-        <v>M3+</v>
+        <v>M3</v>
       </c>
       <c r="C21" t="str">
         <v>SEMUA</v>
@@ -1293,39 +1293,39 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>22,791</v>
+        <v>4,024</v>
       </c>
       <c r="F21" t="str">
-        <v>839</v>
+        <v>38</v>
       </c>
       <c r="G21" t="str">
-        <v>528,504</v>
+        <v>14,112</v>
       </c>
       <c r="H21" t="str">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I21" t="str">
-        <v>70,959,330</v>
+        <v>13,235,001</v>
       </c>
       <c r="J21" t="str">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K21" t="str">
-        <v>263,912,728</v>
+        <v>0</v>
       </c>
       <c r="L21" t="str">
-        <v>100,681,352,248</v>
+        <v>17,317,300,032</v>
       </c>
       <c r="M21" t="str">
-        <v>2,182,903,400</v>
+        <v>106,492,692</v>
       </c>
       <c r="N21" t="str">
-        <v>2.17%</v>
+        <v>0.61%</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>W-SO</v>
+        <v>DC09</v>
       </c>
       <c r="B22" t="str">
         <v>M3+</v>
@@ -1337,42 +1337,42 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>1,207</v>
+        <v>23,024</v>
       </c>
       <c r="F22" t="str">
-        <v>3</v>
+        <v>897</v>
       </c>
       <c r="G22" t="str">
-        <v>11,765</v>
+        <v>552,826</v>
       </c>
       <c r="H22" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I22" t="str">
-        <v>0</v>
+        <v>70,959,330</v>
       </c>
       <c r="J22" t="str">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K22" t="str">
-        <v>0</v>
+        <v>263,912,728</v>
       </c>
       <c r="L22" t="str">
-        <v>13,269,089,536</v>
+        <v>101,391,107,386</v>
       </c>
       <c r="M22" t="str">
-        <v>12,940,251</v>
+        <v>2,319,037,431</v>
       </c>
       <c r="N22" t="str">
-        <v>0.10%</v>
+        <v>2.29%</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>External Collection</v>
+        <v>W-SO</v>
       </c>
       <c r="B23" t="str">
-        <v>S-3</v>
+        <v>M3+</v>
       </c>
       <c r="C23" t="str">
         <v>SEMUA</v>
@@ -1381,42 +1381,42 @@
         <v>SEMUA</v>
       </c>
       <c r="E23" t="str">
-        <v>38,226</v>
+        <v>1,208</v>
       </c>
       <c r="F23" t="str">
-        <v>1,717</v>
+        <v>4</v>
       </c>
       <c r="G23" t="str">
-        <v>3,391</v>
+        <v>12,300</v>
       </c>
       <c r="H23" t="str">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="I23" t="str">
-        <v>3,023,044,016</v>
+        <v>0</v>
       </c>
       <c r="J23" t="str">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="K23" t="str">
-        <v>3,635,918,461</v>
+        <v>0</v>
       </c>
       <c r="L23" t="str">
-        <v>123,791,153,370</v>
+        <v>13,269,462,926</v>
       </c>
       <c r="M23" t="str">
-        <v>9,777,466,345</v>
+        <v>13,240,251</v>
       </c>
       <c r="N23" t="str">
-        <v>7.90%</v>
+        <v>0.10%</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>External Collection-MKM</v>
+        <v>External Collection</v>
       </c>
       <c r="B24" t="str">
-        <v>S0</v>
+        <v>S-3</v>
       </c>
       <c r="C24" t="str">
         <v>SEMUA</v>
@@ -1425,39 +1425,39 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>1,800</v>
+        <v>40,171</v>
       </c>
       <c r="F24" t="str">
-        <v>569</v>
+        <v>1,836</v>
       </c>
       <c r="G24" t="str">
-        <v>127</v>
+        <v>3,561</v>
       </c>
       <c r="H24" t="str">
-        <v>7</v>
+        <v>267</v>
       </c>
       <c r="I24" t="str">
-        <v>85,985,894</v>
+        <v>3,235,725,781</v>
       </c>
       <c r="J24" t="str">
-        <v>23</v>
+        <v>184</v>
       </c>
       <c r="K24" t="str">
-        <v>413,967,834</v>
+        <v>3,926,015,972</v>
       </c>
       <c r="L24" t="str">
-        <v>4,641,615,837</v>
+        <v>129,588,936,871</v>
       </c>
       <c r="M24" t="str">
-        <v>1,247,277,922</v>
+        <v>10,450,028,293</v>
       </c>
       <c r="N24" t="str">
-        <v>26.87%</v>
+        <v>8.06%</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>External Collection-MPT02</v>
+        <v>External Collection-MKM</v>
       </c>
       <c r="B25" t="str">
         <v>S0</v>
@@ -1469,39 +1469,39 @@
         <v>SEMUA</v>
       </c>
       <c r="E25" t="str">
-        <v>4,276</v>
+        <v>1,877</v>
       </c>
       <c r="F25" t="str">
-        <v>1,302</v>
+        <v>595</v>
       </c>
       <c r="G25" t="str">
-        <v>334</v>
+        <v>131</v>
       </c>
       <c r="H25" t="str">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="I25" t="str">
-        <v>382,478,982</v>
+        <v>96,043,207</v>
       </c>
       <c r="J25" t="str">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="K25" t="str">
-        <v>585,219,992</v>
+        <v>413,967,834</v>
       </c>
       <c r="L25" t="str">
-        <v>11,041,126,880</v>
+        <v>4,818,709,539</v>
       </c>
       <c r="M25" t="str">
-        <v>2,729,578,293</v>
+        <v>1,300,149,774</v>
       </c>
       <c r="N25" t="str">
-        <v>24.72%</v>
+        <v>26.98%</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>W-EDN</v>
+        <v>External Collection-MPT02</v>
       </c>
       <c r="B26" t="str">
         <v>S0</v>
@@ -1513,39 +1513,39 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>1,869</v>
+        <v>4,405</v>
       </c>
       <c r="F26" t="str">
-        <v>391</v>
+        <v>1,345</v>
       </c>
       <c r="G26" t="str">
-        <v>0</v>
+        <v>342</v>
       </c>
       <c r="H26" t="str">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I26" t="str">
-        <v>0</v>
+        <v>422,383,557</v>
       </c>
       <c r="J26" t="str">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K26" t="str">
-        <v>0</v>
+        <v>683,635,289</v>
       </c>
       <c r="L26" t="str">
-        <v>2,014,684,788</v>
+        <v>11,340,578,232</v>
       </c>
       <c r="M26" t="str">
-        <v>469,990,014</v>
+        <v>2,881,573,659</v>
       </c>
       <c r="N26" t="str">
-        <v>23.33%</v>
+        <v>25.41%</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>W-MPT02</v>
+        <v>W-EDN</v>
       </c>
       <c r="B27" t="str">
         <v>S0</v>
@@ -1557,19 +1557,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>15,776</v>
+        <v>1,962</v>
       </c>
       <c r="F27" t="str">
-        <v>2,717</v>
+        <v>406</v>
       </c>
       <c r="G27" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I27" t="str">
-        <v>20,960,230</v>
+        <v>0</v>
       </c>
       <c r="J27" t="str">
         <v>0</v>
@@ -1578,18 +1578,18 @@
         <v>0</v>
       </c>
       <c r="L27" t="str">
-        <v>17,031,208,886</v>
+        <v>2,103,760,884</v>
       </c>
       <c r="M27" t="str">
-        <v>3,296,163,715</v>
+        <v>488,858,944</v>
       </c>
       <c r="N27" t="str">
-        <v>19.35%</v>
+        <v>23.24%</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>W-MPT02-BA</v>
+        <v>W-MPT02</v>
       </c>
       <c r="B28" t="str">
         <v>S0</v>
@@ -1601,39 +1601,39 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>3,384</v>
+        <v>16,750</v>
       </c>
       <c r="F28" t="str">
-        <v>1,127</v>
+        <v>2,904</v>
       </c>
       <c r="G28" t="str">
-        <v>1,259</v>
+        <v>1</v>
       </c>
       <c r="H28" t="str">
-        <v>241</v>
+        <v>2</v>
       </c>
       <c r="I28" t="str">
-        <v>2,893,950,526</v>
+        <v>20,960,230</v>
       </c>
       <c r="J28" t="str">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="K28" t="str">
-        <v>3,072,898,645</v>
+        <v>0</v>
       </c>
       <c r="L28" t="str">
-        <v>35,824,141,318</v>
+        <v>17,889,247,963</v>
       </c>
       <c r="M28" t="str">
-        <v>10,071,956,155</v>
+        <v>3,460,879,188</v>
       </c>
       <c r="N28" t="str">
-        <v>28.11%</v>
+        <v>19.35%</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>W-MPT05-S0-01</v>
+        <v>W-MPT02-AVG</v>
       </c>
       <c r="B29" t="str">
         <v>S0</v>
@@ -1645,10 +1645,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>3,090</v>
+        <v>40</v>
       </c>
       <c r="F29" t="str">
-        <v>528</v>
+        <v>5</v>
       </c>
       <c r="G29" t="str">
         <v>0</v>
@@ -1666,21 +1666,21 @@
         <v>0</v>
       </c>
       <c r="L29" t="str">
-        <v>3,412,100,762</v>
+        <v>28,995,076</v>
       </c>
       <c r="M29" t="str">
-        <v>674,900,052</v>
+        <v>4,141,188</v>
       </c>
       <c r="N29" t="str">
-        <v>19.78%</v>
+        <v>14.28%</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>External Collection-MKM</v>
+        <v>W-MPT02-BA</v>
       </c>
       <c r="B30" t="str">
-        <v>S1</v>
+        <v>S0</v>
       </c>
       <c r="C30" t="str">
         <v>SEMUA</v>
@@ -1689,42 +1689,42 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>3,756</v>
+        <v>3,529</v>
       </c>
       <c r="F30" t="str">
-        <v>582</v>
+        <v>1,178</v>
       </c>
       <c r="G30" t="str">
-        <v>1,692</v>
+        <v>1,319</v>
       </c>
       <c r="H30" t="str">
-        <v>7</v>
+        <v>249</v>
       </c>
       <c r="I30" t="str">
-        <v>79,992,199</v>
+        <v>2,991,104,737</v>
       </c>
       <c r="J30" t="str">
-        <v>5</v>
+        <v>164</v>
       </c>
       <c r="K30" t="str">
-        <v>84,536,012</v>
+        <v>3,359,648,889</v>
       </c>
       <c r="L30" t="str">
-        <v>10,068,215,756</v>
+        <v>37,501,516,411</v>
       </c>
       <c r="M30" t="str">
-        <v>931,769,502</v>
+        <v>10,602,342,461</v>
       </c>
       <c r="N30" t="str">
-        <v>9.25%</v>
+        <v>28.27%</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>External Collection-MPT02</v>
+        <v>W-MPT05-S0-01</v>
       </c>
       <c r="B31" t="str">
-        <v>S1</v>
+        <v>S0</v>
       </c>
       <c r="C31" t="str">
         <v>SEMUA</v>
@@ -1733,39 +1733,39 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>1,149</v>
+        <v>3,186</v>
       </c>
       <c r="F31" t="str">
-        <v>230</v>
+        <v>546</v>
       </c>
       <c r="G31" t="str">
-        <v>353</v>
+        <v>0</v>
       </c>
       <c r="H31" t="str">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I31" t="str">
-        <v>57,255,540</v>
+        <v>0</v>
       </c>
       <c r="J31" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K31" t="str">
-        <v>47,809,288</v>
+        <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>2,868,849,416</v>
+        <v>3,518,650,658</v>
       </c>
       <c r="M31" t="str">
-        <v>454,675,517</v>
+        <v>699,511,834</v>
       </c>
       <c r="N31" t="str">
-        <v>15.85%</v>
+        <v>19.88%</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>W-MPT</v>
+        <v>External Collection-MKM</v>
       </c>
       <c r="B32" t="str">
         <v>S1</v>
@@ -1777,39 +1777,39 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>2,560</v>
+        <v>3,879</v>
       </c>
       <c r="F32" t="str">
-        <v>298</v>
+        <v>615</v>
       </c>
       <c r="G32" t="str">
-        <v>96</v>
+        <v>1,763</v>
       </c>
       <c r="H32" t="str">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I32" t="str">
-        <v>10,193,592</v>
+        <v>109,604,909</v>
       </c>
       <c r="J32" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K32" t="str">
-        <v>0</v>
+        <v>102,003,250</v>
       </c>
       <c r="L32" t="str">
-        <v>2,787,992,456</v>
+        <v>10,455,607,372</v>
       </c>
       <c r="M32" t="str">
-        <v>464,824,689</v>
+        <v>1,011,032,095</v>
       </c>
       <c r="N32" t="str">
-        <v>16.67%</v>
+        <v>9.67%</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>W-MPT02</v>
+        <v>External Collection-MPT02</v>
       </c>
       <c r="B33" t="str">
         <v>S1</v>
@@ -1821,39 +1821,39 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>7,663</v>
+        <v>1,199</v>
       </c>
       <c r="F33" t="str">
-        <v>806</v>
+        <v>235</v>
       </c>
       <c r="G33" t="str">
-        <v>341</v>
+        <v>377</v>
       </c>
       <c r="H33" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I33" t="str">
-        <v>47,418,441</v>
+        <v>57,255,540</v>
       </c>
       <c r="J33" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K33" t="str">
-        <v>0</v>
+        <v>47,809,288</v>
       </c>
       <c r="L33" t="str">
-        <v>8,496,154,759</v>
+        <v>2,994,416,933</v>
       </c>
       <c r="M33" t="str">
-        <v>1,002,727,199</v>
+        <v>462,137,032</v>
       </c>
       <c r="N33" t="str">
-        <v>11.80%</v>
+        <v>15.43%</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>W-MPT02-BA</v>
+        <v>W-MPT</v>
       </c>
       <c r="B34" t="str">
         <v>S1</v>
@@ -1865,39 +1865,39 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>1,243</v>
+        <v>2,688</v>
       </c>
       <c r="F34" t="str">
-        <v>280</v>
+        <v>308</v>
       </c>
       <c r="G34" t="str">
-        <v>2,021</v>
+        <v>96</v>
       </c>
       <c r="H34" t="str">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="I34" t="str">
-        <v>589,196,901</v>
+        <v>10,193,592</v>
       </c>
       <c r="J34" t="str">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K34" t="str">
-        <v>864,595,594</v>
+        <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>12,550,224,537</v>
+        <v>2,886,416,851</v>
       </c>
       <c r="M34" t="str">
-        <v>2,265,073,282</v>
+        <v>472,812,825</v>
       </c>
       <c r="N34" t="str">
-        <v>18.05%</v>
+        <v>16.38%</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>W-MPT05</v>
+        <v>W-MPT02</v>
       </c>
       <c r="B35" t="str">
         <v>S1</v>
@@ -1909,19 +1909,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>4,042</v>
+        <v>8,271</v>
       </c>
       <c r="F35" t="str">
-        <v>376</v>
+        <v>878</v>
       </c>
       <c r="G35" t="str">
-        <v>232</v>
+        <v>342</v>
       </c>
       <c r="H35" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I35" t="str">
-        <v>36,724,632</v>
+        <v>47,418,441</v>
       </c>
       <c r="J35" t="str">
         <v>0</v>
@@ -1930,18 +1930,18 @@
         <v>0</v>
       </c>
       <c r="L35" t="str">
-        <v>4,447,050,859</v>
+        <v>9,031,826,233</v>
       </c>
       <c r="M35" t="str">
-        <v>472,230,634</v>
+        <v>1,072,425,528</v>
       </c>
       <c r="N35" t="str">
-        <v>10.62%</v>
+        <v>11.87%</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>W-MPT05-2</v>
+        <v>W-MPT02-AVG</v>
       </c>
       <c r="B36" t="str">
         <v>S1</v>
@@ -1953,13 +1953,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>2,655</v>
+        <v>35</v>
       </c>
       <c r="F36" t="str">
-        <v>267</v>
+        <v>3</v>
       </c>
       <c r="G36" t="str">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H36" t="str">
         <v>0</v>
@@ -1974,18 +1974,18 @@
         <v>0</v>
       </c>
       <c r="L36" t="str">
-        <v>2,819,984,816</v>
+        <v>30,206,013</v>
       </c>
       <c r="M36" t="str">
-        <v>294,439,857</v>
+        <v>2,784,474</v>
       </c>
       <c r="N36" t="str">
-        <v>10.44%</v>
+        <v>9.22%</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>W-MPT05-3</v>
+        <v>W-MPT02-BA</v>
       </c>
       <c r="B37" t="str">
         <v>S1</v>
@@ -1997,39 +1997,39 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>338</v>
+        <v>1,301</v>
       </c>
       <c r="F37" t="str">
-        <v>39</v>
+        <v>297</v>
       </c>
       <c r="G37" t="str">
-        <v>0</v>
+        <v>2,131</v>
       </c>
       <c r="H37" t="str">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I37" t="str">
-        <v>0</v>
+        <v>599,512,776</v>
       </c>
       <c r="J37" t="str">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="K37" t="str">
-        <v>0</v>
+        <v>928,923,672</v>
       </c>
       <c r="L37" t="str">
-        <v>474,103,590</v>
+        <v>13,145,174,561</v>
       </c>
       <c r="M37" t="str">
-        <v>45,067,607</v>
+        <v>2,394,938,766</v>
       </c>
       <c r="N37" t="str">
-        <v>9.51%</v>
+        <v>18.22%</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>W-MPT05-BA</v>
+        <v>W-MPT05</v>
       </c>
       <c r="B38" t="str">
         <v>S1</v>
@@ -2041,42 +2041,42 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>1,042</v>
+        <v>4,220</v>
       </c>
       <c r="F38" t="str">
-        <v>173</v>
+        <v>395</v>
       </c>
       <c r="G38" t="str">
-        <v>1,914</v>
+        <v>233</v>
       </c>
       <c r="H38" t="str">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="I38" t="str">
-        <v>461,157,039</v>
+        <v>36,724,632</v>
       </c>
       <c r="J38" t="str">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K38" t="str">
-        <v>407,358,437</v>
+        <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>10,206,687,047</v>
+        <v>4,603,043,355</v>
       </c>
       <c r="M38" t="str">
-        <v>1,421,067,370</v>
+        <v>481,829,607</v>
       </c>
       <c r="N38" t="str">
-        <v>13.92%</v>
+        <v>10.47%</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>External Collection-MPT</v>
+        <v>W-MPT05-2</v>
       </c>
       <c r="B39" t="str">
-        <v>S2</v>
+        <v>S1</v>
       </c>
       <c r="C39" t="str">
         <v>SEMUA</v>
@@ -2085,42 +2085,42 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>5,570</v>
+        <v>2,822</v>
       </c>
       <c r="F39" t="str">
-        <v>355</v>
+        <v>280</v>
       </c>
       <c r="G39" t="str">
-        <v>6,781</v>
+        <v>15</v>
       </c>
       <c r="H39" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I39" t="str">
-        <v>37,100,895</v>
+        <v>0</v>
       </c>
       <c r="J39" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K39" t="str">
-        <v>84,725,256</v>
+        <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>13,681,366,087</v>
+        <v>2,962,639,337</v>
       </c>
       <c r="M39" t="str">
-        <v>432,645,239</v>
+        <v>306,519,832</v>
       </c>
       <c r="N39" t="str">
-        <v>3.16%</v>
+        <v>10.35%</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>External Collection-MPT02</v>
+        <v>W-MPT05-3</v>
       </c>
       <c r="B40" t="str">
-        <v>S2</v>
+        <v>S1</v>
       </c>
       <c r="C40" t="str">
         <v>SEMUA</v>
@@ -2129,13 +2129,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E40" t="str">
-        <v>0</v>
+        <v>338</v>
       </c>
       <c r="F40" t="str">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="G40" t="str">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H40" t="str">
         <v>0</v>
@@ -2150,21 +2150,21 @@
         <v>0</v>
       </c>
       <c r="L40" t="str">
-        <v>0</v>
+        <v>474,103,590</v>
       </c>
       <c r="M40" t="str">
-        <v>5,451,647</v>
+        <v>45,067,607</v>
       </c>
       <c r="N40" t="str">
-        <v>0.0000%</v>
+        <v>9.51%</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>W-EDN</v>
+        <v>W-MPT05-BA</v>
       </c>
       <c r="B41" t="str">
-        <v>S2</v>
+        <v>S1</v>
       </c>
       <c r="C41" t="str">
         <v>SEMUA</v>
@@ -2173,39 +2173,39 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>1,369</v>
+        <v>1,087</v>
       </c>
       <c r="F41" t="str">
-        <v>43</v>
+        <v>187</v>
       </c>
       <c r="G41" t="str">
-        <v>1,403</v>
+        <v>1,995</v>
       </c>
       <c r="H41" t="str">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="I41" t="str">
-        <v>24,724,376</v>
+        <v>483,021,812</v>
       </c>
       <c r="J41" t="str">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="K41" t="str">
-        <v>50,770,592</v>
+        <v>447,503,665</v>
       </c>
       <c r="L41" t="str">
-        <v>2,958,982,137</v>
+        <v>10,659,300,883</v>
       </c>
       <c r="M41" t="str">
-        <v>143,541,465</v>
+        <v>1,534,336,073</v>
       </c>
       <c r="N41" t="str">
-        <v>4.85%</v>
+        <v>14.39%</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>W-MKM</v>
+        <v>External Collection-MPT</v>
       </c>
       <c r="B42" t="str">
         <v>S2</v>
@@ -2217,39 +2217,39 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>935</v>
+        <v>5,735</v>
       </c>
       <c r="F42" t="str">
-        <v>28</v>
+        <v>371</v>
       </c>
       <c r="G42" t="str">
-        <v>1,434</v>
+        <v>7,088</v>
       </c>
       <c r="H42" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I42" t="str">
-        <v>0</v>
+        <v>37,100,895</v>
       </c>
       <c r="J42" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K42" t="str">
-        <v>66,445,865</v>
+        <v>84,725,256</v>
       </c>
       <c r="L42" t="str">
-        <v>2,322,364,133</v>
+        <v>14,121,259,534</v>
       </c>
       <c r="M42" t="str">
-        <v>94,372,282</v>
+        <v>451,912,601</v>
       </c>
       <c r="N42" t="str">
-        <v>4.06%</v>
+        <v>3.20%</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>W-MPT</v>
+        <v>External Collection-MPT02</v>
       </c>
       <c r="B43" t="str">
         <v>S2</v>
@@ -2261,39 +2261,39 @@
         <v>SEMUA</v>
       </c>
       <c r="E43" t="str">
-        <v>3,743</v>
+        <v>0</v>
       </c>
       <c r="F43" t="str">
-        <v>181</v>
+        <v>4</v>
       </c>
       <c r="G43" t="str">
-        <v>6,000</v>
+        <v>84</v>
       </c>
       <c r="H43" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I43" t="str">
-        <v>112,506,786</v>
+        <v>0</v>
       </c>
       <c r="J43" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="str">
-        <v>19,064,856</v>
+        <v>0</v>
       </c>
       <c r="L43" t="str">
-        <v>9,329,816,221</v>
+        <v>0</v>
       </c>
       <c r="M43" t="str">
-        <v>434,753,150</v>
+        <v>5,451,647</v>
       </c>
       <c r="N43" t="str">
-        <v>4.66%</v>
+        <v>0.0000%</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>W-MPT02</v>
+        <v>W-EDN</v>
       </c>
       <c r="B44" t="str">
         <v>S2</v>
@@ -2305,39 +2305,39 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>3,344</v>
+        <v>1,478</v>
       </c>
       <c r="F44" t="str">
-        <v>154</v>
+        <v>49</v>
       </c>
       <c r="G44" t="str">
-        <v>3,485</v>
+        <v>1,473</v>
       </c>
       <c r="H44" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I44" t="str">
-        <v>49,794,252</v>
+        <v>24,724,376</v>
       </c>
       <c r="J44" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K44" t="str">
-        <v>54,162,704</v>
+        <v>50,770,592</v>
       </c>
       <c r="L44" t="str">
-        <v>8,046,067,672</v>
+        <v>3,232,853,200</v>
       </c>
       <c r="M44" t="str">
-        <v>286,848,533</v>
+        <v>154,941,936</v>
       </c>
       <c r="N44" t="str">
-        <v>3.57%</v>
+        <v>4.79%</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>W-SO</v>
+        <v>W-MKM</v>
       </c>
       <c r="B45" t="str">
         <v>S2</v>
@@ -2349,39 +2349,171 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>3,278</v>
+        <v>989</v>
       </c>
       <c r="F45" t="str">
-        <v>174</v>
+        <v>31</v>
       </c>
       <c r="G45" t="str">
-        <v>4,972</v>
+        <v>1,504</v>
       </c>
       <c r="H45" t="str">
+        <v>0</v>
+      </c>
+      <c r="I45" t="str">
+        <v>0</v>
+      </c>
+      <c r="J45" t="str">
+        <v>3</v>
+      </c>
+      <c r="K45" t="str">
+        <v>66,445,865</v>
+      </c>
+      <c r="L45" t="str">
+        <v>2,505,092,921</v>
+      </c>
+      <c r="M45" t="str">
+        <v>97,525,517</v>
+      </c>
+      <c r="N45" t="str">
+        <v>3.89%</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>W-MPT</v>
+      </c>
+      <c r="B46" t="str">
+        <v>S2</v>
+      </c>
+      <c r="C46" t="str">
+        <v>SEMUA</v>
+      </c>
+      <c r="D46" t="str">
+        <v>SEMUA</v>
+      </c>
+      <c r="E46" t="str">
+        <v>3,962</v>
+      </c>
+      <c r="F46" t="str">
+        <v>201</v>
+      </c>
+      <c r="G46" t="str">
+        <v>6,243</v>
+      </c>
+      <c r="H46" t="str">
+        <v>11</v>
+      </c>
+      <c r="I46" t="str">
+        <v>135,065,374</v>
+      </c>
+      <c r="J46" t="str">
+        <v>1</v>
+      </c>
+      <c r="K46" t="str">
+        <v>19,064,856</v>
+      </c>
+      <c r="L46" t="str">
+        <v>9,735,898,303</v>
+      </c>
+      <c r="M46" t="str">
+        <v>489,890,846</v>
+      </c>
+      <c r="N46" t="str">
+        <v>5.03%</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>W-MPT02</v>
+      </c>
+      <c r="B47" t="str">
+        <v>S2</v>
+      </c>
+      <c r="C47" t="str">
+        <v>SEMUA</v>
+      </c>
+      <c r="D47" t="str">
+        <v>SEMUA</v>
+      </c>
+      <c r="E47" t="str">
+        <v>3,784</v>
+      </c>
+      <c r="F47" t="str">
+        <v>176</v>
+      </c>
+      <c r="G47" t="str">
+        <v>3,681</v>
+      </c>
+      <c r="H47" t="str">
+        <v>4</v>
+      </c>
+      <c r="I47" t="str">
+        <v>49,794,252</v>
+      </c>
+      <c r="J47" t="str">
+        <v>3</v>
+      </c>
+      <c r="K47" t="str">
+        <v>54,162,704</v>
+      </c>
+      <c r="L47" t="str">
+        <v>9,043,419,900</v>
+      </c>
+      <c r="M47" t="str">
+        <v>296,597,871</v>
+      </c>
+      <c r="N47" t="str">
+        <v>3.28%</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>W-SO</v>
+      </c>
+      <c r="B48" t="str">
+        <v>S2</v>
+      </c>
+      <c r="C48" t="str">
+        <v>SEMUA</v>
+      </c>
+      <c r="D48" t="str">
+        <v>SEMUA</v>
+      </c>
+      <c r="E48" t="str">
+        <v>3,471</v>
+      </c>
+      <c r="F48" t="str">
+        <v>184</v>
+      </c>
+      <c r="G48" t="str">
+        <v>5,178</v>
+      </c>
+      <c r="H48" t="str">
         <v>5</v>
       </c>
-      <c r="I45" t="str">
+      <c r="I48" t="str">
         <v>60,689,995</v>
       </c>
-      <c r="J45" t="str">
+      <c r="J48" t="str">
         <v>7</v>
       </c>
-      <c r="K45" t="str">
+      <c r="K48" t="str">
         <v>134,571,733</v>
       </c>
-      <c r="L45" t="str">
-        <v>7,738,536,787</v>
-      </c>
-      <c r="M45" t="str">
-        <v>496,446,330</v>
-      </c>
-      <c r="N45" t="str">
-        <v>6.42%</v>
+      <c r="L48" t="str">
+        <v>8,122,246,466</v>
+      </c>
+      <c r="M48" t="str">
+        <v>515,967,644</v>
+      </c>
+      <c r="N48" t="str">
+        <v>6.35%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N48"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/rawdata/Bulanan/10. Okt-LD.xlsx
+++ b/rawdata/Bulanan/10. Okt-LD.xlsx
@@ -457,34 +457,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>9,301</v>
+        <v>9,606</v>
       </c>
       <c r="F2" t="str">
-        <v>4,556</v>
+        <v>4,718</v>
       </c>
       <c r="G2" t="str">
-        <v>1,258</v>
+        <v>1,304</v>
       </c>
       <c r="H2" t="str">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="I2" t="str">
-        <v>2,695,641,565</v>
+        <v>2,839,497,051</v>
       </c>
       <c r="J2" t="str">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c r="K2" t="str">
-        <v>9,828,345,145</v>
+        <v>10,101,508,890</v>
       </c>
       <c r="L2" t="str">
-        <v>34,444,730,377</v>
+        <v>35,633,873,927</v>
       </c>
       <c r="M2" t="str">
-        <v>19,158,293,992</v>
+        <v>19,861,253,811</v>
       </c>
       <c r="N2" t="str">
-        <v>55.62%</v>
+        <v>55.74%</v>
       </c>
     </row>
     <row r="3">
@@ -501,34 +501,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>14,074</v>
+        <v>14,596</v>
       </c>
       <c r="F3" t="str">
-        <v>2,006</v>
+        <v>2,063</v>
       </c>
       <c r="G3" t="str">
-        <v>2,212</v>
+        <v>2,295</v>
       </c>
       <c r="H3" t="str">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="I3" t="str">
-        <v>1,669,739,332</v>
+        <v>1,765,562,423</v>
       </c>
       <c r="J3" t="str">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="K3" t="str">
-        <v>5,568,131,461</v>
+        <v>5,748,124,031</v>
       </c>
       <c r="L3" t="str">
-        <v>57,461,091,910</v>
+        <v>59,598,684,724</v>
       </c>
       <c r="M3" t="str">
-        <v>10,040,064,352</v>
+        <v>10,343,027,135</v>
       </c>
       <c r="N3" t="str">
-        <v>17.47%</v>
+        <v>17.35%</v>
       </c>
     </row>
     <row r="4">
@@ -545,34 +545,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>2,764</v>
+        <v>2,899</v>
       </c>
       <c r="F4" t="str">
-        <v>1,265</v>
+        <v>1,334</v>
       </c>
       <c r="G4" t="str">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="H4" t="str">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I4" t="str">
-        <v>885,063,456</v>
+        <v>909,752,299</v>
       </c>
       <c r="J4" t="str">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="K4" t="str">
-        <v>3,137,405,783</v>
+        <v>3,203,149,540</v>
       </c>
       <c r="L4" t="str">
-        <v>10,340,982,751</v>
+        <v>10,781,895,404</v>
       </c>
       <c r="M4" t="str">
-        <v>5,939,705,352</v>
+        <v>6,204,351,094</v>
       </c>
       <c r="N4" t="str">
-        <v>57.44%</v>
+        <v>57.54%</v>
       </c>
     </row>
     <row r="5">
@@ -589,13 +589,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>5,134</v>
+        <v>5,362</v>
       </c>
       <c r="F5" t="str">
-        <v>1,210</v>
+        <v>1,257</v>
       </c>
       <c r="G5" t="str">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H5" t="str">
         <v>11</v>
@@ -610,13 +610,13 @@
         <v>38,695,454</v>
       </c>
       <c r="L5" t="str">
-        <v>6,173,575,353</v>
+        <v>6,378,213,490</v>
       </c>
       <c r="M5" t="str">
-        <v>2,186,206,122</v>
+        <v>2,239,448,474</v>
       </c>
       <c r="N5" t="str">
-        <v>35.41%</v>
+        <v>35.11%</v>
       </c>
     </row>
     <row r="6">
@@ -633,13 +633,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>22,991</v>
+        <v>24,087</v>
       </c>
       <c r="F6" t="str">
-        <v>5,426</v>
+        <v>5,673</v>
       </c>
       <c r="G6" t="str">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H6" t="str">
         <v>12</v>
@@ -654,13 +654,13 @@
         <v>101,641,843</v>
       </c>
       <c r="L6" t="str">
-        <v>27,677,676,106</v>
+        <v>28,854,656,197</v>
       </c>
       <c r="M6" t="str">
-        <v>8,490,029,830</v>
+        <v>8,827,737,528</v>
       </c>
       <c r="N6" t="str">
-        <v>30.67%</v>
+        <v>30.59%</v>
       </c>
     </row>
     <row r="7">
@@ -677,10 +677,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>96</v>
+        <v>179</v>
       </c>
       <c r="F7" t="str">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="G7" t="str">
         <v>0</v>
@@ -698,13 +698,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="str">
-        <v>79,660,229</v>
+        <v>156,881,804</v>
       </c>
       <c r="M7" t="str">
-        <v>12,000,373</v>
+        <v>39,083,169</v>
       </c>
       <c r="N7" t="str">
-        <v>15.06%</v>
+        <v>24.91%</v>
       </c>
     </row>
     <row r="8">
@@ -721,34 +721,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>6,917</v>
+        <v>7,185</v>
       </c>
       <c r="F8" t="str">
-        <v>3,277</v>
+        <v>3,411</v>
       </c>
       <c r="G8" t="str">
-        <v>4,727</v>
+        <v>4,920</v>
       </c>
       <c r="H8" t="str">
-        <v>977</v>
+        <v>1,008</v>
       </c>
       <c r="I8" t="str">
-        <v>11,802,682,227</v>
+        <v>12,173,421,385</v>
       </c>
       <c r="J8" t="str">
-        <v>675</v>
+        <v>714</v>
       </c>
       <c r="K8" t="str">
-        <v>14,040,127,147</v>
+        <v>14,899,482,887</v>
       </c>
       <c r="L8" t="str">
-        <v>78,711,565,882</v>
+        <v>82,043,315,773</v>
       </c>
       <c r="M8" t="str">
-        <v>34,708,508,197</v>
+        <v>36,265,224,848</v>
       </c>
       <c r="N8" t="str">
-        <v>44.10%</v>
+        <v>44.20%</v>
       </c>
     </row>
     <row r="9">
@@ -765,13 +765,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>2,195</v>
+        <v>2,330</v>
       </c>
       <c r="F9" t="str">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="G9" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="str">
         <v>0</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="str">
-        <v>2,788,209,709</v>
+        <v>2,945,515,629</v>
       </c>
       <c r="M9" t="str">
-        <v>782,542,220</v>
+        <v>815,333,232</v>
       </c>
       <c r="N9" t="str">
-        <v>28.07%</v>
+        <v>27.68%</v>
       </c>
     </row>
     <row r="10">
@@ -809,13 +809,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>3,159</v>
+        <v>3,267</v>
       </c>
       <c r="F10" t="str">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" t="str">
-        <v>7,521</v>
+        <v>7,817</v>
       </c>
       <c r="H10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>100,379,570</v>
       </c>
       <c r="L10" t="str">
-        <v>8,915,975,098</v>
+        <v>9,303,331,014</v>
       </c>
       <c r="M10" t="str">
-        <v>125,124,135</v>
+        <v>127,704,577</v>
       </c>
       <c r="N10" t="str">
-        <v>1.40%</v>
+        <v>1.37%</v>
       </c>
     </row>
     <row r="11">
@@ -853,13 +853,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>2,633</v>
+        <v>2,723</v>
       </c>
       <c r="F11" t="str">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G11" t="str">
-        <v>5,299</v>
+        <v>5,529</v>
       </c>
       <c r="H11" t="str">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>7,432,463,641</v>
+        <v>7,803,958,175</v>
       </c>
       <c r="M11" t="str">
-        <v>98,996,301</v>
+        <v>102,927,588</v>
       </c>
       <c r="N11" t="str">
-        <v>1.33%</v>
+        <v>1.32%</v>
       </c>
     </row>
     <row r="12">
@@ -897,13 +897,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>3,314</v>
+        <v>3,421</v>
       </c>
       <c r="F12" t="str">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G12" t="str">
-        <v>9,499</v>
+        <v>9,917</v>
       </c>
       <c r="H12" t="str">
         <v>0</v>
@@ -918,10 +918,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>12,564,844,748</v>
+        <v>12,860,505,090</v>
       </c>
       <c r="M12" t="str">
-        <v>121,067,413</v>
+        <v>123,023,773</v>
       </c>
       <c r="N12" t="str">
         <v>0.96%</v>
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>2,060</v>
+        <v>2,127</v>
       </c>
       <c r="F13" t="str">
         <v>60</v>
       </c>
       <c r="G13" t="str">
-        <v>6,535</v>
+        <v>6,825</v>
       </c>
       <c r="H13" t="str">
         <v>3</v>
@@ -962,13 +962,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="str">
-        <v>7,816,657,843</v>
+        <v>8,005,638,963</v>
       </c>
       <c r="M13" t="str">
         <v>229,484,515</v>
       </c>
       <c r="N13" t="str">
-        <v>2.94%</v>
+        <v>2.87%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>1,080</v>
+        <v>1,107</v>
       </c>
       <c r="F14" t="str">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G14" t="str">
-        <v>3,541</v>
+        <v>3,669</v>
       </c>
       <c r="H14" t="str">
         <v>1</v>
@@ -1006,13 +1006,13 @@
         <v>35,694,915</v>
       </c>
       <c r="L14" t="str">
-        <v>4,130,996,484</v>
+        <v>4,210,889,685</v>
       </c>
       <c r="M14" t="str">
-        <v>90,046,614</v>
+        <v>97,506,596</v>
       </c>
       <c r="N14" t="str">
-        <v>2.18%</v>
+        <v>2.32%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,19 +1029,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>2,911</v>
+        <v>3,002</v>
       </c>
       <c r="F15" t="str">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G15" t="str">
-        <v>8,860</v>
+        <v>9,243</v>
       </c>
       <c r="H15" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="str">
-        <v>0</v>
+        <v>10,123,448</v>
       </c>
       <c r="J15" t="str">
         <v>0</v>
@@ -1050,13 +1050,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="str">
-        <v>10,888,319,801</v>
+        <v>11,284,576,089</v>
       </c>
       <c r="M15" t="str">
-        <v>151,425,781</v>
+        <v>176,378,343</v>
       </c>
       <c r="N15" t="str">
-        <v>1.39%</v>
+        <v>1.56%</v>
       </c>
     </row>
     <row r="16">
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>4,205</v>
+        <v>4,366</v>
       </c>
       <c r="F16" t="str">
         <v>26</v>
       </c>
       <c r="G16" t="str">
-        <v>12,409</v>
+        <v>12,909</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>16,240,162,759</v>
+        <v>16,801,114,190</v>
       </c>
       <c r="M16" t="str">
         <v>82,196,516</v>
       </c>
       <c r="N16" t="str">
-        <v>0.51%</v>
+        <v>0.49%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>1,903</v>
+        <v>1,978</v>
       </c>
       <c r="F17" t="str">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G17" t="str">
-        <v>4,665</v>
+        <v>4,870</v>
       </c>
       <c r="H17" t="str">
         <v>0</v>
@@ -1138,13 +1138,13 @@
         <v>233,859,144</v>
       </c>
       <c r="L17" t="str">
-        <v>6,623,417,482</v>
+        <v>6,878,785,699</v>
       </c>
       <c r="M17" t="str">
-        <v>155,198,733</v>
+        <v>155,308,733</v>
       </c>
       <c r="N17" t="str">
-        <v>2.34%</v>
+        <v>2.26%</v>
       </c>
     </row>
     <row r="18">
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>2,380</v>
+        <v>2,473</v>
       </c>
       <c r="F18" t="str">
         <v>33</v>
       </c>
       <c r="G18" t="str">
-        <v>5,422</v>
+        <v>5,660</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>100,898,460</v>
       </c>
       <c r="L18" t="str">
-        <v>7,992,991,844</v>
+        <v>8,250,497,948</v>
       </c>
       <c r="M18" t="str">
         <v>110,870,539</v>
       </c>
       <c r="N18" t="str">
-        <v>1.39%</v>
+        <v>1.34%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>3,446</v>
+        <v>3,577</v>
       </c>
       <c r="F19" t="str">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G19" t="str">
-        <v>12,481</v>
+        <v>13,005</v>
       </c>
       <c r="H19" t="str">
         <v>1</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>15,178,156,444</v>
+        <v>15,725,368,781</v>
       </c>
       <c r="M19" t="str">
-        <v>122,285,122</v>
+        <v>125,057,824</v>
       </c>
       <c r="N19" t="str">
-        <v>0.81%</v>
+        <v>0.80%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>576</v>
+        <v>597</v>
       </c>
       <c r="F20" t="str">
         <v>4</v>
       </c>
       <c r="G20" t="str">
-        <v>2,058</v>
+        <v>2,138</v>
       </c>
       <c r="H20" t="str">
         <v>0</v>
@@ -1270,13 +1270,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="str">
-        <v>2,442,562,559</v>
+        <v>2,561,174,608</v>
       </c>
       <c r="M20" t="str">
         <v>11,695,275</v>
       </c>
       <c r="N20" t="str">
-        <v>0.48%</v>
+        <v>0.46%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>4,024</v>
+        <v>4,176</v>
       </c>
       <c r="F21" t="str">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G21" t="str">
-        <v>14,112</v>
+        <v>14,691</v>
       </c>
       <c r="H21" t="str">
         <v>1</v>
@@ -1314,13 +1314,13 @@
         <v>0</v>
       </c>
       <c r="L21" t="str">
-        <v>17,317,300,032</v>
+        <v>18,024,106,393</v>
       </c>
       <c r="M21" t="str">
-        <v>106,492,692</v>
+        <v>136,401,325</v>
       </c>
       <c r="N21" t="str">
-        <v>0.61%</v>
+        <v>0.76%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,13 +1337,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>23,024</v>
+        <v>23,259</v>
       </c>
       <c r="F22" t="str">
-        <v>897</v>
+        <v>931</v>
       </c>
       <c r="G22" t="str">
-        <v>552,826</v>
+        <v>577,154</v>
       </c>
       <c r="H22" t="str">
         <v>6</v>
@@ -1358,13 +1358,13 @@
         <v>263,912,728</v>
       </c>
       <c r="L22" t="str">
-        <v>101,391,107,386</v>
+        <v>102,107,518,595</v>
       </c>
       <c r="M22" t="str">
-        <v>2,319,037,431</v>
+        <v>2,407,881,089</v>
       </c>
       <c r="N22" t="str">
-        <v>2.29%</v>
+        <v>2.36%</v>
       </c>
     </row>
     <row r="23">
@@ -1387,7 +1387,7 @@
         <v>4</v>
       </c>
       <c r="G23" t="str">
-        <v>12,300</v>
+        <v>12,835</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -1425,34 +1425,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>40,171</v>
+        <v>42,050</v>
       </c>
       <c r="F24" t="str">
-        <v>1,836</v>
+        <v>1,917</v>
       </c>
       <c r="G24" t="str">
-        <v>3,561</v>
+        <v>3,717</v>
       </c>
       <c r="H24" t="str">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="I24" t="str">
-        <v>3,235,725,781</v>
+        <v>3,402,808,002</v>
       </c>
       <c r="J24" t="str">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="K24" t="str">
-        <v>3,926,015,972</v>
+        <v>4,080,462,956</v>
       </c>
       <c r="L24" t="str">
-        <v>129,588,936,871</v>
+        <v>135,028,741,679</v>
       </c>
       <c r="M24" t="str">
-        <v>10,450,028,293</v>
+        <v>10,918,949,537</v>
       </c>
       <c r="N24" t="str">
-        <v>8.06%</v>
+        <v>8.09%</v>
       </c>
     </row>
     <row r="25">
@@ -1469,13 +1469,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E25" t="str">
-        <v>1,877</v>
+        <v>1,942</v>
       </c>
       <c r="F25" t="str">
-        <v>595</v>
+        <v>617</v>
       </c>
       <c r="G25" t="str">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H25" t="str">
         <v>8</v>
@@ -1490,13 +1490,13 @@
         <v>413,967,834</v>
       </c>
       <c r="L25" t="str">
-        <v>4,818,709,539</v>
+        <v>4,965,425,551</v>
       </c>
       <c r="M25" t="str">
-        <v>1,300,149,774</v>
+        <v>1,335,785,789</v>
       </c>
       <c r="N25" t="str">
-        <v>26.98%</v>
+        <v>26.90%</v>
       </c>
     </row>
     <row r="26">
@@ -1513,19 +1513,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>4,405</v>
+        <v>4,535</v>
       </c>
       <c r="F26" t="str">
-        <v>1,345</v>
+        <v>1,382</v>
       </c>
       <c r="G26" t="str">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="H26" t="str">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I26" t="str">
-        <v>422,383,557</v>
+        <v>444,247,055</v>
       </c>
       <c r="J26" t="str">
         <v>36</v>
@@ -1534,13 +1534,13 @@
         <v>683,635,289</v>
       </c>
       <c r="L26" t="str">
-        <v>11,340,578,232</v>
+        <v>11,641,965,174</v>
       </c>
       <c r="M26" t="str">
-        <v>2,881,573,659</v>
+        <v>2,947,178,900</v>
       </c>
       <c r="N26" t="str">
-        <v>25.41%</v>
+        <v>25.32%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,10 +1557,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>1,962</v>
+        <v>2,043</v>
       </c>
       <c r="F27" t="str">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="G27" t="str">
         <v>0</v>
@@ -1578,13 +1578,13 @@
         <v>0</v>
       </c>
       <c r="L27" t="str">
-        <v>2,103,760,884</v>
+        <v>2,173,530,010</v>
       </c>
       <c r="M27" t="str">
-        <v>488,858,944</v>
+        <v>500,139,020</v>
       </c>
       <c r="N27" t="str">
-        <v>23.24%</v>
+        <v>23.01%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,10 +1601,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>16,750</v>
+        <v>17,537</v>
       </c>
       <c r="F28" t="str">
-        <v>2,904</v>
+        <v>3,041</v>
       </c>
       <c r="G28" t="str">
         <v>1</v>
@@ -1622,13 +1622,13 @@
         <v>0</v>
       </c>
       <c r="L28" t="str">
-        <v>17,889,247,963</v>
+        <v>18,629,302,319</v>
       </c>
       <c r="M28" t="str">
-        <v>3,460,879,188</v>
+        <v>3,618,619,686</v>
       </c>
       <c r="N28" t="str">
-        <v>19.35%</v>
+        <v>19.42%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,10 +1645,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F29" t="str">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G29" t="str">
         <v>0</v>
@@ -1666,13 +1666,13 @@
         <v>0</v>
       </c>
       <c r="L29" t="str">
-        <v>28,995,076</v>
+        <v>60,575,456</v>
       </c>
       <c r="M29" t="str">
-        <v>4,141,188</v>
+        <v>11,010,476</v>
       </c>
       <c r="N29" t="str">
-        <v>14.28%</v>
+        <v>18.18%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,34 +1689,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>3,529</v>
+        <v>3,691</v>
       </c>
       <c r="F30" t="str">
-        <v>1,178</v>
+        <v>1,230</v>
       </c>
       <c r="G30" t="str">
-        <v>1,319</v>
+        <v>1,386</v>
       </c>
       <c r="H30" t="str">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="I30" t="str">
-        <v>2,991,104,737</v>
+        <v>3,173,522,777</v>
       </c>
       <c r="J30" t="str">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K30" t="str">
-        <v>3,359,648,889</v>
+        <v>3,408,540,316</v>
       </c>
       <c r="L30" t="str">
-        <v>37,501,516,411</v>
+        <v>39,341,017,096</v>
       </c>
       <c r="M30" t="str">
-        <v>10,602,342,461</v>
+        <v>11,032,854,341</v>
       </c>
       <c r="N30" t="str">
-        <v>28.27%</v>
+        <v>28.04%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,10 +1733,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>3,186</v>
+        <v>3,270</v>
       </c>
       <c r="F31" t="str">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1754,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>3,518,650,658</v>
+        <v>3,593,869,191</v>
       </c>
       <c r="M31" t="str">
-        <v>699,511,834</v>
+        <v>707,851,892</v>
       </c>
       <c r="N31" t="str">
-        <v>19.88%</v>
+        <v>19.70%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,13 +1777,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>3,879</v>
+        <v>3,975</v>
       </c>
       <c r="F32" t="str">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="G32" t="str">
-        <v>1,763</v>
+        <v>1,822</v>
       </c>
       <c r="H32" t="str">
         <v>9</v>
@@ -1798,13 +1798,13 @@
         <v>102,003,250</v>
       </c>
       <c r="L32" t="str">
-        <v>10,455,607,372</v>
+        <v>10,638,945,563</v>
       </c>
       <c r="M32" t="str">
-        <v>1,011,032,095</v>
+        <v>1,025,474,037</v>
       </c>
       <c r="N32" t="str">
-        <v>9.67%</v>
+        <v>9.64%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,13 +1821,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>1,199</v>
+        <v>1,237</v>
       </c>
       <c r="F33" t="str">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="G33" t="str">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="H33" t="str">
         <v>5</v>
@@ -1842,13 +1842,13 @@
         <v>47,809,288</v>
       </c>
       <c r="L33" t="str">
-        <v>2,994,416,933</v>
+        <v>3,054,119,914</v>
       </c>
       <c r="M33" t="str">
-        <v>462,137,032</v>
+        <v>467,571,598</v>
       </c>
       <c r="N33" t="str">
-        <v>15.43%</v>
+        <v>15.31%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,10 +1865,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>2,688</v>
+        <v>2,802</v>
       </c>
       <c r="F34" t="str">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="G34" t="str">
         <v>96</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>2,886,416,851</v>
+        <v>2,981,591,180</v>
       </c>
       <c r="M34" t="str">
-        <v>472,812,825</v>
+        <v>479,450,073</v>
       </c>
       <c r="N34" t="str">
-        <v>16.38%</v>
+        <v>16.08%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,13 +1909,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>8,271</v>
+        <v>8,791</v>
       </c>
       <c r="F35" t="str">
-        <v>878</v>
+        <v>933</v>
       </c>
       <c r="G35" t="str">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H35" t="str">
         <v>4</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="L35" t="str">
-        <v>9,031,826,233</v>
+        <v>9,496,439,883</v>
       </c>
       <c r="M35" t="str">
-        <v>1,072,425,528</v>
+        <v>1,130,007,449</v>
       </c>
       <c r="N35" t="str">
-        <v>11.87%</v>
+        <v>11.90%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,10 +1953,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="F36" t="str">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G36" t="str">
         <v>0</v>
@@ -1974,13 +1974,13 @@
         <v>0</v>
       </c>
       <c r="L36" t="str">
-        <v>30,206,013</v>
+        <v>54,062,418</v>
       </c>
       <c r="M36" t="str">
-        <v>2,784,474</v>
+        <v>11,606,597</v>
       </c>
       <c r="N36" t="str">
-        <v>9.22%</v>
+        <v>21.47%</v>
       </c>
     </row>
     <row r="37">
@@ -1997,34 +1997,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>1,301</v>
+        <v>1,348</v>
       </c>
       <c r="F37" t="str">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="G37" t="str">
-        <v>2,131</v>
+        <v>2,229</v>
       </c>
       <c r="H37" t="str">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I37" t="str">
-        <v>599,512,776</v>
+        <v>633,173,453</v>
       </c>
       <c r="J37" t="str">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K37" t="str">
-        <v>928,923,672</v>
+        <v>947,968,275</v>
       </c>
       <c r="L37" t="str">
-        <v>13,145,174,561</v>
+        <v>13,609,053,171</v>
       </c>
       <c r="M37" t="str">
-        <v>2,394,938,766</v>
+        <v>2,503,298,598</v>
       </c>
       <c r="N37" t="str">
-        <v>18.22%</v>
+        <v>18.39%</v>
       </c>
     </row>
     <row r="38">
@@ -2041,13 +2041,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>4,220</v>
+        <v>4,370</v>
       </c>
       <c r="F38" t="str">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="G38" t="str">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H38" t="str">
         <v>3</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>4,603,043,355</v>
+        <v>4,719,809,606</v>
       </c>
       <c r="M38" t="str">
-        <v>481,829,607</v>
+        <v>491,415,261</v>
       </c>
       <c r="N38" t="str">
-        <v>10.47%</v>
+        <v>10.41%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,13 +2085,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>2,822</v>
+        <v>2,972</v>
       </c>
       <c r="F39" t="str">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="G39" t="str">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H39" t="str">
         <v>0</v>
@@ -2106,13 +2106,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>2,962,639,337</v>
+        <v>3,094,651,673</v>
       </c>
       <c r="M39" t="str">
-        <v>306,519,832</v>
+        <v>317,298,446</v>
       </c>
       <c r="N39" t="str">
-        <v>10.35%</v>
+        <v>10.25%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,13 +2173,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>1,087</v>
+        <v>1,139</v>
       </c>
       <c r="F41" t="str">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G41" t="str">
-        <v>1,995</v>
+        <v>2,082</v>
       </c>
       <c r="H41" t="str">
         <v>41</v>
@@ -2188,19 +2188,19 @@
         <v>483,021,812</v>
       </c>
       <c r="J41" t="str">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K41" t="str">
-        <v>447,503,665</v>
+        <v>466,800,436</v>
       </c>
       <c r="L41" t="str">
-        <v>10,659,300,883</v>
+        <v>11,246,172,027</v>
       </c>
       <c r="M41" t="str">
-        <v>1,534,336,073</v>
+        <v>1,574,321,300</v>
       </c>
       <c r="N41" t="str">
-        <v>14.39%</v>
+        <v>14.00%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>5,735</v>
+        <v>5,889</v>
       </c>
       <c r="F42" t="str">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="G42" t="str">
-        <v>7,088</v>
+        <v>7,386</v>
       </c>
       <c r="H42" t="str">
         <v>3</v>
@@ -2238,13 +2238,13 @@
         <v>84,725,256</v>
       </c>
       <c r="L42" t="str">
-        <v>14,121,259,534</v>
+        <v>14,558,706,075</v>
       </c>
       <c r="M42" t="str">
-        <v>451,912,601</v>
+        <v>463,683,765</v>
       </c>
       <c r="N42" t="str">
-        <v>3.20%</v>
+        <v>3.18%</v>
       </c>
     </row>
     <row r="43">
@@ -2305,13 +2305,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>1,478</v>
+        <v>1,566</v>
       </c>
       <c r="F44" t="str">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G44" t="str">
-        <v>1,473</v>
+        <v>1,555</v>
       </c>
       <c r="H44" t="str">
         <v>2</v>
@@ -2326,13 +2326,13 @@
         <v>50,770,592</v>
       </c>
       <c r="L44" t="str">
-        <v>3,232,853,200</v>
+        <v>3,442,985,016</v>
       </c>
       <c r="M44" t="str">
-        <v>154,941,936</v>
+        <v>158,775,686</v>
       </c>
       <c r="N44" t="str">
-        <v>4.79%</v>
+        <v>4.61%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,13 +2349,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>989</v>
+        <v>1,033</v>
       </c>
       <c r="F45" t="str">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G45" t="str">
-        <v>1,504</v>
+        <v>1,577</v>
       </c>
       <c r="H45" t="str">
         <v>0</v>
@@ -2370,13 +2370,13 @@
         <v>66,445,865</v>
       </c>
       <c r="L45" t="str">
-        <v>2,505,092,921</v>
+        <v>2,570,286,149</v>
       </c>
       <c r="M45" t="str">
-        <v>97,525,517</v>
+        <v>102,766,285</v>
       </c>
       <c r="N45" t="str">
-        <v>3.89%</v>
+        <v>4.00%</v>
       </c>
     </row>
     <row r="46">
@@ -2393,13 +2393,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E46" t="str">
-        <v>3,962</v>
+        <v>4,138</v>
       </c>
       <c r="F46" t="str">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="G46" t="str">
-        <v>6,243</v>
+        <v>6,482</v>
       </c>
       <c r="H46" t="str">
         <v>11</v>
@@ -2408,19 +2408,19 @@
         <v>135,065,374</v>
       </c>
       <c r="J46" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K46" t="str">
-        <v>19,064,856</v>
+        <v>39,032,955</v>
       </c>
       <c r="L46" t="str">
-        <v>9,735,898,303</v>
+        <v>10,063,309,479</v>
       </c>
       <c r="M46" t="str">
-        <v>489,890,846</v>
+        <v>516,074,816</v>
       </c>
       <c r="N46" t="str">
-        <v>5.03%</v>
+        <v>5.13%</v>
       </c>
     </row>
     <row r="47">
@@ -2437,13 +2437,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E47" t="str">
-        <v>3,784</v>
+        <v>4,137</v>
       </c>
       <c r="F47" t="str">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="G47" t="str">
-        <v>3,681</v>
+        <v>3,884</v>
       </c>
       <c r="H47" t="str">
         <v>4</v>
@@ -2458,13 +2458,13 @@
         <v>54,162,704</v>
       </c>
       <c r="L47" t="str">
-        <v>9,043,419,900</v>
+        <v>9,751,114,990</v>
       </c>
       <c r="M47" t="str">
-        <v>296,597,871</v>
+        <v>302,487,543</v>
       </c>
       <c r="N47" t="str">
-        <v>3.28%</v>
+        <v>3.10%</v>
       </c>
     </row>
     <row r="48">
@@ -2481,13 +2481,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E48" t="str">
-        <v>3,471</v>
+        <v>3,625</v>
       </c>
       <c r="F48" t="str">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="G48" t="str">
-        <v>5,178</v>
+        <v>5,388</v>
       </c>
       <c r="H48" t="str">
         <v>5</v>
@@ -2496,19 +2496,19 @@
         <v>60,689,995</v>
       </c>
       <c r="J48" t="str">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K48" t="str">
-        <v>134,571,733</v>
+        <v>151,841,920</v>
       </c>
       <c r="L48" t="str">
-        <v>8,122,246,466</v>
+        <v>8,417,884,746</v>
       </c>
       <c r="M48" t="str">
-        <v>515,967,644</v>
+        <v>545,935,317</v>
       </c>
       <c r="N48" t="str">
-        <v>6.35%</v>
+        <v>6.49%</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata/Bulanan/10. Okt-LD.xlsx
+++ b/rawdata/Bulanan/10. Okt-LD.xlsx
@@ -457,34 +457,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>9,606</v>
+        <v>9,945</v>
       </c>
       <c r="F2" t="str">
-        <v>4,718</v>
+        <v>4,868</v>
       </c>
       <c r="G2" t="str">
-        <v>1,304</v>
+        <v>1,352</v>
       </c>
       <c r="H2" t="str">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I2" t="str">
-        <v>2,839,497,051</v>
+        <v>2,910,226,099</v>
       </c>
       <c r="J2" t="str">
-        <v>512</v>
+        <v>541</v>
       </c>
       <c r="K2" t="str">
-        <v>10,101,508,890</v>
+        <v>10,647,935,074</v>
       </c>
       <c r="L2" t="str">
-        <v>35,633,873,927</v>
+        <v>36,954,256,586</v>
       </c>
       <c r="M2" t="str">
-        <v>19,861,253,811</v>
+        <v>20,611,510,819</v>
       </c>
       <c r="N2" t="str">
-        <v>55.74%</v>
+        <v>55.78%</v>
       </c>
     </row>
     <row r="3">
@@ -501,34 +501,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>14,596</v>
+        <v>15,127</v>
       </c>
       <c r="F3" t="str">
-        <v>2,063</v>
+        <v>2,132</v>
       </c>
       <c r="G3" t="str">
-        <v>2,295</v>
+        <v>2,415</v>
       </c>
       <c r="H3" t="str">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I3" t="str">
-        <v>1,765,562,423</v>
+        <v>1,871,363,851</v>
       </c>
       <c r="J3" t="str">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="K3" t="str">
-        <v>5,748,124,031</v>
+        <v>6,128,629,430</v>
       </c>
       <c r="L3" t="str">
-        <v>59,598,684,724</v>
+        <v>62,322,614,117</v>
       </c>
       <c r="M3" t="str">
-        <v>10,343,027,135</v>
+        <v>10,847,545,022</v>
       </c>
       <c r="N3" t="str">
-        <v>17.35%</v>
+        <v>17.41%</v>
       </c>
     </row>
     <row r="4">
@@ -545,34 +545,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>2,899</v>
+        <v>3,013</v>
       </c>
       <c r="F4" t="str">
-        <v>1,334</v>
+        <v>1,387</v>
       </c>
       <c r="G4" t="str">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="H4" t="str">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I4" t="str">
-        <v>909,752,299</v>
+        <v>937,702,810</v>
       </c>
       <c r="J4" t="str">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="K4" t="str">
-        <v>3,203,149,540</v>
+        <v>3,255,838,430</v>
       </c>
       <c r="L4" t="str">
-        <v>10,781,895,404</v>
+        <v>11,180,975,963</v>
       </c>
       <c r="M4" t="str">
-        <v>6,204,351,094</v>
+        <v>6,399,444,839</v>
       </c>
       <c r="N4" t="str">
-        <v>57.54%</v>
+        <v>57.24%</v>
       </c>
     </row>
     <row r="5">
@@ -589,10 +589,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>5,362</v>
+        <v>5,615</v>
       </c>
       <c r="F5" t="str">
-        <v>1,257</v>
+        <v>1,304</v>
       </c>
       <c r="G5" t="str">
         <v>27</v>
@@ -610,13 +610,13 @@
         <v>38,695,454</v>
       </c>
       <c r="L5" t="str">
-        <v>6,378,213,490</v>
+        <v>6,641,532,781</v>
       </c>
       <c r="M5" t="str">
-        <v>2,239,448,474</v>
+        <v>2,306,444,330</v>
       </c>
       <c r="N5" t="str">
-        <v>35.11%</v>
+        <v>34.73%</v>
       </c>
     </row>
     <row r="6">
@@ -633,13 +633,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>24,087</v>
+        <v>25,082</v>
       </c>
       <c r="F6" t="str">
-        <v>5,673</v>
+        <v>5,892</v>
       </c>
       <c r="G6" t="str">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H6" t="str">
         <v>12</v>
@@ -654,10 +654,10 @@
         <v>101,641,843</v>
       </c>
       <c r="L6" t="str">
-        <v>28,854,656,197</v>
+        <v>29,867,305,408</v>
       </c>
       <c r="M6" t="str">
-        <v>8,827,737,528</v>
+        <v>9,136,187,683</v>
       </c>
       <c r="N6" t="str">
         <v>30.59%</v>
@@ -677,10 +677,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>179</v>
+        <v>279</v>
       </c>
       <c r="F7" t="str">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="G7" t="str">
         <v>0</v>
@@ -698,13 +698,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="str">
-        <v>156,881,804</v>
+        <v>249,343,192</v>
       </c>
       <c r="M7" t="str">
-        <v>39,083,169</v>
+        <v>63,755,445</v>
       </c>
       <c r="N7" t="str">
-        <v>24.91%</v>
+        <v>25.57%</v>
       </c>
     </row>
     <row r="8">
@@ -721,34 +721,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>7,185</v>
+        <v>7,467</v>
       </c>
       <c r="F8" t="str">
-        <v>3,411</v>
+        <v>3,521</v>
       </c>
       <c r="G8" t="str">
-        <v>4,920</v>
+        <v>5,122</v>
       </c>
       <c r="H8" t="str">
-        <v>1,008</v>
+        <v>1,041</v>
       </c>
       <c r="I8" t="str">
-        <v>12,173,421,385</v>
+        <v>12,579,304,545</v>
       </c>
       <c r="J8" t="str">
-        <v>714</v>
+        <v>725</v>
       </c>
       <c r="K8" t="str">
-        <v>14,899,482,887</v>
+        <v>15,119,184,025</v>
       </c>
       <c r="L8" t="str">
-        <v>82,043,315,773</v>
+        <v>85,292,422,368</v>
       </c>
       <c r="M8" t="str">
-        <v>36,265,224,848</v>
+        <v>37,256,976,218</v>
       </c>
       <c r="N8" t="str">
-        <v>44.20%</v>
+        <v>43.68%</v>
       </c>
     </row>
     <row r="9">
@@ -765,13 +765,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>2,330</v>
+        <v>2,481</v>
       </c>
       <c r="F9" t="str">
-        <v>475</v>
+        <v>509</v>
       </c>
       <c r="G9" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H9" t="str">
         <v>0</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="str">
-        <v>2,945,515,629</v>
+        <v>3,111,639,053</v>
       </c>
       <c r="M9" t="str">
-        <v>815,333,232</v>
+        <v>862,809,658</v>
       </c>
       <c r="N9" t="str">
-        <v>27.68%</v>
+        <v>27.73%</v>
       </c>
     </row>
     <row r="10">
@@ -809,13 +809,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>3,267</v>
+        <v>3,366</v>
       </c>
       <c r="F10" t="str">
         <v>71</v>
       </c>
       <c r="G10" t="str">
-        <v>7,817</v>
+        <v>8,100</v>
       </c>
       <c r="H10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>100,379,570</v>
       </c>
       <c r="L10" t="str">
-        <v>9,303,331,014</v>
+        <v>9,551,267,908</v>
       </c>
       <c r="M10" t="str">
         <v>127,704,577</v>
       </c>
       <c r="N10" t="str">
-        <v>1.37%</v>
+        <v>1.34%</v>
       </c>
     </row>
     <row r="11">
@@ -853,19 +853,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>2,723</v>
+        <v>2,805</v>
       </c>
       <c r="F11" t="str">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" t="str">
-        <v>5,529</v>
+        <v>5,749</v>
       </c>
       <c r="H11" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="str">
-        <v>0</v>
+        <v>23,416,014</v>
       </c>
       <c r="J11" t="str">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="str">
-        <v>7,803,958,175</v>
+        <v>8,083,430,350</v>
       </c>
       <c r="M11" t="str">
-        <v>102,927,588</v>
+        <v>112,482,141</v>
       </c>
       <c r="N11" t="str">
-        <v>1.32%</v>
+        <v>1.39%</v>
       </c>
     </row>
     <row r="12">
@@ -897,13 +897,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>3,421</v>
+        <v>3,544</v>
       </c>
       <c r="F12" t="str">
         <v>113</v>
       </c>
       <c r="G12" t="str">
-        <v>9,917</v>
+        <v>10,340</v>
       </c>
       <c r="H12" t="str">
         <v>0</v>
@@ -918,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>12,860,505,090</v>
+        <v>13,358,952,100</v>
       </c>
       <c r="M12" t="str">
         <v>123,023,773</v>
       </c>
       <c r="N12" t="str">
-        <v>0.96%</v>
+        <v>0.92%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>2,127</v>
+        <v>2,204</v>
       </c>
       <c r="F13" t="str">
         <v>60</v>
       </c>
       <c r="G13" t="str">
-        <v>6,825</v>
+        <v>7,105</v>
       </c>
       <c r="H13" t="str">
         <v>3</v>
@@ -962,13 +962,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="str">
-        <v>8,005,638,963</v>
+        <v>8,222,765,594</v>
       </c>
       <c r="M13" t="str">
         <v>229,484,515</v>
       </c>
       <c r="N13" t="str">
-        <v>2.87%</v>
+        <v>2.79%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>1,107</v>
+        <v>1,137</v>
       </c>
       <c r="F14" t="str">
         <v>28</v>
       </c>
       <c r="G14" t="str">
-        <v>3,669</v>
+        <v>3,798</v>
       </c>
       <c r="H14" t="str">
         <v>1</v>
@@ -1006,13 +1006,13 @@
         <v>35,694,915</v>
       </c>
       <c r="L14" t="str">
-        <v>4,210,889,685</v>
+        <v>4,307,233,316</v>
       </c>
       <c r="M14" t="str">
         <v>97,506,596</v>
       </c>
       <c r="N14" t="str">
-        <v>2.32%</v>
+        <v>2.26%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>3,002</v>
+        <v>3,109</v>
       </c>
       <c r="F15" t="str">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G15" t="str">
-        <v>9,243</v>
+        <v>9,620</v>
       </c>
       <c r="H15" t="str">
         <v>1</v>
@@ -1050,13 +1050,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="str">
-        <v>11,284,576,089</v>
+        <v>11,638,130,074</v>
       </c>
       <c r="M15" t="str">
-        <v>176,378,343</v>
+        <v>178,103,693</v>
       </c>
       <c r="N15" t="str">
-        <v>1.56%</v>
+        <v>1.53%</v>
       </c>
     </row>
     <row r="16">
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>4,366</v>
+        <v>4,557</v>
       </c>
       <c r="F16" t="str">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G16" t="str">
-        <v>12,909</v>
+        <v>13,423</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,10 +1094,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>16,801,114,190</v>
+        <v>17,617,320,826</v>
       </c>
       <c r="M16" t="str">
-        <v>82,196,516</v>
+        <v>85,507,028</v>
       </c>
       <c r="N16" t="str">
         <v>0.49%</v>
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>1,978</v>
+        <v>2,076</v>
       </c>
       <c r="F17" t="str">
         <v>29</v>
       </c>
       <c r="G17" t="str">
-        <v>4,870</v>
+        <v>5,081</v>
       </c>
       <c r="H17" t="str">
         <v>0</v>
@@ -1138,13 +1138,13 @@
         <v>233,859,144</v>
       </c>
       <c r="L17" t="str">
-        <v>6,878,785,699</v>
+        <v>7,206,046,666</v>
       </c>
       <c r="M17" t="str">
         <v>155,308,733</v>
       </c>
       <c r="N17" t="str">
-        <v>2.26%</v>
+        <v>2.16%</v>
       </c>
     </row>
     <row r="18">
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>2,473</v>
+        <v>2,597</v>
       </c>
       <c r="F18" t="str">
         <v>33</v>
       </c>
       <c r="G18" t="str">
-        <v>5,660</v>
+        <v>5,902</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>100,898,460</v>
       </c>
       <c r="L18" t="str">
-        <v>8,250,497,948</v>
+        <v>8,649,303,929</v>
       </c>
       <c r="M18" t="str">
         <v>110,870,539</v>
       </c>
       <c r="N18" t="str">
-        <v>1.34%</v>
+        <v>1.28%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>3,577</v>
+        <v>3,716</v>
       </c>
       <c r="F19" t="str">
         <v>68</v>
       </c>
       <c r="G19" t="str">
-        <v>13,005</v>
+        <v>13,537</v>
       </c>
       <c r="H19" t="str">
         <v>1</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>15,725,368,781</v>
+        <v>16,351,952,155</v>
       </c>
       <c r="M19" t="str">
         <v>125,057,824</v>
       </c>
       <c r="N19" t="str">
-        <v>0.80%</v>
+        <v>0.76%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>597</v>
+        <v>620</v>
       </c>
       <c r="F20" t="str">
         <v>4</v>
       </c>
       <c r="G20" t="str">
-        <v>2,138</v>
+        <v>2,217</v>
       </c>
       <c r="H20" t="str">
         <v>0</v>
@@ -1270,13 +1270,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="str">
-        <v>2,561,174,608</v>
+        <v>2,662,011,106</v>
       </c>
       <c r="M20" t="str">
         <v>11,695,275</v>
       </c>
       <c r="N20" t="str">
-        <v>0.46%</v>
+        <v>0.44%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>4,176</v>
+        <v>4,340</v>
       </c>
       <c r="F21" t="str">
         <v>43</v>
       </c>
       <c r="G21" t="str">
-        <v>14,691</v>
+        <v>15,267</v>
       </c>
       <c r="H21" t="str">
         <v>1</v>
@@ -1314,13 +1314,13 @@
         <v>0</v>
       </c>
       <c r="L21" t="str">
-        <v>18,024,106,393</v>
+        <v>18,651,971,123</v>
       </c>
       <c r="M21" t="str">
         <v>136,401,325</v>
       </c>
       <c r="N21" t="str">
-        <v>0.76%</v>
+        <v>0.73%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,13 +1337,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>23,259</v>
+        <v>23,515</v>
       </c>
       <c r="F22" t="str">
-        <v>931</v>
+        <v>950</v>
       </c>
       <c r="G22" t="str">
-        <v>577,154</v>
+        <v>601,496</v>
       </c>
       <c r="H22" t="str">
         <v>6</v>
@@ -1358,13 +1358,13 @@
         <v>263,912,728</v>
       </c>
       <c r="L22" t="str">
-        <v>102,107,518,595</v>
+        <v>102,889,161,404</v>
       </c>
       <c r="M22" t="str">
-        <v>2,407,881,089</v>
+        <v>2,456,859,262</v>
       </c>
       <c r="N22" t="str">
-        <v>2.36%</v>
+        <v>2.39%</v>
       </c>
     </row>
     <row r="23">
@@ -1381,13 +1381,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E23" t="str">
-        <v>1,208</v>
+        <v>1,209</v>
       </c>
       <c r="F23" t="str">
         <v>4</v>
       </c>
       <c r="G23" t="str">
-        <v>12,835</v>
+        <v>13,370</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -1402,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="str">
-        <v>13,269,462,926</v>
+        <v>13,270,209,708</v>
       </c>
       <c r="M23" t="str">
         <v>13,240,251</v>
@@ -1425,34 +1425,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>42,050</v>
+        <v>43,593</v>
       </c>
       <c r="F24" t="str">
-        <v>1,917</v>
+        <v>1,970</v>
       </c>
       <c r="G24" t="str">
-        <v>3,717</v>
+        <v>3,825</v>
       </c>
       <c r="H24" t="str">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="I24" t="str">
-        <v>3,402,808,002</v>
+        <v>3,434,386,767</v>
       </c>
       <c r="J24" t="str">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="K24" t="str">
-        <v>4,080,462,956</v>
+        <v>4,210,434,094</v>
       </c>
       <c r="L24" t="str">
-        <v>135,028,741,679</v>
+        <v>138,985,535,584</v>
       </c>
       <c r="M24" t="str">
-        <v>10,918,949,537</v>
+        <v>11,142,586,538</v>
       </c>
       <c r="N24" t="str">
-        <v>8.09%</v>
+        <v>8.02%</v>
       </c>
     </row>
     <row r="25">
@@ -1469,34 +1469,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E25" t="str">
-        <v>1,942</v>
+        <v>2,018</v>
       </c>
       <c r="F25" t="str">
-        <v>617</v>
+        <v>642</v>
       </c>
       <c r="G25" t="str">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H25" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I25" t="str">
-        <v>96,043,207</v>
+        <v>118,450,419</v>
       </c>
       <c r="J25" t="str">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K25" t="str">
-        <v>413,967,834</v>
+        <v>450,048,488</v>
       </c>
       <c r="L25" t="str">
-        <v>4,965,425,551</v>
+        <v>5,161,980,914</v>
       </c>
       <c r="M25" t="str">
-        <v>1,335,785,789</v>
+        <v>1,399,597,342</v>
       </c>
       <c r="N25" t="str">
-        <v>26.90%</v>
+        <v>27.11%</v>
       </c>
     </row>
     <row r="26">
@@ -1513,13 +1513,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>4,535</v>
+        <v>4,663</v>
       </c>
       <c r="F26" t="str">
-        <v>1,382</v>
+        <v>1,410</v>
       </c>
       <c r="G26" t="str">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="H26" t="str">
         <v>35</v>
@@ -1528,19 +1528,19 @@
         <v>444,247,055</v>
       </c>
       <c r="J26" t="str">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K26" t="str">
-        <v>683,635,289</v>
+        <v>704,191,775</v>
       </c>
       <c r="L26" t="str">
-        <v>11,641,965,174</v>
+        <v>11,949,703,459</v>
       </c>
       <c r="M26" t="str">
-        <v>2,947,178,900</v>
+        <v>3,005,614,040</v>
       </c>
       <c r="N26" t="str">
-        <v>25.32%</v>
+        <v>25.15%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,10 +1557,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>2,043</v>
+        <v>2,136</v>
       </c>
       <c r="F27" t="str">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="G27" t="str">
         <v>0</v>
@@ -1578,13 +1578,13 @@
         <v>0</v>
       </c>
       <c r="L27" t="str">
-        <v>2,173,530,010</v>
+        <v>2,248,471,473</v>
       </c>
       <c r="M27" t="str">
-        <v>500,139,020</v>
+        <v>511,822,983</v>
       </c>
       <c r="N27" t="str">
-        <v>23.01%</v>
+        <v>22.76%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,10 +1601,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>17,537</v>
+        <v>18,338</v>
       </c>
       <c r="F28" t="str">
-        <v>3,041</v>
+        <v>3,155</v>
       </c>
       <c r="G28" t="str">
         <v>1</v>
@@ -1622,13 +1622,13 @@
         <v>0</v>
       </c>
       <c r="L28" t="str">
-        <v>18,629,302,319</v>
+        <v>19,352,306,013</v>
       </c>
       <c r="M28" t="str">
-        <v>3,618,619,686</v>
+        <v>3,764,119,900</v>
       </c>
       <c r="N28" t="str">
-        <v>19.42%</v>
+        <v>19.45%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,10 +1645,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="F29" t="str">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="G29" t="str">
         <v>0</v>
@@ -1666,13 +1666,13 @@
         <v>0</v>
       </c>
       <c r="L29" t="str">
-        <v>60,575,456</v>
+        <v>115,759,662</v>
       </c>
       <c r="M29" t="str">
-        <v>11,010,476</v>
+        <v>18,943,900</v>
       </c>
       <c r="N29" t="str">
-        <v>18.18%</v>
+        <v>16.36%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,34 +1689,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>3,691</v>
+        <v>3,816</v>
       </c>
       <c r="F30" t="str">
-        <v>1,230</v>
+        <v>1,257</v>
       </c>
       <c r="G30" t="str">
-        <v>1,386</v>
+        <v>1,428</v>
       </c>
       <c r="H30" t="str">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I30" t="str">
-        <v>3,173,522,777</v>
+        <v>3,197,428,897</v>
       </c>
       <c r="J30" t="str">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K30" t="str">
-        <v>3,408,540,316</v>
+        <v>3,472,227,994</v>
       </c>
       <c r="L30" t="str">
-        <v>39,341,017,096</v>
+        <v>40,675,041,373</v>
       </c>
       <c r="M30" t="str">
-        <v>11,032,854,341</v>
+        <v>11,243,509,733</v>
       </c>
       <c r="N30" t="str">
-        <v>28.04%</v>
+        <v>27.64%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,10 +1733,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>3,270</v>
+        <v>3,424</v>
       </c>
       <c r="F31" t="str">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1754,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>3,593,869,191</v>
+        <v>3,733,640,131</v>
       </c>
       <c r="M31" t="str">
-        <v>707,851,892</v>
+        <v>747,287,699</v>
       </c>
       <c r="N31" t="str">
-        <v>19.70%</v>
+        <v>20.01%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,13 +1777,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>3,975</v>
+        <v>4,072</v>
       </c>
       <c r="F32" t="str">
-        <v>627</v>
+        <v>645</v>
       </c>
       <c r="G32" t="str">
-        <v>1,822</v>
+        <v>1,875</v>
       </c>
       <c r="H32" t="str">
         <v>9</v>
@@ -1798,13 +1798,13 @@
         <v>102,003,250</v>
       </c>
       <c r="L32" t="str">
-        <v>10,638,945,563</v>
+        <v>10,900,288,137</v>
       </c>
       <c r="M32" t="str">
-        <v>1,025,474,037</v>
+        <v>1,053,755,126</v>
       </c>
       <c r="N32" t="str">
-        <v>9.64%</v>
+        <v>9.67%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,13 +1821,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>1,237</v>
+        <v>1,276</v>
       </c>
       <c r="F33" t="str">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="G33" t="str">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="H33" t="str">
         <v>5</v>
@@ -1842,13 +1842,13 @@
         <v>47,809,288</v>
       </c>
       <c r="L33" t="str">
-        <v>3,054,119,914</v>
+        <v>3,127,931,719</v>
       </c>
       <c r="M33" t="str">
-        <v>467,571,598</v>
+        <v>479,997,985</v>
       </c>
       <c r="N33" t="str">
-        <v>15.31%</v>
+        <v>15.35%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,10 +1865,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>2,802</v>
+        <v>2,912</v>
       </c>
       <c r="F34" t="str">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="G34" t="str">
         <v>96</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>2,981,591,180</v>
+        <v>3,083,599,871</v>
       </c>
       <c r="M34" t="str">
-        <v>479,450,073</v>
+        <v>492,155,395</v>
       </c>
       <c r="N34" t="str">
-        <v>16.08%</v>
+        <v>15.96%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,13 +1909,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>8,791</v>
+        <v>9,255</v>
       </c>
       <c r="F35" t="str">
-        <v>933</v>
+        <v>988</v>
       </c>
       <c r="G35" t="str">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H35" t="str">
         <v>4</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="L35" t="str">
-        <v>9,496,439,883</v>
+        <v>9,880,022,403</v>
       </c>
       <c r="M35" t="str">
-        <v>1,130,007,449</v>
+        <v>1,166,427,750</v>
       </c>
       <c r="N35" t="str">
-        <v>11.90%</v>
+        <v>11.81%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,10 +1953,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="F36" t="str">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G36" t="str">
         <v>0</v>
@@ -1974,13 +1974,13 @@
         <v>0</v>
       </c>
       <c r="L36" t="str">
-        <v>54,062,418</v>
+        <v>81,988,404</v>
       </c>
       <c r="M36" t="str">
-        <v>11,606,597</v>
+        <v>13,305,071</v>
       </c>
       <c r="N36" t="str">
-        <v>21.47%</v>
+        <v>16.23%</v>
       </c>
     </row>
     <row r="37">
@@ -1997,34 +1997,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>1,348</v>
+        <v>1,406</v>
       </c>
       <c r="F37" t="str">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="G37" t="str">
-        <v>2,229</v>
+        <v>2,328</v>
       </c>
       <c r="H37" t="str">
+        <v>56</v>
+      </c>
+      <c r="I37" t="str">
+        <v>668,569,648</v>
+      </c>
+      <c r="J37" t="str">
         <v>53</v>
       </c>
-      <c r="I37" t="str">
-        <v>633,173,453</v>
-      </c>
-      <c r="J37" t="str">
-        <v>49</v>
-      </c>
       <c r="K37" t="str">
-        <v>947,968,275</v>
+        <v>1,028,707,979</v>
       </c>
       <c r="L37" t="str">
-        <v>13,609,053,171</v>
+        <v>14,288,757,782</v>
       </c>
       <c r="M37" t="str">
-        <v>2,503,298,598</v>
+        <v>2,658,305,752</v>
       </c>
       <c r="N37" t="str">
-        <v>18.39%</v>
+        <v>18.60%</v>
       </c>
     </row>
     <row r="38">
@@ -2041,13 +2041,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>4,370</v>
+        <v>4,504</v>
       </c>
       <c r="F38" t="str">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="G38" t="str">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H38" t="str">
         <v>3</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>4,719,809,606</v>
+        <v>4,838,905,828</v>
       </c>
       <c r="M38" t="str">
-        <v>491,415,261</v>
+        <v>500,765,143</v>
       </c>
       <c r="N38" t="str">
-        <v>10.41%</v>
+        <v>10.35%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,13 +2085,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>2,972</v>
+        <v>3,138</v>
       </c>
       <c r="F39" t="str">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="G39" t="str">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H39" t="str">
         <v>0</v>
@@ -2106,13 +2106,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>3,094,651,673</v>
+        <v>3,230,553,106</v>
       </c>
       <c r="M39" t="str">
-        <v>317,298,446</v>
+        <v>324,399,356</v>
       </c>
       <c r="N39" t="str">
-        <v>10.25%</v>
+        <v>10.04%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,19 +2173,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>1,139</v>
+        <v>1,192</v>
       </c>
       <c r="F41" t="str">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="G41" t="str">
-        <v>2,082</v>
+        <v>2,174</v>
       </c>
       <c r="H41" t="str">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I41" t="str">
-        <v>483,021,812</v>
+        <v>495,111,662</v>
       </c>
       <c r="J41" t="str">
         <v>24</v>
@@ -2194,13 +2194,13 @@
         <v>466,800,436</v>
       </c>
       <c r="L41" t="str">
-        <v>11,246,172,027</v>
+        <v>11,817,140,683</v>
       </c>
       <c r="M41" t="str">
-        <v>1,574,321,300</v>
+        <v>1,626,399,686</v>
       </c>
       <c r="N41" t="str">
-        <v>14.00%</v>
+        <v>13.76%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>5,889</v>
+        <v>6,055</v>
       </c>
       <c r="F42" t="str">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="G42" t="str">
-        <v>7,386</v>
+        <v>7,693</v>
       </c>
       <c r="H42" t="str">
         <v>3</v>
@@ -2238,10 +2238,10 @@
         <v>84,725,256</v>
       </c>
       <c r="L42" t="str">
-        <v>14,558,706,075</v>
+        <v>15,035,026,555</v>
       </c>
       <c r="M42" t="str">
-        <v>463,683,765</v>
+        <v>477,415,281</v>
       </c>
       <c r="N42" t="str">
         <v>3.18%</v>
@@ -2305,13 +2305,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>1,566</v>
+        <v>1,662</v>
       </c>
       <c r="F44" t="str">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G44" t="str">
-        <v>1,555</v>
+        <v>1,639</v>
       </c>
       <c r="H44" t="str">
         <v>2</v>
@@ -2326,13 +2326,13 @@
         <v>50,770,592</v>
       </c>
       <c r="L44" t="str">
-        <v>3,442,985,016</v>
+        <v>3,676,906,981</v>
       </c>
       <c r="M44" t="str">
-        <v>158,775,686</v>
+        <v>159,716,954</v>
       </c>
       <c r="N44" t="str">
-        <v>4.61%</v>
+        <v>4.34%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,13 +2349,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>1,033</v>
+        <v>1,081</v>
       </c>
       <c r="F45" t="str">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G45" t="str">
-        <v>1,577</v>
+        <v>1,651</v>
       </c>
       <c r="H45" t="str">
         <v>0</v>
@@ -2370,13 +2370,13 @@
         <v>66,445,865</v>
       </c>
       <c r="L45" t="str">
-        <v>2,570,286,149</v>
+        <v>2,659,307,297</v>
       </c>
       <c r="M45" t="str">
-        <v>102,766,285</v>
+        <v>103,484,997</v>
       </c>
       <c r="N45" t="str">
-        <v>4.00%</v>
+        <v>3.89%</v>
       </c>
     </row>
     <row r="46">
@@ -2393,13 +2393,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E46" t="str">
-        <v>4,138</v>
+        <v>4,332</v>
       </c>
       <c r="F46" t="str">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G46" t="str">
-        <v>6,482</v>
+        <v>6,713</v>
       </c>
       <c r="H46" t="str">
         <v>11</v>
@@ -2414,13 +2414,13 @@
         <v>39,032,955</v>
       </c>
       <c r="L46" t="str">
-        <v>10,063,309,479</v>
+        <v>10,326,210,108</v>
       </c>
       <c r="M46" t="str">
-        <v>516,074,816</v>
+        <v>518,913,077</v>
       </c>
       <c r="N46" t="str">
-        <v>5.13%</v>
+        <v>5.03%</v>
       </c>
     </row>
     <row r="47">
@@ -2437,13 +2437,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E47" t="str">
-        <v>4,137</v>
+        <v>4,525</v>
       </c>
       <c r="F47" t="str">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G47" t="str">
-        <v>3,884</v>
+        <v>4,105</v>
       </c>
       <c r="H47" t="str">
         <v>4</v>
@@ -2458,13 +2458,13 @@
         <v>54,162,704</v>
       </c>
       <c r="L47" t="str">
-        <v>9,751,114,990</v>
+        <v>10,555,394,411</v>
       </c>
       <c r="M47" t="str">
-        <v>302,487,543</v>
+        <v>312,475,061</v>
       </c>
       <c r="N47" t="str">
-        <v>3.10%</v>
+        <v>2.96%</v>
       </c>
     </row>
     <row r="48">
@@ -2481,13 +2481,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E48" t="str">
-        <v>3,625</v>
+        <v>3,793</v>
       </c>
       <c r="F48" t="str">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G48" t="str">
-        <v>5,388</v>
+        <v>5,598</v>
       </c>
       <c r="H48" t="str">
         <v>5</v>
@@ -2502,13 +2502,13 @@
         <v>151,841,920</v>
       </c>
       <c r="L48" t="str">
-        <v>8,417,884,746</v>
+        <v>8,775,265,667</v>
       </c>
       <c r="M48" t="str">
-        <v>545,935,317</v>
+        <v>554,834,428</v>
       </c>
       <c r="N48" t="str">
-        <v>6.49%</v>
+        <v>6.32%</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata/Bulanan/10. Okt-LD.xlsx
+++ b/rawdata/Bulanan/10. Okt-LD.xlsx
@@ -457,34 +457,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>9,945</v>
+        <v>10,258</v>
       </c>
       <c r="F2" t="str">
-        <v>4,868</v>
+        <v>5,051</v>
       </c>
       <c r="G2" t="str">
-        <v>1,352</v>
+        <v>1,417</v>
       </c>
       <c r="H2" t="str">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="I2" t="str">
-        <v>2,910,226,099</v>
+        <v>3,018,755,220</v>
       </c>
       <c r="J2" t="str">
-        <v>541</v>
+        <v>573</v>
       </c>
       <c r="K2" t="str">
-        <v>10,647,935,074</v>
+        <v>11,273,846,791</v>
       </c>
       <c r="L2" t="str">
-        <v>36,954,256,586</v>
+        <v>38,450,434,282</v>
       </c>
       <c r="M2" t="str">
-        <v>20,611,510,819</v>
+        <v>21,572,258,787</v>
       </c>
       <c r="N2" t="str">
-        <v>55.78%</v>
+        <v>56.10%</v>
       </c>
     </row>
     <row r="3">
@@ -501,34 +501,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>15,127</v>
+        <v>15,711</v>
       </c>
       <c r="F3" t="str">
-        <v>2,132</v>
+        <v>2,219</v>
       </c>
       <c r="G3" t="str">
-        <v>2,415</v>
+        <v>2,513</v>
       </c>
       <c r="H3" t="str">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="I3" t="str">
-        <v>1,871,363,851</v>
+        <v>1,937,994,506</v>
       </c>
       <c r="J3" t="str">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="K3" t="str">
-        <v>6,128,629,430</v>
+        <v>6,420,605,807</v>
       </c>
       <c r="L3" t="str">
-        <v>62,322,614,117</v>
+        <v>64,837,754,060</v>
       </c>
       <c r="M3" t="str">
-        <v>10,847,545,022</v>
+        <v>11,351,538,863</v>
       </c>
       <c r="N3" t="str">
-        <v>17.41%</v>
+        <v>17.51%</v>
       </c>
     </row>
     <row r="4">
@@ -545,34 +545,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>3,013</v>
+        <v>3,153</v>
       </c>
       <c r="F4" t="str">
-        <v>1,387</v>
+        <v>1,452</v>
       </c>
       <c r="G4" t="str">
-        <v>413</v>
+        <v>439</v>
       </c>
       <c r="H4" t="str">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I4" t="str">
-        <v>937,702,810</v>
+        <v>963,073,693</v>
       </c>
       <c r="J4" t="str">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="K4" t="str">
-        <v>3,255,838,430</v>
+        <v>3,570,613,016</v>
       </c>
       <c r="L4" t="str">
-        <v>11,180,975,963</v>
+        <v>11,810,930,636</v>
       </c>
       <c r="M4" t="str">
-        <v>6,399,444,839</v>
+        <v>6,778,339,765</v>
       </c>
       <c r="N4" t="str">
-        <v>57.24%</v>
+        <v>57.39%</v>
       </c>
     </row>
     <row r="5">
@@ -589,10 +589,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>5,615</v>
+        <v>5,767</v>
       </c>
       <c r="F5" t="str">
-        <v>1,304</v>
+        <v>1,351</v>
       </c>
       <c r="G5" t="str">
         <v>27</v>
@@ -610,13 +610,13 @@
         <v>38,695,454</v>
       </c>
       <c r="L5" t="str">
-        <v>6,641,532,781</v>
+        <v>6,798,772,596</v>
       </c>
       <c r="M5" t="str">
-        <v>2,306,444,330</v>
+        <v>2,380,550,814</v>
       </c>
       <c r="N5" t="str">
-        <v>34.73%</v>
+        <v>35.01%</v>
       </c>
     </row>
     <row r="6">
@@ -633,10 +633,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>25,082</v>
+        <v>25,958</v>
       </c>
       <c r="F6" t="str">
-        <v>5,892</v>
+        <v>6,121</v>
       </c>
       <c r="G6" t="str">
         <v>99</v>
@@ -654,13 +654,13 @@
         <v>101,641,843</v>
       </c>
       <c r="L6" t="str">
-        <v>29,867,305,408</v>
+        <v>30,686,128,193</v>
       </c>
       <c r="M6" t="str">
-        <v>9,136,187,683</v>
+        <v>9,448,795,185</v>
       </c>
       <c r="N6" t="str">
-        <v>30.59%</v>
+        <v>30.79%</v>
       </c>
     </row>
     <row r="7">
@@ -677,10 +677,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>279</v>
+        <v>388</v>
       </c>
       <c r="F7" t="str">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="G7" t="str">
         <v>0</v>
@@ -698,13 +698,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="str">
-        <v>249,343,192</v>
+        <v>327,996,974</v>
       </c>
       <c r="M7" t="str">
-        <v>63,755,445</v>
+        <v>92,334,389</v>
       </c>
       <c r="N7" t="str">
-        <v>25.57%</v>
+        <v>28.15%</v>
       </c>
     </row>
     <row r="8">
@@ -721,34 +721,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>7,467</v>
+        <v>7,683</v>
       </c>
       <c r="F8" t="str">
-        <v>3,521</v>
+        <v>3,656</v>
       </c>
       <c r="G8" t="str">
-        <v>5,122</v>
+        <v>5,299</v>
       </c>
       <c r="H8" t="str">
-        <v>1,041</v>
+        <v>1,073</v>
       </c>
       <c r="I8" t="str">
-        <v>12,579,304,545</v>
+        <v>12,962,288,818</v>
       </c>
       <c r="J8" t="str">
-        <v>725</v>
+        <v>753</v>
       </c>
       <c r="K8" t="str">
-        <v>15,119,184,025</v>
+        <v>15,715,453,853</v>
       </c>
       <c r="L8" t="str">
-        <v>85,292,422,368</v>
+        <v>87,741,882,283</v>
       </c>
       <c r="M8" t="str">
-        <v>37,256,976,218</v>
+        <v>38,677,721,005</v>
       </c>
       <c r="N8" t="str">
-        <v>43.68%</v>
+        <v>44.08%</v>
       </c>
     </row>
     <row r="9">
@@ -765,10 +765,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>2,481</v>
+        <v>2,608</v>
       </c>
       <c r="F9" t="str">
-        <v>509</v>
+        <v>543</v>
       </c>
       <c r="G9" t="str">
         <v>4</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="str">
-        <v>3,111,639,053</v>
+        <v>3,231,408,548</v>
       </c>
       <c r="M9" t="str">
-        <v>862,809,658</v>
+        <v>905,795,875</v>
       </c>
       <c r="N9" t="str">
-        <v>27.73%</v>
+        <v>28.03%</v>
       </c>
     </row>
     <row r="10">
@@ -809,13 +809,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>3,366</v>
+        <v>3,473</v>
       </c>
       <c r="F10" t="str">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G10" t="str">
-        <v>8,100</v>
+        <v>8,382</v>
       </c>
       <c r="H10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>100,379,570</v>
       </c>
       <c r="L10" t="str">
-        <v>9,551,267,908</v>
+        <v>9,866,256,612</v>
       </c>
       <c r="M10" t="str">
-        <v>127,704,577</v>
+        <v>128,949,995</v>
       </c>
       <c r="N10" t="str">
-        <v>1.34%</v>
+        <v>1.31%</v>
       </c>
     </row>
     <row r="11">
@@ -853,13 +853,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>2,805</v>
+        <v>2,895</v>
       </c>
       <c r="F11" t="str">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G11" t="str">
-        <v>5,749</v>
+        <v>5,967</v>
       </c>
       <c r="H11" t="str">
         <v>2</v>
@@ -868,19 +868,19 @@
         <v>23,416,014</v>
       </c>
       <c r="J11" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" t="str">
-        <v>0</v>
+        <v>37,800,870</v>
       </c>
       <c r="L11" t="str">
-        <v>8,083,430,350</v>
+        <v>8,264,582,048</v>
       </c>
       <c r="M11" t="str">
-        <v>112,482,141</v>
+        <v>137,284,655</v>
       </c>
       <c r="N11" t="str">
-        <v>1.39%</v>
+        <v>1.66%</v>
       </c>
     </row>
     <row r="12">
@@ -897,13 +897,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>3,544</v>
+        <v>3,659</v>
       </c>
       <c r="F12" t="str">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G12" t="str">
-        <v>10,340</v>
+        <v>10,768</v>
       </c>
       <c r="H12" t="str">
         <v>0</v>
@@ -918,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="str">
-        <v>13,358,952,100</v>
+        <v>13,919,008,456</v>
       </c>
       <c r="M12" t="str">
-        <v>123,023,773</v>
+        <v>126,531,938</v>
       </c>
       <c r="N12" t="str">
-        <v>0.92%</v>
+        <v>0.91%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>2,204</v>
+        <v>2,277</v>
       </c>
       <c r="F13" t="str">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G13" t="str">
-        <v>7,105</v>
+        <v>7,388</v>
       </c>
       <c r="H13" t="str">
         <v>3</v>
@@ -962,13 +962,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="str">
-        <v>8,222,765,594</v>
+        <v>8,522,983,974</v>
       </c>
       <c r="M13" t="str">
-        <v>229,484,515</v>
+        <v>233,589,124</v>
       </c>
       <c r="N13" t="str">
-        <v>2.79%</v>
+        <v>2.74%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>1,137</v>
+        <v>1,167</v>
       </c>
       <c r="F14" t="str">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G14" t="str">
-        <v>3,798</v>
+        <v>3,925</v>
       </c>
       <c r="H14" t="str">
         <v>1</v>
@@ -1006,10 +1006,10 @@
         <v>35,694,915</v>
       </c>
       <c r="L14" t="str">
-        <v>4,307,233,316</v>
+        <v>4,385,988,806</v>
       </c>
       <c r="M14" t="str">
-        <v>97,506,596</v>
+        <v>99,157,583</v>
       </c>
       <c r="N14" t="str">
         <v>2.26%</v>
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>3,109</v>
+        <v>3,213</v>
       </c>
       <c r="F15" t="str">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G15" t="str">
-        <v>9,620</v>
+        <v>9,994</v>
       </c>
       <c r="H15" t="str">
         <v>1</v>
@@ -1050,13 +1050,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="str">
-        <v>11,638,130,074</v>
+        <v>11,977,506,745</v>
       </c>
       <c r="M15" t="str">
-        <v>178,103,693</v>
+        <v>188,044,232</v>
       </c>
       <c r="N15" t="str">
-        <v>1.53%</v>
+        <v>1.57%</v>
       </c>
     </row>
     <row r="16">
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>4,557</v>
+        <v>4,723</v>
       </c>
       <c r="F16" t="str">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G16" t="str">
-        <v>13,423</v>
+        <v>13,934</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>17,617,320,826</v>
+        <v>18,185,289,672</v>
       </c>
       <c r="M16" t="str">
-        <v>85,507,028</v>
+        <v>87,534,917</v>
       </c>
       <c r="N16" t="str">
-        <v>0.49%</v>
+        <v>0.48%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>2,076</v>
+        <v>2,153</v>
       </c>
       <c r="F17" t="str">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G17" t="str">
-        <v>5,081</v>
+        <v>5,289</v>
       </c>
       <c r="H17" t="str">
         <v>0</v>
@@ -1138,13 +1138,13 @@
         <v>233,859,144</v>
       </c>
       <c r="L17" t="str">
-        <v>7,206,046,666</v>
+        <v>7,409,208,878</v>
       </c>
       <c r="M17" t="str">
-        <v>155,308,733</v>
+        <v>180,557,351</v>
       </c>
       <c r="N17" t="str">
-        <v>2.16%</v>
+        <v>2.44%</v>
       </c>
     </row>
     <row r="18">
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>2,597</v>
+        <v>2,676</v>
       </c>
       <c r="F18" t="str">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G18" t="str">
-        <v>5,902</v>
+        <v>6,100</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>100,898,460</v>
       </c>
       <c r="L18" t="str">
-        <v>8,649,303,929</v>
+        <v>8,874,026,634</v>
       </c>
       <c r="M18" t="str">
-        <v>110,870,539</v>
+        <v>112,897,398</v>
       </c>
       <c r="N18" t="str">
-        <v>1.28%</v>
+        <v>1.27%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>3,716</v>
+        <v>3,848</v>
       </c>
       <c r="F19" t="str">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G19" t="str">
-        <v>13,537</v>
+        <v>14,078</v>
       </c>
       <c r="H19" t="str">
         <v>1</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>16,351,952,155</v>
+        <v>16,889,553,894</v>
       </c>
       <c r="M19" t="str">
-        <v>125,057,824</v>
+        <v>159,175,408</v>
       </c>
       <c r="N19" t="str">
-        <v>0.76%</v>
+        <v>0.94%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>620</v>
+        <v>642</v>
       </c>
       <c r="F20" t="str">
         <v>4</v>
       </c>
       <c r="G20" t="str">
-        <v>2,217</v>
+        <v>2,294</v>
       </c>
       <c r="H20" t="str">
         <v>0</v>
@@ -1270,13 +1270,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="str">
-        <v>2,662,011,106</v>
+        <v>2,722,063,137</v>
       </c>
       <c r="M20" t="str">
         <v>11,695,275</v>
       </c>
       <c r="N20" t="str">
-        <v>0.44%</v>
+        <v>0.43%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>4,340</v>
+        <v>4,494</v>
       </c>
       <c r="F21" t="str">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G21" t="str">
-        <v>15,267</v>
+        <v>15,848</v>
       </c>
       <c r="H21" t="str">
         <v>1</v>
@@ -1314,13 +1314,13 @@
         <v>0</v>
       </c>
       <c r="L21" t="str">
-        <v>18,651,971,123</v>
+        <v>19,389,653,151</v>
       </c>
       <c r="M21" t="str">
-        <v>136,401,325</v>
+        <v>146,011,843</v>
       </c>
       <c r="N21" t="str">
-        <v>0.73%</v>
+        <v>0.75%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,13 +1337,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>23,515</v>
+        <v>23,728</v>
       </c>
       <c r="F22" t="str">
-        <v>950</v>
+        <v>1,020</v>
       </c>
       <c r="G22" t="str">
-        <v>601,496</v>
+        <v>625,859</v>
       </c>
       <c r="H22" t="str">
         <v>6</v>
@@ -1358,13 +1358,13 @@
         <v>263,912,728</v>
       </c>
       <c r="L22" t="str">
-        <v>102,889,161,404</v>
+        <v>103,678,382,112</v>
       </c>
       <c r="M22" t="str">
-        <v>2,456,859,262</v>
+        <v>2,630,722,303</v>
       </c>
       <c r="N22" t="str">
-        <v>2.39%</v>
+        <v>2.54%</v>
       </c>
     </row>
     <row r="23">
@@ -1381,13 +1381,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E23" t="str">
-        <v>1,209</v>
+        <v>1,211</v>
       </c>
       <c r="F23" t="str">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G23" t="str">
-        <v>13,370</v>
+        <v>13,905</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="str">
-        <v>13,270,209,708</v>
+        <v>13,271,307,078</v>
       </c>
       <c r="M23" t="str">
-        <v>13,240,251</v>
+        <v>45,851,730</v>
       </c>
       <c r="N23" t="str">
-        <v>0.10%</v>
+        <v>0.35%</v>
       </c>
     </row>
     <row r="24">
@@ -1425,34 +1425,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>43,593</v>
+        <v>45,972</v>
       </c>
       <c r="F24" t="str">
-        <v>1,970</v>
+        <v>2,075</v>
       </c>
       <c r="G24" t="str">
-        <v>3,825</v>
+        <v>4,025</v>
       </c>
       <c r="H24" t="str">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="I24" t="str">
-        <v>3,434,386,767</v>
+        <v>3,572,484,304</v>
       </c>
       <c r="J24" t="str">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="K24" t="str">
-        <v>4,210,434,094</v>
+        <v>4,289,475,902</v>
       </c>
       <c r="L24" t="str">
-        <v>138,985,535,584</v>
+        <v>146,463,871,403</v>
       </c>
       <c r="M24" t="str">
-        <v>11,142,586,538</v>
+        <v>11,581,303,699</v>
       </c>
       <c r="N24" t="str">
-        <v>8.02%</v>
+        <v>7.91%</v>
       </c>
     </row>
     <row r="25">
@@ -1469,34 +1469,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E25" t="str">
-        <v>2,018</v>
+        <v>2,141</v>
       </c>
       <c r="F25" t="str">
-        <v>642</v>
+        <v>680</v>
       </c>
       <c r="G25" t="str">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="H25" t="str">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I25" t="str">
-        <v>118,450,419</v>
+        <v>144,285,555</v>
       </c>
       <c r="J25" t="str">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K25" t="str">
-        <v>450,048,488</v>
+        <v>467,753,326</v>
       </c>
       <c r="L25" t="str">
-        <v>5,161,980,914</v>
+        <v>5,481,361,556</v>
       </c>
       <c r="M25" t="str">
-        <v>1,399,597,342</v>
+        <v>1,495,087,404</v>
       </c>
       <c r="N25" t="str">
-        <v>27.11%</v>
+        <v>27.28%</v>
       </c>
     </row>
     <row r="26">
@@ -1513,34 +1513,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>4,663</v>
+        <v>4,785</v>
       </c>
       <c r="F26" t="str">
-        <v>1,410</v>
+        <v>1,447</v>
       </c>
       <c r="G26" t="str">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="H26" t="str">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I26" t="str">
-        <v>444,247,055</v>
+        <v>458,878,585</v>
       </c>
       <c r="J26" t="str">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K26" t="str">
-        <v>704,191,775</v>
+        <v>724,759,796</v>
       </c>
       <c r="L26" t="str">
-        <v>11,949,703,459</v>
+        <v>12,255,286,325</v>
       </c>
       <c r="M26" t="str">
-        <v>3,005,614,040</v>
+        <v>3,092,938,967</v>
       </c>
       <c r="N26" t="str">
-        <v>25.15%</v>
+        <v>25.24%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,10 +1557,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>2,136</v>
+        <v>2,238</v>
       </c>
       <c r="F27" t="str">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="G27" t="str">
         <v>0</v>
@@ -1578,13 +1578,13 @@
         <v>0</v>
       </c>
       <c r="L27" t="str">
-        <v>2,248,471,473</v>
+        <v>2,348,916,888</v>
       </c>
       <c r="M27" t="str">
-        <v>511,822,983</v>
+        <v>535,745,739</v>
       </c>
       <c r="N27" t="str">
-        <v>22.76%</v>
+        <v>22.81%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,13 +1601,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>18,338</v>
+        <v>19,260</v>
       </c>
       <c r="F28" t="str">
-        <v>3,155</v>
+        <v>3,309</v>
       </c>
       <c r="G28" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" t="str">
         <v>2</v>
@@ -1622,13 +1622,13 @@
         <v>0</v>
       </c>
       <c r="L28" t="str">
-        <v>19,352,306,013</v>
+        <v>20,199,587,239</v>
       </c>
       <c r="M28" t="str">
-        <v>3,764,119,900</v>
+        <v>3,905,810,013</v>
       </c>
       <c r="N28" t="str">
-        <v>19.45%</v>
+        <v>19.34%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,10 +1645,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>146</v>
+        <v>200</v>
       </c>
       <c r="F29" t="str">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G29" t="str">
         <v>0</v>
@@ -1666,13 +1666,13 @@
         <v>0</v>
       </c>
       <c r="L29" t="str">
-        <v>115,759,662</v>
+        <v>161,055,536</v>
       </c>
       <c r="M29" t="str">
-        <v>18,943,900</v>
+        <v>32,751,381</v>
       </c>
       <c r="N29" t="str">
-        <v>16.36%</v>
+        <v>20.34%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,34 +1689,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>3,816</v>
+        <v>3,956</v>
       </c>
       <c r="F30" t="str">
-        <v>1,257</v>
+        <v>1,300</v>
       </c>
       <c r="G30" t="str">
-        <v>1,428</v>
+        <v>1,493</v>
       </c>
       <c r="H30" t="str">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="I30" t="str">
-        <v>3,197,428,897</v>
+        <v>3,320,928,304</v>
       </c>
       <c r="J30" t="str">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="K30" t="str">
-        <v>3,472,227,994</v>
+        <v>3,599,383,209</v>
       </c>
       <c r="L30" t="str">
-        <v>40,675,041,373</v>
+        <v>42,299,947,526</v>
       </c>
       <c r="M30" t="str">
-        <v>11,243,509,733</v>
+        <v>11,646,864,124</v>
       </c>
       <c r="N30" t="str">
-        <v>27.64%</v>
+        <v>27.53%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,10 +1733,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>3,424</v>
+        <v>3,543</v>
       </c>
       <c r="F31" t="str">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1754,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>3,733,640,131</v>
+        <v>3,849,602,706</v>
       </c>
       <c r="M31" t="str">
-        <v>747,287,699</v>
+        <v>770,893,302</v>
       </c>
       <c r="N31" t="str">
-        <v>20.01%</v>
+        <v>20.03%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,13 +1777,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>4,072</v>
+        <v>4,166</v>
       </c>
       <c r="F32" t="str">
-        <v>645</v>
+        <v>674</v>
       </c>
       <c r="G32" t="str">
-        <v>1,875</v>
+        <v>1,924</v>
       </c>
       <c r="H32" t="str">
         <v>9</v>
@@ -1798,13 +1798,13 @@
         <v>102,003,250</v>
       </c>
       <c r="L32" t="str">
-        <v>10,900,288,137</v>
+        <v>11,088,051,178</v>
       </c>
       <c r="M32" t="str">
-        <v>1,053,755,126</v>
+        <v>1,075,835,838</v>
       </c>
       <c r="N32" t="str">
-        <v>9.67%</v>
+        <v>9.70%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,34 +1821,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>1,276</v>
+        <v>1,331</v>
       </c>
       <c r="F33" t="str">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="G33" t="str">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="H33" t="str">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I33" t="str">
-        <v>57,255,540</v>
+        <v>80,097,801</v>
       </c>
       <c r="J33" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K33" t="str">
-        <v>47,809,288</v>
+        <v>63,380,328</v>
       </c>
       <c r="L33" t="str">
-        <v>3,127,931,719</v>
+        <v>3,294,844,360</v>
       </c>
       <c r="M33" t="str">
-        <v>479,997,985</v>
+        <v>523,689,023</v>
       </c>
       <c r="N33" t="str">
-        <v>15.35%</v>
+        <v>15.89%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,10 +1865,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>2,912</v>
+        <v>3,002</v>
       </c>
       <c r="F34" t="str">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="G34" t="str">
         <v>96</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>3,083,599,871</v>
+        <v>3,151,018,163</v>
       </c>
       <c r="M34" t="str">
-        <v>492,155,395</v>
+        <v>499,594,894</v>
       </c>
       <c r="N34" t="str">
-        <v>15.96%</v>
+        <v>15.86%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,10 +1909,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>9,255</v>
+        <v>9,769</v>
       </c>
       <c r="F35" t="str">
-        <v>988</v>
+        <v>1,054</v>
       </c>
       <c r="G35" t="str">
         <v>344</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="L35" t="str">
-        <v>9,880,022,403</v>
+        <v>10,259,669,248</v>
       </c>
       <c r="M35" t="str">
-        <v>1,166,427,750</v>
+        <v>1,227,678,626</v>
       </c>
       <c r="N35" t="str">
-        <v>11.81%</v>
+        <v>11.97%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,10 +1953,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="F36" t="str">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G36" t="str">
         <v>0</v>
@@ -1974,13 +1974,13 @@
         <v>0</v>
       </c>
       <c r="L36" t="str">
-        <v>81,988,404</v>
+        <v>126,175,775</v>
       </c>
       <c r="M36" t="str">
-        <v>13,305,071</v>
+        <v>18,518,708</v>
       </c>
       <c r="N36" t="str">
-        <v>16.23%</v>
+        <v>14.68%</v>
       </c>
     </row>
     <row r="37">
@@ -1997,34 +1997,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>1,406</v>
+        <v>1,459</v>
       </c>
       <c r="F37" t="str">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="G37" t="str">
-        <v>2,328</v>
+        <v>2,425</v>
       </c>
       <c r="H37" t="str">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="I37" t="str">
-        <v>668,569,648</v>
+        <v>769,095,253</v>
       </c>
       <c r="J37" t="str">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K37" t="str">
-        <v>1,028,707,979</v>
+        <v>1,049,691,379</v>
       </c>
       <c r="L37" t="str">
-        <v>14,288,757,782</v>
+        <v>14,814,819,947</v>
       </c>
       <c r="M37" t="str">
-        <v>2,658,305,752</v>
+        <v>2,826,256,021</v>
       </c>
       <c r="N37" t="str">
-        <v>18.60%</v>
+        <v>19.08%</v>
       </c>
     </row>
     <row r="38">
@@ -2041,13 +2041,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>4,504</v>
+        <v>4,652</v>
       </c>
       <c r="F38" t="str">
-        <v>422</v>
+        <v>449</v>
       </c>
       <c r="G38" t="str">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H38" t="str">
         <v>3</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>4,838,905,828</v>
+        <v>4,969,148,262</v>
       </c>
       <c r="M38" t="str">
-        <v>500,765,143</v>
+        <v>523,477,100</v>
       </c>
       <c r="N38" t="str">
-        <v>10.35%</v>
+        <v>10.53%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,13 +2085,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>3,138</v>
+        <v>3,277</v>
       </c>
       <c r="F39" t="str">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="G39" t="str">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H39" t="str">
         <v>0</v>
@@ -2106,13 +2106,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>3,230,553,106</v>
+        <v>3,350,905,547</v>
       </c>
       <c r="M39" t="str">
-        <v>324,399,356</v>
+        <v>337,696,201</v>
       </c>
       <c r="N39" t="str">
-        <v>10.04%</v>
+        <v>10.08%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,34 +2173,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>1,192</v>
+        <v>1,243</v>
       </c>
       <c r="F41" t="str">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="G41" t="str">
-        <v>2,174</v>
+        <v>2,270</v>
       </c>
       <c r="H41" t="str">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I41" t="str">
-        <v>495,111,662</v>
+        <v>521,099,440</v>
       </c>
       <c r="J41" t="str">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K41" t="str">
-        <v>466,800,436</v>
+        <v>482,137,111</v>
       </c>
       <c r="L41" t="str">
-        <v>11,817,140,683</v>
+        <v>12,346,299,100</v>
       </c>
       <c r="M41" t="str">
-        <v>1,626,399,686</v>
+        <v>1,712,213,872</v>
       </c>
       <c r="N41" t="str">
-        <v>13.76%</v>
+        <v>13.87%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,19 +2217,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>6,055</v>
+        <v>6,183</v>
       </c>
       <c r="F42" t="str">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="G42" t="str">
-        <v>7,693</v>
+        <v>8,000</v>
       </c>
       <c r="H42" t="str">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I42" t="str">
-        <v>37,100,895</v>
+        <v>58,637,524</v>
       </c>
       <c r="J42" t="str">
         <v>4</v>
@@ -2238,13 +2238,13 @@
         <v>84,725,256</v>
       </c>
       <c r="L42" t="str">
-        <v>15,035,026,555</v>
+        <v>15,285,445,548</v>
       </c>
       <c r="M42" t="str">
-        <v>477,415,281</v>
+        <v>505,271,211</v>
       </c>
       <c r="N42" t="str">
-        <v>3.18%</v>
+        <v>3.31%</v>
       </c>
     </row>
     <row r="43">
@@ -2305,13 +2305,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>1,662</v>
+        <v>1,755</v>
       </c>
       <c r="F44" t="str">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G44" t="str">
-        <v>1,639</v>
+        <v>1,720</v>
       </c>
       <c r="H44" t="str">
         <v>2</v>
@@ -2326,13 +2326,13 @@
         <v>50,770,592</v>
       </c>
       <c r="L44" t="str">
-        <v>3,676,906,981</v>
+        <v>3,863,838,528</v>
       </c>
       <c r="M44" t="str">
-        <v>159,716,954</v>
+        <v>165,075,024</v>
       </c>
       <c r="N44" t="str">
-        <v>4.34%</v>
+        <v>4.27%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,13 +2349,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>1,081</v>
+        <v>1,127</v>
       </c>
       <c r="F45" t="str">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G45" t="str">
-        <v>1,651</v>
+        <v>1,725</v>
       </c>
       <c r="H45" t="str">
         <v>0</v>
@@ -2370,13 +2370,13 @@
         <v>66,445,865</v>
       </c>
       <c r="L45" t="str">
-        <v>2,659,307,297</v>
+        <v>2,746,126,532</v>
       </c>
       <c r="M45" t="str">
-        <v>103,484,997</v>
+        <v>104,672,785</v>
       </c>
       <c r="N45" t="str">
-        <v>3.89%</v>
+        <v>3.81%</v>
       </c>
     </row>
     <row r="46">
@@ -2393,13 +2393,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E46" t="str">
-        <v>4,332</v>
+        <v>4,519</v>
       </c>
       <c r="F46" t="str">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="G46" t="str">
-        <v>6,713</v>
+        <v>6,938</v>
       </c>
       <c r="H46" t="str">
         <v>11</v>
@@ -2414,13 +2414,13 @@
         <v>39,032,955</v>
       </c>
       <c r="L46" t="str">
-        <v>10,326,210,108</v>
+        <v>10,616,227,394</v>
       </c>
       <c r="M46" t="str">
-        <v>518,913,077</v>
+        <v>543,668,580</v>
       </c>
       <c r="N46" t="str">
-        <v>5.03%</v>
+        <v>5.12%</v>
       </c>
     </row>
     <row r="47">
@@ -2437,13 +2437,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E47" t="str">
-        <v>4,525</v>
+        <v>4,899</v>
       </c>
       <c r="F47" t="str">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="G47" t="str">
-        <v>4,105</v>
+        <v>4,331</v>
       </c>
       <c r="H47" t="str">
         <v>4</v>
@@ -2458,13 +2458,13 @@
         <v>54,162,704</v>
       </c>
       <c r="L47" t="str">
-        <v>10,555,394,411</v>
+        <v>11,197,476,330</v>
       </c>
       <c r="M47" t="str">
-        <v>312,475,061</v>
+        <v>335,092,496</v>
       </c>
       <c r="N47" t="str">
-        <v>2.96%</v>
+        <v>2.99%</v>
       </c>
     </row>
     <row r="48">
@@ -2481,13 +2481,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E48" t="str">
-        <v>3,793</v>
+        <v>3,955</v>
       </c>
       <c r="F48" t="str">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="G48" t="str">
-        <v>5,598</v>
+        <v>5,805</v>
       </c>
       <c r="H48" t="str">
         <v>5</v>
@@ -2496,19 +2496,19 @@
         <v>60,689,995</v>
       </c>
       <c r="J48" t="str">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K48" t="str">
-        <v>151,841,920</v>
+        <v>170,628,519</v>
       </c>
       <c r="L48" t="str">
-        <v>8,775,265,667</v>
+        <v>9,024,139,181</v>
       </c>
       <c r="M48" t="str">
-        <v>554,834,428</v>
+        <v>578,984,539</v>
       </c>
       <c r="N48" t="str">
-        <v>6.32%</v>
+        <v>6.42%</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata/Bulanan/10. Okt-LD.xlsx
+++ b/rawdata/Bulanan/10. Okt-LD.xlsx
@@ -457,34 +457,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>10,258</v>
+        <v>10,596</v>
       </c>
       <c r="F2" t="str">
-        <v>5,051</v>
+        <v>5,222</v>
       </c>
       <c r="G2" t="str">
-        <v>1,417</v>
+        <v>1,466</v>
       </c>
       <c r="H2" t="str">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="I2" t="str">
-        <v>3,018,755,220</v>
+        <v>3,134,647,178</v>
       </c>
       <c r="J2" t="str">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="K2" t="str">
-        <v>11,273,846,791</v>
+        <v>11,608,465,076</v>
       </c>
       <c r="L2" t="str">
-        <v>38,450,434,282</v>
+        <v>39,743,265,798</v>
       </c>
       <c r="M2" t="str">
-        <v>21,572,258,787</v>
+        <v>22,298,194,293</v>
       </c>
       <c r="N2" t="str">
-        <v>56.10%</v>
+        <v>56.11%</v>
       </c>
     </row>
     <row r="3">
@@ -501,34 +501,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>15,711</v>
+        <v>16,276</v>
       </c>
       <c r="F3" t="str">
-        <v>2,219</v>
+        <v>2,289</v>
       </c>
       <c r="G3" t="str">
-        <v>2,513</v>
+        <v>2,607</v>
       </c>
       <c r="H3" t="str">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="I3" t="str">
-        <v>1,937,994,506</v>
+        <v>1,974,489,534</v>
       </c>
       <c r="J3" t="str">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="K3" t="str">
-        <v>6,420,605,807</v>
+        <v>6,706,017,619</v>
       </c>
       <c r="L3" t="str">
-        <v>64,837,754,060</v>
+        <v>67,294,884,893</v>
       </c>
       <c r="M3" t="str">
-        <v>11,351,538,863</v>
+        <v>11,739,640,871</v>
       </c>
       <c r="N3" t="str">
-        <v>17.51%</v>
+        <v>17.45%</v>
       </c>
     </row>
     <row r="4">
@@ -545,34 +545,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>3,153</v>
+        <v>3,301</v>
       </c>
       <c r="F4" t="str">
-        <v>1,452</v>
+        <v>1,531</v>
       </c>
       <c r="G4" t="str">
-        <v>439</v>
+        <v>461</v>
       </c>
       <c r="H4" t="str">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I4" t="str">
-        <v>963,073,693</v>
+        <v>976,998,391</v>
       </c>
       <c r="J4" t="str">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="K4" t="str">
-        <v>3,570,613,016</v>
+        <v>3,787,878,818</v>
       </c>
       <c r="L4" t="str">
-        <v>11,810,930,636</v>
+        <v>12,407,326,980</v>
       </c>
       <c r="M4" t="str">
-        <v>6,778,339,765</v>
+        <v>7,134,892,725</v>
       </c>
       <c r="N4" t="str">
-        <v>57.39%</v>
+        <v>57.51%</v>
       </c>
     </row>
     <row r="5">
@@ -589,13 +589,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>5,767</v>
+        <v>6,014</v>
       </c>
       <c r="F5" t="str">
-        <v>1,351</v>
+        <v>1,403</v>
       </c>
       <c r="G5" t="str">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5" t="str">
         <v>11</v>
@@ -610,13 +610,13 @@
         <v>38,695,454</v>
       </c>
       <c r="L5" t="str">
-        <v>6,798,772,596</v>
+        <v>7,107,249,854</v>
       </c>
       <c r="M5" t="str">
-        <v>2,380,550,814</v>
+        <v>2,471,367,154</v>
       </c>
       <c r="N5" t="str">
-        <v>35.01%</v>
+        <v>34.77%</v>
       </c>
     </row>
     <row r="6">
@@ -633,13 +633,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>25,958</v>
+        <v>27,337</v>
       </c>
       <c r="F6" t="str">
-        <v>6,121</v>
+        <v>6,418</v>
       </c>
       <c r="G6" t="str">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H6" t="str">
         <v>12</v>
@@ -654,13 +654,13 @@
         <v>101,641,843</v>
       </c>
       <c r="L6" t="str">
-        <v>30,686,128,193</v>
+        <v>32,365,011,769</v>
       </c>
       <c r="M6" t="str">
-        <v>9,448,795,185</v>
+        <v>9,921,284,751</v>
       </c>
       <c r="N6" t="str">
-        <v>30.79%</v>
+        <v>30.65%</v>
       </c>
     </row>
     <row r="7">
@@ -677,10 +677,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>388</v>
+        <v>480</v>
       </c>
       <c r="F7" t="str">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="G7" t="str">
         <v>0</v>
@@ -698,13 +698,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="str">
-        <v>327,996,974</v>
+        <v>397,477,617</v>
       </c>
       <c r="M7" t="str">
-        <v>92,334,389</v>
+        <v>117,160,827</v>
       </c>
       <c r="N7" t="str">
-        <v>28.15%</v>
+        <v>29.48%</v>
       </c>
     </row>
     <row r="8">
@@ -721,34 +721,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>7,683</v>
+        <v>8,057</v>
       </c>
       <c r="F8" t="str">
-        <v>3,656</v>
+        <v>3,805</v>
       </c>
       <c r="G8" t="str">
-        <v>5,299</v>
+        <v>5,522</v>
       </c>
       <c r="H8" t="str">
-        <v>1,073</v>
+        <v>1,110</v>
       </c>
       <c r="I8" t="str">
-        <v>12,962,288,818</v>
+        <v>13,393,067,085</v>
       </c>
       <c r="J8" t="str">
-        <v>753</v>
+        <v>791</v>
       </c>
       <c r="K8" t="str">
-        <v>15,715,453,853</v>
+        <v>16,528,185,787</v>
       </c>
       <c r="L8" t="str">
-        <v>87,741,882,283</v>
+        <v>92,132,816,311</v>
       </c>
       <c r="M8" t="str">
-        <v>38,677,721,005</v>
+        <v>40,331,540,096</v>
       </c>
       <c r="N8" t="str">
-        <v>44.08%</v>
+        <v>43.78%</v>
       </c>
     </row>
     <row r="9">
@@ -765,10 +765,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>2,608</v>
+        <v>2,772</v>
       </c>
       <c r="F9" t="str">
-        <v>543</v>
+        <v>574</v>
       </c>
       <c r="G9" t="str">
         <v>4</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="str">
-        <v>3,231,408,548</v>
+        <v>3,423,594,673</v>
       </c>
       <c r="M9" t="str">
-        <v>905,795,875</v>
+        <v>955,010,690</v>
       </c>
       <c r="N9" t="str">
-        <v>28.03%</v>
+        <v>27.89%</v>
       </c>
     </row>
     <row r="10">
@@ -809,13 +809,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>3,473</v>
+        <v>3,567</v>
       </c>
       <c r="F10" t="str">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G10" t="str">
-        <v>8,382</v>
+        <v>8,649</v>
       </c>
       <c r="H10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>100,379,570</v>
       </c>
       <c r="L10" t="str">
-        <v>9,866,256,612</v>
+        <v>10,092,694,786</v>
       </c>
       <c r="M10" t="str">
-        <v>128,949,995</v>
+        <v>144,948,059</v>
       </c>
       <c r="N10" t="str">
-        <v>1.31%</v>
+        <v>1.44%</v>
       </c>
     </row>
     <row r="11">
@@ -853,13 +853,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>2,895</v>
+        <v>2,971</v>
       </c>
       <c r="F11" t="str">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" t="str">
-        <v>5,967</v>
+        <v>6,177</v>
       </c>
       <c r="H11" t="str">
         <v>2</v>
@@ -874,13 +874,13 @@
         <v>37,800,870</v>
       </c>
       <c r="L11" t="str">
-        <v>8,264,582,048</v>
+        <v>8,460,429,309</v>
       </c>
       <c r="M11" t="str">
-        <v>137,284,655</v>
+        <v>137,751,067</v>
       </c>
       <c r="N11" t="str">
-        <v>1.66%</v>
+        <v>1.63%</v>
       </c>
     </row>
     <row r="12">
@@ -897,34 +897,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>3,659</v>
+        <v>3,779</v>
       </c>
       <c r="F12" t="str">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="G12" t="str">
-        <v>10,768</v>
+        <v>11,186</v>
       </c>
       <c r="H12" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="str">
-        <v>0</v>
+        <v>13,440,344</v>
       </c>
       <c r="J12" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" t="str">
-        <v>0</v>
+        <v>40,288,174</v>
       </c>
       <c r="L12" t="str">
-        <v>13,919,008,456</v>
+        <v>14,310,214,309</v>
       </c>
       <c r="M12" t="str">
-        <v>126,531,938</v>
+        <v>179,955,521</v>
       </c>
       <c r="N12" t="str">
-        <v>0.91%</v>
+        <v>1.26%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>2,277</v>
+        <v>2,354</v>
       </c>
       <c r="F13" t="str">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G13" t="str">
-        <v>7,388</v>
+        <v>7,670</v>
       </c>
       <c r="H13" t="str">
         <v>3</v>
@@ -962,13 +962,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="str">
-        <v>8,522,983,974</v>
+        <v>8,702,040,088</v>
       </c>
       <c r="M13" t="str">
-        <v>233,589,124</v>
+        <v>234,173,803</v>
       </c>
       <c r="N13" t="str">
-        <v>2.74%</v>
+        <v>2.69%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>1,167</v>
+        <v>1,197</v>
       </c>
       <c r="F14" t="str">
         <v>31</v>
       </c>
       <c r="G14" t="str">
-        <v>3,925</v>
+        <v>4,048</v>
       </c>
       <c r="H14" t="str">
         <v>1</v>
@@ -1006,13 +1006,13 @@
         <v>35,694,915</v>
       </c>
       <c r="L14" t="str">
-        <v>4,385,988,806</v>
+        <v>4,494,164,262</v>
       </c>
       <c r="M14" t="str">
         <v>99,157,583</v>
       </c>
       <c r="N14" t="str">
-        <v>2.26%</v>
+        <v>2.21%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>3,213</v>
+        <v>3,320</v>
       </c>
       <c r="F15" t="str">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G15" t="str">
-        <v>9,994</v>
+        <v>10,357</v>
       </c>
       <c r="H15" t="str">
         <v>1</v>
@@ -1050,13 +1050,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="str">
-        <v>11,977,506,745</v>
+        <v>12,288,701,048</v>
       </c>
       <c r="M15" t="str">
-        <v>188,044,232</v>
+        <v>199,661,285</v>
       </c>
       <c r="N15" t="str">
-        <v>1.57%</v>
+        <v>1.62%</v>
       </c>
     </row>
     <row r="16">
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>4,723</v>
+        <v>5,082</v>
       </c>
       <c r="F16" t="str">
         <v>30</v>
       </c>
       <c r="G16" t="str">
-        <v>13,934</v>
+        <v>14,466</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>18,185,289,672</v>
+        <v>19,564,604,586</v>
       </c>
       <c r="M16" t="str">
         <v>87,534,917</v>
       </c>
       <c r="N16" t="str">
-        <v>0.48%</v>
+        <v>0.45%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>2,153</v>
+        <v>2,429</v>
       </c>
       <c r="F17" t="str">
         <v>36</v>
       </c>
       <c r="G17" t="str">
-        <v>5,289</v>
+        <v>5,515</v>
       </c>
       <c r="H17" t="str">
         <v>0</v>
@@ -1138,13 +1138,13 @@
         <v>233,859,144</v>
       </c>
       <c r="L17" t="str">
-        <v>7,409,208,878</v>
+        <v>8,413,662,921</v>
       </c>
       <c r="M17" t="str">
         <v>180,557,351</v>
       </c>
       <c r="N17" t="str">
-        <v>2.44%</v>
+        <v>2.15%</v>
       </c>
     </row>
     <row r="18">
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>2,676</v>
+        <v>3,021</v>
       </c>
       <c r="F18" t="str">
         <v>39</v>
       </c>
       <c r="G18" t="str">
-        <v>6,100</v>
+        <v>6,320</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>100,898,460</v>
       </c>
       <c r="L18" t="str">
-        <v>8,874,026,634</v>
+        <v>10,107,741,497</v>
       </c>
       <c r="M18" t="str">
         <v>112,897,398</v>
       </c>
       <c r="N18" t="str">
-        <v>1.27%</v>
+        <v>1.12%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>3,848</v>
+        <v>3,972</v>
       </c>
       <c r="F19" t="str">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G19" t="str">
-        <v>14,078</v>
+        <v>14,623</v>
       </c>
       <c r="H19" t="str">
         <v>1</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>16,889,553,894</v>
+        <v>17,390,672,942</v>
       </c>
       <c r="M19" t="str">
-        <v>159,175,408</v>
+        <v>159,775,408</v>
       </c>
       <c r="N19" t="str">
-        <v>0.94%</v>
+        <v>0.92%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>642</v>
+        <v>662</v>
       </c>
       <c r="F20" t="str">
         <v>4</v>
       </c>
       <c r="G20" t="str">
-        <v>2,294</v>
+        <v>2,371</v>
       </c>
       <c r="H20" t="str">
         <v>0</v>
@@ -1270,13 +1270,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="str">
-        <v>2,722,063,137</v>
+        <v>2,824,766,667</v>
       </c>
       <c r="M20" t="str">
         <v>11,695,275</v>
       </c>
       <c r="N20" t="str">
-        <v>0.43%</v>
+        <v>0.41%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,19 +1293,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>4,494</v>
+        <v>4,638</v>
       </c>
       <c r="F21" t="str">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G21" t="str">
-        <v>15,848</v>
+        <v>16,429</v>
       </c>
       <c r="H21" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" t="str">
-        <v>13,235,001</v>
+        <v>27,847,701</v>
       </c>
       <c r="J21" t="str">
         <v>0</v>
@@ -1314,13 +1314,13 @@
         <v>0</v>
       </c>
       <c r="L21" t="str">
-        <v>19,389,653,151</v>
+        <v>20,021,180,554</v>
       </c>
       <c r="M21" t="str">
-        <v>146,011,843</v>
+        <v>162,343,463</v>
       </c>
       <c r="N21" t="str">
-        <v>0.75%</v>
+        <v>0.81%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,34 +1337,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>23,728</v>
+        <v>23,985</v>
       </c>
       <c r="F22" t="str">
-        <v>1,020</v>
+        <v>1,088</v>
       </c>
       <c r="G22" t="str">
-        <v>625,859</v>
+        <v>650,236</v>
       </c>
       <c r="H22" t="str">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I22" t="str">
-        <v>70,959,330</v>
+        <v>158,624,610</v>
       </c>
       <c r="J22" t="str">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K22" t="str">
-        <v>263,912,728</v>
+        <v>295,866,488</v>
       </c>
       <c r="L22" t="str">
-        <v>103,678,382,112</v>
+        <v>104,459,226,255</v>
       </c>
       <c r="M22" t="str">
-        <v>2,630,722,303</v>
+        <v>2,897,522,696</v>
       </c>
       <c r="N22" t="str">
-        <v>2.54%</v>
+        <v>2.77%</v>
       </c>
     </row>
     <row r="23">
@@ -1381,13 +1381,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E23" t="str">
-        <v>1,211</v>
+        <v>1,214</v>
       </c>
       <c r="F23" t="str">
         <v>11</v>
       </c>
       <c r="G23" t="str">
-        <v>13,905</v>
+        <v>14,438</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -1402,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="str">
-        <v>13,271,307,078</v>
+        <v>13,273,913,212</v>
       </c>
       <c r="M23" t="str">
         <v>45,851,730</v>
@@ -1425,34 +1425,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>45,972</v>
+        <v>47,871</v>
       </c>
       <c r="F24" t="str">
-        <v>2,075</v>
+        <v>2,183</v>
       </c>
       <c r="G24" t="str">
-        <v>4,025</v>
+        <v>4,207</v>
       </c>
       <c r="H24" t="str">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="I24" t="str">
-        <v>3,572,484,304</v>
+        <v>3,736,231,710</v>
       </c>
       <c r="J24" t="str">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K24" t="str">
-        <v>4,289,475,902</v>
+        <v>4,463,908,555</v>
       </c>
       <c r="L24" t="str">
-        <v>146,463,871,403</v>
+        <v>152,813,586,821</v>
       </c>
       <c r="M24" t="str">
-        <v>11,581,303,699</v>
+        <v>12,072,834,352</v>
       </c>
       <c r="N24" t="str">
-        <v>7.91%</v>
+        <v>7.90%</v>
       </c>
     </row>
     <row r="25">
@@ -1469,13 +1469,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E25" t="str">
-        <v>2,141</v>
+        <v>2,227</v>
       </c>
       <c r="F25" t="str">
-        <v>680</v>
+        <v>715</v>
       </c>
       <c r="G25" t="str">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="H25" t="str">
         <v>12</v>
@@ -1484,19 +1484,19 @@
         <v>144,285,555</v>
       </c>
       <c r="J25" t="str">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K25" t="str">
-        <v>467,753,326</v>
+        <v>566,472,818</v>
       </c>
       <c r="L25" t="str">
-        <v>5,481,361,556</v>
+        <v>5,741,933,982</v>
       </c>
       <c r="M25" t="str">
-        <v>1,495,087,404</v>
+        <v>1,603,632,707</v>
       </c>
       <c r="N25" t="str">
-        <v>27.28%</v>
+        <v>27.93%</v>
       </c>
     </row>
     <row r="26">
@@ -1513,19 +1513,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>4,785</v>
+        <v>4,900</v>
       </c>
       <c r="F26" t="str">
-        <v>1,447</v>
+        <v>1,490</v>
       </c>
       <c r="G26" t="str">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H26" t="str">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I26" t="str">
-        <v>458,878,585</v>
+        <v>483,567,428</v>
       </c>
       <c r="J26" t="str">
         <v>38</v>
@@ -1534,13 +1534,13 @@
         <v>724,759,796</v>
       </c>
       <c r="L26" t="str">
-        <v>12,255,286,325</v>
+        <v>12,560,946,340</v>
       </c>
       <c r="M26" t="str">
-        <v>3,092,938,967</v>
+        <v>3,180,455,638</v>
       </c>
       <c r="N26" t="str">
-        <v>25.24%</v>
+        <v>25.32%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,10 +1557,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>2,238</v>
+        <v>2,325</v>
       </c>
       <c r="F27" t="str">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="G27" t="str">
         <v>0</v>
@@ -1578,13 +1578,13 @@
         <v>0</v>
       </c>
       <c r="L27" t="str">
-        <v>2,348,916,888</v>
+        <v>2,418,999,375</v>
       </c>
       <c r="M27" t="str">
-        <v>535,745,739</v>
+        <v>553,715,433</v>
       </c>
       <c r="N27" t="str">
-        <v>22.81%</v>
+        <v>22.89%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,10 +1601,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>19,260</v>
+        <v>20,100</v>
       </c>
       <c r="F28" t="str">
-        <v>3,309</v>
+        <v>3,456</v>
       </c>
       <c r="G28" t="str">
         <v>2</v>
@@ -1622,13 +1622,13 @@
         <v>0</v>
       </c>
       <c r="L28" t="str">
-        <v>20,199,587,239</v>
+        <v>20,890,426,709</v>
       </c>
       <c r="M28" t="str">
-        <v>3,905,810,013</v>
+        <v>4,044,869,919</v>
       </c>
       <c r="N28" t="str">
-        <v>19.34%</v>
+        <v>19.36%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,10 +1645,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>200</v>
+        <v>265</v>
       </c>
       <c r="F29" t="str">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="G29" t="str">
         <v>0</v>
@@ -1666,13 +1666,13 @@
         <v>0</v>
       </c>
       <c r="L29" t="str">
-        <v>161,055,536</v>
+        <v>218,487,525</v>
       </c>
       <c r="M29" t="str">
-        <v>32,751,381</v>
+        <v>47,200,969</v>
       </c>
       <c r="N29" t="str">
-        <v>20.34%</v>
+        <v>21.60%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,34 +1689,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>3,956</v>
+        <v>4,086</v>
       </c>
       <c r="F30" t="str">
-        <v>1,300</v>
+        <v>1,346</v>
       </c>
       <c r="G30" t="str">
-        <v>1,493</v>
+        <v>1,545</v>
       </c>
       <c r="H30" t="str">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="I30" t="str">
-        <v>3,320,928,304</v>
+        <v>3,441,730,647</v>
       </c>
       <c r="J30" t="str">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="K30" t="str">
-        <v>3,599,383,209</v>
+        <v>3,847,913,612</v>
       </c>
       <c r="L30" t="str">
-        <v>42,299,947,526</v>
+        <v>43,740,750,003</v>
       </c>
       <c r="M30" t="str">
-        <v>11,646,864,124</v>
+        <v>12,146,715,448</v>
       </c>
       <c r="N30" t="str">
-        <v>27.53%</v>
+        <v>27.77%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,10 +1733,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>3,543</v>
+        <v>3,659</v>
       </c>
       <c r="F31" t="str">
-        <v>601</v>
+        <v>629</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1754,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>3,849,602,706</v>
+        <v>3,941,522,206</v>
       </c>
       <c r="M31" t="str">
-        <v>770,893,302</v>
+        <v>791,516,456</v>
       </c>
       <c r="N31" t="str">
-        <v>20.03%</v>
+        <v>20.08%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,13 +1777,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>4,166</v>
+        <v>4,270</v>
       </c>
       <c r="F32" t="str">
-        <v>674</v>
+        <v>708</v>
       </c>
       <c r="G32" t="str">
-        <v>1,924</v>
+        <v>1,974</v>
       </c>
       <c r="H32" t="str">
         <v>9</v>
@@ -1798,13 +1798,13 @@
         <v>102,003,250</v>
       </c>
       <c r="L32" t="str">
-        <v>11,088,051,178</v>
+        <v>11,360,036,868</v>
       </c>
       <c r="M32" t="str">
-        <v>1,075,835,838</v>
+        <v>1,125,397,530</v>
       </c>
       <c r="N32" t="str">
-        <v>9.70%</v>
+        <v>9.91%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,13 +1821,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>1,331</v>
+        <v>1,393</v>
       </c>
       <c r="F33" t="str">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="G33" t="str">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="H33" t="str">
         <v>7</v>
@@ -1836,19 +1836,19 @@
         <v>80,097,801</v>
       </c>
       <c r="J33" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K33" t="str">
-        <v>63,380,328</v>
+        <v>81,160,766</v>
       </c>
       <c r="L33" t="str">
-        <v>3,294,844,360</v>
+        <v>3,439,534,439</v>
       </c>
       <c r="M33" t="str">
-        <v>523,689,023</v>
+        <v>548,014,872</v>
       </c>
       <c r="N33" t="str">
-        <v>15.89%</v>
+        <v>15.93%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,10 +1865,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>3,002</v>
+        <v>3,104</v>
       </c>
       <c r="F34" t="str">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="G34" t="str">
         <v>96</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>3,151,018,163</v>
+        <v>3,252,684,192</v>
       </c>
       <c r="M34" t="str">
-        <v>499,594,894</v>
+        <v>510,846,414</v>
       </c>
       <c r="N34" t="str">
-        <v>15.86%</v>
+        <v>15.71%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,10 +1909,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>9,769</v>
+        <v>10,303</v>
       </c>
       <c r="F35" t="str">
-        <v>1,054</v>
+        <v>1,128</v>
       </c>
       <c r="G35" t="str">
         <v>344</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="L35" t="str">
-        <v>10,259,669,248</v>
+        <v>10,704,516,154</v>
       </c>
       <c r="M35" t="str">
-        <v>1,227,678,626</v>
+        <v>1,299,987,721</v>
       </c>
       <c r="N35" t="str">
-        <v>11.97%</v>
+        <v>12.14%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,10 +1953,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="F36" t="str">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G36" t="str">
         <v>0</v>
@@ -1974,13 +1974,13 @@
         <v>0</v>
       </c>
       <c r="L36" t="str">
-        <v>126,175,775</v>
+        <v>156,877,423</v>
       </c>
       <c r="M36" t="str">
-        <v>18,518,708</v>
+        <v>29,370,108</v>
       </c>
       <c r="N36" t="str">
-        <v>14.68%</v>
+        <v>18.72%</v>
       </c>
     </row>
     <row r="37">
@@ -1997,34 +1997,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>1,459</v>
+        <v>1,516</v>
       </c>
       <c r="F37" t="str">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="G37" t="str">
-        <v>2,425</v>
+        <v>2,525</v>
       </c>
       <c r="H37" t="str">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I37" t="str">
-        <v>769,095,253</v>
+        <v>795,918,300</v>
       </c>
       <c r="J37" t="str">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K37" t="str">
-        <v>1,049,691,379</v>
+        <v>1,080,916,560</v>
       </c>
       <c r="L37" t="str">
-        <v>14,814,819,947</v>
+        <v>15,444,316,691</v>
       </c>
       <c r="M37" t="str">
-        <v>2,826,256,021</v>
+        <v>2,943,980,476</v>
       </c>
       <c r="N37" t="str">
-        <v>19.08%</v>
+        <v>19.06%</v>
       </c>
     </row>
     <row r="38">
@@ -2041,13 +2041,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>4,652</v>
+        <v>4,812</v>
       </c>
       <c r="F38" t="str">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="G38" t="str">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H38" t="str">
         <v>3</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>4,969,148,262</v>
+        <v>5,104,560,171</v>
       </c>
       <c r="M38" t="str">
-        <v>523,477,100</v>
+        <v>533,614,050</v>
       </c>
       <c r="N38" t="str">
-        <v>10.53%</v>
+        <v>10.45%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,13 +2085,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>3,277</v>
+        <v>3,416</v>
       </c>
       <c r="F39" t="str">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="G39" t="str">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H39" t="str">
         <v>0</v>
@@ -2106,13 +2106,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>3,350,905,547</v>
+        <v>3,455,631,585</v>
       </c>
       <c r="M39" t="str">
-        <v>337,696,201</v>
+        <v>350,304,103</v>
       </c>
       <c r="N39" t="str">
-        <v>10.08%</v>
+        <v>10.14%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,34 +2173,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>1,243</v>
+        <v>1,286</v>
       </c>
       <c r="F41" t="str">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="G41" t="str">
-        <v>2,270</v>
+        <v>2,375</v>
       </c>
       <c r="H41" t="str">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I41" t="str">
-        <v>521,099,440</v>
+        <v>553,969,585</v>
       </c>
       <c r="J41" t="str">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K41" t="str">
-        <v>482,137,111</v>
+        <v>498,822,325</v>
       </c>
       <c r="L41" t="str">
-        <v>12,346,299,100</v>
+        <v>12,855,488,618</v>
       </c>
       <c r="M41" t="str">
-        <v>1,712,213,872</v>
+        <v>1,824,634,380</v>
       </c>
       <c r="N41" t="str">
-        <v>13.87%</v>
+        <v>14.19%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>6,183</v>
+        <v>6,303</v>
       </c>
       <c r="F42" t="str">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="G42" t="str">
-        <v>8,000</v>
+        <v>8,308</v>
       </c>
       <c r="H42" t="str">
         <v>5</v>
@@ -2232,19 +2232,19 @@
         <v>58,637,524</v>
       </c>
       <c r="J42" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K42" t="str">
-        <v>84,725,256</v>
+        <v>118,821,394</v>
       </c>
       <c r="L42" t="str">
-        <v>15,285,445,548</v>
+        <v>15,613,923,960</v>
       </c>
       <c r="M42" t="str">
-        <v>505,271,211</v>
+        <v>549,752,523</v>
       </c>
       <c r="N42" t="str">
-        <v>3.31%</v>
+        <v>3.52%</v>
       </c>
     </row>
     <row r="43">
@@ -2305,13 +2305,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>1,755</v>
+        <v>1,872</v>
       </c>
       <c r="F44" t="str">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G44" t="str">
-        <v>1,720</v>
+        <v>1,801</v>
       </c>
       <c r="H44" t="str">
         <v>2</v>
@@ -2326,13 +2326,13 @@
         <v>50,770,592</v>
       </c>
       <c r="L44" t="str">
-        <v>3,863,838,528</v>
+        <v>4,044,957,618</v>
       </c>
       <c r="M44" t="str">
-        <v>165,075,024</v>
+        <v>168,020,901</v>
       </c>
       <c r="N44" t="str">
-        <v>4.27%</v>
+        <v>4.15%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,13 +2349,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>1,127</v>
+        <v>1,185</v>
       </c>
       <c r="F45" t="str">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G45" t="str">
-        <v>1,725</v>
+        <v>1,805</v>
       </c>
       <c r="H45" t="str">
         <v>0</v>
@@ -2370,13 +2370,13 @@
         <v>66,445,865</v>
       </c>
       <c r="L45" t="str">
-        <v>2,746,126,532</v>
+        <v>2,899,815,498</v>
       </c>
       <c r="M45" t="str">
-        <v>104,672,785</v>
+        <v>106,598,447</v>
       </c>
       <c r="N45" t="str">
-        <v>3.81%</v>
+        <v>3.68%</v>
       </c>
     </row>
     <row r="46">
@@ -2393,34 +2393,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E46" t="str">
-        <v>4,519</v>
+        <v>4,754</v>
       </c>
       <c r="F46" t="str">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="G46" t="str">
-        <v>6,938</v>
+        <v>7,173</v>
       </c>
       <c r="H46" t="str">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I46" t="str">
-        <v>135,065,374</v>
+        <v>159,496,582</v>
       </c>
       <c r="J46" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K46" t="str">
-        <v>39,032,955</v>
+        <v>80,274,644</v>
       </c>
       <c r="L46" t="str">
-        <v>10,616,227,394</v>
+        <v>11,038,725,023</v>
       </c>
       <c r="M46" t="str">
-        <v>543,668,580</v>
+        <v>622,194,722</v>
       </c>
       <c r="N46" t="str">
-        <v>5.12%</v>
+        <v>5.64%</v>
       </c>
     </row>
     <row r="47">
@@ -2437,34 +2437,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E47" t="str">
-        <v>4,899</v>
+        <v>5,340</v>
       </c>
       <c r="F47" t="str">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="G47" t="str">
-        <v>4,331</v>
+        <v>4,567</v>
       </c>
       <c r="H47" t="str">
+        <v>5</v>
+      </c>
+      <c r="I47" t="str">
+        <v>61,245,665</v>
+      </c>
+      <c r="J47" t="str">
         <v>4</v>
       </c>
-      <c r="I47" t="str">
-        <v>49,794,252</v>
-      </c>
-      <c r="J47" t="str">
-        <v>3</v>
-      </c>
       <c r="K47" t="str">
-        <v>54,162,704</v>
+        <v>69,477,384</v>
       </c>
       <c r="L47" t="str">
-        <v>11,197,476,330</v>
+        <v>12,028,682,914</v>
       </c>
       <c r="M47" t="str">
-        <v>335,092,496</v>
+        <v>433,843,645</v>
       </c>
       <c r="N47" t="str">
-        <v>2.99%</v>
+        <v>3.61%</v>
       </c>
     </row>
     <row r="48">
@@ -2481,13 +2481,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E48" t="str">
-        <v>3,955</v>
+        <v>4,162</v>
       </c>
       <c r="F48" t="str">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="G48" t="str">
-        <v>5,805</v>
+        <v>6,011</v>
       </c>
       <c r="H48" t="str">
         <v>5</v>
@@ -2502,13 +2502,13 @@
         <v>170,628,519</v>
       </c>
       <c r="L48" t="str">
-        <v>9,024,139,181</v>
+        <v>9,343,739,104</v>
       </c>
       <c r="M48" t="str">
-        <v>578,984,539</v>
+        <v>597,227,966</v>
       </c>
       <c r="N48" t="str">
-        <v>6.42%</v>
+        <v>6.39%</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata/Bulanan/10. Okt-LD.xlsx
+++ b/rawdata/Bulanan/10. Okt-LD.xlsx
@@ -457,34 +457,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>10,596</v>
+        <v>10,956</v>
       </c>
       <c r="F2" t="str">
-        <v>5,222</v>
+        <v>5,409</v>
       </c>
       <c r="G2" t="str">
-        <v>1,466</v>
+        <v>1,513</v>
       </c>
       <c r="H2" t="str">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="I2" t="str">
-        <v>3,134,647,178</v>
+        <v>3,247,266,292</v>
       </c>
       <c r="J2" t="str">
-        <v>591</v>
+        <v>620</v>
       </c>
       <c r="K2" t="str">
-        <v>11,608,465,076</v>
+        <v>12,215,942,787</v>
       </c>
       <c r="L2" t="str">
-        <v>39,743,265,798</v>
+        <v>41,133,352,935</v>
       </c>
       <c r="M2" t="str">
-        <v>22,298,194,293</v>
+        <v>23,225,101,637</v>
       </c>
       <c r="N2" t="str">
-        <v>56.11%</v>
+        <v>56.46%</v>
       </c>
     </row>
     <row r="3">
@@ -501,34 +501,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>16,276</v>
+        <v>16,834</v>
       </c>
       <c r="F3" t="str">
-        <v>2,289</v>
+        <v>2,387</v>
       </c>
       <c r="G3" t="str">
-        <v>2,607</v>
+        <v>2,694</v>
       </c>
       <c r="H3" t="str">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="I3" t="str">
-        <v>1,974,489,534</v>
+        <v>2,039,124,065</v>
       </c>
       <c r="J3" t="str">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="K3" t="str">
-        <v>6,706,017,619</v>
+        <v>6,879,639,526</v>
       </c>
       <c r="L3" t="str">
-        <v>67,294,884,893</v>
+        <v>69,562,286,217</v>
       </c>
       <c r="M3" t="str">
-        <v>11,739,640,871</v>
+        <v>12,165,318,704</v>
       </c>
       <c r="N3" t="str">
-        <v>17.45%</v>
+        <v>17.49%</v>
       </c>
     </row>
     <row r="4">
@@ -545,34 +545,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>3,301</v>
+        <v>3,421</v>
       </c>
       <c r="F4" t="str">
-        <v>1,531</v>
+        <v>1,585</v>
       </c>
       <c r="G4" t="str">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="H4" t="str">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="I4" t="str">
-        <v>976,998,391</v>
+        <v>1,040,617,099</v>
       </c>
       <c r="J4" t="str">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K4" t="str">
-        <v>3,787,878,818</v>
+        <v>3,879,296,320</v>
       </c>
       <c r="L4" t="str">
-        <v>12,407,326,980</v>
+        <v>12,900,689,979</v>
       </c>
       <c r="M4" t="str">
-        <v>7,134,892,725</v>
+        <v>7,394,626,715</v>
       </c>
       <c r="N4" t="str">
-        <v>57.51%</v>
+        <v>57.32%</v>
       </c>
     </row>
     <row r="5">
@@ -589,13 +589,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>6,014</v>
+        <v>6,209</v>
       </c>
       <c r="F5" t="str">
-        <v>1,403</v>
+        <v>1,457</v>
       </c>
       <c r="G5" t="str">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H5" t="str">
         <v>11</v>
@@ -610,13 +610,13 @@
         <v>38,695,454</v>
       </c>
       <c r="L5" t="str">
-        <v>7,107,249,854</v>
+        <v>7,373,196,604</v>
       </c>
       <c r="M5" t="str">
-        <v>2,471,367,154</v>
+        <v>2,559,814,053</v>
       </c>
       <c r="N5" t="str">
-        <v>34.77%</v>
+        <v>34.72%</v>
       </c>
     </row>
     <row r="6">
@@ -633,13 +633,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>27,337</v>
+        <v>28,413</v>
       </c>
       <c r="F6" t="str">
-        <v>6,418</v>
+        <v>6,744</v>
       </c>
       <c r="G6" t="str">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H6" t="str">
         <v>12</v>
@@ -654,13 +654,13 @@
         <v>101,641,843</v>
       </c>
       <c r="L6" t="str">
-        <v>32,365,011,769</v>
+        <v>33,800,026,831</v>
       </c>
       <c r="M6" t="str">
-        <v>9,921,284,751</v>
+        <v>10,467,171,232</v>
       </c>
       <c r="N6" t="str">
-        <v>30.65%</v>
+        <v>30.97%</v>
       </c>
     </row>
     <row r="7">
@@ -677,10 +677,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>480</v>
+        <v>569</v>
       </c>
       <c r="F7" t="str">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="G7" t="str">
         <v>0</v>
@@ -698,13 +698,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="str">
-        <v>397,477,617</v>
+        <v>468,576,528</v>
       </c>
       <c r="M7" t="str">
-        <v>117,160,827</v>
+        <v>143,664,152</v>
       </c>
       <c r="N7" t="str">
-        <v>29.48%</v>
+        <v>30.66%</v>
       </c>
     </row>
     <row r="8">
@@ -721,34 +721,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>8,057</v>
+        <v>8,386</v>
       </c>
       <c r="F8" t="str">
-        <v>3,805</v>
+        <v>3,996</v>
       </c>
       <c r="G8" t="str">
-        <v>5,522</v>
+        <v>5,789</v>
       </c>
       <c r="H8" t="str">
-        <v>1,110</v>
+        <v>1,175</v>
       </c>
       <c r="I8" t="str">
-        <v>13,393,067,085</v>
+        <v>14,178,338,595</v>
       </c>
       <c r="J8" t="str">
-        <v>791</v>
+        <v>833</v>
       </c>
       <c r="K8" t="str">
-        <v>16,528,185,787</v>
+        <v>17,433,137,413</v>
       </c>
       <c r="L8" t="str">
-        <v>92,132,816,311</v>
+        <v>96,078,155,745</v>
       </c>
       <c r="M8" t="str">
-        <v>40,331,540,096</v>
+        <v>42,447,071,786</v>
       </c>
       <c r="N8" t="str">
-        <v>43.78%</v>
+        <v>44.18%</v>
       </c>
     </row>
     <row r="9">
@@ -765,10 +765,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>2,772</v>
+        <v>2,871</v>
       </c>
       <c r="F9" t="str">
-        <v>574</v>
+        <v>610</v>
       </c>
       <c r="G9" t="str">
         <v>4</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="str">
-        <v>3,423,594,673</v>
+        <v>3,541,611,756</v>
       </c>
       <c r="M9" t="str">
-        <v>955,010,690</v>
+        <v>1,005,266,904</v>
       </c>
       <c r="N9" t="str">
-        <v>27.89%</v>
+        <v>28.38%</v>
       </c>
     </row>
     <row r="10">
@@ -809,13 +809,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>3,567</v>
+        <v>3,676</v>
       </c>
       <c r="F10" t="str">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G10" t="str">
-        <v>8,649</v>
+        <v>8,910</v>
       </c>
       <c r="H10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>100,379,570</v>
       </c>
       <c r="L10" t="str">
-        <v>10,092,694,786</v>
+        <v>10,359,177,960</v>
       </c>
       <c r="M10" t="str">
-        <v>144,948,059</v>
+        <v>145,672,869</v>
       </c>
       <c r="N10" t="str">
-        <v>1.44%</v>
+        <v>1.41%</v>
       </c>
     </row>
     <row r="11">
@@ -853,13 +853,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>2,971</v>
+        <v>3,062</v>
       </c>
       <c r="F11" t="str">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G11" t="str">
-        <v>6,177</v>
+        <v>6,384</v>
       </c>
       <c r="H11" t="str">
         <v>2</v>
@@ -874,10 +874,10 @@
         <v>37,800,870</v>
       </c>
       <c r="L11" t="str">
-        <v>8,460,429,309</v>
+        <v>8,702,537,497</v>
       </c>
       <c r="M11" t="str">
-        <v>137,751,067</v>
+        <v>141,741,478</v>
       </c>
       <c r="N11" t="str">
         <v>1.63%</v>
@@ -897,13 +897,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>3,779</v>
+        <v>3,891</v>
       </c>
       <c r="F12" t="str">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G12" t="str">
-        <v>11,186</v>
+        <v>11,600</v>
       </c>
       <c r="H12" t="str">
         <v>1</v>
@@ -918,13 +918,13 @@
         <v>40,288,174</v>
       </c>
       <c r="L12" t="str">
-        <v>14,310,214,309</v>
+        <v>14,706,679,663</v>
       </c>
       <c r="M12" t="str">
-        <v>179,955,521</v>
+        <v>193,213,312</v>
       </c>
       <c r="N12" t="str">
-        <v>1.26%</v>
+        <v>1.31%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>2,354</v>
+        <v>2,424</v>
       </c>
       <c r="F13" t="str">
         <v>66</v>
       </c>
       <c r="G13" t="str">
-        <v>7,670</v>
+        <v>7,950</v>
       </c>
       <c r="H13" t="str">
         <v>3</v>
@@ -962,13 +962,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="str">
-        <v>8,702,040,088</v>
+        <v>8,975,867,377</v>
       </c>
       <c r="M13" t="str">
         <v>234,173,803</v>
       </c>
       <c r="N13" t="str">
-        <v>2.69%</v>
+        <v>2.61%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>1,197</v>
+        <v>1,225</v>
       </c>
       <c r="F14" t="str">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G14" t="str">
-        <v>4,048</v>
+        <v>4,168</v>
       </c>
       <c r="H14" t="str">
         <v>1</v>
@@ -1006,10 +1006,10 @@
         <v>35,694,915</v>
       </c>
       <c r="L14" t="str">
-        <v>4,494,164,262</v>
+        <v>4,541,876,626</v>
       </c>
       <c r="M14" t="str">
-        <v>99,157,583</v>
+        <v>100,519,190</v>
       </c>
       <c r="N14" t="str">
         <v>2.21%</v>
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>3,320</v>
+        <v>3,419</v>
       </c>
       <c r="F15" t="str">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G15" t="str">
-        <v>10,357</v>
+        <v>10,716</v>
       </c>
       <c r="H15" t="str">
         <v>1</v>
@@ -1050,10 +1050,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="str">
-        <v>12,288,701,048</v>
+        <v>12,637,260,166</v>
       </c>
       <c r="M15" t="str">
-        <v>199,661,285</v>
+        <v>204,841,834</v>
       </c>
       <c r="N15" t="str">
         <v>1.62%</v>
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>5,082</v>
+        <v>5,267</v>
       </c>
       <c r="F16" t="str">
         <v>30</v>
       </c>
       <c r="G16" t="str">
-        <v>14,466</v>
+        <v>14,996</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>19,564,604,586</v>
+        <v>20,182,330,854</v>
       </c>
       <c r="M16" t="str">
         <v>87,534,917</v>
       </c>
       <c r="N16" t="str">
-        <v>0.45%</v>
+        <v>0.43%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>2,429</v>
+        <v>2,517</v>
       </c>
       <c r="F17" t="str">
         <v>36</v>
       </c>
       <c r="G17" t="str">
-        <v>5,515</v>
+        <v>5,744</v>
       </c>
       <c r="H17" t="str">
         <v>0</v>
@@ -1138,13 +1138,13 @@
         <v>233,859,144</v>
       </c>
       <c r="L17" t="str">
-        <v>8,413,662,921</v>
+        <v>8,733,525,412</v>
       </c>
       <c r="M17" t="str">
         <v>180,557,351</v>
       </c>
       <c r="N17" t="str">
-        <v>2.15%</v>
+        <v>2.07%</v>
       </c>
     </row>
     <row r="18">
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>3,021</v>
+        <v>3,131</v>
       </c>
       <c r="F18" t="str">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G18" t="str">
-        <v>6,320</v>
+        <v>6,543</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
@@ -1176,19 +1176,19 @@
         <v>0</v>
       </c>
       <c r="J18" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K18" t="str">
-        <v>100,898,460</v>
+        <v>138,416,984</v>
       </c>
       <c r="L18" t="str">
-        <v>10,107,741,497</v>
+        <v>10,411,294,895</v>
       </c>
       <c r="M18" t="str">
-        <v>112,897,398</v>
+        <v>138,635,142</v>
       </c>
       <c r="N18" t="str">
-        <v>1.12%</v>
+        <v>1.33%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>3,972</v>
+        <v>4,117</v>
       </c>
       <c r="F19" t="str">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G19" t="str">
-        <v>14,623</v>
+        <v>15,171</v>
       </c>
       <c r="H19" t="str">
         <v>1</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>17,390,672,942</v>
+        <v>18,066,145,218</v>
       </c>
       <c r="M19" t="str">
-        <v>159,775,408</v>
+        <v>172,607,958</v>
       </c>
       <c r="N19" t="str">
-        <v>0.92%</v>
+        <v>0.96%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>662</v>
+        <v>686</v>
       </c>
       <c r="F20" t="str">
         <v>4</v>
       </c>
       <c r="G20" t="str">
-        <v>2,371</v>
+        <v>2,454</v>
       </c>
       <c r="H20" t="str">
         <v>0</v>
@@ -1270,13 +1270,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="str">
-        <v>2,824,766,667</v>
+        <v>2,975,295,688</v>
       </c>
       <c r="M20" t="str">
         <v>11,695,275</v>
       </c>
       <c r="N20" t="str">
-        <v>0.41%</v>
+        <v>0.39%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>4,638</v>
+        <v>4,806</v>
       </c>
       <c r="F21" t="str">
         <v>49</v>
       </c>
       <c r="G21" t="str">
-        <v>16,429</v>
+        <v>17,014</v>
       </c>
       <c r="H21" t="str">
         <v>2</v>
@@ -1314,13 +1314,13 @@
         <v>0</v>
       </c>
       <c r="L21" t="str">
-        <v>20,021,180,554</v>
+        <v>20,717,993,539</v>
       </c>
       <c r="M21" t="str">
         <v>162,343,463</v>
       </c>
       <c r="N21" t="str">
-        <v>0.81%</v>
+        <v>0.78%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,13 +1337,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>23,985</v>
+        <v>24,225</v>
       </c>
       <c r="F22" t="str">
-        <v>1,088</v>
+        <v>1,165</v>
       </c>
       <c r="G22" t="str">
-        <v>650,236</v>
+        <v>674,626</v>
       </c>
       <c r="H22" t="str">
         <v>14</v>
@@ -1358,13 +1358,13 @@
         <v>295,866,488</v>
       </c>
       <c r="L22" t="str">
-        <v>104,459,226,255</v>
+        <v>105,274,210,576</v>
       </c>
       <c r="M22" t="str">
-        <v>2,897,522,696</v>
+        <v>3,053,505,524</v>
       </c>
       <c r="N22" t="str">
-        <v>2.77%</v>
+        <v>2.90%</v>
       </c>
     </row>
     <row r="23">
@@ -1384,10 +1384,10 @@
         <v>1,214</v>
       </c>
       <c r="F23" t="str">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G23" t="str">
-        <v>14,438</v>
+        <v>14,971</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -1405,10 +1405,10 @@
         <v>13,273,913,212</v>
       </c>
       <c r="M23" t="str">
-        <v>45,851,730</v>
+        <v>55,473,160</v>
       </c>
       <c r="N23" t="str">
-        <v>0.35%</v>
+        <v>0.42%</v>
       </c>
     </row>
     <row r="24">
@@ -1425,34 +1425,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>47,871</v>
+        <v>49,669</v>
       </c>
       <c r="F24" t="str">
-        <v>2,183</v>
+        <v>2,279</v>
       </c>
       <c r="G24" t="str">
-        <v>4,207</v>
+        <v>4,374</v>
       </c>
       <c r="H24" t="str">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="I24" t="str">
-        <v>3,736,231,710</v>
+        <v>3,898,102,974</v>
       </c>
       <c r="J24" t="str">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="K24" t="str">
-        <v>4,463,908,555</v>
+        <v>4,574,035,759</v>
       </c>
       <c r="L24" t="str">
-        <v>152,813,586,821</v>
+        <v>158,745,925,955</v>
       </c>
       <c r="M24" t="str">
-        <v>12,072,834,352</v>
+        <v>12,470,463,786</v>
       </c>
       <c r="N24" t="str">
-        <v>7.90%</v>
+        <v>7.86%</v>
       </c>
     </row>
     <row r="25">
@@ -1469,13 +1469,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E25" t="str">
-        <v>2,227</v>
+        <v>2,327</v>
       </c>
       <c r="F25" t="str">
-        <v>715</v>
+        <v>745</v>
       </c>
       <c r="G25" t="str">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="H25" t="str">
         <v>12</v>
@@ -1490,13 +1490,13 @@
         <v>566,472,818</v>
       </c>
       <c r="L25" t="str">
-        <v>5,741,933,982</v>
+        <v>6,002,129,191</v>
       </c>
       <c r="M25" t="str">
-        <v>1,603,632,707</v>
+        <v>1,645,428,745</v>
       </c>
       <c r="N25" t="str">
-        <v>27.93%</v>
+        <v>27.41%</v>
       </c>
     </row>
     <row r="26">
@@ -1513,31 +1513,31 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>4,900</v>
+        <v>5,034</v>
       </c>
       <c r="F26" t="str">
-        <v>1,490</v>
+        <v>1,535</v>
       </c>
       <c r="G26" t="str">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="H26" t="str">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I26" t="str">
-        <v>483,567,428</v>
+        <v>493,624,741</v>
       </c>
       <c r="J26" t="str">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K26" t="str">
-        <v>724,759,796</v>
+        <v>739,841,326</v>
       </c>
       <c r="L26" t="str">
-        <v>12,560,946,340</v>
+        <v>12,930,200,469</v>
       </c>
       <c r="M26" t="str">
-        <v>3,180,455,638</v>
+        <v>3,274,430,096</v>
       </c>
       <c r="N26" t="str">
         <v>25.32%</v>
@@ -1557,10 +1557,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>2,325</v>
+        <v>2,403</v>
       </c>
       <c r="F27" t="str">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="G27" t="str">
         <v>0</v>
@@ -1578,13 +1578,13 @@
         <v>0</v>
       </c>
       <c r="L27" t="str">
-        <v>2,418,999,375</v>
+        <v>2,474,116,563</v>
       </c>
       <c r="M27" t="str">
-        <v>553,715,433</v>
+        <v>566,013,779</v>
       </c>
       <c r="N27" t="str">
-        <v>22.89%</v>
+        <v>22.88%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,10 +1601,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>20,100</v>
+        <v>20,780</v>
       </c>
       <c r="F28" t="str">
-        <v>3,456</v>
+        <v>3,582</v>
       </c>
       <c r="G28" t="str">
         <v>2</v>
@@ -1622,13 +1622,13 @@
         <v>0</v>
       </c>
       <c r="L28" t="str">
-        <v>20,890,426,709</v>
+        <v>21,411,463,682</v>
       </c>
       <c r="M28" t="str">
-        <v>4,044,869,919</v>
+        <v>4,160,697,894</v>
       </c>
       <c r="N28" t="str">
-        <v>19.36%</v>
+        <v>19.43%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,10 +1645,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>265</v>
+        <v>332</v>
       </c>
       <c r="F29" t="str">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G29" t="str">
         <v>0</v>
@@ -1666,13 +1666,13 @@
         <v>0</v>
       </c>
       <c r="L29" t="str">
-        <v>218,487,525</v>
+        <v>263,802,741</v>
       </c>
       <c r="M29" t="str">
-        <v>47,200,969</v>
+        <v>59,442,044</v>
       </c>
       <c r="N29" t="str">
-        <v>21.60%</v>
+        <v>22.53%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,34 +1689,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>4,086</v>
+        <v>4,180</v>
       </c>
       <c r="F30" t="str">
-        <v>1,346</v>
+        <v>1,377</v>
       </c>
       <c r="G30" t="str">
-        <v>1,545</v>
+        <v>1,578</v>
       </c>
       <c r="H30" t="str">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="I30" t="str">
-        <v>3,441,730,647</v>
+        <v>3,477,825,196</v>
       </c>
       <c r="J30" t="str">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="K30" t="str">
-        <v>3,847,913,612</v>
+        <v>3,905,872,912</v>
       </c>
       <c r="L30" t="str">
-        <v>43,740,750,003</v>
+        <v>44,752,692,041</v>
       </c>
       <c r="M30" t="str">
-        <v>12,146,715,448</v>
+        <v>12,384,968,618</v>
       </c>
       <c r="N30" t="str">
-        <v>27.77%</v>
+        <v>27.67%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,10 +1733,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>3,659</v>
+        <v>3,791</v>
       </c>
       <c r="F31" t="str">
-        <v>629</v>
+        <v>663</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1754,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>3,941,522,206</v>
+        <v>4,052,564,500</v>
       </c>
       <c r="M31" t="str">
-        <v>791,516,456</v>
+        <v>827,878,776</v>
       </c>
       <c r="N31" t="str">
-        <v>20.08%</v>
+        <v>20.43%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,13 +1777,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>4,270</v>
+        <v>4,345</v>
       </c>
       <c r="F32" t="str">
-        <v>708</v>
+        <v>724</v>
       </c>
       <c r="G32" t="str">
-        <v>1,974</v>
+        <v>2,022</v>
       </c>
       <c r="H32" t="str">
         <v>9</v>
@@ -1798,13 +1798,13 @@
         <v>102,003,250</v>
       </c>
       <c r="L32" t="str">
-        <v>11,360,036,868</v>
+        <v>11,612,964,542</v>
       </c>
       <c r="M32" t="str">
-        <v>1,125,397,530</v>
+        <v>1,145,306,815</v>
       </c>
       <c r="N32" t="str">
-        <v>9.91%</v>
+        <v>9.86%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,13 +1821,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>1,393</v>
+        <v>1,438</v>
       </c>
       <c r="F33" t="str">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="G33" t="str">
-        <v>466</v>
+        <v>487</v>
       </c>
       <c r="H33" t="str">
         <v>7</v>
@@ -1842,13 +1842,13 @@
         <v>81,160,766</v>
       </c>
       <c r="L33" t="str">
-        <v>3,439,534,439</v>
+        <v>3,543,764,880</v>
       </c>
       <c r="M33" t="str">
-        <v>548,014,872</v>
+        <v>558,629,206</v>
       </c>
       <c r="N33" t="str">
-        <v>15.93%</v>
+        <v>15.76%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,10 +1865,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>3,104</v>
+        <v>3,198</v>
       </c>
       <c r="F34" t="str">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="G34" t="str">
         <v>96</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>3,252,684,192</v>
+        <v>3,331,904,890</v>
       </c>
       <c r="M34" t="str">
-        <v>510,846,414</v>
+        <v>520,575,313</v>
       </c>
       <c r="N34" t="str">
-        <v>15.71%</v>
+        <v>15.62%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,13 +1909,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>10,303</v>
+        <v>10,812</v>
       </c>
       <c r="F35" t="str">
-        <v>1,128</v>
+        <v>1,201</v>
       </c>
       <c r="G35" t="str">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="H35" t="str">
         <v>4</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="L35" t="str">
-        <v>10,704,516,154</v>
+        <v>11,166,010,626</v>
       </c>
       <c r="M35" t="str">
-        <v>1,299,987,721</v>
+        <v>1,357,509,859</v>
       </c>
       <c r="N35" t="str">
-        <v>12.14%</v>
+        <v>12.16%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,10 +1953,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>192</v>
+        <v>240</v>
       </c>
       <c r="F36" t="str">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G36" t="str">
         <v>0</v>
@@ -1974,13 +1974,13 @@
         <v>0</v>
       </c>
       <c r="L36" t="str">
-        <v>156,877,423</v>
+        <v>201,260,014</v>
       </c>
       <c r="M36" t="str">
-        <v>29,370,108</v>
+        <v>31,822,951</v>
       </c>
       <c r="N36" t="str">
-        <v>18.72%</v>
+        <v>15.81%</v>
       </c>
     </row>
     <row r="37">
@@ -1997,34 +1997,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>1,516</v>
+        <v>1,571</v>
       </c>
       <c r="F37" t="str">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="G37" t="str">
-        <v>2,525</v>
+        <v>2,626</v>
       </c>
       <c r="H37" t="str">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I37" t="str">
-        <v>795,918,300</v>
+        <v>831,711,648</v>
       </c>
       <c r="J37" t="str">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K37" t="str">
-        <v>1,080,916,560</v>
+        <v>1,111,128,016</v>
       </c>
       <c r="L37" t="str">
-        <v>15,444,316,691</v>
+        <v>16,018,593,367</v>
       </c>
       <c r="M37" t="str">
-        <v>2,943,980,476</v>
+        <v>3,057,792,419</v>
       </c>
       <c r="N37" t="str">
-        <v>19.06%</v>
+        <v>19.09%</v>
       </c>
     </row>
     <row r="38">
@@ -2041,13 +2041,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>4,812</v>
+        <v>4,946</v>
       </c>
       <c r="F38" t="str">
-        <v>469</v>
+        <v>495</v>
       </c>
       <c r="G38" t="str">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H38" t="str">
         <v>3</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>5,104,560,171</v>
+        <v>5,206,832,481</v>
       </c>
       <c r="M38" t="str">
-        <v>533,614,050</v>
+        <v>547,753,842</v>
       </c>
       <c r="N38" t="str">
-        <v>10.45%</v>
+        <v>10.52%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,13 +2085,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>3,416</v>
+        <v>3,547</v>
       </c>
       <c r="F39" t="str">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="G39" t="str">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H39" t="str">
         <v>0</v>
@@ -2106,13 +2106,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>3,455,631,585</v>
+        <v>3,637,108,609</v>
       </c>
       <c r="M39" t="str">
-        <v>350,304,103</v>
+        <v>368,215,846</v>
       </c>
       <c r="N39" t="str">
-        <v>10.14%</v>
+        <v>10.12%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,34 +2173,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>1,286</v>
+        <v>1,336</v>
       </c>
       <c r="F41" t="str">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="G41" t="str">
-        <v>2,375</v>
+        <v>2,458</v>
       </c>
       <c r="H41" t="str">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I41" t="str">
-        <v>553,969,585</v>
+        <v>597,492,511</v>
       </c>
       <c r="J41" t="str">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K41" t="str">
-        <v>498,822,325</v>
+        <v>522,990,481</v>
       </c>
       <c r="L41" t="str">
-        <v>12,855,488,618</v>
+        <v>13,334,774,602</v>
       </c>
       <c r="M41" t="str">
-        <v>1,824,634,380</v>
+        <v>1,910,258,411</v>
       </c>
       <c r="N41" t="str">
-        <v>14.19%</v>
+        <v>14.33%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>6,303</v>
+        <v>6,427</v>
       </c>
       <c r="F42" t="str">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="G42" t="str">
-        <v>8,308</v>
+        <v>8,619</v>
       </c>
       <c r="H42" t="str">
         <v>5</v>
@@ -2232,19 +2232,19 @@
         <v>58,637,524</v>
       </c>
       <c r="J42" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K42" t="str">
-        <v>118,821,394</v>
+        <v>151,104,880</v>
       </c>
       <c r="L42" t="str">
-        <v>15,613,923,960</v>
+        <v>15,977,561,982</v>
       </c>
       <c r="M42" t="str">
-        <v>549,752,523</v>
+        <v>600,742,248</v>
       </c>
       <c r="N42" t="str">
-        <v>3.52%</v>
+        <v>3.76%</v>
       </c>
     </row>
     <row r="43">
@@ -2305,13 +2305,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>1,872</v>
+        <v>1,976</v>
       </c>
       <c r="F44" t="str">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G44" t="str">
-        <v>1,801</v>
+        <v>1,881</v>
       </c>
       <c r="H44" t="str">
         <v>2</v>
@@ -2326,13 +2326,13 @@
         <v>50,770,592</v>
       </c>
       <c r="L44" t="str">
-        <v>4,044,957,618</v>
+        <v>4,198,775,030</v>
       </c>
       <c r="M44" t="str">
-        <v>168,020,901</v>
+        <v>169,979,375</v>
       </c>
       <c r="N44" t="str">
-        <v>4.15%</v>
+        <v>4.05%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,13 +2349,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>1,185</v>
+        <v>1,237</v>
       </c>
       <c r="F45" t="str">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G45" t="str">
-        <v>1,805</v>
+        <v>1,881</v>
       </c>
       <c r="H45" t="str">
         <v>0</v>
@@ -2370,13 +2370,13 @@
         <v>66,445,865</v>
       </c>
       <c r="L45" t="str">
-        <v>2,899,815,498</v>
+        <v>2,951,284,238</v>
       </c>
       <c r="M45" t="str">
-        <v>106,598,447</v>
+        <v>107,397,804</v>
       </c>
       <c r="N45" t="str">
-        <v>3.68%</v>
+        <v>3.64%</v>
       </c>
     </row>
     <row r="46">
@@ -2393,13 +2393,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E46" t="str">
-        <v>4,754</v>
+        <v>4,962</v>
       </c>
       <c r="F46" t="str">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="G46" t="str">
-        <v>7,173</v>
+        <v>7,397</v>
       </c>
       <c r="H46" t="str">
         <v>13</v>
@@ -2414,13 +2414,13 @@
         <v>80,274,644</v>
       </c>
       <c r="L46" t="str">
-        <v>11,038,725,023</v>
+        <v>11,386,050,418</v>
       </c>
       <c r="M46" t="str">
-        <v>622,194,722</v>
+        <v>636,280,217</v>
       </c>
       <c r="N46" t="str">
-        <v>5.64%</v>
+        <v>5.59%</v>
       </c>
     </row>
     <row r="47">
@@ -2437,13 +2437,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E47" t="str">
-        <v>5,340</v>
+        <v>5,719</v>
       </c>
       <c r="F47" t="str">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="G47" t="str">
-        <v>4,567</v>
+        <v>4,818</v>
       </c>
       <c r="H47" t="str">
         <v>5</v>
@@ -2452,19 +2452,19 @@
         <v>61,245,665</v>
       </c>
       <c r="J47" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K47" t="str">
-        <v>69,477,384</v>
+        <v>86,522,238</v>
       </c>
       <c r="L47" t="str">
-        <v>12,028,682,914</v>
+        <v>12,842,838,917</v>
       </c>
       <c r="M47" t="str">
-        <v>433,843,645</v>
+        <v>475,609,805</v>
       </c>
       <c r="N47" t="str">
-        <v>3.61%</v>
+        <v>3.70%</v>
       </c>
     </row>
     <row r="48">
@@ -2481,19 +2481,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E48" t="str">
-        <v>4,162</v>
+        <v>4,344</v>
       </c>
       <c r="F48" t="str">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="G48" t="str">
-        <v>6,011</v>
+        <v>6,215</v>
       </c>
       <c r="H48" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I48" t="str">
-        <v>60,689,995</v>
+        <v>71,679,870</v>
       </c>
       <c r="J48" t="str">
         <v>9</v>
@@ -2502,13 +2502,13 @@
         <v>170,628,519</v>
       </c>
       <c r="L48" t="str">
-        <v>9,343,739,104</v>
+        <v>9,664,394,925</v>
       </c>
       <c r="M48" t="str">
-        <v>597,227,966</v>
+        <v>640,005,866</v>
       </c>
       <c r="N48" t="str">
-        <v>6.39%</v>
+        <v>6.62%</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata/Bulanan/10. Okt-LD.xlsx
+++ b/rawdata/Bulanan/10. Okt-LD.xlsx
@@ -457,34 +457,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>10,956</v>
+        <v>11,296</v>
       </c>
       <c r="F2" t="str">
-        <v>5,409</v>
+        <v>5,590</v>
       </c>
       <c r="G2" t="str">
-        <v>1,513</v>
+        <v>1,561</v>
       </c>
       <c r="H2" t="str">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="I2" t="str">
-        <v>3,247,266,292</v>
+        <v>3,314,937,394</v>
       </c>
       <c r="J2" t="str">
-        <v>620</v>
+        <v>642</v>
       </c>
       <c r="K2" t="str">
-        <v>12,215,942,787</v>
+        <v>12,630,469,896</v>
       </c>
       <c r="L2" t="str">
-        <v>41,133,352,935</v>
+        <v>42,442,213,594</v>
       </c>
       <c r="M2" t="str">
-        <v>23,225,101,637</v>
+        <v>24,050,794,996</v>
       </c>
       <c r="N2" t="str">
-        <v>56.46%</v>
+        <v>56.67%</v>
       </c>
     </row>
     <row r="3">
@@ -501,34 +501,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>16,834</v>
+        <v>17,408</v>
       </c>
       <c r="F3" t="str">
-        <v>2,387</v>
+        <v>2,461</v>
       </c>
       <c r="G3" t="str">
-        <v>2,694</v>
+        <v>2,790</v>
       </c>
       <c r="H3" t="str">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="I3" t="str">
-        <v>2,039,124,065</v>
+        <v>2,109,663,491</v>
       </c>
       <c r="J3" t="str">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="K3" t="str">
-        <v>6,879,639,526</v>
+        <v>7,082,402,150</v>
       </c>
       <c r="L3" t="str">
-        <v>69,562,286,217</v>
+        <v>71,931,837,729</v>
       </c>
       <c r="M3" t="str">
-        <v>12,165,318,704</v>
+        <v>12,556,847,062</v>
       </c>
       <c r="N3" t="str">
-        <v>17.49%</v>
+        <v>17.46%</v>
       </c>
     </row>
     <row r="4">
@@ -545,34 +545,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>3,421</v>
+        <v>3,533</v>
       </c>
       <c r="F4" t="str">
-        <v>1,585</v>
+        <v>1,632</v>
       </c>
       <c r="G4" t="str">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="H4" t="str">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I4" t="str">
-        <v>1,040,617,099</v>
+        <v>1,092,505,805</v>
       </c>
       <c r="J4" t="str">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="K4" t="str">
-        <v>3,879,296,320</v>
+        <v>4,079,726,266</v>
       </c>
       <c r="L4" t="str">
-        <v>12,900,689,979</v>
+        <v>13,354,791,701</v>
       </c>
       <c r="M4" t="str">
-        <v>7,394,626,715</v>
+        <v>7,666,317,079</v>
       </c>
       <c r="N4" t="str">
-        <v>57.32%</v>
+        <v>57.40%</v>
       </c>
     </row>
     <row r="5">
@@ -589,10 +589,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>6,209</v>
+        <v>6,390</v>
       </c>
       <c r="F5" t="str">
-        <v>1,457</v>
+        <v>1,511</v>
       </c>
       <c r="G5" t="str">
         <v>29</v>
@@ -610,13 +610,13 @@
         <v>38,695,454</v>
       </c>
       <c r="L5" t="str">
-        <v>7,373,196,604</v>
+        <v>7,601,290,053</v>
       </c>
       <c r="M5" t="str">
-        <v>2,559,814,053</v>
+        <v>2,641,295,116</v>
       </c>
       <c r="N5" t="str">
-        <v>34.72%</v>
+        <v>34.75%</v>
       </c>
     </row>
     <row r="6">
@@ -633,13 +633,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>28,413</v>
+        <v>29,406</v>
       </c>
       <c r="F6" t="str">
-        <v>6,744</v>
+        <v>7,058</v>
       </c>
       <c r="G6" t="str">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H6" t="str">
         <v>12</v>
@@ -648,19 +648,19 @@
         <v>139,226,472</v>
       </c>
       <c r="J6" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6" t="str">
-        <v>101,641,843</v>
+        <v>123,598,123</v>
       </c>
       <c r="L6" t="str">
-        <v>33,800,026,831</v>
+        <v>35,072,316,034</v>
       </c>
       <c r="M6" t="str">
-        <v>10,467,171,232</v>
+        <v>10,989,746,875</v>
       </c>
       <c r="N6" t="str">
-        <v>30.97%</v>
+        <v>31.33%</v>
       </c>
     </row>
     <row r="7">
@@ -677,10 +677,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>569</v>
+        <v>673</v>
       </c>
       <c r="F7" t="str">
-        <v>183</v>
+        <v>226</v>
       </c>
       <c r="G7" t="str">
         <v>0</v>
@@ -698,13 +698,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="str">
-        <v>468,576,528</v>
+        <v>563,133,137</v>
       </c>
       <c r="M7" t="str">
-        <v>143,664,152</v>
+        <v>189,314,024</v>
       </c>
       <c r="N7" t="str">
-        <v>30.66%</v>
+        <v>33.62%</v>
       </c>
     </row>
     <row r="8">
@@ -721,34 +721,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>8,386</v>
+        <v>8,670</v>
       </c>
       <c r="F8" t="str">
-        <v>3,996</v>
+        <v>4,149</v>
       </c>
       <c r="G8" t="str">
-        <v>5,789</v>
+        <v>6,010</v>
       </c>
       <c r="H8" t="str">
-        <v>1,175</v>
+        <v>1,209</v>
       </c>
       <c r="I8" t="str">
-        <v>14,178,338,595</v>
+        <v>14,589,649,920</v>
       </c>
       <c r="J8" t="str">
-        <v>833</v>
+        <v>882</v>
       </c>
       <c r="K8" t="str">
-        <v>17,433,137,413</v>
+        <v>18,489,304,096</v>
       </c>
       <c r="L8" t="str">
-        <v>96,078,155,745</v>
+        <v>99,620,802,693</v>
       </c>
       <c r="M8" t="str">
-        <v>42,447,071,786</v>
+        <v>44,256,128,593</v>
       </c>
       <c r="N8" t="str">
-        <v>44.18%</v>
+        <v>44.42%</v>
       </c>
     </row>
     <row r="9">
@@ -765,10 +765,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>2,871</v>
+        <v>2,989</v>
       </c>
       <c r="F9" t="str">
-        <v>610</v>
+        <v>645</v>
       </c>
       <c r="G9" t="str">
         <v>4</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="str">
-        <v>3,541,611,756</v>
+        <v>3,674,091,511</v>
       </c>
       <c r="M9" t="str">
-        <v>1,005,266,904</v>
+        <v>1,054,259,454</v>
       </c>
       <c r="N9" t="str">
-        <v>28.38%</v>
+        <v>28.69%</v>
       </c>
     </row>
     <row r="10">
@@ -809,13 +809,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>3,676</v>
+        <v>3,772</v>
       </c>
       <c r="F10" t="str">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G10" t="str">
-        <v>8,910</v>
+        <v>9,163</v>
       </c>
       <c r="H10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>100,379,570</v>
       </c>
       <c r="L10" t="str">
-        <v>10,359,177,960</v>
+        <v>10,620,396,578</v>
       </c>
       <c r="M10" t="str">
-        <v>145,672,869</v>
+        <v>154,146,794</v>
       </c>
       <c r="N10" t="str">
-        <v>1.41%</v>
+        <v>1.45%</v>
       </c>
     </row>
     <row r="11">
@@ -853,13 +853,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>3,062</v>
+        <v>3,141</v>
       </c>
       <c r="F11" t="str">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G11" t="str">
-        <v>6,384</v>
+        <v>6,593</v>
       </c>
       <c r="H11" t="str">
         <v>2</v>
@@ -874,13 +874,13 @@
         <v>37,800,870</v>
       </c>
       <c r="L11" t="str">
-        <v>8,702,537,497</v>
+        <v>9,002,927,289</v>
       </c>
       <c r="M11" t="str">
-        <v>141,741,478</v>
+        <v>151,051,933</v>
       </c>
       <c r="N11" t="str">
-        <v>1.63%</v>
+        <v>1.68%</v>
       </c>
     </row>
     <row r="12">
@@ -897,13 +897,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>3,891</v>
+        <v>4,023</v>
       </c>
       <c r="F12" t="str">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G12" t="str">
-        <v>11,600</v>
+        <v>12,005</v>
       </c>
       <c r="H12" t="str">
         <v>1</v>
@@ -918,13 +918,13 @@
         <v>40,288,174</v>
       </c>
       <c r="L12" t="str">
-        <v>14,706,679,663</v>
+        <v>15,147,203,026</v>
       </c>
       <c r="M12" t="str">
-        <v>193,213,312</v>
+        <v>196,180,772</v>
       </c>
       <c r="N12" t="str">
-        <v>1.31%</v>
+        <v>1.30%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>2,424</v>
+        <v>2,506</v>
       </c>
       <c r="F13" t="str">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G13" t="str">
-        <v>7,950</v>
+        <v>8,213</v>
       </c>
       <c r="H13" t="str">
         <v>3</v>
@@ -962,13 +962,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="str">
-        <v>8,975,867,377</v>
+        <v>9,255,466,365</v>
       </c>
       <c r="M13" t="str">
-        <v>234,173,803</v>
+        <v>234,373,803</v>
       </c>
       <c r="N13" t="str">
-        <v>2.61%</v>
+        <v>2.53%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>1,225</v>
+        <v>1,259</v>
       </c>
       <c r="F14" t="str">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G14" t="str">
-        <v>4,168</v>
+        <v>4,282</v>
       </c>
       <c r="H14" t="str">
         <v>1</v>
@@ -1006,13 +1006,13 @@
         <v>35,694,915</v>
       </c>
       <c r="L14" t="str">
-        <v>4,541,876,626</v>
+        <v>4,635,326,661</v>
       </c>
       <c r="M14" t="str">
-        <v>100,519,190</v>
+        <v>100,819,190</v>
       </c>
       <c r="N14" t="str">
-        <v>2.21%</v>
+        <v>2.18%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>3,419</v>
+        <v>3,533</v>
       </c>
       <c r="F15" t="str">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G15" t="str">
-        <v>10,716</v>
+        <v>11,073</v>
       </c>
       <c r="H15" t="str">
         <v>1</v>
@@ -1050,13 +1050,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="str">
-        <v>12,637,260,166</v>
+        <v>13,069,471,797</v>
       </c>
       <c r="M15" t="str">
-        <v>204,841,834</v>
+        <v>213,877,175</v>
       </c>
       <c r="N15" t="str">
-        <v>1.62%</v>
+        <v>1.64%</v>
       </c>
     </row>
     <row r="16">
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>5,267</v>
+        <v>5,447</v>
       </c>
       <c r="F16" t="str">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G16" t="str">
-        <v>14,996</v>
+        <v>15,538</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>20,182,330,854</v>
+        <v>20,958,046,120</v>
       </c>
       <c r="M16" t="str">
-        <v>87,534,917</v>
+        <v>87,906,529</v>
       </c>
       <c r="N16" t="str">
-        <v>0.43%</v>
+        <v>0.42%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>2,517</v>
+        <v>2,603</v>
       </c>
       <c r="F17" t="str">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G17" t="str">
-        <v>5,744</v>
+        <v>5,976</v>
       </c>
       <c r="H17" t="str">
         <v>0</v>
@@ -1138,13 +1138,13 @@
         <v>233,859,144</v>
       </c>
       <c r="L17" t="str">
-        <v>8,733,525,412</v>
+        <v>9,067,003,190</v>
       </c>
       <c r="M17" t="str">
-        <v>180,557,351</v>
+        <v>181,207,138</v>
       </c>
       <c r="N17" t="str">
-        <v>2.07%</v>
+        <v>2.00%</v>
       </c>
     </row>
     <row r="18">
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>3,131</v>
+        <v>3,237</v>
       </c>
       <c r="F18" t="str">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G18" t="str">
-        <v>6,543</v>
+        <v>6,760</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>138,416,984</v>
       </c>
       <c r="L18" t="str">
-        <v>10,411,294,895</v>
+        <v>10,664,437,060</v>
       </c>
       <c r="M18" t="str">
-        <v>138,635,142</v>
+        <v>142,663,635</v>
       </c>
       <c r="N18" t="str">
-        <v>1.33%</v>
+        <v>1.34%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>4,117</v>
+        <v>4,260</v>
       </c>
       <c r="F19" t="str">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G19" t="str">
-        <v>15,171</v>
+        <v>15,712</v>
       </c>
       <c r="H19" t="str">
         <v>1</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>18,066,145,218</v>
+        <v>18,789,750,001</v>
       </c>
       <c r="M19" t="str">
-        <v>172,607,958</v>
+        <v>173,507,958</v>
       </c>
       <c r="N19" t="str">
-        <v>0.96%</v>
+        <v>0.92%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>686</v>
+        <v>709</v>
       </c>
       <c r="F20" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20" t="str">
-        <v>2,454</v>
+        <v>2,537</v>
       </c>
       <c r="H20" t="str">
         <v>0</v>
@@ -1270,13 +1270,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="str">
-        <v>2,975,295,688</v>
+        <v>3,103,336,592</v>
       </c>
       <c r="M20" t="str">
-        <v>11,695,275</v>
+        <v>13,558,436</v>
       </c>
       <c r="N20" t="str">
-        <v>0.39%</v>
+        <v>0.44%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>4,806</v>
+        <v>4,970</v>
       </c>
       <c r="F21" t="str">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G21" t="str">
-        <v>17,014</v>
+        <v>17,613</v>
       </c>
       <c r="H21" t="str">
         <v>2</v>
@@ -1314,13 +1314,13 @@
         <v>0</v>
       </c>
       <c r="L21" t="str">
-        <v>20,717,993,539</v>
+        <v>21,609,540,150</v>
       </c>
       <c r="M21" t="str">
-        <v>162,343,463</v>
+        <v>167,438,520</v>
       </c>
       <c r="N21" t="str">
-        <v>0.78%</v>
+        <v>0.77%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,13 +1337,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>24,225</v>
+        <v>24,484</v>
       </c>
       <c r="F22" t="str">
-        <v>1,165</v>
+        <v>1,238</v>
       </c>
       <c r="G22" t="str">
-        <v>674,626</v>
+        <v>699,026</v>
       </c>
       <c r="H22" t="str">
         <v>14</v>
@@ -1352,19 +1352,19 @@
         <v>158,624,610</v>
       </c>
       <c r="J22" t="str">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K22" t="str">
-        <v>295,866,488</v>
+        <v>341,466,488</v>
       </c>
       <c r="L22" t="str">
-        <v>105,274,210,576</v>
+        <v>106,041,841,688</v>
       </c>
       <c r="M22" t="str">
-        <v>3,053,505,524</v>
+        <v>3,254,427,058</v>
       </c>
       <c r="N22" t="str">
-        <v>2.90%</v>
+        <v>3.07%</v>
       </c>
     </row>
     <row r="23">
@@ -1381,13 +1381,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E23" t="str">
-        <v>1,214</v>
+        <v>1,220</v>
       </c>
       <c r="F23" t="str">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G23" t="str">
-        <v>14,971</v>
+        <v>15,501</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -1396,19 +1396,19 @@
         <v>0</v>
       </c>
       <c r="J23" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23" t="str">
-        <v>0</v>
+        <v>47,921,760</v>
       </c>
       <c r="L23" t="str">
-        <v>13,273,913,212</v>
+        <v>13,278,032,392</v>
       </c>
       <c r="M23" t="str">
-        <v>55,473,160</v>
+        <v>78,552,160</v>
       </c>
       <c r="N23" t="str">
-        <v>0.42%</v>
+        <v>0.59%</v>
       </c>
     </row>
     <row r="24">
@@ -1425,34 +1425,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>49,669</v>
+        <v>51,316</v>
       </c>
       <c r="F24" t="str">
-        <v>2,279</v>
+        <v>2,370</v>
       </c>
       <c r="G24" t="str">
-        <v>4,374</v>
+        <v>4,543</v>
       </c>
       <c r="H24" t="str">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="I24" t="str">
-        <v>3,898,102,974</v>
+        <v>4,068,722,460</v>
       </c>
       <c r="J24" t="str">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="K24" t="str">
-        <v>4,574,035,759</v>
+        <v>4,834,117,833</v>
       </c>
       <c r="L24" t="str">
-        <v>158,745,925,955</v>
+        <v>164,429,082,585</v>
       </c>
       <c r="M24" t="str">
-        <v>12,470,463,786</v>
+        <v>13,046,186,181</v>
       </c>
       <c r="N24" t="str">
-        <v>7.86%</v>
+        <v>7.93%</v>
       </c>
     </row>
     <row r="25">
@@ -1469,13 +1469,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E25" t="str">
-        <v>2,327</v>
+        <v>2,405</v>
       </c>
       <c r="F25" t="str">
-        <v>745</v>
+        <v>767</v>
       </c>
       <c r="G25" t="str">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H25" t="str">
         <v>12</v>
@@ -1490,13 +1490,13 @@
         <v>566,472,818</v>
       </c>
       <c r="L25" t="str">
-        <v>6,002,129,191</v>
+        <v>6,197,478,032</v>
       </c>
       <c r="M25" t="str">
-        <v>1,645,428,745</v>
+        <v>1,664,050,492</v>
       </c>
       <c r="N25" t="str">
-        <v>27.41%</v>
+        <v>26.85%</v>
       </c>
     </row>
     <row r="26">
@@ -1513,13 +1513,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>5,034</v>
+        <v>5,191</v>
       </c>
       <c r="F26" t="str">
-        <v>1,535</v>
+        <v>1,598</v>
       </c>
       <c r="G26" t="str">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="H26" t="str">
         <v>39</v>
@@ -1528,19 +1528,19 @@
         <v>493,624,741</v>
       </c>
       <c r="J26" t="str">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K26" t="str">
-        <v>739,841,326</v>
+        <v>774,711,002</v>
       </c>
       <c r="L26" t="str">
-        <v>12,930,200,469</v>
+        <v>13,321,120,465</v>
       </c>
       <c r="M26" t="str">
-        <v>3,274,430,096</v>
+        <v>3,423,856,885</v>
       </c>
       <c r="N26" t="str">
-        <v>25.32%</v>
+        <v>25.70%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,10 +1557,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>2,403</v>
+        <v>2,520</v>
       </c>
       <c r="F27" t="str">
-        <v>478</v>
+        <v>504</v>
       </c>
       <c r="G27" t="str">
         <v>0</v>
@@ -1578,13 +1578,13 @@
         <v>0</v>
       </c>
       <c r="L27" t="str">
-        <v>2,474,116,563</v>
+        <v>2,589,773,104</v>
       </c>
       <c r="M27" t="str">
-        <v>566,013,779</v>
+        <v>592,274,565</v>
       </c>
       <c r="N27" t="str">
-        <v>22.88%</v>
+        <v>22.87%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,10 +1601,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>20,780</v>
+        <v>21,804</v>
       </c>
       <c r="F28" t="str">
-        <v>3,582</v>
+        <v>3,776</v>
       </c>
       <c r="G28" t="str">
         <v>2</v>
@@ -1622,13 +1622,13 @@
         <v>0</v>
       </c>
       <c r="L28" t="str">
-        <v>21,411,463,682</v>
+        <v>22,440,916,812</v>
       </c>
       <c r="M28" t="str">
-        <v>4,160,697,894</v>
+        <v>4,364,367,525</v>
       </c>
       <c r="N28" t="str">
-        <v>19.43%</v>
+        <v>19.45%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,10 +1645,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>332</v>
+        <v>391</v>
       </c>
       <c r="F29" t="str">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="G29" t="str">
         <v>0</v>
@@ -1666,13 +1666,13 @@
         <v>0</v>
       </c>
       <c r="L29" t="str">
-        <v>263,802,741</v>
+        <v>307,784,344</v>
       </c>
       <c r="M29" t="str">
-        <v>59,442,044</v>
+        <v>71,783,964</v>
       </c>
       <c r="N29" t="str">
-        <v>22.53%</v>
+        <v>23.32%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,34 +1689,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>4,180</v>
+        <v>4,392</v>
       </c>
       <c r="F30" t="str">
-        <v>1,377</v>
+        <v>1,446</v>
       </c>
       <c r="G30" t="str">
-        <v>1,578</v>
+        <v>1,661</v>
       </c>
       <c r="H30" t="str">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="I30" t="str">
-        <v>3,477,825,196</v>
+        <v>3,652,906,003</v>
       </c>
       <c r="J30" t="str">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="K30" t="str">
-        <v>3,905,872,912</v>
+        <v>4,081,073,857</v>
       </c>
       <c r="L30" t="str">
-        <v>44,752,692,041</v>
+        <v>47,082,140,684</v>
       </c>
       <c r="M30" t="str">
-        <v>12,384,968,618</v>
+        <v>12,986,226,963</v>
       </c>
       <c r="N30" t="str">
-        <v>27.67%</v>
+        <v>27.58%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,10 +1733,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>3,791</v>
+        <v>3,948</v>
       </c>
       <c r="F31" t="str">
-        <v>663</v>
+        <v>702</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1754,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>4,052,564,500</v>
+        <v>4,202,736,621</v>
       </c>
       <c r="M31" t="str">
-        <v>827,878,776</v>
+        <v>872,537,396</v>
       </c>
       <c r="N31" t="str">
-        <v>20.43%</v>
+        <v>20.76%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,13 +1777,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>4,345</v>
+        <v>4,442</v>
       </c>
       <c r="F32" t="str">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="G32" t="str">
-        <v>2,022</v>
+        <v>2,071</v>
       </c>
       <c r="H32" t="str">
         <v>9</v>
@@ -1798,13 +1798,13 @@
         <v>102,003,250</v>
       </c>
       <c r="L32" t="str">
-        <v>11,612,964,542</v>
+        <v>11,915,209,732</v>
       </c>
       <c r="M32" t="str">
-        <v>1,145,306,815</v>
+        <v>1,161,271,263</v>
       </c>
       <c r="N32" t="str">
-        <v>9.86%</v>
+        <v>9.75%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,13 +1821,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>1,438</v>
+        <v>1,498</v>
       </c>
       <c r="F33" t="str">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="G33" t="str">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="H33" t="str">
         <v>7</v>
@@ -1842,13 +1842,13 @@
         <v>81,160,766</v>
       </c>
       <c r="L33" t="str">
-        <v>3,543,764,880</v>
+        <v>3,710,191,295</v>
       </c>
       <c r="M33" t="str">
-        <v>558,629,206</v>
+        <v>576,569,354</v>
       </c>
       <c r="N33" t="str">
-        <v>15.76%</v>
+        <v>15.54%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,10 +1865,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>3,198</v>
+        <v>3,273</v>
       </c>
       <c r="F34" t="str">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="G34" t="str">
         <v>96</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>3,331,904,890</v>
+        <v>3,381,087,456</v>
       </c>
       <c r="M34" t="str">
-        <v>520,575,313</v>
+        <v>526,372,210</v>
       </c>
       <c r="N34" t="str">
-        <v>15.62%</v>
+        <v>15.57%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,13 +1909,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>10,812</v>
+        <v>11,203</v>
       </c>
       <c r="F35" t="str">
-        <v>1,201</v>
+        <v>1,258</v>
       </c>
       <c r="G35" t="str">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="H35" t="str">
         <v>4</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="L35" t="str">
-        <v>11,166,010,626</v>
+        <v>11,429,887,521</v>
       </c>
       <c r="M35" t="str">
-        <v>1,357,509,859</v>
+        <v>1,403,870,153</v>
       </c>
       <c r="N35" t="str">
-        <v>12.16%</v>
+        <v>12.28%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,10 +1953,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>240</v>
+        <v>282</v>
       </c>
       <c r="F36" t="str">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G36" t="str">
         <v>0</v>
@@ -1974,13 +1974,13 @@
         <v>0</v>
       </c>
       <c r="L36" t="str">
-        <v>201,260,014</v>
+        <v>232,381,159</v>
       </c>
       <c r="M36" t="str">
-        <v>31,822,951</v>
+        <v>32,645,248</v>
       </c>
       <c r="N36" t="str">
-        <v>15.81%</v>
+        <v>14.05%</v>
       </c>
     </row>
     <row r="37">
@@ -1997,34 +1997,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>1,571</v>
+        <v>1,605</v>
       </c>
       <c r="F37" t="str">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="G37" t="str">
-        <v>2,626</v>
+        <v>2,719</v>
       </c>
       <c r="H37" t="str">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I37" t="str">
-        <v>831,711,648</v>
+        <v>860,230,790</v>
       </c>
       <c r="J37" t="str">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K37" t="str">
-        <v>1,111,128,016</v>
+        <v>1,145,782,044</v>
       </c>
       <c r="L37" t="str">
-        <v>16,018,593,367</v>
+        <v>16,360,920,969</v>
       </c>
       <c r="M37" t="str">
-        <v>3,057,792,419</v>
+        <v>3,151,118,473</v>
       </c>
       <c r="N37" t="str">
-        <v>19.09%</v>
+        <v>19.26%</v>
       </c>
     </row>
     <row r="38">
@@ -2041,10 +2041,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>4,946</v>
+        <v>5,066</v>
       </c>
       <c r="F38" t="str">
-        <v>495</v>
+        <v>516</v>
       </c>
       <c r="G38" t="str">
         <v>238</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>5,206,832,481</v>
+        <v>5,289,811,061</v>
       </c>
       <c r="M38" t="str">
-        <v>547,753,842</v>
+        <v>572,719,128</v>
       </c>
       <c r="N38" t="str">
-        <v>10.52%</v>
+        <v>10.83%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,13 +2085,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>3,547</v>
+        <v>3,667</v>
       </c>
       <c r="F39" t="str">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="G39" t="str">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H39" t="str">
         <v>0</v>
@@ -2106,13 +2106,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>3,637,108,609</v>
+        <v>3,714,182,265</v>
       </c>
       <c r="M39" t="str">
-        <v>368,215,846</v>
+        <v>378,954,815</v>
       </c>
       <c r="N39" t="str">
-        <v>10.12%</v>
+        <v>10.20%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,19 +2173,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>1,336</v>
+        <v>1,370</v>
       </c>
       <c r="F41" t="str">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="G41" t="str">
-        <v>2,458</v>
+        <v>2,547</v>
       </c>
       <c r="H41" t="str">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I41" t="str">
-        <v>597,492,511</v>
+        <v>607,808,386</v>
       </c>
       <c r="J41" t="str">
         <v>27</v>
@@ -2194,13 +2194,13 @@
         <v>522,990,481</v>
       </c>
       <c r="L41" t="str">
-        <v>13,334,774,602</v>
+        <v>13,695,258,786</v>
       </c>
       <c r="M41" t="str">
-        <v>1,910,258,411</v>
+        <v>1,943,806,908</v>
       </c>
       <c r="N41" t="str">
-        <v>14.33%</v>
+        <v>14.19%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>6,427</v>
+        <v>6,558</v>
       </c>
       <c r="F42" t="str">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="G42" t="str">
-        <v>8,619</v>
+        <v>8,930</v>
       </c>
       <c r="H42" t="str">
         <v>5</v>
@@ -2238,13 +2238,13 @@
         <v>151,104,880</v>
       </c>
       <c r="L42" t="str">
-        <v>15,977,561,982</v>
+        <v>16,359,819,583</v>
       </c>
       <c r="M42" t="str">
-        <v>600,742,248</v>
+        <v>611,398,639</v>
       </c>
       <c r="N42" t="str">
-        <v>3.76%</v>
+        <v>3.74%</v>
       </c>
     </row>
     <row r="43">
@@ -2305,13 +2305,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>1,976</v>
+        <v>2,060</v>
       </c>
       <c r="F44" t="str">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G44" t="str">
-        <v>1,881</v>
+        <v>1,965</v>
       </c>
       <c r="H44" t="str">
         <v>2</v>
@@ -2326,13 +2326,13 @@
         <v>50,770,592</v>
       </c>
       <c r="L44" t="str">
-        <v>4,198,775,030</v>
+        <v>4,372,970,372</v>
       </c>
       <c r="M44" t="str">
-        <v>169,979,375</v>
+        <v>173,372,367</v>
       </c>
       <c r="N44" t="str">
-        <v>4.05%</v>
+        <v>3.96%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,13 +2349,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>1,237</v>
+        <v>1,279</v>
       </c>
       <c r="F45" t="str">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G45" t="str">
-        <v>1,881</v>
+        <v>1,958</v>
       </c>
       <c r="H45" t="str">
         <v>0</v>
@@ -2370,13 +2370,13 @@
         <v>66,445,865</v>
       </c>
       <c r="L45" t="str">
-        <v>2,951,284,238</v>
+        <v>3,018,990,411</v>
       </c>
       <c r="M45" t="str">
-        <v>107,397,804</v>
+        <v>108,097,875</v>
       </c>
       <c r="N45" t="str">
-        <v>3.64%</v>
+        <v>3.58%</v>
       </c>
     </row>
     <row r="46">
@@ -2393,19 +2393,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E46" t="str">
-        <v>4,962</v>
+        <v>5,131</v>
       </c>
       <c r="F46" t="str">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="G46" t="str">
-        <v>7,397</v>
+        <v>7,613</v>
       </c>
       <c r="H46" t="str">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I46" t="str">
-        <v>159,496,582</v>
+        <v>191,379,503</v>
       </c>
       <c r="J46" t="str">
         <v>4</v>
@@ -2414,13 +2414,13 @@
         <v>80,274,644</v>
       </c>
       <c r="L46" t="str">
-        <v>11,386,050,418</v>
+        <v>11,693,598,550</v>
       </c>
       <c r="M46" t="str">
-        <v>636,280,217</v>
+        <v>683,640,800</v>
       </c>
       <c r="N46" t="str">
-        <v>5.59%</v>
+        <v>5.85%</v>
       </c>
     </row>
     <row r="47">
@@ -2437,19 +2437,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E47" t="str">
-        <v>5,719</v>
+        <v>6,122</v>
       </c>
       <c r="F47" t="str">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="G47" t="str">
-        <v>4,818</v>
+        <v>5,061</v>
       </c>
       <c r="H47" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I47" t="str">
-        <v>61,245,665</v>
+        <v>73,735,944</v>
       </c>
       <c r="J47" t="str">
         <v>5</v>
@@ -2458,13 +2458,13 @@
         <v>86,522,238</v>
       </c>
       <c r="L47" t="str">
-        <v>12,842,838,917</v>
+        <v>13,571,556,899</v>
       </c>
       <c r="M47" t="str">
-        <v>475,609,805</v>
+        <v>505,483,697</v>
       </c>
       <c r="N47" t="str">
-        <v>3.70%</v>
+        <v>3.72%</v>
       </c>
     </row>
     <row r="48">
@@ -2481,19 +2481,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E48" t="str">
-        <v>4,344</v>
+        <v>4,494</v>
       </c>
       <c r="F48" t="str">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="G48" t="str">
-        <v>6,215</v>
+        <v>6,423</v>
       </c>
       <c r="H48" t="str">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I48" t="str">
-        <v>71,679,870</v>
+        <v>82,418,874</v>
       </c>
       <c r="J48" t="str">
         <v>9</v>
@@ -2502,13 +2502,13 @@
         <v>170,628,519</v>
       </c>
       <c r="L48" t="str">
-        <v>9,664,394,925</v>
+        <v>9,897,403,356</v>
       </c>
       <c r="M48" t="str">
-        <v>640,005,866</v>
+        <v>658,713,326</v>
       </c>
       <c r="N48" t="str">
-        <v>6.62%</v>
+        <v>6.66%</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata/Bulanan/10. Okt-LD.xlsx
+++ b/rawdata/Bulanan/10. Okt-LD.xlsx
@@ -457,34 +457,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>11,296</v>
+        <v>11,663</v>
       </c>
       <c r="F2" t="str">
-        <v>5,590</v>
+        <v>5,760</v>
       </c>
       <c r="G2" t="str">
-        <v>1,561</v>
+        <v>1,610</v>
       </c>
       <c r="H2" t="str">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="I2" t="str">
-        <v>3,314,937,394</v>
+        <v>3,451,771,255</v>
       </c>
       <c r="J2" t="str">
-        <v>642</v>
+        <v>663</v>
       </c>
       <c r="K2" t="str">
-        <v>12,630,469,896</v>
+        <v>13,044,216,652</v>
       </c>
       <c r="L2" t="str">
-        <v>42,442,213,594</v>
+        <v>43,750,574,833</v>
       </c>
       <c r="M2" t="str">
-        <v>24,050,794,996</v>
+        <v>24,828,946,751</v>
       </c>
       <c r="N2" t="str">
-        <v>56.67%</v>
+        <v>56.75%</v>
       </c>
     </row>
     <row r="3">
@@ -501,34 +501,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>17,408</v>
+        <v>17,901</v>
       </c>
       <c r="F3" t="str">
-        <v>2,461</v>
+        <v>2,535</v>
       </c>
       <c r="G3" t="str">
-        <v>2,790</v>
+        <v>2,862</v>
       </c>
       <c r="H3" t="str">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="I3" t="str">
-        <v>2,109,663,491</v>
+        <v>2,200,302,418</v>
       </c>
       <c r="J3" t="str">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="K3" t="str">
-        <v>7,082,402,150</v>
+        <v>7,264,807,514</v>
       </c>
       <c r="L3" t="str">
-        <v>71,931,837,729</v>
+        <v>73,862,772,603</v>
       </c>
       <c r="M3" t="str">
-        <v>12,556,847,062</v>
+        <v>12,928,820,479</v>
       </c>
       <c r="N3" t="str">
-        <v>17.46%</v>
+        <v>17.50%</v>
       </c>
     </row>
     <row r="4">
@@ -545,34 +545,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>3,533</v>
+        <v>3,654</v>
       </c>
       <c r="F4" t="str">
-        <v>1,632</v>
+        <v>1,694</v>
       </c>
       <c r="G4" t="str">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="H4" t="str">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I4" t="str">
-        <v>1,092,505,805</v>
+        <v>1,133,959,847</v>
       </c>
       <c r="J4" t="str">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="K4" t="str">
-        <v>4,079,726,266</v>
+        <v>4,305,104,279</v>
       </c>
       <c r="L4" t="str">
-        <v>13,354,791,701</v>
+        <v>13,842,617,667</v>
       </c>
       <c r="M4" t="str">
-        <v>7,666,317,079</v>
+        <v>8,012,389,892</v>
       </c>
       <c r="N4" t="str">
-        <v>57.40%</v>
+        <v>57.88%</v>
       </c>
     </row>
     <row r="5">
@@ -589,10 +589,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>6,390</v>
+        <v>6,544</v>
       </c>
       <c r="F5" t="str">
-        <v>1,511</v>
+        <v>1,563</v>
       </c>
       <c r="G5" t="str">
         <v>29</v>
@@ -610,13 +610,13 @@
         <v>38,695,454</v>
       </c>
       <c r="L5" t="str">
-        <v>7,601,290,053</v>
+        <v>7,793,635,276</v>
       </c>
       <c r="M5" t="str">
-        <v>2,641,295,116</v>
+        <v>2,722,072,280</v>
       </c>
       <c r="N5" t="str">
-        <v>34.75%</v>
+        <v>34.93%</v>
       </c>
     </row>
     <row r="6">
@@ -633,13 +633,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>29,406</v>
+        <v>30,311</v>
       </c>
       <c r="F6" t="str">
-        <v>7,058</v>
+        <v>7,335</v>
       </c>
       <c r="G6" t="str">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H6" t="str">
         <v>12</v>
@@ -654,13 +654,13 @@
         <v>123,598,123</v>
       </c>
       <c r="L6" t="str">
-        <v>35,072,316,034</v>
+        <v>36,260,993,218</v>
       </c>
       <c r="M6" t="str">
-        <v>10,989,746,875</v>
+        <v>11,401,445,910</v>
       </c>
       <c r="N6" t="str">
-        <v>31.33%</v>
+        <v>31.44%</v>
       </c>
     </row>
     <row r="7">
@@ -677,10 +677,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>673</v>
+        <v>771</v>
       </c>
       <c r="F7" t="str">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="G7" t="str">
         <v>0</v>
@@ -698,13 +698,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="str">
-        <v>563,133,137</v>
+        <v>651,640,647</v>
       </c>
       <c r="M7" t="str">
-        <v>189,314,024</v>
+        <v>218,281,496</v>
       </c>
       <c r="N7" t="str">
-        <v>33.62%</v>
+        <v>33.50%</v>
       </c>
     </row>
     <row r="8">
@@ -721,34 +721,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>8,670</v>
+        <v>8,948</v>
       </c>
       <c r="F8" t="str">
-        <v>4,149</v>
+        <v>4,279</v>
       </c>
       <c r="G8" t="str">
-        <v>6,010</v>
+        <v>6,228</v>
       </c>
       <c r="H8" t="str">
-        <v>1,209</v>
+        <v>1,235</v>
       </c>
       <c r="I8" t="str">
-        <v>14,589,649,920</v>
+        <v>14,899,035,161</v>
       </c>
       <c r="J8" t="str">
-        <v>882</v>
+        <v>912</v>
       </c>
       <c r="K8" t="str">
-        <v>18,489,304,096</v>
+        <v>19,106,263,205</v>
       </c>
       <c r="L8" t="str">
-        <v>99,620,802,693</v>
+        <v>102,927,242,166</v>
       </c>
       <c r="M8" t="str">
-        <v>44,256,128,593</v>
+        <v>45,605,864,974</v>
       </c>
       <c r="N8" t="str">
-        <v>44.42%</v>
+        <v>44.31%</v>
       </c>
     </row>
     <row r="9">
@@ -765,10 +765,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>2,989</v>
+        <v>3,092</v>
       </c>
       <c r="F9" t="str">
-        <v>645</v>
+        <v>676</v>
       </c>
       <c r="G9" t="str">
         <v>4</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="str">
-        <v>3,674,091,511</v>
+        <v>3,796,631,274</v>
       </c>
       <c r="M9" t="str">
-        <v>1,054,259,454</v>
+        <v>1,097,075,397</v>
       </c>
       <c r="N9" t="str">
-        <v>28.69%</v>
+        <v>28.90%</v>
       </c>
     </row>
     <row r="10">
@@ -809,13 +809,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>3,772</v>
+        <v>3,878</v>
       </c>
       <c r="F10" t="str">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G10" t="str">
-        <v>9,163</v>
+        <v>9,420</v>
       </c>
       <c r="H10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>100,379,570</v>
       </c>
       <c r="L10" t="str">
-        <v>10,620,396,578</v>
+        <v>10,916,313,097</v>
       </c>
       <c r="M10" t="str">
-        <v>154,146,794</v>
+        <v>155,857,136</v>
       </c>
       <c r="N10" t="str">
-        <v>1.45%</v>
+        <v>1.43%</v>
       </c>
     </row>
     <row r="11">
@@ -853,13 +853,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>3,141</v>
+        <v>3,227</v>
       </c>
       <c r="F11" t="str">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G11" t="str">
-        <v>6,593</v>
+        <v>6,807</v>
       </c>
       <c r="H11" t="str">
         <v>2</v>
@@ -874,13 +874,13 @@
         <v>37,800,870</v>
       </c>
       <c r="L11" t="str">
-        <v>9,002,927,289</v>
+        <v>9,270,947,854</v>
       </c>
       <c r="M11" t="str">
-        <v>151,051,933</v>
+        <v>154,266,252</v>
       </c>
       <c r="N11" t="str">
-        <v>1.68%</v>
+        <v>1.66%</v>
       </c>
     </row>
     <row r="12">
@@ -897,13 +897,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>4,023</v>
+        <v>4,145</v>
       </c>
       <c r="F12" t="str">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G12" t="str">
-        <v>12,005</v>
+        <v>12,406</v>
       </c>
       <c r="H12" t="str">
         <v>1</v>
@@ -918,13 +918,13 @@
         <v>40,288,174</v>
       </c>
       <c r="L12" t="str">
-        <v>15,147,203,026</v>
+        <v>15,541,054,050</v>
       </c>
       <c r="M12" t="str">
-        <v>196,180,772</v>
+        <v>198,756,839</v>
       </c>
       <c r="N12" t="str">
-        <v>1.30%</v>
+        <v>1.28%</v>
       </c>
     </row>
     <row r="13">
@@ -941,19 +941,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>2,506</v>
+        <v>2,584</v>
       </c>
       <c r="F13" t="str">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G13" t="str">
-        <v>8,213</v>
+        <v>8,482</v>
       </c>
       <c r="H13" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13" t="str">
-        <v>32,410,311</v>
+        <v>45,729,968</v>
       </c>
       <c r="J13" t="str">
         <v>0</v>
@@ -962,13 +962,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="str">
-        <v>9,255,466,365</v>
+        <v>9,527,883,131</v>
       </c>
       <c r="M13" t="str">
-        <v>234,373,803</v>
+        <v>260,585,857</v>
       </c>
       <c r="N13" t="str">
-        <v>2.53%</v>
+        <v>2.73%</v>
       </c>
     </row>
     <row r="14">
@@ -985,13 +985,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>1,259</v>
+        <v>1,289</v>
       </c>
       <c r="F14" t="str">
         <v>35</v>
       </c>
       <c r="G14" t="str">
-        <v>4,282</v>
+        <v>4,391</v>
       </c>
       <c r="H14" t="str">
         <v>1</v>
@@ -1006,13 +1006,13 @@
         <v>35,694,915</v>
       </c>
       <c r="L14" t="str">
-        <v>4,635,326,661</v>
+        <v>4,769,869,432</v>
       </c>
       <c r="M14" t="str">
         <v>100,819,190</v>
       </c>
       <c r="N14" t="str">
-        <v>2.18%</v>
+        <v>2.11%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>3,533</v>
+        <v>3,639</v>
       </c>
       <c r="F15" t="str">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="G15" t="str">
-        <v>11,073</v>
+        <v>11,429</v>
       </c>
       <c r="H15" t="str">
         <v>1</v>
@@ -1050,13 +1050,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="str">
-        <v>13,069,471,797</v>
+        <v>13,394,862,390</v>
       </c>
       <c r="M15" t="str">
-        <v>213,877,175</v>
+        <v>230,518,812</v>
       </c>
       <c r="N15" t="str">
-        <v>1.64%</v>
+        <v>1.72%</v>
       </c>
     </row>
     <row r="16">
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>5,447</v>
+        <v>5,608</v>
       </c>
       <c r="F16" t="str">
         <v>31</v>
       </c>
       <c r="G16" t="str">
-        <v>15,538</v>
+        <v>16,076</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>20,958,046,120</v>
+        <v>21,470,601,321</v>
       </c>
       <c r="M16" t="str">
         <v>87,906,529</v>
       </c>
       <c r="N16" t="str">
-        <v>0.42%</v>
+        <v>0.41%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>2,603</v>
+        <v>2,674</v>
       </c>
       <c r="F17" t="str">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G17" t="str">
-        <v>5,976</v>
+        <v>6,203</v>
       </c>
       <c r="H17" t="str">
         <v>0</v>
@@ -1138,13 +1138,13 @@
         <v>233,859,144</v>
       </c>
       <c r="L17" t="str">
-        <v>9,067,003,190</v>
+        <v>9,250,822,606</v>
       </c>
       <c r="M17" t="str">
-        <v>181,207,138</v>
+        <v>181,695,019</v>
       </c>
       <c r="N17" t="str">
-        <v>2.00%</v>
+        <v>1.96%</v>
       </c>
     </row>
     <row r="18">
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>3,237</v>
+        <v>3,324</v>
       </c>
       <c r="F18" t="str">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G18" t="str">
-        <v>6,760</v>
+        <v>6,975</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>138,416,984</v>
       </c>
       <c r="L18" t="str">
-        <v>10,664,437,060</v>
+        <v>10,979,096,256</v>
       </c>
       <c r="M18" t="str">
-        <v>142,663,635</v>
+        <v>144,555,202</v>
       </c>
       <c r="N18" t="str">
-        <v>1.34%</v>
+        <v>1.32%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>4,260</v>
+        <v>4,398</v>
       </c>
       <c r="F19" t="str">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G19" t="str">
-        <v>15,712</v>
+        <v>16,255</v>
       </c>
       <c r="H19" t="str">
         <v>1</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>18,789,750,001</v>
+        <v>19,288,403,775</v>
       </c>
       <c r="M19" t="str">
-        <v>173,507,958</v>
+        <v>180,218,230</v>
       </c>
       <c r="N19" t="str">
-        <v>0.92%</v>
+        <v>0.93%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>709</v>
+        <v>732</v>
       </c>
       <c r="F20" t="str">
         <v>5</v>
       </c>
       <c r="G20" t="str">
-        <v>2,537</v>
+        <v>2,617</v>
       </c>
       <c r="H20" t="str">
         <v>0</v>
@@ -1270,13 +1270,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="str">
-        <v>3,103,336,592</v>
+        <v>3,174,227,989</v>
       </c>
       <c r="M20" t="str">
         <v>13,558,436</v>
       </c>
       <c r="N20" t="str">
-        <v>0.44%</v>
+        <v>0.43%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>4,970</v>
+        <v>5,130</v>
       </c>
       <c r="F21" t="str">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G21" t="str">
-        <v>17,613</v>
+        <v>18,217</v>
       </c>
       <c r="H21" t="str">
         <v>2</v>
@@ -1314,13 +1314,13 @@
         <v>0</v>
       </c>
       <c r="L21" t="str">
-        <v>21,609,540,150</v>
+        <v>22,155,396,373</v>
       </c>
       <c r="M21" t="str">
-        <v>167,438,520</v>
+        <v>177,440,985</v>
       </c>
       <c r="N21" t="str">
-        <v>0.77%</v>
+        <v>0.80%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,34 +1337,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>24,484</v>
+        <v>24,699</v>
       </c>
       <c r="F22" t="str">
-        <v>1,238</v>
+        <v>1,380</v>
       </c>
       <c r="G22" t="str">
-        <v>699,026</v>
+        <v>723,443</v>
       </c>
       <c r="H22" t="str">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I22" t="str">
-        <v>158,624,610</v>
+        <v>190,624,610</v>
       </c>
       <c r="J22" t="str">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K22" t="str">
-        <v>341,466,488</v>
+        <v>476,826,156</v>
       </c>
       <c r="L22" t="str">
-        <v>106,041,841,688</v>
+        <v>106,723,749,882</v>
       </c>
       <c r="M22" t="str">
-        <v>3,254,427,058</v>
+        <v>3,676,786,686</v>
       </c>
       <c r="N22" t="str">
-        <v>3.07%</v>
+        <v>3.45%</v>
       </c>
     </row>
     <row r="23">
@@ -1381,13 +1381,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E23" t="str">
-        <v>1,220</v>
+        <v>1,224</v>
       </c>
       <c r="F23" t="str">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G23" t="str">
-        <v>15,501</v>
+        <v>16,030</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -1402,13 +1402,13 @@
         <v>47,921,760</v>
       </c>
       <c r="L23" t="str">
-        <v>13,278,032,392</v>
+        <v>13,279,712,648</v>
       </c>
       <c r="M23" t="str">
-        <v>78,552,160</v>
+        <v>90,825,450</v>
       </c>
       <c r="N23" t="str">
-        <v>0.59%</v>
+        <v>0.68%</v>
       </c>
     </row>
     <row r="24">
@@ -1425,34 +1425,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>51,316</v>
+        <v>52,909</v>
       </c>
       <c r="F24" t="str">
-        <v>2,370</v>
+        <v>2,476</v>
       </c>
       <c r="G24" t="str">
-        <v>4,543</v>
+        <v>4,710</v>
       </c>
       <c r="H24" t="str">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="I24" t="str">
-        <v>4,068,722,460</v>
+        <v>4,197,022,633</v>
       </c>
       <c r="J24" t="str">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="K24" t="str">
-        <v>4,834,117,833</v>
+        <v>5,086,964,183</v>
       </c>
       <c r="L24" t="str">
-        <v>164,429,082,585</v>
+        <v>170,030,614,300</v>
       </c>
       <c r="M24" t="str">
-        <v>13,046,186,181</v>
+        <v>13,634,773,232</v>
       </c>
       <c r="N24" t="str">
-        <v>7.93%</v>
+        <v>8.02%</v>
       </c>
     </row>
     <row r="25">
@@ -1469,13 +1469,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E25" t="str">
-        <v>2,405</v>
+        <v>2,480</v>
       </c>
       <c r="F25" t="str">
-        <v>767</v>
+        <v>795</v>
       </c>
       <c r="G25" t="str">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H25" t="str">
         <v>12</v>
@@ -1490,13 +1490,13 @@
         <v>566,472,818</v>
       </c>
       <c r="L25" t="str">
-        <v>6,197,478,032</v>
+        <v>6,355,033,472</v>
       </c>
       <c r="M25" t="str">
-        <v>1,664,050,492</v>
+        <v>1,699,684,410</v>
       </c>
       <c r="N25" t="str">
-        <v>26.85%</v>
+        <v>26.75%</v>
       </c>
     </row>
     <row r="26">
@@ -1513,34 +1513,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>5,191</v>
+        <v>5,339</v>
       </c>
       <c r="F26" t="str">
-        <v>1,598</v>
+        <v>1,662</v>
       </c>
       <c r="G26" t="str">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="H26" t="str">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I26" t="str">
-        <v>493,624,741</v>
+        <v>507,627,067</v>
       </c>
       <c r="J26" t="str">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K26" t="str">
-        <v>774,711,002</v>
+        <v>831,348,142</v>
       </c>
       <c r="L26" t="str">
-        <v>13,321,120,465</v>
+        <v>13,667,073,609</v>
       </c>
       <c r="M26" t="str">
-        <v>3,423,856,885</v>
+        <v>3,544,247,726</v>
       </c>
       <c r="N26" t="str">
-        <v>25.70%</v>
+        <v>25.93%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,10 +1557,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>2,520</v>
+        <v>2,608</v>
       </c>
       <c r="F27" t="str">
-        <v>504</v>
+        <v>528</v>
       </c>
       <c r="G27" t="str">
         <v>0</v>
@@ -1578,13 +1578,13 @@
         <v>0</v>
       </c>
       <c r="L27" t="str">
-        <v>2,589,773,104</v>
+        <v>2,674,912,814</v>
       </c>
       <c r="M27" t="str">
-        <v>592,274,565</v>
+        <v>621,203,794</v>
       </c>
       <c r="N27" t="str">
-        <v>22.87%</v>
+        <v>23.22%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,10 +1601,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>21,804</v>
+        <v>22,537</v>
       </c>
       <c r="F28" t="str">
-        <v>3,776</v>
+        <v>3,936</v>
       </c>
       <c r="G28" t="str">
         <v>2</v>
@@ -1622,13 +1622,13 @@
         <v>0</v>
       </c>
       <c r="L28" t="str">
-        <v>22,440,916,812</v>
+        <v>23,241,937,840</v>
       </c>
       <c r="M28" t="str">
-        <v>4,364,367,525</v>
+        <v>4,537,395,946</v>
       </c>
       <c r="N28" t="str">
-        <v>19.45%</v>
+        <v>19.52%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,10 +1645,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>391</v>
+        <v>450</v>
       </c>
       <c r="F29" t="str">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="G29" t="str">
         <v>0</v>
@@ -1666,13 +1666,13 @@
         <v>0</v>
       </c>
       <c r="L29" t="str">
-        <v>307,784,344</v>
+        <v>351,436,051</v>
       </c>
       <c r="M29" t="str">
-        <v>71,783,964</v>
+        <v>88,207,785</v>
       </c>
       <c r="N29" t="str">
-        <v>23.32%</v>
+        <v>25.10%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,34 +1689,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>4,392</v>
+        <v>4,521</v>
       </c>
       <c r="F30" t="str">
-        <v>1,446</v>
+        <v>1,492</v>
       </c>
       <c r="G30" t="str">
-        <v>1,661</v>
+        <v>1,707</v>
       </c>
       <c r="H30" t="str">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="I30" t="str">
-        <v>3,652,906,003</v>
+        <v>3,803,147,690</v>
       </c>
       <c r="J30" t="str">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K30" t="str">
-        <v>4,081,073,857</v>
+        <v>4,147,614,834</v>
       </c>
       <c r="L30" t="str">
-        <v>47,082,140,684</v>
+        <v>48,486,102,484</v>
       </c>
       <c r="M30" t="str">
-        <v>12,986,226,963</v>
+        <v>13,398,750,549</v>
       </c>
       <c r="N30" t="str">
-        <v>27.58%</v>
+        <v>27.63%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,10 +1733,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>3,948</v>
+        <v>4,109</v>
       </c>
       <c r="F31" t="str">
-        <v>702</v>
+        <v>752</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1754,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>4,202,736,621</v>
+        <v>4,379,798,973</v>
       </c>
       <c r="M31" t="str">
-        <v>872,537,396</v>
+        <v>919,888,188</v>
       </c>
       <c r="N31" t="str">
-        <v>20.76%</v>
+        <v>21.00%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,13 +1777,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>4,442</v>
+        <v>4,534</v>
       </c>
       <c r="F32" t="str">
-        <v>736</v>
+        <v>758</v>
       </c>
       <c r="G32" t="str">
-        <v>2,071</v>
+        <v>2,112</v>
       </c>
       <c r="H32" t="str">
         <v>9</v>
@@ -1798,13 +1798,13 @@
         <v>102,003,250</v>
       </c>
       <c r="L32" t="str">
-        <v>11,915,209,732</v>
+        <v>12,149,342,286</v>
       </c>
       <c r="M32" t="str">
-        <v>1,161,271,263</v>
+        <v>1,186,884,373</v>
       </c>
       <c r="N32" t="str">
-        <v>9.75%</v>
+        <v>9.77%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,19 +1821,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>1,498</v>
+        <v>1,553</v>
       </c>
       <c r="F33" t="str">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="G33" t="str">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="H33" t="str">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I33" t="str">
-        <v>80,097,801</v>
+        <v>94,916,313</v>
       </c>
       <c r="J33" t="str">
         <v>5</v>
@@ -1842,13 +1842,13 @@
         <v>81,160,766</v>
       </c>
       <c r="L33" t="str">
-        <v>3,710,191,295</v>
+        <v>3,832,603,710</v>
       </c>
       <c r="M33" t="str">
-        <v>576,569,354</v>
+        <v>611,947,424</v>
       </c>
       <c r="N33" t="str">
-        <v>15.54%</v>
+        <v>15.97%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,10 +1865,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>3,273</v>
+        <v>3,380</v>
       </c>
       <c r="F34" t="str">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="G34" t="str">
         <v>96</v>
@@ -1886,10 +1886,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>3,381,087,456</v>
+        <v>3,478,648,619</v>
       </c>
       <c r="M34" t="str">
-        <v>526,372,210</v>
+        <v>541,690,140</v>
       </c>
       <c r="N34" t="str">
         <v>15.57%</v>
@@ -1909,13 +1909,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>11,203</v>
+        <v>11,792</v>
       </c>
       <c r="F35" t="str">
-        <v>1,258</v>
+        <v>1,370</v>
       </c>
       <c r="G35" t="str">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="H35" t="str">
         <v>4</v>
@@ -1924,19 +1924,19 @@
         <v>47,418,441</v>
       </c>
       <c r="J35" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35" t="str">
-        <v>0</v>
+        <v>36,748,407</v>
       </c>
       <c r="L35" t="str">
-        <v>11,429,887,521</v>
+        <v>11,979,240,074</v>
       </c>
       <c r="M35" t="str">
-        <v>1,403,870,153</v>
+        <v>1,525,408,404</v>
       </c>
       <c r="N35" t="str">
-        <v>12.28%</v>
+        <v>12.73%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,10 +1953,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>282</v>
+        <v>321</v>
       </c>
       <c r="F36" t="str">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="G36" t="str">
         <v>0</v>
@@ -1974,13 +1974,13 @@
         <v>0</v>
       </c>
       <c r="L36" t="str">
-        <v>232,381,159</v>
+        <v>263,754,589</v>
       </c>
       <c r="M36" t="str">
-        <v>32,645,248</v>
+        <v>39,201,739</v>
       </c>
       <c r="N36" t="str">
-        <v>14.05%</v>
+        <v>14.86%</v>
       </c>
     </row>
     <row r="37">
@@ -1997,34 +1997,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>1,605</v>
+        <v>1,689</v>
       </c>
       <c r="F37" t="str">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="G37" t="str">
-        <v>2,719</v>
+        <v>2,824</v>
       </c>
       <c r="H37" t="str">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I37" t="str">
-        <v>860,230,790</v>
+        <v>870,810,508</v>
       </c>
       <c r="J37" t="str">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K37" t="str">
-        <v>1,145,782,044</v>
+        <v>1,199,485,955</v>
       </c>
       <c r="L37" t="str">
-        <v>16,360,920,969</v>
+        <v>17,277,918,945</v>
       </c>
       <c r="M37" t="str">
-        <v>3,151,118,473</v>
+        <v>3,244,243,421</v>
       </c>
       <c r="N37" t="str">
-        <v>19.26%</v>
+        <v>18.78%</v>
       </c>
     </row>
     <row r="38">
@@ -2041,10 +2041,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>5,066</v>
+        <v>5,262</v>
       </c>
       <c r="F38" t="str">
-        <v>516</v>
+        <v>551</v>
       </c>
       <c r="G38" t="str">
         <v>238</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>5,289,811,061</v>
+        <v>5,478,580,230</v>
       </c>
       <c r="M38" t="str">
-        <v>572,719,128</v>
+        <v>607,848,076</v>
       </c>
       <c r="N38" t="str">
-        <v>10.83%</v>
+        <v>11.09%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,13 +2085,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>3,667</v>
+        <v>3,800</v>
       </c>
       <c r="F39" t="str">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="G39" t="str">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H39" t="str">
         <v>0</v>
@@ -2106,13 +2106,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>3,714,182,265</v>
+        <v>3,849,154,606</v>
       </c>
       <c r="M39" t="str">
-        <v>378,954,815</v>
+        <v>391,915,026</v>
       </c>
       <c r="N39" t="str">
-        <v>10.20%</v>
+        <v>10.18%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,34 +2173,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>1,370</v>
+        <v>1,433</v>
       </c>
       <c r="F41" t="str">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="G41" t="str">
-        <v>2,547</v>
+        <v>2,644</v>
       </c>
       <c r="H41" t="str">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I41" t="str">
-        <v>607,808,386</v>
+        <v>656,445,185</v>
       </c>
       <c r="J41" t="str">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K41" t="str">
-        <v>522,990,481</v>
+        <v>547,161,403</v>
       </c>
       <c r="L41" t="str">
-        <v>13,695,258,786</v>
+        <v>14,370,081,796</v>
       </c>
       <c r="M41" t="str">
-        <v>1,943,806,908</v>
+        <v>2,056,181,772</v>
       </c>
       <c r="N41" t="str">
-        <v>14.19%</v>
+        <v>14.31%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,19 +2217,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>6,558</v>
+        <v>6,693</v>
       </c>
       <c r="F42" t="str">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="G42" t="str">
-        <v>8,930</v>
+        <v>9,240</v>
       </c>
       <c r="H42" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I42" t="str">
-        <v>58,637,524</v>
+        <v>71,993,878</v>
       </c>
       <c r="J42" t="str">
         <v>8</v>
@@ -2238,13 +2238,13 @@
         <v>151,104,880</v>
       </c>
       <c r="L42" t="str">
-        <v>16,359,819,583</v>
+        <v>16,823,095,452</v>
       </c>
       <c r="M42" t="str">
-        <v>611,398,639</v>
+        <v>645,197,068</v>
       </c>
       <c r="N42" t="str">
-        <v>3.74%</v>
+        <v>3.84%</v>
       </c>
     </row>
     <row r="43">
@@ -2305,13 +2305,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>2,060</v>
+        <v>2,151</v>
       </c>
       <c r="F44" t="str">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G44" t="str">
-        <v>1,965</v>
+        <v>2,052</v>
       </c>
       <c r="H44" t="str">
         <v>2</v>
@@ -2326,13 +2326,13 @@
         <v>50,770,592</v>
       </c>
       <c r="L44" t="str">
-        <v>4,372,970,372</v>
+        <v>4,509,691,904</v>
       </c>
       <c r="M44" t="str">
-        <v>173,372,367</v>
+        <v>179,508,681</v>
       </c>
       <c r="N44" t="str">
-        <v>3.96%</v>
+        <v>3.98%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,13 +2349,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>1,279</v>
+        <v>1,324</v>
       </c>
       <c r="F45" t="str">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G45" t="str">
-        <v>1,958</v>
+        <v>2,033</v>
       </c>
       <c r="H45" t="str">
         <v>0</v>
@@ -2370,13 +2370,13 @@
         <v>66,445,865</v>
       </c>
       <c r="L45" t="str">
-        <v>3,018,990,411</v>
+        <v>3,114,785,630</v>
       </c>
       <c r="M45" t="str">
-        <v>108,097,875</v>
+        <v>112,818,217</v>
       </c>
       <c r="N45" t="str">
-        <v>3.58%</v>
+        <v>3.62%</v>
       </c>
     </row>
     <row r="46">
@@ -2393,19 +2393,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E46" t="str">
-        <v>5,131</v>
+        <v>5,312</v>
       </c>
       <c r="F46" t="str">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="G46" t="str">
-        <v>7,613</v>
+        <v>7,827</v>
       </c>
       <c r="H46" t="str">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I46" t="str">
-        <v>191,379,503</v>
+        <v>201,535,859</v>
       </c>
       <c r="J46" t="str">
         <v>4</v>
@@ -2414,13 +2414,13 @@
         <v>80,274,644</v>
       </c>
       <c r="L46" t="str">
-        <v>11,693,598,550</v>
+        <v>11,995,223,504</v>
       </c>
       <c r="M46" t="str">
-        <v>683,640,800</v>
+        <v>713,177,562</v>
       </c>
       <c r="N46" t="str">
-        <v>5.85%</v>
+        <v>5.95%</v>
       </c>
     </row>
     <row r="47">
@@ -2437,19 +2437,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E47" t="str">
-        <v>6,122</v>
+        <v>6,527</v>
       </c>
       <c r="F47" t="str">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="G47" t="str">
-        <v>5,061</v>
+        <v>5,321</v>
       </c>
       <c r="H47" t="str">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I47" t="str">
-        <v>73,735,944</v>
+        <v>86,198,628</v>
       </c>
       <c r="J47" t="str">
         <v>5</v>
@@ -2458,13 +2458,13 @@
         <v>86,522,238</v>
       </c>
       <c r="L47" t="str">
-        <v>13,571,556,899</v>
+        <v>14,215,030,943</v>
       </c>
       <c r="M47" t="str">
-        <v>505,483,697</v>
+        <v>557,626,211</v>
       </c>
       <c r="N47" t="str">
-        <v>3.72%</v>
+        <v>3.92%</v>
       </c>
     </row>
     <row r="48">
@@ -2481,34 +2481,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E48" t="str">
-        <v>4,494</v>
+        <v>4,651</v>
       </c>
       <c r="F48" t="str">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="G48" t="str">
-        <v>6,423</v>
+        <v>6,632</v>
       </c>
       <c r="H48" t="str">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I48" t="str">
-        <v>82,418,874</v>
+        <v>95,073,606</v>
       </c>
       <c r="J48" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K48" t="str">
-        <v>170,628,519</v>
+        <v>186,264,594</v>
       </c>
       <c r="L48" t="str">
-        <v>9,897,403,356</v>
+        <v>10,229,005,159</v>
       </c>
       <c r="M48" t="str">
-        <v>658,713,326</v>
+        <v>700,033,332</v>
       </c>
       <c r="N48" t="str">
-        <v>6.66%</v>
+        <v>6.84%</v>
       </c>
     </row>
   </sheetData>

--- a/rawdata/Bulanan/10. Okt-LD.xlsx
+++ b/rawdata/Bulanan/10. Okt-LD.xlsx
@@ -457,34 +457,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E2" t="str">
-        <v>11,663</v>
+        <v>11,970</v>
       </c>
       <c r="F2" t="str">
-        <v>5,760</v>
+        <v>5,911</v>
       </c>
       <c r="G2" t="str">
-        <v>1,610</v>
+        <v>1,645</v>
       </c>
       <c r="H2" t="str">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="I2" t="str">
-        <v>3,451,771,255</v>
+        <v>3,582,589,789</v>
       </c>
       <c r="J2" t="str">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="K2" t="str">
-        <v>13,044,216,652</v>
+        <v>13,228,337,486</v>
       </c>
       <c r="L2" t="str">
-        <v>43,750,574,833</v>
+        <v>44,779,827,440</v>
       </c>
       <c r="M2" t="str">
-        <v>24,828,946,751</v>
+        <v>25,390,513,978</v>
       </c>
       <c r="N2" t="str">
-        <v>56.75%</v>
+        <v>56.70%</v>
       </c>
     </row>
     <row r="3">
@@ -501,34 +501,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E3" t="str">
-        <v>17,901</v>
+        <v>18,258</v>
       </c>
       <c r="F3" t="str">
-        <v>2,535</v>
+        <v>2,573</v>
       </c>
       <c r="G3" t="str">
-        <v>2,862</v>
+        <v>2,921</v>
       </c>
       <c r="H3" t="str">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I3" t="str">
-        <v>2,200,302,418</v>
+        <v>2,229,813,442</v>
       </c>
       <c r="J3" t="str">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="K3" t="str">
-        <v>7,264,807,514</v>
+        <v>7,430,139,667</v>
       </c>
       <c r="L3" t="str">
-        <v>73,862,772,603</v>
+        <v>75,236,887,931</v>
       </c>
       <c r="M3" t="str">
-        <v>12,928,820,479</v>
+        <v>13,139,304,844</v>
       </c>
       <c r="N3" t="str">
-        <v>17.50%</v>
+        <v>17.46%</v>
       </c>
     </row>
     <row r="4">
@@ -545,34 +545,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E4" t="str">
-        <v>3,654</v>
+        <v>3,756</v>
       </c>
       <c r="F4" t="str">
-        <v>1,694</v>
+        <v>1,736</v>
       </c>
       <c r="G4" t="str">
-        <v>520</v>
+        <v>535</v>
       </c>
       <c r="H4" t="str">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I4" t="str">
-        <v>1,133,959,847</v>
+        <v>1,148,715,359</v>
       </c>
       <c r="J4" t="str">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="K4" t="str">
-        <v>4,305,104,279</v>
+        <v>4,520,517,789</v>
       </c>
       <c r="L4" t="str">
-        <v>13,842,617,667</v>
+        <v>14,225,027,250</v>
       </c>
       <c r="M4" t="str">
-        <v>8,012,389,892</v>
+        <v>8,273,000,624</v>
       </c>
       <c r="N4" t="str">
-        <v>57.88%</v>
+        <v>58.16%</v>
       </c>
     </row>
     <row r="5">
@@ -589,10 +589,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E5" t="str">
-        <v>6,544</v>
+        <v>6,707</v>
       </c>
       <c r="F5" t="str">
-        <v>1,563</v>
+        <v>1,599</v>
       </c>
       <c r="G5" t="str">
         <v>29</v>
@@ -610,13 +610,13 @@
         <v>38,695,454</v>
       </c>
       <c r="L5" t="str">
-        <v>7,793,635,276</v>
+        <v>7,994,618,179</v>
       </c>
       <c r="M5" t="str">
-        <v>2,722,072,280</v>
+        <v>2,775,856,801</v>
       </c>
       <c r="N5" t="str">
-        <v>34.93%</v>
+        <v>34.72%</v>
       </c>
     </row>
     <row r="6">
@@ -633,19 +633,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E6" t="str">
-        <v>30,311</v>
+        <v>31,188</v>
       </c>
       <c r="F6" t="str">
-        <v>7,335</v>
+        <v>7,622</v>
       </c>
       <c r="G6" t="str">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H6" t="str">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I6" t="str">
-        <v>139,226,472</v>
+        <v>151,136,105</v>
       </c>
       <c r="J6" t="str">
         <v>6</v>
@@ -654,13 +654,13 @@
         <v>123,598,123</v>
       </c>
       <c r="L6" t="str">
-        <v>36,260,993,218</v>
+        <v>37,407,509,535</v>
       </c>
       <c r="M6" t="str">
-        <v>11,401,445,910</v>
+        <v>11,838,430,415</v>
       </c>
       <c r="N6" t="str">
-        <v>31.44%</v>
+        <v>31.65%</v>
       </c>
     </row>
     <row r="7">
@@ -677,10 +677,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E7" t="str">
-        <v>771</v>
+        <v>830</v>
       </c>
       <c r="F7" t="str">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="G7" t="str">
         <v>0</v>
@@ -698,13 +698,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="str">
-        <v>651,640,647</v>
+        <v>702,770,994</v>
       </c>
       <c r="M7" t="str">
-        <v>218,281,496</v>
+        <v>246,423,143</v>
       </c>
       <c r="N7" t="str">
-        <v>33.50%</v>
+        <v>35.06%</v>
       </c>
     </row>
     <row r="8">
@@ -721,34 +721,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E8" t="str">
-        <v>8,948</v>
+        <v>9,210</v>
       </c>
       <c r="F8" t="str">
-        <v>4,279</v>
+        <v>4,419</v>
       </c>
       <c r="G8" t="str">
-        <v>6,228</v>
+        <v>6,450</v>
       </c>
       <c r="H8" t="str">
-        <v>1,235</v>
+        <v>1,266</v>
       </c>
       <c r="I8" t="str">
-        <v>14,899,035,161</v>
+        <v>15,271,253,991</v>
       </c>
       <c r="J8" t="str">
-        <v>912</v>
+        <v>942</v>
       </c>
       <c r="K8" t="str">
-        <v>19,106,263,205</v>
+        <v>19,756,501,998</v>
       </c>
       <c r="L8" t="str">
-        <v>102,927,242,166</v>
+        <v>106,150,507,879</v>
       </c>
       <c r="M8" t="str">
-        <v>45,605,864,974</v>
+        <v>47,057,650,769</v>
       </c>
       <c r="N8" t="str">
-        <v>44.31%</v>
+        <v>44.33%</v>
       </c>
     </row>
     <row r="9">
@@ -765,10 +765,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E9" t="str">
-        <v>3,092</v>
+        <v>3,202</v>
       </c>
       <c r="F9" t="str">
-        <v>676</v>
+        <v>697</v>
       </c>
       <c r="G9" t="str">
         <v>4</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="str">
-        <v>3,796,631,274</v>
+        <v>3,925,222,056</v>
       </c>
       <c r="M9" t="str">
-        <v>1,097,075,397</v>
+        <v>1,124,012,399</v>
       </c>
       <c r="N9" t="str">
-        <v>28.90%</v>
+        <v>28.64%</v>
       </c>
     </row>
     <row r="10">
@@ -809,13 +809,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E10" t="str">
-        <v>3,878</v>
+        <v>3,965</v>
       </c>
       <c r="F10" t="str">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G10" t="str">
-        <v>9,420</v>
+        <v>9,674</v>
       </c>
       <c r="H10" t="str">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>100,379,570</v>
       </c>
       <c r="L10" t="str">
-        <v>10,916,313,097</v>
+        <v>11,217,915,268</v>
       </c>
       <c r="M10" t="str">
-        <v>155,857,136</v>
+        <v>157,237,227</v>
       </c>
       <c r="N10" t="str">
-        <v>1.43%</v>
+        <v>1.40%</v>
       </c>
     </row>
     <row r="11">
@@ -853,13 +853,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E11" t="str">
-        <v>3,227</v>
+        <v>3,300</v>
       </c>
       <c r="F11" t="str">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G11" t="str">
-        <v>6,807</v>
+        <v>7,023</v>
       </c>
       <c r="H11" t="str">
         <v>2</v>
@@ -874,13 +874,13 @@
         <v>37,800,870</v>
       </c>
       <c r="L11" t="str">
-        <v>9,270,947,854</v>
+        <v>9,509,581,021</v>
       </c>
       <c r="M11" t="str">
-        <v>154,266,252</v>
+        <v>155,759,932</v>
       </c>
       <c r="N11" t="str">
-        <v>1.66%</v>
+        <v>1.64%</v>
       </c>
     </row>
     <row r="12">
@@ -897,13 +897,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E12" t="str">
-        <v>4,145</v>
+        <v>4,282</v>
       </c>
       <c r="F12" t="str">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="G12" t="str">
-        <v>12,406</v>
+        <v>12,814</v>
       </c>
       <c r="H12" t="str">
         <v>1</v>
@@ -918,13 +918,13 @@
         <v>40,288,174</v>
       </c>
       <c r="L12" t="str">
-        <v>15,541,054,050</v>
+        <v>16,012,846,531</v>
       </c>
       <c r="M12" t="str">
-        <v>198,756,839</v>
+        <v>209,661,113</v>
       </c>
       <c r="N12" t="str">
-        <v>1.28%</v>
+        <v>1.31%</v>
       </c>
     </row>
     <row r="13">
@@ -941,13 +941,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E13" t="str">
-        <v>2,584</v>
+        <v>2,669</v>
       </c>
       <c r="F13" t="str">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G13" t="str">
-        <v>8,482</v>
+        <v>8,753</v>
       </c>
       <c r="H13" t="str">
         <v>4</v>
@@ -962,13 +962,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="str">
-        <v>9,527,883,131</v>
+        <v>9,820,012,513</v>
       </c>
       <c r="M13" t="str">
-        <v>260,585,857</v>
+        <v>261,735,857</v>
       </c>
       <c r="N13" t="str">
-        <v>2.73%</v>
+        <v>2.67%</v>
       </c>
     </row>
     <row r="14">
@@ -985,19 +985,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E14" t="str">
-        <v>1,289</v>
+        <v>1,323</v>
       </c>
       <c r="F14" t="str">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G14" t="str">
-        <v>4,391</v>
+        <v>4,502</v>
       </c>
       <c r="H14" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="str">
-        <v>11,911,540</v>
+        <v>24,260,361</v>
       </c>
       <c r="J14" t="str">
         <v>2</v>
@@ -1006,13 +1006,13 @@
         <v>35,694,915</v>
       </c>
       <c r="L14" t="str">
-        <v>4,769,869,432</v>
+        <v>4,909,756,398</v>
       </c>
       <c r="M14" t="str">
-        <v>100,819,190</v>
+        <v>112,127,025</v>
       </c>
       <c r="N14" t="str">
-        <v>2.11%</v>
+        <v>2.28%</v>
       </c>
     </row>
     <row r="15">
@@ -1029,13 +1029,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E15" t="str">
-        <v>3,639</v>
+        <v>3,758</v>
       </c>
       <c r="F15" t="str">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G15" t="str">
-        <v>11,429</v>
+        <v>11,779</v>
       </c>
       <c r="H15" t="str">
         <v>1</v>
@@ -1050,10 +1050,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="str">
-        <v>13,394,862,390</v>
+        <v>13,861,993,156</v>
       </c>
       <c r="M15" t="str">
-        <v>230,518,812</v>
+        <v>238,948,224</v>
       </c>
       <c r="N15" t="str">
         <v>1.72%</v>
@@ -1073,13 +1073,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E16" t="str">
-        <v>5,608</v>
+        <v>5,772</v>
       </c>
       <c r="F16" t="str">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G16" t="str">
-        <v>16,076</v>
+        <v>16,608</v>
       </c>
       <c r="H16" t="str">
         <v>0</v>
@@ -1094,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="str">
-        <v>21,470,601,321</v>
+        <v>22,022,327,097</v>
       </c>
       <c r="M16" t="str">
-        <v>87,906,529</v>
+        <v>88,802,253</v>
       </c>
       <c r="N16" t="str">
-        <v>0.41%</v>
+        <v>0.40%</v>
       </c>
     </row>
     <row r="17">
@@ -1117,13 +1117,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E17" t="str">
-        <v>2,674</v>
+        <v>2,743</v>
       </c>
       <c r="F17" t="str">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G17" t="str">
-        <v>6,203</v>
+        <v>6,430</v>
       </c>
       <c r="H17" t="str">
         <v>0</v>
@@ -1138,13 +1138,13 @@
         <v>233,859,144</v>
       </c>
       <c r="L17" t="str">
-        <v>9,250,822,606</v>
+        <v>9,491,369,445</v>
       </c>
       <c r="M17" t="str">
-        <v>181,695,019</v>
+        <v>184,248,668</v>
       </c>
       <c r="N17" t="str">
-        <v>1.96%</v>
+        <v>1.94%</v>
       </c>
     </row>
     <row r="18">
@@ -1161,13 +1161,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E18" t="str">
-        <v>3,324</v>
+        <v>3,410</v>
       </c>
       <c r="F18" t="str">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G18" t="str">
-        <v>6,975</v>
+        <v>7,187</v>
       </c>
       <c r="H18" t="str">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>138,416,984</v>
       </c>
       <c r="L18" t="str">
-        <v>10,979,096,256</v>
+        <v>11,271,455,249</v>
       </c>
       <c r="M18" t="str">
-        <v>144,555,202</v>
+        <v>145,624,748</v>
       </c>
       <c r="N18" t="str">
-        <v>1.32%</v>
+        <v>1.29%</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E19" t="str">
-        <v>4,398</v>
+        <v>4,541</v>
       </c>
       <c r="F19" t="str">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G19" t="str">
-        <v>16,255</v>
+        <v>16,775</v>
       </c>
       <c r="H19" t="str">
         <v>1</v>
@@ -1226,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="L19" t="str">
-        <v>19,288,403,775</v>
+        <v>19,795,855,203</v>
       </c>
       <c r="M19" t="str">
-        <v>180,218,230</v>
+        <v>191,523,568</v>
       </c>
       <c r="N19" t="str">
-        <v>0.93%</v>
+        <v>0.97%</v>
       </c>
     </row>
     <row r="20">
@@ -1249,13 +1249,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E20" t="str">
-        <v>732</v>
+        <v>755</v>
       </c>
       <c r="F20" t="str">
         <v>5</v>
       </c>
       <c r="G20" t="str">
-        <v>2,617</v>
+        <v>2,699</v>
       </c>
       <c r="H20" t="str">
         <v>0</v>
@@ -1270,13 +1270,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="str">
-        <v>3,174,227,989</v>
+        <v>3,321,959,371</v>
       </c>
       <c r="M20" t="str">
         <v>13,558,436</v>
       </c>
       <c r="N20" t="str">
-        <v>0.43%</v>
+        <v>0.41%</v>
       </c>
     </row>
     <row r="21">
@@ -1293,13 +1293,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E21" t="str">
-        <v>5,130</v>
+        <v>5,294</v>
       </c>
       <c r="F21" t="str">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G21" t="str">
-        <v>18,217</v>
+        <v>18,828</v>
       </c>
       <c r="H21" t="str">
         <v>2</v>
@@ -1314,13 +1314,13 @@
         <v>0</v>
       </c>
       <c r="L21" t="str">
-        <v>22,155,396,373</v>
+        <v>22,897,317,949</v>
       </c>
       <c r="M21" t="str">
-        <v>177,440,985</v>
+        <v>184,434,003</v>
       </c>
       <c r="N21" t="str">
-        <v>0.80%</v>
+        <v>0.81%</v>
       </c>
     </row>
     <row r="22">
@@ -1337,13 +1337,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E22" t="str">
-        <v>24,699</v>
+        <v>24,961</v>
       </c>
       <c r="F22" t="str">
-        <v>1,380</v>
+        <v>1,484</v>
       </c>
       <c r="G22" t="str">
-        <v>723,443</v>
+        <v>747,875</v>
       </c>
       <c r="H22" t="str">
         <v>17</v>
@@ -1358,13 +1358,13 @@
         <v>476,826,156</v>
       </c>
       <c r="L22" t="str">
-        <v>106,723,749,882</v>
+        <v>107,663,590,071</v>
       </c>
       <c r="M22" t="str">
-        <v>3,676,786,686</v>
+        <v>3,891,638,425</v>
       </c>
       <c r="N22" t="str">
-        <v>3.45%</v>
+        <v>3.61%</v>
       </c>
     </row>
     <row r="23">
@@ -1387,7 +1387,7 @@
         <v>16</v>
       </c>
       <c r="G23" t="str">
-        <v>16,030</v>
+        <v>16,559</v>
       </c>
       <c r="H23" t="str">
         <v>0</v>
@@ -1425,34 +1425,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E24" t="str">
-        <v>52,909</v>
+        <v>54,681</v>
       </c>
       <c r="F24" t="str">
-        <v>2,476</v>
+        <v>2,574</v>
       </c>
       <c r="G24" t="str">
-        <v>4,710</v>
+        <v>4,904</v>
       </c>
       <c r="H24" t="str">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="I24" t="str">
-        <v>4,197,022,633</v>
+        <v>4,350,381,026</v>
       </c>
       <c r="J24" t="str">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="K24" t="str">
-        <v>5,086,964,183</v>
+        <v>5,297,292,778</v>
       </c>
       <c r="L24" t="str">
-        <v>170,030,614,300</v>
+        <v>176,555,042,062</v>
       </c>
       <c r="M24" t="str">
-        <v>13,634,773,232</v>
+        <v>14,132,428,446</v>
       </c>
       <c r="N24" t="str">
-        <v>8.02%</v>
+        <v>8.00%</v>
       </c>
     </row>
     <row r="25">
@@ -1469,19 +1469,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E25" t="str">
-        <v>2,480</v>
+        <v>2,574</v>
       </c>
       <c r="F25" t="str">
-        <v>795</v>
+        <v>825</v>
       </c>
       <c r="G25" t="str">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H25" t="str">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I25" t="str">
-        <v>144,285,555</v>
+        <v>158,917,085</v>
       </c>
       <c r="J25" t="str">
         <v>30</v>
@@ -1490,13 +1490,13 @@
         <v>566,472,818</v>
       </c>
       <c r="L25" t="str">
-        <v>6,355,033,472</v>
+        <v>6,520,160,479</v>
       </c>
       <c r="M25" t="str">
-        <v>1,699,684,410</v>
+        <v>1,756,262,509</v>
       </c>
       <c r="N25" t="str">
-        <v>26.75%</v>
+        <v>26.94%</v>
       </c>
     </row>
     <row r="26">
@@ -1513,34 +1513,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E26" t="str">
-        <v>5,339</v>
+        <v>5,494</v>
       </c>
       <c r="F26" t="str">
-        <v>1,662</v>
+        <v>1,709</v>
       </c>
       <c r="G26" t="str">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="H26" t="str">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I26" t="str">
-        <v>507,627,067</v>
+        <v>518,830,673</v>
       </c>
       <c r="J26" t="str">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K26" t="str">
-        <v>831,348,142</v>
+        <v>876,592,732</v>
       </c>
       <c r="L26" t="str">
-        <v>13,667,073,609</v>
+        <v>14,013,725,560</v>
       </c>
       <c r="M26" t="str">
-        <v>3,544,247,726</v>
+        <v>3,654,527,769</v>
       </c>
       <c r="N26" t="str">
-        <v>25.93%</v>
+        <v>26.08%</v>
       </c>
     </row>
     <row r="27">
@@ -1557,10 +1557,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E27" t="str">
-        <v>2,608</v>
+        <v>2,686</v>
       </c>
       <c r="F27" t="str">
-        <v>528</v>
+        <v>547</v>
       </c>
       <c r="G27" t="str">
         <v>0</v>
@@ -1578,13 +1578,13 @@
         <v>0</v>
       </c>
       <c r="L27" t="str">
-        <v>2,674,912,814</v>
+        <v>2,766,196,908</v>
       </c>
       <c r="M27" t="str">
-        <v>621,203,794</v>
+        <v>639,120,156</v>
       </c>
       <c r="N27" t="str">
-        <v>23.22%</v>
+        <v>23.10%</v>
       </c>
     </row>
     <row r="28">
@@ -1601,10 +1601,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E28" t="str">
-        <v>22,537</v>
+        <v>23,170</v>
       </c>
       <c r="F28" t="str">
-        <v>3,936</v>
+        <v>4,051</v>
       </c>
       <c r="G28" t="str">
         <v>2</v>
@@ -1622,13 +1622,13 @@
         <v>0</v>
       </c>
       <c r="L28" t="str">
-        <v>23,241,937,840</v>
+        <v>23,916,082,385</v>
       </c>
       <c r="M28" t="str">
-        <v>4,537,395,946</v>
+        <v>4,661,725,275</v>
       </c>
       <c r="N28" t="str">
-        <v>19.52%</v>
+        <v>19.49%</v>
       </c>
     </row>
     <row r="29">
@@ -1645,10 +1645,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E29" t="str">
-        <v>450</v>
+        <v>508</v>
       </c>
       <c r="F29" t="str">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="G29" t="str">
         <v>0</v>
@@ -1666,13 +1666,13 @@
         <v>0</v>
       </c>
       <c r="L29" t="str">
-        <v>351,436,051</v>
+        <v>396,638,292</v>
       </c>
       <c r="M29" t="str">
-        <v>88,207,785</v>
+        <v>95,153,313</v>
       </c>
       <c r="N29" t="str">
-        <v>25.10%</v>
+        <v>23.99%</v>
       </c>
     </row>
     <row r="30">
@@ -1689,34 +1689,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E30" t="str">
-        <v>4,521</v>
+        <v>4,663</v>
       </c>
       <c r="F30" t="str">
-        <v>1,492</v>
+        <v>1,530</v>
       </c>
       <c r="G30" t="str">
-        <v>1,707</v>
+        <v>1,772</v>
       </c>
       <c r="H30" t="str">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="I30" t="str">
-        <v>3,803,147,690</v>
+        <v>3,900,480,450</v>
       </c>
       <c r="J30" t="str">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="K30" t="str">
-        <v>4,147,614,834</v>
+        <v>4,277,980,700</v>
       </c>
       <c r="L30" t="str">
-        <v>48,486,102,484</v>
+        <v>50,165,093,185</v>
       </c>
       <c r="M30" t="str">
-        <v>13,398,750,549</v>
+        <v>13,781,781,502</v>
       </c>
       <c r="N30" t="str">
-        <v>27.63%</v>
+        <v>27.47%</v>
       </c>
     </row>
     <row r="31">
@@ -1733,10 +1733,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E31" t="str">
-        <v>4,109</v>
+        <v>4,268</v>
       </c>
       <c r="F31" t="str">
-        <v>752</v>
+        <v>785</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1754,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="str">
-        <v>4,379,798,973</v>
+        <v>4,559,273,335</v>
       </c>
       <c r="M31" t="str">
-        <v>919,888,188</v>
+        <v>952,433,465</v>
       </c>
       <c r="N31" t="str">
-        <v>21.00%</v>
+        <v>20.89%</v>
       </c>
     </row>
     <row r="32">
@@ -1777,19 +1777,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E32" t="str">
-        <v>4,534</v>
+        <v>4,613</v>
       </c>
       <c r="F32" t="str">
-        <v>758</v>
+        <v>772</v>
       </c>
       <c r="G32" t="str">
-        <v>2,112</v>
+        <v>2,155</v>
       </c>
       <c r="H32" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I32" t="str">
-        <v>109,604,909</v>
+        <v>122,896,229</v>
       </c>
       <c r="J32" t="str">
         <v>6</v>
@@ -1798,13 +1798,13 @@
         <v>102,003,250</v>
       </c>
       <c r="L32" t="str">
-        <v>12,149,342,286</v>
+        <v>12,292,584,968</v>
       </c>
       <c r="M32" t="str">
-        <v>1,186,884,373</v>
+        <v>1,210,228,171</v>
       </c>
       <c r="N32" t="str">
-        <v>9.77%</v>
+        <v>9.85%</v>
       </c>
     </row>
     <row r="33">
@@ -1821,13 +1821,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E33" t="str">
-        <v>1,553</v>
+        <v>1,599</v>
       </c>
       <c r="F33" t="str">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="G33" t="str">
-        <v>524</v>
+        <v>546</v>
       </c>
       <c r="H33" t="str">
         <v>8</v>
@@ -1842,13 +1842,13 @@
         <v>81,160,766</v>
       </c>
       <c r="L33" t="str">
-        <v>3,832,603,710</v>
+        <v>3,989,706,546</v>
       </c>
       <c r="M33" t="str">
-        <v>611,947,424</v>
+        <v>619,645,657</v>
       </c>
       <c r="N33" t="str">
-        <v>15.97%</v>
+        <v>15.53%</v>
       </c>
     </row>
     <row r="34">
@@ -1865,10 +1865,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E34" t="str">
-        <v>3,380</v>
+        <v>3,462</v>
       </c>
       <c r="F34" t="str">
-        <v>395</v>
+        <v>412</v>
       </c>
       <c r="G34" t="str">
         <v>96</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="str">
-        <v>3,478,648,619</v>
+        <v>3,562,541,716</v>
       </c>
       <c r="M34" t="str">
-        <v>541,690,140</v>
+        <v>554,384,741</v>
       </c>
       <c r="N34" t="str">
-        <v>15.57%</v>
+        <v>15.56%</v>
       </c>
     </row>
     <row r="35">
@@ -1909,13 +1909,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E35" t="str">
-        <v>11,792</v>
+        <v>12,231</v>
       </c>
       <c r="F35" t="str">
-        <v>1,370</v>
+        <v>1,434</v>
       </c>
       <c r="G35" t="str">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="H35" t="str">
         <v>4</v>
@@ -1930,13 +1930,13 @@
         <v>36,748,407</v>
       </c>
       <c r="L35" t="str">
-        <v>11,979,240,074</v>
+        <v>12,449,204,868</v>
       </c>
       <c r="M35" t="str">
-        <v>1,525,408,404</v>
+        <v>1,565,803,499</v>
       </c>
       <c r="N35" t="str">
-        <v>12.73%</v>
+        <v>12.58%</v>
       </c>
     </row>
     <row r="36">
@@ -1953,10 +1953,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E36" t="str">
-        <v>321</v>
+        <v>359</v>
       </c>
       <c r="F36" t="str">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G36" t="str">
         <v>0</v>
@@ -1974,13 +1974,13 @@
         <v>0</v>
       </c>
       <c r="L36" t="str">
-        <v>263,754,589</v>
+        <v>289,896,037</v>
       </c>
       <c r="M36" t="str">
-        <v>39,201,739</v>
+        <v>41,425,044</v>
       </c>
       <c r="N36" t="str">
-        <v>14.86%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="37">
@@ -1997,34 +1997,34 @@
         <v>SEMUA</v>
       </c>
       <c r="E37" t="str">
-        <v>1,689</v>
+        <v>1,735</v>
       </c>
       <c r="F37" t="str">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="G37" t="str">
-        <v>2,824</v>
+        <v>2,932</v>
       </c>
       <c r="H37" t="str">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I37" t="str">
-        <v>870,810,508</v>
+        <v>881,390,226</v>
       </c>
       <c r="J37" t="str">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K37" t="str">
-        <v>1,199,485,955</v>
+        <v>1,240,198,235</v>
       </c>
       <c r="L37" t="str">
-        <v>17,277,918,945</v>
+        <v>17,718,229,723</v>
       </c>
       <c r="M37" t="str">
-        <v>3,244,243,421</v>
+        <v>3,345,099,891</v>
       </c>
       <c r="N37" t="str">
-        <v>18.78%</v>
+        <v>18.88%</v>
       </c>
     </row>
     <row r="38">
@@ -2041,10 +2041,10 @@
         <v>SEMUA</v>
       </c>
       <c r="E38" t="str">
-        <v>5,262</v>
+        <v>5,391</v>
       </c>
       <c r="F38" t="str">
-        <v>551</v>
+        <v>584</v>
       </c>
       <c r="G38" t="str">
         <v>238</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="str">
-        <v>5,478,580,230</v>
+        <v>5,620,013,752</v>
       </c>
       <c r="M38" t="str">
-        <v>607,848,076</v>
+        <v>642,736,731</v>
       </c>
       <c r="N38" t="str">
-        <v>11.09%</v>
+        <v>11.44%</v>
       </c>
     </row>
     <row r="39">
@@ -2085,13 +2085,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E39" t="str">
-        <v>3,800</v>
+        <v>3,900</v>
       </c>
       <c r="F39" t="str">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="G39" t="str">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H39" t="str">
         <v>0</v>
@@ -2106,13 +2106,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="str">
-        <v>3,849,154,606</v>
+        <v>3,948,515,177</v>
       </c>
       <c r="M39" t="str">
-        <v>391,915,026</v>
+        <v>406,083,176</v>
       </c>
       <c r="N39" t="str">
-        <v>10.18%</v>
+        <v>10.28%</v>
       </c>
     </row>
     <row r="40">
@@ -2173,13 +2173,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E41" t="str">
-        <v>1,433</v>
+        <v>1,476</v>
       </c>
       <c r="F41" t="str">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="G41" t="str">
-        <v>2,644</v>
+        <v>2,733</v>
       </c>
       <c r="H41" t="str">
         <v>56</v>
@@ -2188,19 +2188,19 @@
         <v>656,445,185</v>
       </c>
       <c r="J41" t="str">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K41" t="str">
-        <v>547,161,403</v>
+        <v>574,760,316</v>
       </c>
       <c r="L41" t="str">
-        <v>14,370,081,796</v>
+        <v>14,830,076,268</v>
       </c>
       <c r="M41" t="str">
-        <v>2,056,181,772</v>
+        <v>2,108,486,942</v>
       </c>
       <c r="N41" t="str">
-        <v>14.31%</v>
+        <v>14.22%</v>
       </c>
     </row>
     <row r="42">
@@ -2217,13 +2217,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E42" t="str">
-        <v>6,693</v>
+        <v>6,808</v>
       </c>
       <c r="F42" t="str">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="G42" t="str">
-        <v>9,240</v>
+        <v>9,539</v>
       </c>
       <c r="H42" t="str">
         <v>6</v>
@@ -2238,13 +2238,13 @@
         <v>151,104,880</v>
       </c>
       <c r="L42" t="str">
-        <v>16,823,095,452</v>
+        <v>17,053,658,355</v>
       </c>
       <c r="M42" t="str">
-        <v>645,197,068</v>
+        <v>667,114,445</v>
       </c>
       <c r="N42" t="str">
-        <v>3.84%</v>
+        <v>3.91%</v>
       </c>
     </row>
     <row r="43">
@@ -2305,13 +2305,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E44" t="str">
-        <v>2,151</v>
+        <v>2,255</v>
       </c>
       <c r="F44" t="str">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G44" t="str">
-        <v>2,052</v>
+        <v>2,139</v>
       </c>
       <c r="H44" t="str">
         <v>2</v>
@@ -2326,13 +2326,13 @@
         <v>50,770,592</v>
       </c>
       <c r="L44" t="str">
-        <v>4,509,691,904</v>
+        <v>4,687,796,630</v>
       </c>
       <c r="M44" t="str">
-        <v>179,508,681</v>
+        <v>180,569,791</v>
       </c>
       <c r="N44" t="str">
-        <v>3.98%</v>
+        <v>3.85%</v>
       </c>
     </row>
     <row r="45">
@@ -2349,13 +2349,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E45" t="str">
-        <v>1,324</v>
+        <v>1,377</v>
       </c>
       <c r="F45" t="str">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G45" t="str">
-        <v>2,033</v>
+        <v>2,105</v>
       </c>
       <c r="H45" t="str">
         <v>0</v>
@@ -2370,13 +2370,13 @@
         <v>66,445,865</v>
       </c>
       <c r="L45" t="str">
-        <v>3,114,785,630</v>
+        <v>3,199,264,715</v>
       </c>
       <c r="M45" t="str">
-        <v>112,818,217</v>
+        <v>113,539,911</v>
       </c>
       <c r="N45" t="str">
-        <v>3.62%</v>
+        <v>3.55%</v>
       </c>
     </row>
     <row r="46">
@@ -2393,19 +2393,19 @@
         <v>SEMUA</v>
       </c>
       <c r="E46" t="str">
-        <v>5,312</v>
+        <v>5,520</v>
       </c>
       <c r="F46" t="str">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="G46" t="str">
-        <v>7,827</v>
+        <v>8,035</v>
       </c>
       <c r="H46" t="str">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I46" t="str">
-        <v>201,535,859</v>
+        <v>212,517,395</v>
       </c>
       <c r="J46" t="str">
         <v>4</v>
@@ -2414,13 +2414,13 @@
         <v>80,274,644</v>
       </c>
       <c r="L46" t="str">
-        <v>11,995,223,504</v>
+        <v>12,384,781,076</v>
       </c>
       <c r="M46" t="str">
-        <v>713,177,562</v>
+        <v>731,732,409</v>
       </c>
       <c r="N46" t="str">
-        <v>5.95%</v>
+        <v>5.91%</v>
       </c>
     </row>
     <row r="47">
@@ -2437,13 +2437,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E47" t="str">
-        <v>6,527</v>
+        <v>7,000</v>
       </c>
       <c r="F47" t="str">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="G47" t="str">
-        <v>5,321</v>
+        <v>5,581</v>
       </c>
       <c r="H47" t="str">
         <v>7</v>
@@ -2458,13 +2458,13 @@
         <v>86,522,238</v>
       </c>
       <c r="L47" t="str">
-        <v>14,215,030,943</v>
+        <v>15,043,592,431</v>
       </c>
       <c r="M47" t="str">
-        <v>557,626,211</v>
+        <v>584,743,580</v>
       </c>
       <c r="N47" t="str">
-        <v>3.92%</v>
+        <v>3.89%</v>
       </c>
     </row>
     <row r="48">
@@ -2481,13 +2481,13 @@
         <v>SEMUA</v>
       </c>
       <c r="E48" t="str">
-        <v>4,651</v>
+        <v>4,834</v>
       </c>
       <c r="F48" t="str">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="G48" t="str">
-        <v>6,632</v>
+        <v>6,838</v>
       </c>
       <c r="H48" t="str">
         <v>8</v>
@@ -2502,13 +2502,13 @@
         <v>186,264,594</v>
       </c>
       <c r="L48" t="str">
-        <v>10,229,005,159</v>
+        <v>10,544,500,857</v>
       </c>
       <c r="M48" t="str">
-        <v>700,033,332</v>
+        <v>707,473,080</v>
       </c>
       <c r="N48" t="str">
-        <v>6.84%</v>
+        <v>6.71%</v>
       </c>
     </row>
   </sheetData>
